--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/junsik_choi_harman_com/Documents/문서/TF자료/Assertion TF/Assertion Script/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2372" documentId="8_{1594ECDE-2767-4759-96A7-6FE2F184C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45EF610C-9EF8-4AC6-B71E-9AD4DCB187A2}"/>
+  <xr:revisionPtr revIDLastSave="2373" documentId="8_{1594ECDE-2767-4759-96A7-6FE2F184C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F4ED20-E562-4B49-A219-AF0D2E163B48}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5070" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="2" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-28800" yWindow="5535" windowWidth="38700" windowHeight="15345" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -55,9 +55,9 @@
   <commentList>
     <comment ref="I3" authorId="0" shapeId="0" xr:uid="{372E79E2-B979-45EA-A3D7-4E90DC8A7E1F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     승훈님 좋습니다!!</t>
       </text>
     </comment>
@@ -75,38 +75,38 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{11F28A3C-C90D-4418-BB46-9B6DADCDBE4E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     Default를 Posedge로 가정하는 것은 어떻게 생각하시나요
-Reply:
+답글:
     좋아요</t>
       </text>
     </comment>
     <comment ref="C4" authorId="1" shapeId="0" xr:uid="{EAEF4952-1559-4391-A03C-03F57B7ADC3C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     사실 Clock도 왠만하면 한 IP나 블록에서 동일한 것을 사용할 것 같은데 따로 만든 이유는 Clock 대신 sync signal 같은거 활용하기 위함인가요?
 만약 그렇지 않다면 blk로 들어오는 main clock으로 고정하고 이 칸 간소화 가능할 것 같아요
-Reply:
+답글:
     rx assertion 보니까, clk을 base clk만 사용하지 않더라구요
-Reply:
+답글:
     그럼 유지해야겠군요 확인 감사합니다.</t>
       </text>
     </comment>
     <comment ref="G4" authorId="2" shapeId="0" xr:uid="{066F6494-15CB-41D2-A5E8-F35BD8460361}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     |-&gt; 이거로 통일해 버리면 칸 하나 줄일 수 있을 것 같은데 어떻게 생각하시나요?
-Reply:
+답글:
     오케이~
-Reply:
+답글:
     ㅋㅋㅋㅋㅋ갑자기 다빈님이 전자과에 가게된 스토리가 오버랩되는데
-Reply:
+답글:
     일할땐 생각해요ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ
 </t>
       </text>
@@ -125,38 +125,38 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{A5EE3683-DAAF-4AD0-95D0-B34E9981B26B}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     Default를 Posedge로 가정하는 것은 어떻게 생각하시나요
-Reply:
+답글:
     좋아요</t>
       </text>
     </comment>
     <comment ref="C4" authorId="1" shapeId="0" xr:uid="{FBABEDF7-5267-49E5-B5C6-B213E24A5F77}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     사실 Clock도 왠만하면 한 IP나 블록에서 동일한 것을 사용할 것 같은데 따로 만든 이유는 Clock 대신 sync signal 같은거 활용하기 위함인가요?
 만약 그렇지 않다면 blk로 들어오는 main clock으로 고정하고 이 칸 간소화 가능할 것 같아요
-Reply:
+답글:
     rx assertion 보니까, clk을 base clk만 사용하지 않더라구요
-Reply:
+답글:
     그럼 유지해야겠군요 확인 감사합니다.</t>
       </text>
     </comment>
     <comment ref="G4" authorId="2" shapeId="0" xr:uid="{AB18BE64-54B0-4373-A63D-1F608B3F50E6}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
     |-&gt; 이거로 통일해 버리면 칸 하나 줄일 수 있을 것 같은데 어떻게 생각하시나요?
-Reply:
+답글:
     오케이~
-Reply:
+답글:
     ㅋㅋㅋㅋㅋ갑자기 다빈님이 전자과에 가게된 스토리가 오버랩되는데
-Reply:
+답글:
     일할땐 생각해요ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ
 </t>
       </text>
@@ -4677,7 +4677,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{BB1E0E6C-DA0D-43B5-A5C3-94756A668AC2}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5096,7 +5096,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="B1:N10"/>
+  <dimension ref="B1:N9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="53"/>
@@ -5279,11 +5279,6 @@
       </c>
       <c r="N9" s="64" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="F10" s="55">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -8891,7 +8886,7 @@
       <c r="AP20" s="74"/>
       <c r="AQ20" s="74"/>
     </row>
-    <row r="21" spans="2:43" ht="18.75">
+    <row r="21" spans="2:43" ht="20.25">
       <c r="B21"/>
       <c r="I21" s="113" t="s">
         <v>70</v>
@@ -9439,7 +9434,7 @@
     <row r="43" spans="2:19">
       <c r="B43"/>
     </row>
-    <row r="44" spans="2:19" ht="18.75">
+    <row r="44" spans="2:19" ht="20.25">
       <c r="B44"/>
       <c r="I44" s="113" t="s">
         <v>72</v>

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C3FCE2-8117-45B9-B743-EC5D50A6BCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7543FB6B-2018-4E5D-8374-789C43EBCADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="327">
   <si>
     <t>Base Information</t>
   </si>
@@ -356,13 +356,7 @@
     <t>...</t>
   </si>
   <si>
-    <t>Base_Clock</t>
-  </si>
-  <si>
     <t>=Define!C5</t>
-  </si>
-  <si>
-    <t>Base_Reset</t>
   </si>
   <si>
     <t>Expected Preset(Ready/Valid)</t>
@@ -6105,7 +6099,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="133" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -6120,7 +6114,7 @@
       <c r="L1" s="134"/>
       <c r="M1" s="135"/>
       <c r="O1" s="133" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P1" s="134"/>
       <c r="Q1" s="134"/>
@@ -6132,7 +6126,7 @@
       <c r="W1" s="134"/>
       <c r="X1" s="135"/>
       <c r="Z1" s="193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA1" s="194"/>
       <c r="AB1" s="194"/>
@@ -6179,7 +6173,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="199" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B3" s="200"/>
       <c r="C3" s="200"/>
@@ -6188,7 +6182,7 @@
       <c r="F3" s="200"/>
       <c r="G3" s="200"/>
       <c r="H3" s="199" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I3" s="200"/>
       <c r="J3" s="200"/>
@@ -6206,14 +6200,14 @@
       <c r="W3" s="191"/>
       <c r="X3" s="192"/>
       <c r="Z3" s="202" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA3" s="203"/>
       <c r="AB3" s="203"/>
       <c r="AC3" s="203"/>
       <c r="AD3" s="204"/>
       <c r="AE3" s="202" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AF3" s="205"/>
       <c r="AG3" s="205"/>
@@ -6221,131 +6215,131 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>222</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>224</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J4" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="M4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="L4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="M4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="O4" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="U4" s="40" t="s">
+      <c r="V4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="W4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="V4" s="40" t="s">
+      <c r="X4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="W4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="Z4" s="41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>261</v>
-      </c>
-      <c r="AF4" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -6360,54 +6354,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD5" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="AE5" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="AA5" t="s">
-        <v>232</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>233</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD5" s="44" t="s">
+      <c r="AF5" t="s">
         <v>271</v>
       </c>
-      <c r="AE5" s="43" t="s">
+      <c r="AG5" t="s">
         <v>272</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" s="44" t="s">
         <v>273</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>274</v>
-      </c>
-      <c r="AH5" s="44" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -6426,39 +6420,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AF6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -6477,36 +6471,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AF7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH7" s="44" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -6891,7 +6885,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="119" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -6906,7 +6900,7 @@
       <c r="L1" s="120"/>
       <c r="M1" s="121"/>
       <c r="O1" s="119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P1" s="120"/>
       <c r="Q1" s="120"/>
@@ -6918,7 +6912,7 @@
       <c r="W1" s="120"/>
       <c r="X1" s="121"/>
       <c r="Z1" s="208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA1" s="209"/>
       <c r="AB1" s="209"/>
@@ -6965,7 +6959,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="116" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117"/>
@@ -6974,7 +6968,7 @@
       <c r="F3" s="117"/>
       <c r="G3" s="117"/>
       <c r="H3" s="116" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I3" s="117"/>
       <c r="J3" s="117"/>
@@ -6992,14 +6986,14 @@
       <c r="W3" s="217"/>
       <c r="X3" s="218"/>
       <c r="Z3" s="207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA3" s="203"/>
       <c r="AB3" s="203"/>
       <c r="AC3" s="203"/>
       <c r="AD3" s="204"/>
       <c r="AE3" s="207" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AF3" s="214"/>
       <c r="AG3" s="214"/>
@@ -7007,161 +7001,161 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>222</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>224</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J4" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="L4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="M4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="L4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="M4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="O4" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="U4" s="40" t="s">
+      <c r="V4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="W4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="V4" s="40" t="s">
+      <c r="X4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="W4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="Z4" s="41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>261</v>
-      </c>
-      <c r="AF4" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="S5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -7170,66 +7164,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AA5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AB5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AC5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AF5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>281</v>
+      </c>
+      <c r="AH5" s="44" t="s">
         <v>273</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>283</v>
-      </c>
-      <c r="AH5" s="44" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -7248,13 +7242,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -7266,16 +7260,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -7294,7 +7288,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -7306,16 +7300,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -7455,7 +7449,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="119" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -7467,7 +7461,7 @@
       <c r="I1" s="120"/>
       <c r="J1" s="121"/>
       <c r="L1" s="119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M1" s="120"/>
       <c r="N1" s="120"/>
@@ -7479,7 +7473,7 @@
       <c r="T1" s="120"/>
       <c r="U1" s="121"/>
       <c r="W1" s="208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X1" s="209"/>
       <c r="Y1" s="209"/>
@@ -7523,13 +7517,13 @@
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="116" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117"/>
       <c r="D3" s="117"/>
       <c r="E3" s="116" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F3" s="117"/>
       <c r="G3" s="117"/>
@@ -7547,14 +7541,14 @@
       <c r="T3" s="217"/>
       <c r="U3" s="218"/>
       <c r="W3" s="207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X3" s="203"/>
       <c r="Y3" s="203"/>
       <c r="Z3" s="203"/>
       <c r="AA3" s="204"/>
       <c r="AB3" s="207" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AC3" s="214"/>
       <c r="AD3" s="214"/>
@@ -7562,143 +7556,143 @@
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>221</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>223</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G4" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="J4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="I4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="L4" s="41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P4" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="R4" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="Q4" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="R4" s="40" t="s">
+      <c r="S4" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="T4" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="S4" s="40" t="s">
+      <c r="U4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="U4" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="W4" s="41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="P5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -7707,57 +7701,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Y5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AC5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AD5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -7782,16 +7776,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -7816,16 +7810,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -7936,7 +7930,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="21">
       <c r="B2" s="219" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C2" s="219"/>
       <c r="D2" s="219"/>
@@ -7948,10 +7942,10 @@
     <row r="3" spans="2:8" ht="17.25" customHeight="1">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D3" s="220" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E3" s="220"/>
       <c r="F3" s="220"/>
@@ -7962,10 +7956,10 @@
       <c r="B4" s="46"/>
       <c r="C4" s="47"/>
       <c r="D4" s="52" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E4" s="220" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F4" s="220"/>
       <c r="G4" s="47"/>
@@ -7975,10 +7969,10 @@
       <c r="B5" s="46"/>
       <c r="C5" s="47"/>
       <c r="D5" s="52" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E5" s="220" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F5" s="220"/>
       <c r="G5" s="47"/>
@@ -8040,339 +8034,339 @@
     </row>
     <row r="13" spans="2:8" ht="15">
       <c r="B13" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="2:8" ht="15">
       <c r="B14" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="23" t="s">
         <v>304</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15">
       <c r="B16" s="24" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="E24" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="F24" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="G24" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="H24" s="23" t="s">
         <v>304</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15">
       <c r="B26" s="24" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D32" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="E32" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="F32" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="G32" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="H32" s="23" t="s">
         <v>304</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D35" s="1">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -9247,16 +9241,16 @@
     </row>
     <row r="2" spans="2:42">
       <c r="C2" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="145" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" s="145" t="s">
-        <v>63</v>
       </c>
       <c r="E2" s="146"/>
     </row>
     <row r="3" spans="2:42" ht="14.25" thickBot="1">
       <c r="C3" s="87" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D3" s="147">
         <f>Define!C6</f>
@@ -9276,7 +9270,7 @@
       <c r="D5" s="117"/>
       <c r="E5" s="118"/>
       <c r="H5" s="133" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I5" s="134"/>
       <c r="J5" s="134"/>
@@ -9289,7 +9283,7 @@
       <c r="Q5" s="134"/>
       <c r="R5" s="135"/>
       <c r="U5" s="133" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V5" s="134"/>
       <c r="W5" s="134"/>
@@ -9325,7 +9319,7 @@
         <v>27</v>
       </c>
       <c r="H6" s="136" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I6" s="137"/>
       <c r="J6" s="137"/>
@@ -9338,7 +9332,7 @@
       <c r="Q6" s="137"/>
       <c r="R6" s="138"/>
       <c r="U6" s="124" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V6" s="125"/>
       <c r="W6" s="125"/>
@@ -9365,7 +9359,7 @@
     <row r="7" spans="2:42" ht="15" customHeight="1">
       <c r="B7" s="1"/>
       <c r="C7" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" s="37" t="s">
         <v>41</v>
@@ -9410,7 +9404,7 @@
     <row r="8" spans="2:42" ht="15">
       <c r="B8" s="1"/>
       <c r="C8" s="26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" s="37" t="s">
         <v>54</v>
@@ -9455,7 +9449,7 @@
     <row r="9" spans="2:42" ht="15">
       <c r="B9" s="1"/>
       <c r="C9" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" s="37" t="s">
         <v>54</v>
@@ -10102,7 +10096,7 @@
     </row>
     <row r="27" spans="8:42" ht="13.5" customHeight="1">
       <c r="H27" s="133" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I27" s="134"/>
       <c r="J27" s="134"/>
@@ -10139,7 +10133,7 @@
     </row>
     <row r="28" spans="8:42" ht="13.5" customHeight="1">
       <c r="H28" s="136" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I28" s="137"/>
       <c r="J28" s="137"/>
@@ -10753,7 +10747,7 @@
     <row r="74" spans="8:18" ht="13.5" customHeight="1"/>
     <row r="75" spans="8:18" ht="13.5" customHeight="1">
       <c r="H75" s="133" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I75" s="134"/>
       <c r="J75" s="134"/>
@@ -10768,7 +10762,7 @@
     </row>
     <row r="76" spans="8:18" ht="13.5" customHeight="1">
       <c r="H76" s="136" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I76" s="137"/>
       <c r="J76" s="137"/>
@@ -11374,10 +11368,10 @@
     </row>
     <row r="2" spans="3:32">
       <c r="C2" s="86" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D2" s="149" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E2" s="225"/>
       <c r="F2" s="225"/>
@@ -11385,10 +11379,10 @@
     </row>
     <row r="3" spans="3:32">
       <c r="C3" s="87" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D3" s="150" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E3" s="227"/>
       <c r="F3" s="227"/>
@@ -11408,7 +11402,7 @@
       <c r="F5" s="120"/>
       <c r="G5" s="118"/>
       <c r="J5" s="161" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K5" s="162"/>
       <c r="L5" s="162"/>
@@ -11421,7 +11415,7 @@
       <c r="S5" s="162"/>
       <c r="T5" s="163"/>
       <c r="V5" s="161" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W5" s="162"/>
       <c r="X5" s="162"/>
@@ -11439,19 +11433,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="222" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="G6" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="J6" s="136" t="s">
         <v>82</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="136" t="s">
-        <v>84</v>
       </c>
       <c r="K6" s="137"/>
       <c r="L6" s="137"/>
@@ -11464,7 +11458,7 @@
       <c r="S6" s="137"/>
       <c r="T6" s="138"/>
       <c r="V6" s="136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W6" s="137"/>
       <c r="X6" s="137"/>
@@ -11479,19 +11473,19 @@
     </row>
     <row r="7" spans="3:32" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="223" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="223" t="s">
+      <c r="F7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="27" t="s">
         <v>88</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>90</v>
       </c>
       <c r="J7" s="139"/>
       <c r="K7" s="221"/>
@@ -11518,19 +11512,19 @@
     </row>
     <row r="8" spans="3:32" ht="13.5" customHeight="1">
       <c r="C8" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D8" s="223" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>88</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>90</v>
       </c>
       <c r="J8" s="139"/>
       <c r="K8" s="221"/>
@@ -12619,7 +12613,7 @@
       <c r="F4" s="120"/>
       <c r="G4" s="70"/>
       <c r="I4" s="152" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J4" s="152"/>
       <c r="K4" s="152"/>
@@ -12642,7 +12636,7 @@
       <c r="F5" s="123"/>
       <c r="G5" s="72"/>
       <c r="I5" s="151" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J5" s="151"/>
       <c r="K5" s="151"/>
@@ -12843,7 +12837,7 @@
     </row>
     <row r="22" spans="9:15" ht="21">
       <c r="I22" s="152" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J22" s="152"/>
       <c r="K22" s="152"/>
@@ -12854,7 +12848,7 @@
     </row>
     <row r="23" spans="9:15" ht="13.5" customHeight="1">
       <c r="I23" s="151" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J23" s="151"/>
       <c r="K23" s="151"/>
@@ -13052,7 +13046,7 @@
       <c r="F3" s="117"/>
       <c r="G3" s="118"/>
       <c r="J3" s="161" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K3" s="162"/>
       <c r="L3" s="162"/>
@@ -13073,16 +13067,16 @@
         <v>31</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G4" s="42" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="136" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K4" s="153"/>
       <c r="L4" s="153"/>
@@ -13488,7 +13482,7 @@
       <c r="Q3" s="117"/>
       <c r="R3" s="118"/>
       <c r="T3" s="116" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="U3" s="117"/>
       <c r="V3" s="118"/>
@@ -13498,10 +13492,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>39</v>
@@ -13517,10 +13511,10 @@
         <v>27</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N4" s="41" t="s">
         <v>35</v>
@@ -13529,27 +13523,27 @@
         <v>21</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>31</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="V4" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="15">
       <c r="B5" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -13563,28 +13557,28 @@
       <c r="K5" s="26"/>
       <c r="L5" s="27"/>
       <c r="N5" s="26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O5" s="37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P5" s="37">
         <v>3</v>
       </c>
       <c r="Q5" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="T5" s="26" t="s">
         <v>112</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="T5" s="26" t="s">
-        <v>114</v>
       </c>
       <c r="U5" s="37">
         <v>2</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="15">
@@ -13594,7 +13588,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="27"/>
@@ -13616,17 +13610,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="27"/>
       <c r="K7" s="26"/>
       <c r="L7" s="27"/>
       <c r="N7" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P7" s="37">
         <v>5</v>
@@ -13729,348 +13723,348 @@
     <row r="4" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="5" spans="3:9" ht="16.5" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>125</v>
-      </c>
       <c r="H7" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="G8" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="G9" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="G10" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="H10" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>142</v>
-      </c>
       <c r="I10" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="G11" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="H11" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="I11" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="G12" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="H12" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="I12" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="G13" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="H13" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="I13" s="13" t="s">
         <v>157</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="14" spans="3:9" ht="17.25">
       <c r="C14" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="G14" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="H14" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="G15" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="H15" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="I15" s="13" t="s">
         <v>169</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="H16" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>175</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="H17" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="I17" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="H18" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="I18" s="13" t="s">
         <v>187</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="G19" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="H19" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="I19" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -14106,7 +14100,7 @@
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="119" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
@@ -14146,46 +14140,46 @@
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>218</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>220</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="I4" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="J4" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="L4" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="J4" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="K4" s="36" t="s">
+      <c r="M4" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="N4" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="O4" s="167" t="s">
         <v>227</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="O4" s="167" t="s">
-        <v>229</v>
       </c>
       <c r="P4" s="168"/>
       <c r="Q4" s="168"/>
@@ -14193,28 +14187,28 @@
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -14228,7 +14222,7 @@
     </row>
     <row r="6" spans="2:22" ht="15">
       <c r="B6" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -14241,10 +14235,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -14259,7 +14253,7 @@
     </row>
     <row r="7" spans="2:22" ht="15">
       <c r="B7" s="25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -14272,10 +14266,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -14290,7 +14284,7 @@
     </row>
     <row r="8" spans="2:22" ht="15">
       <c r="B8" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -14303,10 +14297,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -14321,28 +14315,28 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -14356,7 +14350,7 @@
     </row>
     <row r="10" spans="2:22" ht="15">
       <c r="B10" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -14369,10 +14363,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -14387,7 +14381,7 @@
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -14408,7 +14402,7 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -14429,7 +14423,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -14450,7 +14444,7 @@
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -14469,13 +14463,13 @@
       <c r="Q14" s="171"/>
       <c r="R14" s="172"/>
       <c r="U14" s="185" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="V14" s="185"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -14498,7 +14492,7 @@
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -14517,15 +14511,15 @@
       <c r="Q16" s="171"/>
       <c r="R16" s="172"/>
       <c r="U16" s="185" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V16" s="186" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -14548,7 +14542,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -14568,12 +14562,12 @@
       <c r="R18" s="172"/>
       <c r="U18" s="185"/>
       <c r="V18" s="186" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -14596,7 +14590,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -14616,12 +14610,12 @@
       <c r="R20" s="172"/>
       <c r="U20" s="185"/>
       <c r="V20" s="186" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -14644,7 +14638,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -14664,12 +14658,12 @@
       <c r="R22" s="172"/>
       <c r="U22" s="185"/>
       <c r="V22" s="186" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -14692,7 +14686,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -14712,12 +14706,12 @@
       <c r="R24" s="172"/>
       <c r="U24" s="185"/>
       <c r="V24" s="186" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -14740,7 +14734,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -14760,12 +14754,12 @@
       <c r="R26" s="172"/>
       <c r="U26" s="185"/>
       <c r="V26" s="186" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -14788,7 +14782,7 @@
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C30" s="120"/>
       <c r="D30" s="120"/>
@@ -14826,46 +14820,46 @@
       <c r="Q31" s="165"/>
       <c r="R31" s="166"/>
       <c r="U31" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="15">
       <c r="B32" s="38" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F32" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="G32" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="H32" s="36" t="s">
+      <c r="I32" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="J32" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="K32" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="J32" s="36" t="s">
+      <c r="L32" s="176" t="s">
         <v>227</v>
-      </c>
-      <c r="K32" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="L32" s="176" t="s">
-        <v>229</v>
       </c>
       <c r="M32" s="177"/>
       <c r="N32" s="177"/>
@@ -14878,36 +14872,36 @@
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Y32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="2:29" ht="15">
       <c r="B33" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -14923,7 +14917,7 @@
       <c r="Q33" s="180"/>
       <c r="R33" s="181"/>
       <c r="U33" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -14946,17 +14940,17 @@
       <c r="Q34" s="180"/>
       <c r="R34" s="181"/>
       <c r="U34" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Y34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Z34" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="2:29" ht="15">
@@ -14979,14 +14973,14 @@
       <c r="R35" s="181"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="2:29" ht="15">
@@ -15030,11 +15024,11 @@
       <c r="Q37" s="180"/>
       <c r="R37" s="181"/>
       <c r="U37" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="2:29" ht="15">
@@ -15056,11 +15050,11 @@
       <c r="Q38" s="180"/>
       <c r="R38" s="181"/>
       <c r="U38" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="2:29" ht="15">
@@ -15082,26 +15076,26 @@
       <c r="Q39" s="180"/>
       <c r="R39" s="181"/>
       <c r="U39" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Y39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Z39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AA39" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AB39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AC39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="2:29">

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\13.Asserion TF\2_repository\Assertion-Checker-Generator\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DABEEN\workspace_been\git_assertion_tf\Assertion-Checker-Generator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A38045D-1F7F-45DC-854A-BA0C8D77F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9098BB-90DD-4028-AE56-E9919DA832D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3165" windowWidth="29040" windowHeight="15720" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="4" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -27,21 +27,10 @@
     <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId12"/>
     <sheet name="aw_builder" sheetId="2" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -53,12 +42,22 @@
     <author>tc={372E79E2-B979-45EA-A3D7-4E90DC8A7E1F}</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{372E79E2-B979-45EA-A3D7-4E90DC8A7E1F}">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{372E79E2-B979-45EA-A3D7-4E90DC8A7E1F}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     승훈님 좋습니다!!</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -75,17 +74,36 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{11F28A3C-C90D-4418-BB46-9B6DADCDBE4E}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Default를 Posedge로 가정하는 것은 어떻게 생각하시나요
 Reply:
     좋아요</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="1" shapeId="0" xr:uid="{EAEF4952-1559-4391-A03C-03F57B7ADC3C}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     사실 Clock도 왠만하면 한 IP나 블록에서 동일한 것을 사용할 것 같은데 따로 만든 이유는 Clock 대신 sync signal 같은거 활용하기 위함인가요?
@@ -94,11 +112,21 @@
     rx assertion 보니까, clk을 base clk만 사용하지 않더라구요
 Reply:
     그럼 유지해야겠군요 확인 감사합니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="2" shapeId="0" xr:uid="{066F6494-15CB-41D2-A5E8-F35BD8460361}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     |-&gt; 이거로 통일해 버리면 칸 하나 줄일 수 있을 것 같은데 어떻게 생각하시나요?
@@ -109,6 +137,7 @@
 Reply:
     일할땐 생각해요ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -125,17 +154,36 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0" xr:uid="{A5EE3683-DAAF-4AD0-95D0-B34E9981B26B}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Default를 Posedge로 가정하는 것은 어떻게 생각하시나요
 Reply:
     좋아요</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="1" shapeId="0" xr:uid="{FBABEDF7-5267-49E5-B5C6-B213E24A5F77}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     사실 Clock도 왠만하면 한 IP나 블록에서 동일한 것을 사용할 것 같은데 따로 만든 이유는 Clock 대신 sync signal 같은거 활용하기 위함인가요?
@@ -144,11 +192,21 @@
     rx assertion 보니까, clk을 base clk만 사용하지 않더라구요
 Reply:
     그럼 유지해야겠군요 확인 감사합니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="2" shapeId="0" xr:uid="{AB18BE64-54B0-4373-A63D-1F608B3F50E6}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <charset val="129"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     |-&gt; 이거로 통일해 버리면 칸 하나 줄일 수 있을 것 같은데 어떻게 생각하시나요?
@@ -159,6 +217,7 @@
 Reply:
     일할땐 생각해요ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -166,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="326">
   <si>
     <t>Base Information</t>
   </si>
@@ -2431,6 +2490,1556 @@
     <t>Expected Preset(Logic Part)</t>
   </si>
   <si>
+    <t>Expected Preset(Property Part)</t>
+  </si>
+  <si>
+    <t>Expected Preset(Condition)</t>
+  </si>
+  <si>
+    <t>Delay*_1(숫자)</t>
+  </si>
+  <si>
+    <t>Delay*_2(숫자)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>property p_condition_check1(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trigger_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);
+    @(posedge clk) disable iff(!resetn)
+    $rose(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trigger_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) |-&gt; ##[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3C7D22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delay1_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3C7D22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delay1_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] $rose(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);
+endproperty
+assert property (p_condition_check1(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i_trigger_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i_result_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)  else $error("failed at %t", $time")
+property p_condition_check2();
+    @(posedge clk) disable iff(!resetn)
+    $rose(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trigger_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) |-&gt; ##[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3C7D22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delay2_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3C7D22"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delay2_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] $rose(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>result_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);
+endproperty
+assert property (p_condition_check2(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i_trigger_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i_result_2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)  else $error("failed at %t", $time")</t>
+    </r>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Expect Width</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>Clk OUt</t>
+  </si>
+  <si>
+    <t>SFR_CLK_SEL</t>
+  </si>
+  <si>
+    <t>CLK_1</t>
+  </si>
+  <si>
+    <t>OSC_CLK</t>
+  </si>
+  <si>
+    <t>CJS</t>
+  </si>
+  <si>
+    <t>Very Handsome</t>
+  </si>
+  <si>
+    <t>req/ack</t>
+  </si>
+  <si>
+    <t>Two-Phase</t>
+  </si>
+  <si>
+    <t>OPTION_OUTPUT</t>
+  </si>
+  <si>
+    <t>SFR_OPTION_OUT_EN &amp;&amp; OPTION_OUT_TRIGGER</t>
+  </si>
+  <si>
+    <t>EVENT TRRIGER</t>
+  </si>
+  <si>
+    <t>Assertion Temporal Operators(시간 연산자)</t>
+  </si>
+  <si>
+    <t>함수</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>예시</t>
+  </si>
+  <si>
+    <t>연산자</t>
+  </si>
+  <si>
+    <t>$past(expr, [n], [clk_enable])</t>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 사이클 전의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 값을 반환. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>clk_enable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 조건이 있을 때만 추적.</t>
+    </r>
+  </si>
+  <si>
+    <t>$past(req, 2)</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>항상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>assert property (always (a -&gt; b));</t>
+  </si>
+  <si>
+    <t>$rose(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>이 0 → 1로 상승했는지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$rose(start)</t>
+  </si>
+  <si>
+    <t>s_eventually</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>언젠가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함 (strong eventually)</t>
+    </r>
+  </si>
+  <si>
+    <t>`assert property (a</t>
+  </si>
+  <si>
+    <t>$fell(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>이 1 → 0으로 하강했는지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$fell(reset)</t>
+  </si>
+  <si>
+    <t>eventually</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>언젠가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함 (weak eventually)</t>
+    </r>
+  </si>
+  <si>
+    <t>$stable(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>이 이전 사이클과 동일한지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$stable(state)</t>
+  </si>
+  <si>
+    <t>nexttime</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>다음 사이클에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>$changed(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>이 이전 사이클과 달라졌는지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$changed(data)</t>
+  </si>
+  <si>
+    <t>until</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>다른 조건이 참이 될 때까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 계속 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>assert property (a until b);</t>
+  </si>
+  <si>
+    <t>$isunknown(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>이 X 또는 Z 상태인지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$isunknown(signal)</t>
+  </si>
+  <si>
+    <t>until_with</t>
+  </si>
+  <si>
+    <r>
+      <t>until</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 비슷하지만, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 참인 사이클에도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>가 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>assert property (a until_with b);</t>
+  </si>
+  <si>
+    <t>$onehot(expr)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에서 정확히 1비트만 1인지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$onehot(sel)</t>
+  </si>
+  <si>
+    <r>
+      <t>implies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>|-&gt;</t>
+  </si>
+  <si>
+    <t>앞의 event가 참이면 같은 사이클에 뒤의 조건 참인지 확인</t>
+  </si>
+  <si>
+    <t>$onehot0(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에서 0개 또는 1개의 비트만 1인지 확인</t>
+    </r>
+  </si>
+  <si>
+    <t>$onehot0(sel)</t>
+  </si>
+  <si>
+    <r>
+      <t>followed by</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">두 조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>지정된 시간 간격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>으로 순차적으로 발생해야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>a ##1 b</t>
+  </si>
+  <si>
+    <t>$countones(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에서 1의 개수를 반환</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$countones(4'b1011)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>overlapped implies</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>|=&gt;</t>
+  </si>
+  <si>
+    <t>앞의 event가 참이면 한 사이클 후 뒤의 조건이 참인지 확인</t>
+  </si>
+  <si>
+    <t>$countbits(expr, value)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>와 같은 비트 수를 반환</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$countbits(4'b1011, 1'b0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 1</t>
+    </r>
+  </si>
+  <si>
+    <t>throughout</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>지속적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>assert property (a throughout b);</t>
+  </si>
+  <si>
+    <t>$clog2(expr)</t>
+  </si>
+  <si>
+    <r>
+      <t>expr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>보다 크거나 같은 최소 2의 제곱수의 log2 값을 반환</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$clog2(9)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 4</t>
+    </r>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">조건이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>지정된 시간 내에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 참이어야 함</t>
+    </r>
+  </si>
+  <si>
+    <t>assert property (a within [1:5]);</t>
+  </si>
+  <si>
+    <t>$size(array)</t>
+  </si>
+  <si>
+    <t>배열의 크기를 반환</t>
+  </si>
+  <si>
+    <t>$size(my_array)</t>
+  </si>
+  <si>
+    <t>disable iff</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">특정 조건이 참일 때 Assertion을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>비활성화</t>
+    </r>
+  </si>
+  <si>
+    <t>disable iff (reset)</t>
+  </si>
+  <si>
+    <t>$dimensions(array)</t>
+  </si>
+  <si>
+    <t>배열의 차원 수를 반환</t>
+  </si>
+  <si>
+    <t>$dimensions(my_array)</t>
+  </si>
+  <si>
+    <t>$left(array, dim)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">배열의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 차원의 왼쪽 인덱스 반환</t>
+    </r>
+  </si>
+  <si>
+    <t>$left(my_array, 1)</t>
+  </si>
+  <si>
+    <t>$right(array, dim)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">배열의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 차원의 오른쪽 인덱스 반환</t>
+    </r>
+  </si>
+  <si>
+    <t>$right(my_array, 1)</t>
+  </si>
+  <si>
+    <t>$low(array, dim)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">배열의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 차원의 최소 인덱스 반환</t>
+    </r>
+  </si>
+  <si>
+    <t>$low(my_array, 1)</t>
+  </si>
+  <si>
+    <t>$high(array, dim)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">배열의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF424242"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF424242"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 차원의 최대 인덱스 반환</t>
+    </r>
+  </si>
+  <si>
+    <t>$high(my_array, 1)</t>
+  </si>
+  <si>
+    <t>$increment(array, dim)</t>
+  </si>
+  <si>
+    <t>배열의 인덱스 증가 방향 반환</t>
+  </si>
+  <si>
+    <t>$increment(my_array, 1)</t>
+  </si>
+  <si>
+    <t>$typename(var)</t>
+  </si>
+  <si>
+    <t>변수의 타입 이름을 문자열로 반환</t>
+  </si>
+  <si>
+    <t>$typename(my_var)</t>
+  </si>
+  <si>
+    <t>Property Generator</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Property Name</t>
+  </si>
+  <si>
+    <t>Edge Types</t>
+  </si>
+  <si>
+    <t>Disable Condition</t>
+  </si>
+  <si>
+    <t>Antecedent Syntax</t>
+  </si>
+  <si>
+    <t>Antecedent</t>
+  </si>
+  <si>
+    <t>implication</t>
+  </si>
+  <si>
+    <t>Consequence Syntax</t>
+  </si>
+  <si>
+    <t>Consequence</t>
+  </si>
+  <si>
+    <t>Signal Duration(min)</t>
+  </si>
+  <si>
+    <t>Signal Duration(max)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>p_assert0</t>
+  </si>
+  <si>
+    <t>posedge</t>
+  </si>
+  <si>
+    <t>clk</t>
+  </si>
+  <si>
+    <t>~rstn</t>
+  </si>
+  <si>
+    <t>$rose</t>
+  </si>
+  <si>
+    <t>ㄴConsequence</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>p_assert1</t>
+  </si>
+  <si>
+    <t>Not used</t>
+  </si>
+  <si>
+    <t>Property Info &amp; Antecedent</t>
+  </si>
+  <si>
+    <t>Delay &amp;
+Consequence</t>
+  </si>
+  <si>
+    <t>1st Consequence</t>
+  </si>
+  <si>
+    <t>2nd Consequence</t>
+  </si>
+  <si>
+    <t>3rd Consequence</t>
+  </si>
+  <si>
+    <t>4th Conseqeucne</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>Sequence Generator</t>
+  </si>
+  <si>
+    <t>{User_input}</t>
+  </si>
+  <si>
+    <t>Sequence Name</t>
+  </si>
+  <si>
+    <t>negedge</t>
+  </si>
+  <si>
+    <t>s_assert</t>
+  </si>
+  <si>
+    <t>Event Trigger</t>
+  </si>
+  <si>
+    <t>$fell</t>
+  </si>
+  <si>
+    <t>$changed</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>Signal Duration</t>
+  </si>
+  <si>
+    <t>[*m:n]</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>$past</t>
+  </si>
+  <si>
+    <t>Counter Name</t>
+  </si>
+  <si>
+    <t>property</t>
+  </si>
+  <si>
+    <t>consequence</t>
+  </si>
+  <si>
+    <t>Counter Condition</t>
+  </si>
+  <si>
+    <t>property name</t>
+  </si>
+  <si>
+    <t>Edge Type</t>
+  </si>
+  <si>
+    <t>condition statement</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>hsync</t>
+  </si>
+  <si>
+    <t>hsw_conter</t>
+  </si>
+  <si>
+    <t>rstn</t>
+  </si>
+  <si>
+    <t>hsw_counter</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>!rstn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counter &lt;= 0 </t>
+  </si>
+  <si>
+    <t>else if</t>
+  </si>
+  <si>
+    <t>counter &lt;= counter + 1</t>
+  </si>
+  <si>
+    <t>p_assert2</t>
+  </si>
+  <si>
+    <t>else</t>
+  </si>
+  <si>
+    <t>p_assert3</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>Hsync_counter</t>
+  </si>
+  <si>
+    <t>Resetn</t>
+  </si>
+  <si>
+    <t>hsw</t>
+  </si>
+  <si>
+    <t>counter condition</t>
+  </si>
+  <si>
+    <t>counter state</t>
+  </si>
+  <si>
+    <t>flag == 1</t>
+  </si>
+  <si>
+    <t>counter = counter +1</t>
+  </si>
+  <si>
+    <t>Assertion Waiver Builder</t>
+  </si>
+  <si>
+    <t>문서 가이드</t>
+  </si>
+  <si>
+    <t>Checker Name으로 시작하는</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checker Name :  </t>
+  </si>
+  <si>
+    <t>Waiver가 적용될 Checker의 이름으로, Waiver도 해당 이름을 따라 각각의 이름이 정해진다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checker Path : </t>
+  </si>
+  <si>
+    <t>Waiver가 적용될 Checker의 Path</t>
+  </si>
+  <si>
+    <t>Checker Name</t>
+  </si>
+  <si>
+    <t>Example_DE_GEN</t>
+  </si>
+  <si>
+    <t>Checker Path</t>
+  </si>
+  <si>
+    <t>top.incr_top.de_gen_model_intf</t>
+  </si>
+  <si>
+    <t>Waiver Type</t>
+  </si>
+  <si>
+    <t>Event Trigger Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Repeat</t>
+  </si>
+  <si>
+    <t>Event Trigger Type</t>
+  </si>
+  <si>
+    <t>Event Trigger Path</t>
+  </si>
+  <si>
+    <t>Waive Target Assertion (Blank = All in Checker)</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>On Event</t>
+  </si>
+  <si>
+    <t>RSTN</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
+    <t>top.dut.BLK_TX.ISO_TX.u_DE_GEN_TOP.i_nRST</t>
+  </si>
+  <si>
+    <t>CHK_DE_START_CHK</t>
+  </si>
+  <si>
+    <t>└</t>
+  </si>
+  <si>
+    <t>FRAME_START</t>
+  </si>
+  <si>
+    <t>top.dut.BLK_TX.ISO_TX.u_AHB_LSI_DIVIDER.o_Div_to_Gate_Frame_Start_Pulse</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Posedge</t>
+  </si>
+  <si>
+    <t>Example_CSG_GS[25:0]</t>
+  </si>
+  <si>
+    <t>top.incr_top.csg_all_path_model_top_intf.gs_model[25:0].u_mask_model</t>
+  </si>
+  <si>
+    <t>OUTPUT_GLITCH_CHK</t>
+  </si>
+  <si>
+    <t>TCON_RDY</t>
+  </si>
+  <si>
+    <t>`TX_TOP_PATH.i_tcon_rdy</t>
+  </si>
+  <si>
+    <t>Example_CSG_OSG[9:0]</t>
+  </si>
+  <si>
+    <t>top.incr_top.csg_all_path_model_top_intf.osg_model[9:0].u_mask_model</t>
+  </si>
+  <si>
+    <t>always begin</t>
+  </si>
+  <si>
+    <t>top.dut.BLK_TX.ISO_TX.u_IP_15_01_CSG_WRAPPER_inst.u_IP_15_01.u_csg_top._u_csg_osg_top.iframe_start</t>
+  </si>
+  <si>
+    <t>└ +On Event</t>
+  </si>
+  <si>
+    <t>Clock</t>
+  </si>
+  <si>
+    <t>top.dut.BLK_TX.ISO_TX.u_IP_15_01_CSG_WRAPPER_inst.u_IP_15_01.u_csg_top.i_sclk</t>
+  </si>
+  <si>
     <t>always @(posedge clk or negedge resetn) begin
   if(!resetn) begin
     cnt &lt;= 0;
@@ -2445,1563 +4054,23 @@
     cnt &lt;= cnt;
   end
 end</t>
-  </si>
-  <si>
-    <t>Expected Preset(Property Part)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plus Condition</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trigger Condition</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>property p_counter_check
     @(posedge clk) disable iff(!resetn)
     trigger_condition |-&gt; (cnt == expect_count_value);
 endproperty
-assert property (p_counter_check)  else $error("failed at %t", $time")</t>
-  </si>
-  <si>
-    <t>Expected Preset(Condition)</t>
-  </si>
-  <si>
-    <t>Delay*_1(숫자)</t>
-  </si>
-  <si>
-    <t>Delay*_2(숫자)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>property p_condition_check1(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>trigger_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>result_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);
-    @(posedge clk) disable iff(!resetn)
-    $rose(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>trigger_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) |-&gt; ##[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3C7D22"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>delay1_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3C7D22"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>delay1_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>] $rose(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>result_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);
-endproperty
-assert property (p_condition_check1(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i_trigger_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i_result_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)  else $error("failed at %t", $time")
-property p_condition_check2();
-    @(posedge clk) disable iff(!resetn)
-    $rose(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>trigger_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) |-&gt; ##[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3C7D22"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>delay2_1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3C7D22"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>delay2_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>] $rose(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>result_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);
-endproperty
-assert property (p_condition_check2(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i_trigger_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i_result_2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)  else $error("failed at %t", $time")</t>
-    </r>
-  </si>
-  <si>
-    <t>Delay</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Expect Width</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>Clk OUt</t>
-  </si>
-  <si>
-    <t>SFR_CLK_SEL</t>
-  </si>
-  <si>
-    <t>CLK_1</t>
-  </si>
-  <si>
-    <t>OSC_CLK</t>
-  </si>
-  <si>
-    <t>CJS</t>
-  </si>
-  <si>
-    <t>Very Handsome</t>
-  </si>
-  <si>
-    <t>req/ack</t>
-  </si>
-  <si>
-    <t>Two-Phase</t>
-  </si>
-  <si>
-    <t>OPTION_OUTPUT</t>
-  </si>
-  <si>
-    <t>SFR_OPTION_OUT_EN &amp;&amp; OPTION_OUT_TRIGGER</t>
-  </si>
-  <si>
-    <t>EVENT TRRIGER</t>
-  </si>
-  <si>
-    <t>Assertion Temporal Operators(시간 연산자)</t>
-  </si>
-  <si>
-    <t>함수</t>
-  </si>
-  <si>
-    <t>설명</t>
-  </si>
-  <si>
-    <t>예시</t>
-  </si>
-  <si>
-    <t>연산자</t>
-  </si>
-  <si>
-    <t>$past(expr, [n], [clk_enable])</t>
-  </si>
-  <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 사이클 전의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 값을 반환. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>clk_enable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 조건이 있을 때만 추적.</t>
-    </r>
-  </si>
-  <si>
-    <t>$past(req, 2)</t>
-  </si>
-  <si>
-    <t>always</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>항상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>assert property (always (a -&gt; b));</t>
-  </si>
-  <si>
-    <t>$rose(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>이 0 → 1로 상승했는지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$rose(start)</t>
-  </si>
-  <si>
-    <t>s_eventually</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>언젠가는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함 (strong eventually)</t>
-    </r>
-  </si>
-  <si>
-    <t>`assert property (a</t>
-  </si>
-  <si>
-    <t>$fell(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>이 1 → 0으로 하강했는지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$fell(reset)</t>
-  </si>
-  <si>
-    <t>eventually</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>언젠가는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함 (weak eventually)</t>
-    </r>
-  </si>
-  <si>
-    <t>$stable(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>이 이전 사이클과 동일한지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$stable(state)</t>
-  </si>
-  <si>
-    <t>nexttime</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>다음 사이클에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>$changed(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>이 이전 사이클과 달라졌는지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$changed(data)</t>
-  </si>
-  <si>
-    <t>until</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>다른 조건이 참이 될 때까지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 계속 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>assert property (a until b);</t>
-  </si>
-  <si>
-    <t>$isunknown(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>이 X 또는 Z 상태인지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$isunknown(signal)</t>
-  </si>
-  <si>
-    <t>until_with</t>
-  </si>
-  <si>
-    <r>
-      <t>until</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과 비슷하지만, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가 참인 사이클에도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>가 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>assert property (a until_with b);</t>
-  </si>
-  <si>
-    <t>$onehot(expr)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>에서 정확히 1비트만 1인지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$onehot(sel)</t>
-  </si>
-  <si>
-    <r>
-      <t>implies</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>|-&gt;</t>
-  </si>
-  <si>
-    <t>앞의 event가 참이면 같은 사이클에 뒤의 조건 참인지 확인</t>
-  </si>
-  <si>
-    <t>$onehot0(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>에서 0개 또는 1개의 비트만 1인지 확인</t>
-    </r>
-  </si>
-  <si>
-    <t>$onehot0(sel)</t>
-  </si>
-  <si>
-    <r>
-      <t>followed by</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">두 조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>지정된 시간 간격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>으로 순차적으로 발생해야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>a ##1 b</t>
-  </si>
-  <si>
-    <t>$countones(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>에서 1의 개수를 반환</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$countones(4'b1011)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> → 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>overlapped implies</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>|=&gt;</t>
-  </si>
-  <si>
-    <t>앞의 event가 참이면 한 사이클 후 뒤의 조건이 참인지 확인</t>
-  </si>
-  <si>
-    <t>$countbits(expr, value)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에서 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>와 같은 비트 수를 반환</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$countbits(4'b1011, 1'b0)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> → 1</t>
-    </r>
-  </si>
-  <si>
-    <t>throughout</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>지속적으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>assert property (a throughout b);</t>
-  </si>
-  <si>
-    <t>$clog2(expr)</t>
-  </si>
-  <si>
-    <r>
-      <t>expr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>보다 크거나 같은 최소 2의 제곱수의 log2 값을 반환</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$clog2(9)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> → 4</t>
-    </r>
-  </si>
-  <si>
-    <t>within</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">조건이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>지정된 시간 내에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 참이어야 함</t>
-    </r>
-  </si>
-  <si>
-    <t>assert property (a within [1:5]);</t>
-  </si>
-  <si>
-    <t>$size(array)</t>
-  </si>
-  <si>
-    <t>배열의 크기를 반환</t>
-  </si>
-  <si>
-    <t>$size(my_array)</t>
-  </si>
-  <si>
-    <t>disable iff</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">특정 조건이 참일 때 Assertion을 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>비활성화</t>
-    </r>
-  </si>
-  <si>
-    <t>disable iff (reset)</t>
-  </si>
-  <si>
-    <t>$dimensions(array)</t>
-  </si>
-  <si>
-    <t>배열의 차원 수를 반환</t>
-  </si>
-  <si>
-    <t>$dimensions(my_array)</t>
-  </si>
-  <si>
-    <t>$left(array, dim)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">배열의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 차원의 왼쪽 인덱스 반환</t>
-    </r>
-  </si>
-  <si>
-    <t>$left(my_array, 1)</t>
-  </si>
-  <si>
-    <t>$right(array, dim)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">배열의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 차원의 오른쪽 인덱스 반환</t>
-    </r>
-  </si>
-  <si>
-    <t>$right(my_array, 1)</t>
-  </si>
-  <si>
-    <t>$low(array, dim)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">배열의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 차원의 최소 인덱스 반환</t>
-    </r>
-  </si>
-  <si>
-    <t>$low(my_array, 1)</t>
-  </si>
-  <si>
-    <t>$high(array, dim)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">배열의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF424242"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF424242"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 차원의 최대 인덱스 반환</t>
-    </r>
-  </si>
-  <si>
-    <t>$high(my_array, 1)</t>
-  </si>
-  <si>
-    <t>$increment(array, dim)</t>
-  </si>
-  <si>
-    <t>배열의 인덱스 증가 방향 반환</t>
-  </si>
-  <si>
-    <t>$increment(my_array, 1)</t>
-  </si>
-  <si>
-    <t>$typename(var)</t>
-  </si>
-  <si>
-    <t>변수의 타입 이름을 문자열로 반환</t>
-  </si>
-  <si>
-    <t>$typename(my_var)</t>
-  </si>
-  <si>
-    <t>Property Generator</t>
-  </si>
-  <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Property Name</t>
-  </si>
-  <si>
-    <t>Edge Types</t>
-  </si>
-  <si>
-    <t>Disable Condition</t>
-  </si>
-  <si>
-    <t>Antecedent Syntax</t>
-  </si>
-  <si>
-    <t>Antecedent</t>
-  </si>
-  <si>
-    <t>implication</t>
-  </si>
-  <si>
-    <t>Consequence Syntax</t>
-  </si>
-  <si>
-    <t>Consequence</t>
-  </si>
-  <si>
-    <t>Signal Duration(min)</t>
-  </si>
-  <si>
-    <t>Signal Duration(max)</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Property</t>
-  </si>
-  <si>
-    <t>p_assert0</t>
-  </si>
-  <si>
-    <t>posedge</t>
-  </si>
-  <si>
-    <t>clk</t>
-  </si>
-  <si>
-    <t>~rstn</t>
-  </si>
-  <si>
-    <t>$rose</t>
-  </si>
-  <si>
-    <t>ㄴConsequence</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>p_assert1</t>
-  </si>
-  <si>
-    <t>Not used</t>
-  </si>
-  <si>
-    <t>Property Info &amp; Antecedent</t>
-  </si>
-  <si>
-    <t>Delay &amp;
-Consequence</t>
-  </si>
-  <si>
-    <t>1st Consequence</t>
-  </si>
-  <si>
-    <t>2nd Consequence</t>
-  </si>
-  <si>
-    <t>3rd Consequence</t>
-  </si>
-  <si>
-    <t>4th Conseqeucne</t>
-  </si>
-  <si>
-    <t>Nothing</t>
-  </si>
-  <si>
-    <t>Sequence Generator</t>
-  </si>
-  <si>
-    <t>{User_input}</t>
-  </si>
-  <si>
-    <t>Sequence Name</t>
-  </si>
-  <si>
-    <t>negedge</t>
-  </si>
-  <si>
-    <t>s_assert</t>
-  </si>
-  <si>
-    <t>Event Trigger</t>
-  </si>
-  <si>
-    <t>$fell</t>
-  </si>
-  <si>
-    <t>$changed</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>Signal Duration</t>
-  </si>
-  <si>
-    <t>[*m:n]</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>$past</t>
-  </si>
-  <si>
-    <t>Counter Name</t>
-  </si>
-  <si>
-    <t>property</t>
-  </si>
-  <si>
-    <t>consequence</t>
-  </si>
-  <si>
-    <t>Counter Condition</t>
-  </si>
-  <si>
-    <t>property name</t>
-  </si>
-  <si>
-    <t>Edge Type</t>
-  </si>
-  <si>
-    <t>condition statement</t>
-  </si>
-  <si>
-    <t>condition</t>
-  </si>
-  <si>
-    <t>hsync</t>
-  </si>
-  <si>
-    <t>hsw_conter</t>
-  </si>
-  <si>
-    <t>rstn</t>
-  </si>
-  <si>
-    <t>hsw_counter</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>!rstn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">counter &lt;= 0 </t>
-  </si>
-  <si>
-    <t>else if</t>
-  </si>
-  <si>
-    <t>counter &lt;= counter + 1</t>
-  </si>
-  <si>
-    <t>p_assert2</t>
-  </si>
-  <si>
-    <t>else</t>
-  </si>
-  <si>
-    <t>p_assert3</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>Hsync_counter</t>
-  </si>
-  <si>
-    <t>Resetn</t>
-  </si>
-  <si>
-    <t>hsw</t>
-  </si>
-  <si>
-    <t>counter condition</t>
-  </si>
-  <si>
-    <t>counter state</t>
-  </si>
-  <si>
-    <t>flag == 1</t>
-  </si>
-  <si>
-    <t>counter = counter +1</t>
-  </si>
-  <si>
-    <t>Assertion Waiver Builder</t>
-  </si>
-  <si>
-    <t>문서 가이드</t>
-  </si>
-  <si>
-    <t>Checker Name으로 시작하는</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checker Name :  </t>
-  </si>
-  <si>
-    <t>Waiver가 적용될 Checker의 이름으로, Waiver도 해당 이름을 따라 각각의 이름이 정해진다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checker Path : </t>
-  </si>
-  <si>
-    <t>Waiver가 적용될 Checker의 Path</t>
-  </si>
-  <si>
-    <t>Checker Name</t>
-  </si>
-  <si>
-    <t>Example_DE_GEN</t>
-  </si>
-  <si>
-    <t>Checker Path</t>
-  </si>
-  <si>
-    <t>top.incr_top.de_gen_model_intf</t>
-  </si>
-  <si>
-    <t>Waiver Type</t>
-  </si>
-  <si>
-    <t>Event Trigger Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Repeat</t>
-  </si>
-  <si>
-    <t>Event Trigger Type</t>
-  </si>
-  <si>
-    <t>Event Trigger Path</t>
-  </si>
-  <si>
-    <t>Waive Target Assertion (Blank = All in Checker)</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>On Event</t>
-  </si>
-  <si>
-    <t>RSTN</t>
-  </si>
-  <si>
-    <t>Wait</t>
-  </si>
-  <si>
-    <t>top.dut.BLK_TX.ISO_TX.u_DE_GEN_TOP.i_nRST</t>
-  </si>
-  <si>
-    <t>CHK_DE_START_CHK</t>
-  </si>
-  <si>
-    <t>└</t>
-  </si>
-  <si>
-    <t>FRAME_START</t>
-  </si>
-  <si>
-    <t>top.dut.BLK_TX.ISO_TX.u_AHB_LSI_DIVIDER.o_Div_to_Gate_Frame_Start_Pulse</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Posedge</t>
-  </si>
-  <si>
-    <t>Example_CSG_GS[25:0]</t>
-  </si>
-  <si>
-    <t>top.incr_top.csg_all_path_model_top_intf.gs_model[25:0].u_mask_model</t>
-  </si>
-  <si>
-    <t>OUTPUT_GLITCH_CHK</t>
-  </si>
-  <si>
-    <t>TCON_RDY</t>
-  </si>
-  <si>
-    <t>`TX_TOP_PATH.i_tcon_rdy</t>
-  </si>
-  <si>
-    <t>Example_CSG_OSG[9:0]</t>
-  </si>
-  <si>
-    <t>top.incr_top.csg_all_path_model_top_intf.osg_model[9:0].u_mask_model</t>
-  </si>
-  <si>
-    <t>always begin</t>
-  </si>
-  <si>
-    <t>top.dut.BLK_TX.ISO_TX.u_IP_15_01_CSG_WRAPPER_inst.u_IP_15_01.u_csg_top._u_csg_osg_top.iframe_start</t>
-  </si>
-  <si>
-    <t>└ +On Event</t>
-  </si>
-  <si>
-    <t>Clock</t>
-  </si>
-  <si>
-    <t>top.dut.BLK_TX.ISO_TX.u_IP_15_01_CSG_WRAPPER_inst.u_IP_15_01.u_csg_top.i_sclk</t>
+assert property (p_counter_check)  else $error("failed at %t", $time);</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4932,7 +5001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5356,6 +5425,18 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5559,7 +5640,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{BB1E0E6C-DA0D-43B5-A5C3-94756A668AC2}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5979,21 +6060,21 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B1:N9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="53"/>
     <col min="2" max="2" width="12.5" style="65" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="67" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="53" customWidth="1"/>
-    <col min="5" max="5" width="16.625" style="65" customWidth="1"/>
+    <col min="4" max="4" width="2.58203125" style="53" customWidth="1"/>
+    <col min="5" max="5" width="16.58203125" style="65" customWidth="1"/>
     <col min="6" max="6" width="9" style="55"/>
     <col min="7" max="7" width="16.75" style="66" customWidth="1"/>
     <col min="8" max="8" width="9" style="55"/>
     <col min="9" max="9" width="19.25" style="66" customWidth="1"/>
     <col min="10" max="10" width="9" style="56"/>
-    <col min="11" max="11" width="2.625" style="53" customWidth="1"/>
+    <col min="11" max="11" width="2.58203125" style="53" customWidth="1"/>
     <col min="12" max="12" width="17" style="65" customWidth="1"/>
-    <col min="13" max="13" width="29.125" style="66" customWidth="1"/>
+    <col min="13" max="13" width="29.08203125" style="66" customWidth="1"/>
     <col min="14" max="14" width="9" style="56"/>
     <col min="15" max="16384" width="9" style="53"/>
   </cols>
@@ -6184,36 +6265,36 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D35609-775E-4A26-9091-D70AA658E418}">
   <dimension ref="A1:AH37"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="43" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
-    <col min="12" max="12" width="20.625" customWidth="1"/>
-    <col min="13" max="13" width="21.125" style="44" customWidth="1"/>
-    <col min="14" max="14" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.58203125" customWidth="1"/>
+    <col min="13" max="13" width="21.08203125" style="44" customWidth="1"/>
+    <col min="14" max="14" width="3.33203125" customWidth="1"/>
     <col min="15" max="15" width="14" style="43" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.25" customWidth="1"/>
-    <col min="19" max="19" width="10.875" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" customWidth="1"/>
     <col min="21" max="21" width="18.75" customWidth="1"/>
-    <col min="22" max="22" width="11.875" customWidth="1"/>
+    <col min="22" max="22" width="11.83203125" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
     <col min="24" max="24" width="17.5" style="44" customWidth="1"/>
     <col min="26" max="26" width="15" style="43" customWidth="1"/>
     <col min="27" max="27" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="10.875" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
     <col min="30" max="30" width="9" style="44" bestFit="1"/>
-    <col min="31" max="31" width="13.875" style="43" customWidth="1"/>
+    <col min="31" max="31" width="13.83203125" style="43" customWidth="1"/>
     <col min="32" max="32" width="19.75" customWidth="1"/>
     <col min="33" max="33" width="16.75" customWidth="1"/>
     <col min="34" max="34" width="19.5" style="44" customWidth="1"/>
@@ -6221,7 +6302,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="144" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B1" s="145"/>
       <c r="C1" s="145"/>
@@ -6236,7 +6317,7 @@
       <c r="L1" s="145"/>
       <c r="M1" s="146"/>
       <c r="O1" s="144" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P1" s="145"/>
       <c r="Q1" s="145"/>
@@ -6247,221 +6328,221 @@
       <c r="V1" s="145"/>
       <c r="W1" s="145"/>
       <c r="X1" s="146"/>
-      <c r="Z1" s="192" t="s">
+      <c r="Z1" s="196" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA1" s="197"/>
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="197"/>
+      <c r="AD1" s="197"/>
+      <c r="AE1" s="197"/>
+      <c r="AF1" s="197"/>
+      <c r="AG1" s="197"/>
+      <c r="AH1" s="198"/>
+    </row>
+    <row r="2" spans="1:34" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A2" s="190"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="192"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="191"/>
+      <c r="Q2" s="191"/>
+      <c r="R2" s="191"/>
+      <c r="S2" s="191"/>
+      <c r="T2" s="191"/>
+      <c r="U2" s="191"/>
+      <c r="V2" s="191"/>
+      <c r="W2" s="191"/>
+      <c r="X2" s="192"/>
+      <c r="Z2" s="199"/>
+      <c r="AA2" s="200"/>
+      <c r="AB2" s="200"/>
+      <c r="AC2" s="200"/>
+      <c r="AD2" s="200"/>
+      <c r="AE2" s="200"/>
+      <c r="AF2" s="200"/>
+      <c r="AG2" s="200"/>
+      <c r="AH2" s="201"/>
+    </row>
+    <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A3" s="202" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="203"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="202" t="s">
         <v>256</v>
       </c>
-      <c r="AA1" s="193"/>
-      <c r="AB1" s="193"/>
-      <c r="AC1" s="193"/>
-      <c r="AD1" s="193"/>
-      <c r="AE1" s="193"/>
-      <c r="AF1" s="193"/>
-      <c r="AG1" s="193"/>
-      <c r="AH1" s="194"/>
-    </row>
-    <row r="2" spans="1:34" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A2" s="186"/>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="187"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="187"/>
-      <c r="M2" s="188"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="187"/>
-      <c r="Q2" s="187"/>
-      <c r="R2" s="187"/>
-      <c r="S2" s="187"/>
-      <c r="T2" s="187"/>
-      <c r="U2" s="187"/>
-      <c r="V2" s="187"/>
-      <c r="W2" s="187"/>
-      <c r="X2" s="188"/>
-      <c r="Z2" s="195"/>
-      <c r="AA2" s="196"/>
-      <c r="AB2" s="196"/>
-      <c r="AC2" s="196"/>
-      <c r="AD2" s="196"/>
-      <c r="AE2" s="196"/>
-      <c r="AF2" s="196"/>
-      <c r="AG2" s="196"/>
-      <c r="AH2" s="197"/>
-    </row>
-    <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A3" s="198" t="s">
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="204"/>
+      <c r="O3" s="193"/>
+      <c r="P3" s="194"/>
+      <c r="Q3" s="194"/>
+      <c r="R3" s="194"/>
+      <c r="S3" s="194"/>
+      <c r="T3" s="194"/>
+      <c r="U3" s="194"/>
+      <c r="V3" s="194"/>
+      <c r="W3" s="194"/>
+      <c r="X3" s="195"/>
+      <c r="Z3" s="205" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA3" s="206"/>
+      <c r="AB3" s="206"/>
+      <c r="AC3" s="206"/>
+      <c r="AD3" s="207"/>
+      <c r="AE3" s="205" t="s">
         <v>257</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="198" t="s">
-        <v>258</v>
-      </c>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="200"/>
-      <c r="O3" s="189"/>
-      <c r="P3" s="190"/>
-      <c r="Q3" s="190"/>
-      <c r="R3" s="190"/>
-      <c r="S3" s="190"/>
-      <c r="T3" s="190"/>
-      <c r="U3" s="190"/>
-      <c r="V3" s="190"/>
-      <c r="W3" s="190"/>
-      <c r="X3" s="191"/>
-      <c r="Z3" s="201" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA3" s="202"/>
-      <c r="AB3" s="202"/>
-      <c r="AC3" s="202"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="201" t="s">
-        <v>259</v>
-      </c>
-      <c r="AF3" s="204"/>
-      <c r="AG3" s="204"/>
-      <c r="AH3" s="205"/>
+      <c r="AF3" s="208"/>
+      <c r="AG3" s="208"/>
+      <c r="AH3" s="209"/>
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>217</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>219</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J4" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="L4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="M4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="L4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="M4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="O4" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="U4" s="40" t="s">
+      <c r="V4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="W4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="V4" s="40" t="s">
+      <c r="X4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="W4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="Z4" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>256</v>
-      </c>
-      <c r="AF4" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -6476,54 +6557,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD5" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE5" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="AA5" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>246</v>
-      </c>
-      <c r="AD5" s="44" t="s">
+      <c r="AF5" t="s">
         <v>266</v>
       </c>
-      <c r="AE5" s="43" t="s">
+      <c r="AG5" t="s">
         <v>267</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" s="44" t="s">
         <v>268</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>269</v>
-      </c>
-      <c r="AH5" s="44" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -6542,39 +6623,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AF6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -6593,36 +6674,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AF7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AH7" s="44" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -6970,36 +7051,36 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A12CEB-23C8-48B1-A30D-D9BBB9DB2391}">
   <dimension ref="A1:AH36"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="20.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="43" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
-    <col min="12" max="12" width="20.625" customWidth="1"/>
-    <col min="13" max="13" width="21.125" style="44" customWidth="1"/>
-    <col min="14" max="14" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.58203125" customWidth="1"/>
+    <col min="13" max="13" width="21.08203125" style="44" customWidth="1"/>
+    <col min="14" max="14" width="3.33203125" customWidth="1"/>
     <col min="15" max="15" width="14" style="43" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.25" customWidth="1"/>
-    <col min="19" max="19" width="10.875" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" customWidth="1"/>
     <col min="21" max="21" width="18.75" customWidth="1"/>
-    <col min="22" max="22" width="11.875" customWidth="1"/>
+    <col min="22" max="22" width="11.83203125" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
     <col min="24" max="24" width="17.5" style="44" customWidth="1"/>
     <col min="26" max="26" width="15" style="43" customWidth="1"/>
     <col min="27" max="27" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="10.875" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
     <col min="30" max="30" width="9" style="44"/>
-    <col min="31" max="31" width="13.875" style="43" customWidth="1"/>
+    <col min="31" max="31" width="13.83203125" style="43" customWidth="1"/>
     <col min="32" max="32" width="19.75" customWidth="1"/>
     <col min="33" max="33" width="16.75" customWidth="1"/>
     <col min="34" max="34" width="19.5" style="44" customWidth="1"/>
@@ -7007,7 +7088,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="119" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -7022,7 +7103,7 @@
       <c r="L1" s="120"/>
       <c r="M1" s="121"/>
       <c r="O1" s="119" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P1" s="120"/>
       <c r="Q1" s="120"/>
@@ -7033,55 +7114,55 @@
       <c r="V1" s="120"/>
       <c r="W1" s="120"/>
       <c r="X1" s="121"/>
-      <c r="Z1" s="207" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA1" s="208"/>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="208"/>
-      <c r="AD1" s="208"/>
-      <c r="AE1" s="208"/>
-      <c r="AF1" s="208"/>
-      <c r="AG1" s="208"/>
-      <c r="AH1" s="209"/>
+      <c r="Z1" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA1" s="212"/>
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="212"/>
+      <c r="AE1" s="212"/>
+      <c r="AF1" s="212"/>
+      <c r="AG1" s="212"/>
+      <c r="AH1" s="213"/>
     </row>
     <row r="2" spans="1:34" ht="13.5" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="164"/>
-      <c r="M2" s="165"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="164"/>
-      <c r="Q2" s="164"/>
-      <c r="R2" s="164"/>
-      <c r="S2" s="164"/>
-      <c r="T2" s="164"/>
-      <c r="U2" s="164"/>
-      <c r="V2" s="164"/>
-      <c r="W2" s="164"/>
-      <c r="X2" s="165"/>
-      <c r="Z2" s="210"/>
-      <c r="AA2" s="211"/>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
-      <c r="AD2" s="211"/>
-      <c r="AE2" s="211"/>
-      <c r="AF2" s="211"/>
-      <c r="AG2" s="211"/>
-      <c r="AH2" s="212"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="169"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="168"/>
+      <c r="V2" s="168"/>
+      <c r="W2" s="168"/>
+      <c r="X2" s="169"/>
+      <c r="Z2" s="214"/>
+      <c r="AA2" s="215"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
+      <c r="AD2" s="215"/>
+      <c r="AE2" s="215"/>
+      <c r="AF2" s="215"/>
+      <c r="AG2" s="215"/>
+      <c r="AH2" s="216"/>
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="116" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117"/>
@@ -7090,194 +7171,194 @@
       <c r="F3" s="117"/>
       <c r="G3" s="117"/>
       <c r="H3" s="116" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I3" s="117"/>
       <c r="J3" s="117"/>
       <c r="K3" s="117"/>
       <c r="L3" s="117"/>
       <c r="M3" s="118"/>
-      <c r="O3" s="215"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="217"/>
-      <c r="Z3" s="206" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA3" s="202"/>
-      <c r="AB3" s="202"/>
-      <c r="AC3" s="202"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="206" t="s">
-        <v>259</v>
-      </c>
-      <c r="AF3" s="213"/>
-      <c r="AG3" s="213"/>
-      <c r="AH3" s="214"/>
+      <c r="O3" s="219"/>
+      <c r="P3" s="220"/>
+      <c r="Q3" s="220"/>
+      <c r="R3" s="220"/>
+      <c r="S3" s="220"/>
+      <c r="T3" s="220"/>
+      <c r="U3" s="220"/>
+      <c r="V3" s="220"/>
+      <c r="W3" s="220"/>
+      <c r="X3" s="221"/>
+      <c r="Z3" s="210" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA3" s="206"/>
+      <c r="AB3" s="206"/>
+      <c r="AC3" s="206"/>
+      <c r="AD3" s="207"/>
+      <c r="AE3" s="210" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF3" s="217"/>
+      <c r="AG3" s="217"/>
+      <c r="AH3" s="218"/>
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>217</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>219</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J4" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="L4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="M4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="L4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="M4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="O4" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="U4" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="U4" s="40" t="s">
+      <c r="V4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="W4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="V4" s="40" t="s">
+      <c r="X4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="W4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="Z4" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>256</v>
-      </c>
-      <c r="AF4" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="S5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -7286,66 +7367,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AA5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AB5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AC5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AF5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>276</v>
+      </c>
+      <c r="AH5" s="44" t="s">
         <v>268</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH5" s="44" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -7364,13 +7445,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -7382,16 +7463,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -7410,7 +7491,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -7422,16 +7503,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -7538,33 +7619,33 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8D5FDC-1119-4995-AFF6-CB9868EEC023}">
   <dimension ref="A1:AE36"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="43" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="43" customWidth="1"/>
-    <col min="6" max="6" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="10" width="21.125" style="44" customWidth="1"/>
-    <col min="11" max="11" width="3.375" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="20.58203125" customWidth="1"/>
+    <col min="10" max="10" width="21.08203125" style="44" customWidth="1"/>
+    <col min="11" max="11" width="3.33203125" customWidth="1"/>
     <col min="12" max="12" width="14" style="43" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.25" customWidth="1"/>
-    <col min="16" max="16" width="10.875" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
     <col min="18" max="18" width="18.75" customWidth="1"/>
-    <col min="19" max="19" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="11.83203125" customWidth="1"/>
     <col min="20" max="20" width="17" customWidth="1"/>
     <col min="21" max="21" width="17.5" style="44" customWidth="1"/>
     <col min="23" max="23" width="15" style="43" customWidth="1"/>
     <col min="24" max="24" width="11.75" customWidth="1"/>
-    <col min="25" max="25" width="10.875" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" customWidth="1"/>
     <col min="27" max="27" width="9" style="44"/>
-    <col min="28" max="28" width="13.875" style="43" customWidth="1"/>
+    <col min="28" max="28" width="13.83203125" style="43" customWidth="1"/>
     <col min="29" max="29" width="19.75" customWidth="1"/>
     <col min="30" max="30" width="16.75" customWidth="1"/>
     <col min="31" max="31" width="19.5" style="44" customWidth="1"/>
@@ -7572,7 +7653,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="119" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -7584,7 +7665,7 @@
       <c r="I1" s="120"/>
       <c r="J1" s="121"/>
       <c r="L1" s="119" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M1" s="120"/>
       <c r="N1" s="120"/>
@@ -7595,227 +7676,227 @@
       <c r="S1" s="120"/>
       <c r="T1" s="120"/>
       <c r="U1" s="121"/>
-      <c r="W1" s="207" t="s">
-        <v>256</v>
-      </c>
-      <c r="X1" s="208"/>
-      <c r="Y1" s="208"/>
-      <c r="Z1" s="208"/>
-      <c r="AA1" s="208"/>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="208"/>
-      <c r="AD1" s="208"/>
-      <c r="AE1" s="209"/>
+      <c r="W1" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="212"/>
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="212"/>
+      <c r="AE1" s="213"/>
     </row>
     <row r="2" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="165"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="164"/>
-      <c r="O2" s="164"/>
-      <c r="P2" s="164"/>
-      <c r="Q2" s="164"/>
-      <c r="R2" s="164"/>
-      <c r="S2" s="164"/>
-      <c r="T2" s="164"/>
-      <c r="U2" s="165"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="211"/>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
-      <c r="AD2" s="211"/>
-      <c r="AE2" s="212"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="169"/>
+      <c r="L2" s="167"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="168"/>
+      <c r="U2" s="169"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="215"/>
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="215"/>
+      <c r="AD2" s="215"/>
+      <c r="AE2" s="216"/>
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="116" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117"/>
       <c r="D3" s="117"/>
       <c r="E3" s="116" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F3" s="117"/>
       <c r="G3" s="117"/>
       <c r="H3" s="117"/>
       <c r="I3" s="117"/>
       <c r="J3" s="118"/>
-      <c r="L3" s="215"/>
-      <c r="M3" s="216"/>
-      <c r="N3" s="216"/>
-      <c r="O3" s="216"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="217"/>
-      <c r="W3" s="206" t="s">
-        <v>256</v>
-      </c>
-      <c r="X3" s="202"/>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
-      <c r="AA3" s="203"/>
-      <c r="AB3" s="206" t="s">
-        <v>259</v>
-      </c>
-      <c r="AC3" s="213"/>
-      <c r="AD3" s="213"/>
-      <c r="AE3" s="214"/>
+      <c r="L3" s="219"/>
+      <c r="M3" s="220"/>
+      <c r="N3" s="220"/>
+      <c r="O3" s="220"/>
+      <c r="P3" s="220"/>
+      <c r="Q3" s="220"/>
+      <c r="R3" s="220"/>
+      <c r="S3" s="220"/>
+      <c r="T3" s="220"/>
+      <c r="U3" s="221"/>
+      <c r="W3" s="210" t="s">
+        <v>254</v>
+      </c>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="206"/>
+      <c r="AA3" s="207"/>
+      <c r="AB3" s="210" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC3" s="217"/>
+      <c r="AD3" s="217"/>
+      <c r="AE3" s="218"/>
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>216</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>218</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G4" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="J4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="I4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="L4" s="41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P4" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="R4" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="Q4" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="R4" s="40" t="s">
+      <c r="S4" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="T4" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="S4" s="40" t="s">
+      <c r="U4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="T4" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="U4" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="W4" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="P5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -7824,57 +7905,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="X5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Z5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AD5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -7899,16 +7980,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -7933,16 +8014,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -8042,37 +8123,37 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD588F34-D77B-42F6-9174-CC0FF762963C}">
   <dimension ref="B2:H37"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
     <col min="3" max="4" width="26.25" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
     <col min="6" max="6" width="72.5" customWidth="1"/>
-    <col min="7" max="7" width="43.625" customWidth="1"/>
+    <col min="7" max="7" width="43.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="26.25">
-      <c r="B2" s="218" t="s">
-        <v>284</v>
-      </c>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
+    <row r="2" spans="2:8" ht="25.5">
+      <c r="B2" s="222" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="222"/>
+      <c r="D2" s="222"/>
+      <c r="E2" s="222"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
     </row>
     <row r="3" spans="2:8" ht="17.25" customHeight="1">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="D3" s="219" t="s">
-        <v>286</v>
-      </c>
-      <c r="E3" s="219"/>
-      <c r="F3" s="219"/>
+        <v>283</v>
+      </c>
+      <c r="D3" s="223" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="223"/>
+      <c r="F3" s="223"/>
       <c r="G3" s="47"/>
       <c r="H3" s="45"/>
     </row>
@@ -8080,12 +8161,12 @@
       <c r="B4" s="46"/>
       <c r="C4" s="47"/>
       <c r="D4" s="52" t="s">
-        <v>287</v>
-      </c>
-      <c r="E4" s="219" t="s">
-        <v>288</v>
-      </c>
-      <c r="F4" s="219"/>
+        <v>285</v>
+      </c>
+      <c r="E4" s="223" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="223"/>
       <c r="G4" s="47"/>
       <c r="H4" s="45"/>
     </row>
@@ -8093,12 +8174,12 @@
       <c r="B5" s="46"/>
       <c r="C5" s="47"/>
       <c r="D5" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="E5" s="219" t="s">
-        <v>290</v>
-      </c>
-      <c r="F5" s="219"/>
+        <v>287</v>
+      </c>
+      <c r="E5" s="223" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="223"/>
       <c r="G5" s="47"/>
       <c r="H5" s="45"/>
     </row>
@@ -8158,339 +8239,339 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="23" t="s">
         <v>299</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="24" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="E24" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="F24" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="G24" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="H24" s="23" t="s">
         <v>299</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="24" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="E32" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="F32" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="G32" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="H32" s="23" t="s">
         <v>299</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D35" s="1">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -8538,16 +8619,16 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:S136"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="6" width="18.625" customWidth="1"/>
-    <col min="8" max="10" width="18.625" customWidth="1"/>
-    <col min="12" max="12" width="18.625" style="43" customWidth="1"/>
-    <col min="13" max="13" width="18.625" style="44" customWidth="1"/>
-    <col min="15" max="16" width="18.625" style="43" customWidth="1"/>
-    <col min="17" max="18" width="18.625" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="44" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="6" width="18.58203125" customWidth="1"/>
+    <col min="8" max="10" width="18.58203125" customWidth="1"/>
+    <col min="12" max="12" width="18.58203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="18.58203125" style="44" customWidth="1"/>
+    <col min="15" max="16" width="18.58203125" style="43" customWidth="1"/>
+    <col min="17" max="18" width="18.58203125" customWidth="1"/>
+    <col min="19" max="19" width="18.58203125" style="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19">
@@ -8574,7 +8655,7 @@
       <c r="P3"/>
       <c r="S3"/>
     </row>
-    <row r="4" spans="2:19" ht="26.25">
+    <row r="4" spans="2:19" ht="25.5">
       <c r="B4" s="119" t="s">
         <v>18</v>
       </c>
@@ -9350,22 +9431,22 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:AP118"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" style="44" customWidth="1"/>
-    <col min="6" max="6" width="3.375" customWidth="1"/>
-    <col min="7" max="7" width="3.125" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" customWidth="1"/>
+    <col min="7" max="7" width="3.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:42" ht="17.25" thickBot="1">
+    <row r="1" spans="2:42" ht="17.5" thickBot="1">
       <c r="C1"/>
       <c r="E1"/>
     </row>
-    <row r="2" spans="2:42" ht="17.25" thickBot="1">
+    <row r="2" spans="2:42" ht="17.5" thickBot="1">
       <c r="C2" s="86" t="s">
         <v>5</v>
       </c>
@@ -9375,7 +9456,7 @@
       </c>
       <c r="E2" s="134"/>
     </row>
-    <row r="3" spans="2:42" ht="17.25" thickBot="1">
+    <row r="3" spans="2:42" ht="17.5" thickBot="1">
       <c r="C3" s="87" t="s">
         <v>6</v>
       </c>
@@ -11477,22 +11558,22 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:AF53"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="3.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="43" customWidth="1"/>
-    <col min="4" max="6" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="43" customWidth="1"/>
+    <col min="4" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="44" customWidth="1"/>
-    <col min="8" max="8" width="3.375" customWidth="1"/>
-    <col min="9" max="9" width="3.125" customWidth="1"/>
+    <col min="8" max="8" width="3.33203125" customWidth="1"/>
+    <col min="9" max="9" width="3.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:32" ht="17.25" thickBot="1">
+    <row r="1" spans="3:32" ht="17.5" thickBot="1">
       <c r="C1"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="3:32" ht="17.25" thickBot="1">
+    <row r="2" spans="3:32" ht="17.5" thickBot="1">
       <c r="C2" s="86" t="s">
         <v>5</v>
       </c>
@@ -11504,7 +11585,7 @@
       <c r="F2" s="151"/>
       <c r="G2" s="152"/>
     </row>
-    <row r="3" spans="3:32" ht="17.25" thickBot="1">
+    <row r="3" spans="3:32" ht="17.5" thickBot="1">
       <c r="C3" s="87" t="s">
         <v>6</v>
       </c>
@@ -11516,7 +11597,7 @@
       <c r="F3" s="151"/>
       <c r="G3" s="152"/>
     </row>
-    <row r="4" spans="3:32" ht="17.25" thickBot="1">
+    <row r="4" spans="3:32" ht="17.5" thickBot="1">
       <c r="C4"/>
       <c r="G4"/>
     </row>
@@ -12702,141 +12783,142 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:O38"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="B1:O39"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="3" width="18.125" style="43" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" style="43" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="44" customWidth="1"/>
     <col min="5" max="5" width="17.25" customWidth="1"/>
-    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4" style="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" ht="17.5" thickBot="1">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="2:15">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
+    <row r="2" spans="2:15" ht="17.5" thickBot="1">
+      <c r="B2" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="153">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="154"/>
       <c r="G2"/>
     </row>
-    <row r="3" spans="2:15">
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
+    <row r="3" spans="2:15" ht="17.5" thickBot="1">
+      <c r="B3" s="87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="155">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="156"/>
       <c r="G3"/>
     </row>
-    <row r="4" spans="2:15" ht="26.25">
-      <c r="B4" s="119" t="s">
+    <row r="4" spans="2:15" ht="17.5" thickBot="1">
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="2:15" ht="25.5">
+      <c r="B5" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="70"/>
-      <c r="I4" s="154" t="s">
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="70"/>
+      <c r="I5" s="158" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="154"/>
-      <c r="K4" s="154"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="154"/>
-      <c r="N4" s="154"/>
-      <c r="O4" s="154"/>
-    </row>
-    <row r="5" spans="2:15" ht="13.5" customHeight="1">
-      <c r="B5" s="85" t="s">
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
+      <c r="L5" s="158"/>
+      <c r="M5" s="158"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+    </row>
+    <row r="6" spans="2:15" ht="13.5" customHeight="1">
+      <c r="B6" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="122" t="s">
+      <c r="C6" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="122"/>
-      <c r="E5" s="123" t="s">
+      <c r="D6" s="122"/>
+      <c r="E6" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="123"/>
-      <c r="G5" s="72"/>
-      <c r="I5" s="153" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="B6" s="41" t="s">
+      <c r="F6" s="123"/>
+      <c r="G6" s="72"/>
+      <c r="I6" s="157" t="s">
+        <v>322</v>
+      </c>
+      <c r="J6" s="157"/>
+      <c r="K6" s="157"/>
+      <c r="L6" s="157"/>
+      <c r="M6" s="157"/>
+      <c r="N6" s="157"/>
+      <c r="O6" s="157"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C7" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E7" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="157"/>
+      <c r="K7" s="157"/>
+      <c r="L7" s="157"/>
+      <c r="M7" s="157"/>
+      <c r="N7" s="157"/>
+      <c r="O7" s="157"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="26"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="153"/>
-      <c r="K6" s="153"/>
-      <c r="L6" s="153"/>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-    </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="153"/>
-      <c r="M7" s="153"/>
-      <c r="N7" s="153"/>
-      <c r="O7" s="153"/>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
       <c r="G8" s="26"/>
-      <c r="I8" s="153"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="153"/>
-      <c r="L8" s="153"/>
-      <c r="M8" s="153"/>
-      <c r="N8" s="153"/>
-      <c r="O8" s="153"/>
+      <c r="I8" s="157"/>
+      <c r="J8" s="157"/>
+      <c r="K8" s="157"/>
+      <c r="L8" s="157"/>
+      <c r="M8" s="157"/>
+      <c r="N8" s="157"/>
+      <c r="O8" s="157"/>
     </row>
     <row r="9" spans="2:15">
       <c r="B9" s="26"/>
@@ -12845,13 +12927,13 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="26"/>
-      <c r="I9" s="153"/>
-      <c r="J9" s="153"/>
-      <c r="K9" s="153"/>
-      <c r="L9" s="153"/>
-      <c r="M9" s="153"/>
-      <c r="N9" s="153"/>
-      <c r="O9" s="153"/>
+      <c r="I9" s="157"/>
+      <c r="J9" s="157"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
+      <c r="M9" s="157"/>
+      <c r="N9" s="157"/>
+      <c r="O9" s="157"/>
     </row>
     <row r="10" spans="2:15">
       <c r="B10" s="26"/>
@@ -12859,284 +12941,302 @@
       <c r="D10" s="27"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="I10" s="153"/>
-      <c r="J10" s="153"/>
-      <c r="K10" s="153"/>
-      <c r="L10" s="153"/>
-      <c r="M10" s="153"/>
-      <c r="N10" s="153"/>
-      <c r="O10" s="153"/>
+      <c r="G10" s="26"/>
+      <c r="I10" s="157"/>
+      <c r="J10" s="157"/>
+      <c r="K10" s="157"/>
+      <c r="L10" s="157"/>
+      <c r="M10" s="157"/>
+      <c r="N10" s="157"/>
+      <c r="O10" s="157"/>
     </row>
     <row r="11" spans="2:15">
-      <c r="G11" s="26"/>
-      <c r="I11" s="153"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="153"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="153"/>
-      <c r="N11" s="153"/>
-      <c r="O11" s="153"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
+      <c r="G12" s="26"/>
+      <c r="I12" s="157"/>
+      <c r="J12" s="157"/>
+      <c r="K12" s="157"/>
+      <c r="L12" s="157"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="157"/>
+      <c r="O12" s="157"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-      <c r="L13" s="153"/>
-      <c r="M13" s="153"/>
-      <c r="N13" s="153"/>
-      <c r="O13" s="153"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="157"/>
+      <c r="J13" s="157"/>
+      <c r="K13" s="157"/>
+      <c r="L13" s="157"/>
+      <c r="M13" s="157"/>
+      <c r="N13" s="157"/>
+      <c r="O13" s="157"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="I14" s="153"/>
-      <c r="J14" s="153"/>
-      <c r="K14" s="153"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="153"/>
+      <c r="I14" s="157"/>
+      <c r="J14" s="157"/>
+      <c r="K14" s="157"/>
+      <c r="L14" s="157"/>
+      <c r="M14" s="157"/>
+      <c r="N14" s="157"/>
+      <c r="O14" s="157"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="I15" s="153"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="153"/>
-      <c r="N15" s="153"/>
-      <c r="O15" s="153"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="157"/>
+      <c r="K15" s="157"/>
+      <c r="L15" s="157"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="157"/>
+      <c r="O15" s="157"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="I16" s="153"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="153"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="153"/>
+      <c r="I16" s="157"/>
+      <c r="J16" s="157"/>
+      <c r="K16" s="157"/>
+      <c r="L16" s="157"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="157"/>
+      <c r="O16" s="157"/>
     </row>
     <row r="17" spans="9:15">
-      <c r="I17" s="153"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="153"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="157"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="157"/>
     </row>
     <row r="18" spans="9:15">
-      <c r="I18" s="153"/>
-      <c r="J18" s="153"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="153"/>
-      <c r="M18" s="153"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="153"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="157"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="157"/>
+      <c r="N18" s="157"/>
+      <c r="O18" s="157"/>
     </row>
     <row r="19" spans="9:15">
-      <c r="I19" s="153"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="153"/>
-      <c r="L19" s="153"/>
-      <c r="M19" s="153"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="153"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="157"/>
+      <c r="K19" s="157"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="157"/>
+      <c r="O19" s="157"/>
     </row>
     <row r="20" spans="9:15">
-      <c r="I20" s="153"/>
-      <c r="J20" s="153"/>
-      <c r="K20" s="153"/>
-      <c r="L20" s="153"/>
-      <c r="M20" s="153"/>
-      <c r="N20" s="153"/>
-      <c r="O20" s="153"/>
-    </row>
-    <row r="22" spans="9:15" ht="26.25">
-      <c r="I22" s="154" t="s">
-        <v>90</v>
-      </c>
-      <c r="J22" s="154"/>
-      <c r="K22" s="154"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="154"/>
-      <c r="O22" s="154"/>
-    </row>
-    <row r="23" spans="9:15" ht="13.5" customHeight="1">
-      <c r="I23" s="153" t="s">
-        <v>91</v>
-      </c>
-      <c r="J23" s="153"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="153"/>
-      <c r="N23" s="153"/>
-      <c r="O23" s="153"/>
-    </row>
-    <row r="24" spans="9:15">
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="153"/>
-      <c r="O24" s="153"/>
+      <c r="I20" s="157"/>
+      <c r="J20" s="157"/>
+      <c r="K20" s="157"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="157"/>
+      <c r="O20" s="157"/>
+    </row>
+    <row r="21" spans="9:15">
+      <c r="I21" s="157"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="157"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+    </row>
+    <row r="23" spans="9:15" ht="25.5">
+      <c r="I23" s="158" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="158"/>
+      <c r="K23" s="158"/>
+      <c r="L23" s="158"/>
+      <c r="M23" s="158"/>
+      <c r="N23" s="158"/>
+      <c r="O23" s="158"/>
+    </row>
+    <row r="24" spans="9:15" ht="13.5" customHeight="1">
+      <c r="I24" s="157" t="s">
+        <v>325</v>
+      </c>
+      <c r="J24" s="157"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="157"/>
+      <c r="O24" s="157"/>
     </row>
     <row r="25" spans="9:15">
-      <c r="I25" s="153"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="153"/>
-      <c r="N25" s="153"/>
-      <c r="O25" s="153"/>
+      <c r="I25" s="157"/>
+      <c r="J25" s="157"/>
+      <c r="K25" s="157"/>
+      <c r="L25" s="157"/>
+      <c r="M25" s="157"/>
+      <c r="N25" s="157"/>
+      <c r="O25" s="157"/>
     </row>
     <row r="26" spans="9:15">
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="153"/>
-      <c r="N26" s="153"/>
-      <c r="O26" s="153"/>
+      <c r="I26" s="157"/>
+      <c r="J26" s="157"/>
+      <c r="K26" s="157"/>
+      <c r="L26" s="157"/>
+      <c r="M26" s="157"/>
+      <c r="N26" s="157"/>
+      <c r="O26" s="157"/>
     </row>
     <row r="27" spans="9:15">
-      <c r="I27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="153"/>
-      <c r="N27" s="153"/>
-      <c r="O27" s="153"/>
+      <c r="I27" s="157"/>
+      <c r="J27" s="157"/>
+      <c r="K27" s="157"/>
+      <c r="L27" s="157"/>
+      <c r="M27" s="157"/>
+      <c r="N27" s="157"/>
+      <c r="O27" s="157"/>
     </row>
     <row r="28" spans="9:15">
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="153"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="157"/>
+      <c r="K28" s="157"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="157"/>
+      <c r="N28" s="157"/>
+      <c r="O28" s="157"/>
     </row>
     <row r="29" spans="9:15">
-      <c r="I29" s="153"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="153"/>
-      <c r="M29" s="153"/>
-      <c r="N29" s="153"/>
-      <c r="O29" s="153"/>
+      <c r="I29" s="157"/>
+      <c r="J29" s="157"/>
+      <c r="K29" s="157"/>
+      <c r="L29" s="157"/>
+      <c r="M29" s="157"/>
+      <c r="N29" s="157"/>
+      <c r="O29" s="157"/>
     </row>
     <row r="30" spans="9:15">
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="153"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="153"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="157"/>
     </row>
     <row r="31" spans="9:15">
-      <c r="I31" s="153"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="153"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="157"/>
+      <c r="K31" s="157"/>
+      <c r="L31" s="157"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="157"/>
+      <c r="O31" s="157"/>
     </row>
     <row r="32" spans="9:15">
-      <c r="I32" s="153"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="153"/>
-      <c r="N32" s="153"/>
-      <c r="O32" s="153"/>
+      <c r="I32" s="157"/>
+      <c r="J32" s="157"/>
+      <c r="K32" s="157"/>
+      <c r="L32" s="157"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="157"/>
+      <c r="O32" s="157"/>
     </row>
     <row r="33" spans="9:15">
-      <c r="I33" s="153"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="153"/>
-      <c r="N33" s="153"/>
-      <c r="O33" s="153"/>
+      <c r="I33" s="157"/>
+      <c r="J33" s="157"/>
+      <c r="K33" s="157"/>
+      <c r="L33" s="157"/>
+      <c r="M33" s="157"/>
+      <c r="N33" s="157"/>
+      <c r="O33" s="157"/>
     </row>
     <row r="34" spans="9:15">
-      <c r="I34" s="153"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="153"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="153"/>
-      <c r="N34" s="153"/>
-      <c r="O34" s="153"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="157"/>
+      <c r="L34" s="157"/>
+      <c r="M34" s="157"/>
+      <c r="N34" s="157"/>
+      <c r="O34" s="157"/>
     </row>
     <row r="35" spans="9:15">
-      <c r="I35" s="153"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="153"/>
-      <c r="L35" s="153"/>
-      <c r="M35" s="153"/>
-      <c r="N35" s="153"/>
-      <c r="O35" s="153"/>
+      <c r="I35" s="157"/>
+      <c r="J35" s="157"/>
+      <c r="K35" s="157"/>
+      <c r="L35" s="157"/>
+      <c r="M35" s="157"/>
+      <c r="N35" s="157"/>
+      <c r="O35" s="157"/>
     </row>
     <row r="36" spans="9:15">
-      <c r="I36" s="153"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="153"/>
-      <c r="N36" s="153"/>
-      <c r="O36" s="153"/>
+      <c r="I36" s="157"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="157"/>
+      <c r="L36" s="157"/>
+      <c r="M36" s="157"/>
+      <c r="N36" s="157"/>
+      <c r="O36" s="157"/>
     </row>
     <row r="37" spans="9:15">
-      <c r="I37" s="153"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="153"/>
-      <c r="L37" s="153"/>
-      <c r="M37" s="153"/>
-      <c r="N37" s="153"/>
-      <c r="O37" s="153"/>
+      <c r="I37" s="157"/>
+      <c r="J37" s="157"/>
+      <c r="K37" s="157"/>
+      <c r="L37" s="157"/>
+      <c r="M37" s="157"/>
+      <c r="N37" s="157"/>
+      <c r="O37" s="157"/>
     </row>
     <row r="38" spans="9:15">
-      <c r="I38" s="153"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="153"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="153"/>
-      <c r="N38" s="153"/>
-      <c r="O38" s="153"/>
+      <c r="I38" s="157"/>
+      <c r="J38" s="157"/>
+      <c r="K38" s="157"/>
+      <c r="L38" s="157"/>
+      <c r="M38" s="157"/>
+      <c r="N38" s="157"/>
+      <c r="O38" s="157"/>
+    </row>
+    <row r="39" spans="9:15">
+      <c r="I39" s="157"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="157"/>
+      <c r="L39" s="157"/>
+      <c r="M39" s="157"/>
+      <c r="N39" s="157"/>
+      <c r="O39" s="157"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="I23:O38"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="I5:O20"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
+  <mergeCells count="9">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="I24:O39"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I6:O21"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B7:C10" xr:uid="{F0C12A19-5B7C-43E6-878B-953093678A31}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 D1:D4 D6:D1048576" xr:uid="{8EE0318C-3A2F-4D03-8AC3-17A868D0D886}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B8:C11" xr:uid="{F0C12A19-5B7C-43E6-878B-953093678A31}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 D7:D1048576 D4:D5" xr:uid="{8EE0318C-3A2F-4D03-8AC3-17A868D0D886}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -13146,16 +13246,16 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="C1:T25"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="3.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="79" customWidth="1"/>
-    <col min="4" max="4" width="40.375" customWidth="1"/>
-    <col min="5" max="6" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="79" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="44" customWidth="1"/>
     <col min="8" max="8" width="4.5" customWidth="1"/>
-    <col min="9" max="9" width="3.125" customWidth="1"/>
+    <col min="9" max="9" width="3.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:20">
@@ -13175,7 +13275,7 @@
       <c r="F3" s="117"/>
       <c r="G3" s="118"/>
       <c r="J3" s="147" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K3" s="148"/>
       <c r="L3" s="148"/>
@@ -13196,27 +13296,27 @@
         <v>31</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G4" s="42" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="124" t="s">
-        <v>95</v>
-      </c>
-      <c r="K4" s="155"/>
-      <c r="L4" s="155"/>
-      <c r="M4" s="155"/>
-      <c r="N4" s="155"/>
-      <c r="O4" s="155"/>
-      <c r="P4" s="155"/>
-      <c r="Q4" s="155"/>
-      <c r="R4" s="155"/>
-      <c r="S4" s="155"/>
-      <c r="T4" s="156"/>
+        <v>93</v>
+      </c>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="159"/>
+      <c r="O4" s="159"/>
+      <c r="P4" s="159"/>
+      <c r="Q4" s="159"/>
+      <c r="R4" s="159"/>
+      <c r="S4" s="159"/>
+      <c r="T4" s="160"/>
     </row>
     <row r="5" spans="3:20">
       <c r="C5" s="78">
@@ -13234,17 +13334,17 @@
       <c r="G5" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="157"/>
-      <c r="K5" s="158"/>
-      <c r="L5" s="158"/>
-      <c r="M5" s="158"/>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="158"/>
-      <c r="R5" s="158"/>
-      <c r="S5" s="158"/>
-      <c r="T5" s="159"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="162"/>
+      <c r="R5" s="162"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="163"/>
     </row>
     <row r="6" spans="3:20">
       <c r="C6" s="78">
@@ -13262,17 +13362,17 @@
       <c r="G6" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="157"/>
-      <c r="K6" s="158"/>
-      <c r="L6" s="158"/>
-      <c r="M6" s="158"/>
-      <c r="N6" s="158"/>
-      <c r="O6" s="158"/>
-      <c r="P6" s="158"/>
-      <c r="Q6" s="158"/>
-      <c r="R6" s="158"/>
-      <c r="S6" s="158"/>
-      <c r="T6" s="159"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="162"/>
+      <c r="Q6" s="162"/>
+      <c r="R6" s="162"/>
+      <c r="S6" s="162"/>
+      <c r="T6" s="163"/>
     </row>
     <row r="7" spans="3:20">
       <c r="C7" s="78">
@@ -13282,17 +13382,17 @@
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="76"/>
-      <c r="J7" s="157"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="158"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="158"/>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="158"/>
-      <c r="R7" s="158"/>
-      <c r="S7" s="158"/>
-      <c r="T7" s="159"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="162"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="162"/>
+      <c r="N7" s="162"/>
+      <c r="O7" s="162"/>
+      <c r="P7" s="162"/>
+      <c r="Q7" s="162"/>
+      <c r="R7" s="162"/>
+      <c r="S7" s="162"/>
+      <c r="T7" s="163"/>
     </row>
     <row r="8" spans="3:20">
       <c r="C8" s="78">
@@ -13302,17 +13402,17 @@
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="27"/>
-      <c r="J8" s="157"/>
-      <c r="K8" s="158"/>
-      <c r="L8" s="158"/>
-      <c r="M8" s="158"/>
-      <c r="N8" s="158"/>
-      <c r="O8" s="158"/>
-      <c r="P8" s="158"/>
-      <c r="Q8" s="158"/>
-      <c r="R8" s="158"/>
-      <c r="S8" s="158"/>
-      <c r="T8" s="159"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="162"/>
+      <c r="L8" s="162"/>
+      <c r="M8" s="162"/>
+      <c r="N8" s="162"/>
+      <c r="O8" s="162"/>
+      <c r="P8" s="162"/>
+      <c r="Q8" s="162"/>
+      <c r="R8" s="162"/>
+      <c r="S8" s="162"/>
+      <c r="T8" s="163"/>
     </row>
     <row r="9" spans="3:20">
       <c r="C9" s="78">
@@ -13322,161 +13422,161 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="27"/>
-      <c r="J9" s="157"/>
-      <c r="K9" s="158"/>
-      <c r="L9" s="158"/>
-      <c r="M9" s="158"/>
-      <c r="N9" s="158"/>
-      <c r="O9" s="158"/>
-      <c r="P9" s="158"/>
-      <c r="Q9" s="158"/>
-      <c r="R9" s="158"/>
-      <c r="S9" s="158"/>
-      <c r="T9" s="159"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="162"/>
+      <c r="M9" s="162"/>
+      <c r="N9" s="162"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="162"/>
+      <c r="Q9" s="162"/>
+      <c r="R9" s="162"/>
+      <c r="S9" s="162"/>
+      <c r="T9" s="163"/>
     </row>
     <row r="10" spans="3:20">
       <c r="C10" s="78">
         <v>6</v>
       </c>
-      <c r="J10" s="157"/>
-      <c r="K10" s="158"/>
-      <c r="L10" s="158"/>
-      <c r="M10" s="158"/>
-      <c r="N10" s="158"/>
-      <c r="O10" s="158"/>
-      <c r="P10" s="158"/>
-      <c r="Q10" s="158"/>
-      <c r="R10" s="158"/>
-      <c r="S10" s="158"/>
-      <c r="T10" s="159"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="162"/>
+      <c r="L10" s="162"/>
+      <c r="M10" s="162"/>
+      <c r="N10" s="162"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="162"/>
+      <c r="Q10" s="162"/>
+      <c r="R10" s="162"/>
+      <c r="S10" s="162"/>
+      <c r="T10" s="163"/>
     </row>
     <row r="11" spans="3:20">
       <c r="C11" s="78">
         <v>7</v>
       </c>
-      <c r="J11" s="157"/>
-      <c r="K11" s="158"/>
-      <c r="L11" s="158"/>
-      <c r="M11" s="158"/>
-      <c r="N11" s="158"/>
-      <c r="O11" s="158"/>
-      <c r="P11" s="158"/>
-      <c r="Q11" s="158"/>
-      <c r="R11" s="158"/>
-      <c r="S11" s="158"/>
-      <c r="T11" s="159"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="162"/>
+      <c r="L11" s="162"/>
+      <c r="M11" s="162"/>
+      <c r="N11" s="162"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="162"/>
+      <c r="Q11" s="162"/>
+      <c r="R11" s="162"/>
+      <c r="S11" s="162"/>
+      <c r="T11" s="163"/>
     </row>
     <row r="12" spans="3:20">
       <c r="C12" s="78">
         <v>8</v>
       </c>
-      <c r="J12" s="157"/>
-      <c r="K12" s="158"/>
-      <c r="L12" s="158"/>
-      <c r="M12" s="158"/>
-      <c r="N12" s="158"/>
-      <c r="O12" s="158"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="158"/>
-      <c r="S12" s="158"/>
-      <c r="T12" s="159"/>
+      <c r="J12" s="161"/>
+      <c r="K12" s="162"/>
+      <c r="L12" s="162"/>
+      <c r="M12" s="162"/>
+      <c r="N12" s="162"/>
+      <c r="O12" s="162"/>
+      <c r="P12" s="162"/>
+      <c r="Q12" s="162"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="162"/>
+      <c r="T12" s="163"/>
     </row>
     <row r="13" spans="3:20">
       <c r="C13" s="78">
         <v>9</v>
       </c>
-      <c r="J13" s="157"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="158"/>
-      <c r="M13" s="158"/>
-      <c r="N13" s="158"/>
-      <c r="O13" s="158"/>
-      <c r="P13" s="158"/>
-      <c r="Q13" s="158"/>
-      <c r="R13" s="158"/>
-      <c r="S13" s="158"/>
-      <c r="T13" s="159"/>
+      <c r="J13" s="161"/>
+      <c r="K13" s="162"/>
+      <c r="L13" s="162"/>
+      <c r="M13" s="162"/>
+      <c r="N13" s="162"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="162"/>
+      <c r="Q13" s="162"/>
+      <c r="R13" s="162"/>
+      <c r="S13" s="162"/>
+      <c r="T13" s="163"/>
     </row>
     <row r="14" spans="3:20">
       <c r="C14" s="78">
         <v>10</v>
       </c>
-      <c r="J14" s="157"/>
-      <c r="K14" s="158"/>
-      <c r="L14" s="158"/>
-      <c r="M14" s="158"/>
-      <c r="N14" s="158"/>
-      <c r="O14" s="158"/>
-      <c r="P14" s="158"/>
-      <c r="Q14" s="158"/>
-      <c r="R14" s="158"/>
-      <c r="S14" s="158"/>
-      <c r="T14" s="159"/>
+      <c r="J14" s="161"/>
+      <c r="K14" s="162"/>
+      <c r="L14" s="162"/>
+      <c r="M14" s="162"/>
+      <c r="N14" s="162"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="162"/>
+      <c r="Q14" s="162"/>
+      <c r="R14" s="162"/>
+      <c r="S14" s="162"/>
+      <c r="T14" s="163"/>
     </row>
     <row r="15" spans="3:20">
       <c r="C15" s="78">
         <v>11</v>
       </c>
-      <c r="J15" s="157"/>
-      <c r="K15" s="158"/>
-      <c r="L15" s="158"/>
-      <c r="M15" s="158"/>
-      <c r="N15" s="158"/>
-      <c r="O15" s="158"/>
-      <c r="P15" s="158"/>
-      <c r="Q15" s="158"/>
-      <c r="R15" s="158"/>
-      <c r="S15" s="158"/>
-      <c r="T15" s="159"/>
+      <c r="J15" s="161"/>
+      <c r="K15" s="162"/>
+      <c r="L15" s="162"/>
+      <c r="M15" s="162"/>
+      <c r="N15" s="162"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="162"/>
+      <c r="Q15" s="162"/>
+      <c r="R15" s="162"/>
+      <c r="S15" s="162"/>
+      <c r="T15" s="163"/>
     </row>
     <row r="16" spans="3:20">
       <c r="C16" s="78">
         <v>12</v>
       </c>
-      <c r="J16" s="157"/>
-      <c r="K16" s="158"/>
-      <c r="L16" s="158"/>
-      <c r="M16" s="158"/>
-      <c r="N16" s="158"/>
-      <c r="O16" s="158"/>
-      <c r="P16" s="158"/>
-      <c r="Q16" s="158"/>
-      <c r="R16" s="158"/>
-      <c r="S16" s="158"/>
-      <c r="T16" s="159"/>
+      <c r="J16" s="161"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="162"/>
+      <c r="M16" s="162"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="162"/>
+      <c r="Q16" s="162"/>
+      <c r="R16" s="162"/>
+      <c r="S16" s="162"/>
+      <c r="T16" s="163"/>
     </row>
     <row r="17" spans="3:20">
       <c r="C17" s="78">
         <v>13</v>
       </c>
-      <c r="J17" s="157"/>
-      <c r="K17" s="158"/>
-      <c r="L17" s="158"/>
-      <c r="M17" s="158"/>
-      <c r="N17" s="158"/>
-      <c r="O17" s="158"/>
-      <c r="P17" s="158"/>
-      <c r="Q17" s="158"/>
-      <c r="R17" s="158"/>
-      <c r="S17" s="158"/>
-      <c r="T17" s="159"/>
+      <c r="J17" s="161"/>
+      <c r="K17" s="162"/>
+      <c r="L17" s="162"/>
+      <c r="M17" s="162"/>
+      <c r="N17" s="162"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="162"/>
+      <c r="Q17" s="162"/>
+      <c r="R17" s="162"/>
+      <c r="S17" s="162"/>
+      <c r="T17" s="163"/>
     </row>
     <row r="18" spans="3:20">
       <c r="C18" s="78">
         <v>14</v>
       </c>
-      <c r="J18" s="160"/>
-      <c r="K18" s="161"/>
-      <c r="L18" s="161"/>
-      <c r="M18" s="161"/>
-      <c r="N18" s="161"/>
-      <c r="O18" s="161"/>
-      <c r="P18" s="161"/>
-      <c r="Q18" s="161"/>
-      <c r="R18" s="161"/>
-      <c r="S18" s="161"/>
-      <c r="T18" s="162"/>
+      <c r="J18" s="164"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="165"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="165"/>
+      <c r="Q18" s="165"/>
+      <c r="R18" s="165"/>
+      <c r="S18" s="165"/>
+      <c r="T18" s="166"/>
     </row>
     <row r="19" spans="3:20">
       <c r="C19" s="78">
@@ -13537,30 +13637,30 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B1:V36"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.08203125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="17.25" customWidth="1"/>
-    <col min="5" max="5" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="43" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="44" customWidth="1"/>
-    <col min="10" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="15.875" style="43" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" style="43" customWidth="1"/>
     <col min="12" max="12" width="21.5" style="44" customWidth="1"/>
-    <col min="13" max="13" width="3.375" customWidth="1"/>
-    <col min="14" max="14" width="15.875" style="43" customWidth="1"/>
-    <col min="15" max="15" width="40.375" customWidth="1"/>
-    <col min="16" max="17" width="17.375" customWidth="1"/>
+    <col min="13" max="13" width="3.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" style="43" customWidth="1"/>
+    <col min="15" max="15" width="40.33203125" customWidth="1"/>
+    <col min="16" max="17" width="17.33203125" customWidth="1"/>
     <col min="18" max="18" width="21.5" style="44" customWidth="1"/>
     <col min="19" max="19" width="4.5" customWidth="1"/>
-    <col min="20" max="20" width="15.875" style="43" customWidth="1"/>
-    <col min="21" max="21" width="17.375" customWidth="1"/>
+    <col min="20" max="20" width="15.83203125" style="43" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" customWidth="1"/>
     <col min="22" max="22" width="21.5" style="44" customWidth="1"/>
-    <col min="23" max="23" width="3.125" customWidth="1"/>
+    <col min="23" max="23" width="3.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22">
@@ -13612,7 +13712,7 @@
       <c r="Q3" s="117"/>
       <c r="R3" s="118"/>
       <c r="T3" s="116" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="U3" s="117"/>
       <c r="V3" s="118"/>
@@ -13622,10 +13722,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>39</v>
@@ -13641,10 +13741,10 @@
         <v>27</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N4" s="41" t="s">
         <v>35</v>
@@ -13653,27 +13753,27 @@
         <v>21</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>31</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V4" s="42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -13687,28 +13787,28 @@
       <c r="K5" s="26"/>
       <c r="L5" s="27"/>
       <c r="N5" s="26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O5" s="37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P5" s="37">
         <v>3</v>
       </c>
       <c r="Q5" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="T5" s="26" t="s">
         <v>107</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="T5" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="U5" s="37">
         <v>2</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="2:22">
@@ -13718,7 +13818,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="27"/>
@@ -13740,17 +13840,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="27"/>
       <c r="K7" s="26"/>
       <c r="L7" s="27"/>
       <c r="N7" s="26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P7" s="37">
         <v>5</v>
@@ -13841,361 +13941,361 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52C9A5D-390C-4EB4-8E0E-6218D55EFC0C}">
   <dimension ref="C4:I26"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="53" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:9" ht="17.25" thickBot="1"/>
+    <row r="4" spans="3:9" ht="17.5" thickBot="1"/>
     <row r="5" spans="3:9" ht="18" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9" ht="17.25" thickBot="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="17.5" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>120</v>
-      </c>
       <c r="H7" s="22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="G8" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="G9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="G10" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="H10" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>137</v>
-      </c>
       <c r="I10" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="G11" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="H11" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>142</v>
-      </c>
       <c r="I11" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="G12" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="H12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="I12" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="G13" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="H13" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="I13" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="H13" s="13" t="s">
+    </row>
+    <row r="14" spans="3:9" ht="17.5">
+      <c r="C14" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="D14" s="18" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="14" spans="3:9" ht="17.25">
-      <c r="C14" s="17" t="s">
+      <c r="E14" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="G14" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="H14" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="G15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="H15" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="I15" s="13" t="s">
         <v>164</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="H16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>170</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="H17" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="I17" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="H18" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="I18" s="13" t="s">
         <v>182</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="G19" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="H19" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="I19" s="13" t="s">
         <v>188</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>206</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -14207,32 +14307,32 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713538E3-68C7-46EF-9BF7-7D86C6D2932B}">
   <dimension ref="B2:AC45"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="16.375" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
     <col min="7" max="7" width="20.25" customWidth="1"/>
-    <col min="8" max="8" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.875" customWidth="1"/>
-    <col min="10" max="10" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.125" customWidth="1"/>
-    <col min="16" max="16" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="12.125" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="17.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.08203125" customWidth="1"/>
     <col min="19" max="19" width="11.25" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="119" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
@@ -14252,109 +14352,109 @@
       <c r="R2" s="121"/>
     </row>
     <row r="3" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B3" s="163"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
-      <c r="R3" s="165"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
+      <c r="L3" s="168"/>
+      <c r="M3" s="168"/>
+      <c r="N3" s="168"/>
+      <c r="O3" s="168"/>
+      <c r="P3" s="168"/>
+      <c r="Q3" s="168"/>
+      <c r="R3" s="169"/>
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>213</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>215</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="I4" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="J4" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="L4" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="J4" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="36" t="s">
+      <c r="M4" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="N4" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="O4" s="170" t="s">
         <v>222</v>
       </c>
-      <c r="N4" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="O4" s="166" t="s">
-        <v>224</v>
-      </c>
-      <c r="P4" s="167"/>
-      <c r="Q4" s="167"/>
-      <c r="R4" s="168"/>
+      <c r="P4" s="171"/>
+      <c r="Q4" s="171"/>
+      <c r="R4" s="172"/>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="170"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="171"/>
+      <c r="O5" s="173"/>
+      <c r="P5" s="174"/>
+      <c r="Q5" s="174"/>
+      <c r="R5" s="175"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -14367,10 +14467,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -14378,14 +14478,14 @@
       <c r="N6" s="31">
         <v>4</v>
       </c>
-      <c r="O6" s="169"/>
-      <c r="P6" s="170"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="171"/>
+      <c r="O6" s="173"/>
+      <c r="P6" s="174"/>
+      <c r="Q6" s="174"/>
+      <c r="R6" s="175"/>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -14398,10 +14498,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -14409,14 +14509,14 @@
       <c r="N7" s="31">
         <v>4</v>
       </c>
-      <c r="O7" s="169"/>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="171"/>
+      <c r="O7" s="173"/>
+      <c r="P7" s="174"/>
+      <c r="Q7" s="174"/>
+      <c r="R7" s="175"/>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -14429,10 +14529,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -14440,49 +14540,49 @@
       <c r="N8" s="31">
         <v>4</v>
       </c>
-      <c r="O8" s="169"/>
-      <c r="P8" s="170"/>
-      <c r="Q8" s="170"/>
-      <c r="R8" s="171"/>
+      <c r="O8" s="173"/>
+      <c r="P8" s="174"/>
+      <c r="Q8" s="174"/>
+      <c r="R8" s="175"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="170"/>
-      <c r="Q9" s="170"/>
-      <c r="R9" s="171"/>
+      <c r="O9" s="173"/>
+      <c r="P9" s="174"/>
+      <c r="Q9" s="174"/>
+      <c r="R9" s="175"/>
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -14495,10 +14595,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -14506,14 +14606,14 @@
       <c r="N10" s="31">
         <v>4</v>
       </c>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170"/>
-      <c r="Q10" s="170"/>
-      <c r="R10" s="171"/>
+      <c r="O10" s="173"/>
+      <c r="P10" s="174"/>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="175"/>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -14527,14 +14627,14 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="170"/>
-      <c r="Q11" s="170"/>
-      <c r="R11" s="171"/>
+      <c r="O11" s="173"/>
+      <c r="P11" s="174"/>
+      <c r="Q11" s="174"/>
+      <c r="R11" s="175"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -14548,14 +14648,14 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="170"/>
-      <c r="Q12" s="170"/>
-      <c r="R12" s="171"/>
+      <c r="O12" s="173"/>
+      <c r="P12" s="174"/>
+      <c r="Q12" s="174"/>
+      <c r="R12" s="175"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -14569,14 +14669,14 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="170"/>
-      <c r="Q13" s="170"/>
-      <c r="R13" s="171"/>
+      <c r="O13" s="173"/>
+      <c r="P13" s="174"/>
+      <c r="Q13" s="174"/>
+      <c r="R13" s="175"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -14590,18 +14690,18 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="169"/>
-      <c r="P14" s="170"/>
-      <c r="Q14" s="170"/>
-      <c r="R14" s="171"/>
-      <c r="U14" s="184" t="s">
-        <v>236</v>
-      </c>
-      <c r="V14" s="184"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="174"/>
+      <c r="Q14" s="174"/>
+      <c r="R14" s="175"/>
+      <c r="U14" s="188" t="s">
+        <v>234</v>
+      </c>
+      <c r="V14" s="188"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -14615,16 +14715,16 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="170"/>
-      <c r="Q15" s="170"/>
-      <c r="R15" s="171"/>
-      <c r="U15" s="184"/>
-      <c r="V15" s="184"/>
+      <c r="O15" s="173"/>
+      <c r="P15" s="174"/>
+      <c r="Q15" s="174"/>
+      <c r="R15" s="175"/>
+      <c r="U15" s="188"/>
+      <c r="V15" s="188"/>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -14638,20 +14738,20 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="170"/>
-      <c r="Q16" s="170"/>
-      <c r="R16" s="171"/>
-      <c r="U16" s="184" t="s">
-        <v>237</v>
-      </c>
-      <c r="V16" s="185" t="s">
-        <v>238</v>
+      <c r="O16" s="173"/>
+      <c r="P16" s="174"/>
+      <c r="Q16" s="174"/>
+      <c r="R16" s="175"/>
+      <c r="U16" s="188" t="s">
+        <v>235</v>
+      </c>
+      <c r="V16" s="189" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -14665,16 +14765,16 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="169"/>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="170"/>
-      <c r="R17" s="171"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="185"/>
+      <c r="O17" s="173"/>
+      <c r="P17" s="174"/>
+      <c r="Q17" s="174"/>
+      <c r="R17" s="175"/>
+      <c r="U17" s="188"/>
+      <c r="V17" s="189"/>
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -14688,18 +14788,18 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="169"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="170"/>
-      <c r="R18" s="171"/>
-      <c r="U18" s="184"/>
-      <c r="V18" s="185" t="s">
-        <v>239</v>
+      <c r="O18" s="173"/>
+      <c r="P18" s="174"/>
+      <c r="Q18" s="174"/>
+      <c r="R18" s="175"/>
+      <c r="U18" s="188"/>
+      <c r="V18" s="189" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -14713,16 +14813,16 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="169"/>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="170"/>
-      <c r="R19" s="171"/>
-      <c r="U19" s="184"/>
-      <c r="V19" s="185"/>
+      <c r="O19" s="173"/>
+      <c r="P19" s="174"/>
+      <c r="Q19" s="174"/>
+      <c r="R19" s="175"/>
+      <c r="U19" s="188"/>
+      <c r="V19" s="189"/>
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -14736,18 +14836,18 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="169"/>
-      <c r="P20" s="170"/>
-      <c r="Q20" s="170"/>
-      <c r="R20" s="171"/>
-      <c r="U20" s="184"/>
-      <c r="V20" s="185" t="s">
-        <v>240</v>
+      <c r="O20" s="173"/>
+      <c r="P20" s="174"/>
+      <c r="Q20" s="174"/>
+      <c r="R20" s="175"/>
+      <c r="U20" s="188"/>
+      <c r="V20" s="189" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -14761,16 +14861,16 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="169"/>
-      <c r="P21" s="170"/>
-      <c r="Q21" s="170"/>
-      <c r="R21" s="171"/>
-      <c r="U21" s="184"/>
-      <c r="V21" s="185"/>
+      <c r="O21" s="173"/>
+      <c r="P21" s="174"/>
+      <c r="Q21" s="174"/>
+      <c r="R21" s="175"/>
+      <c r="U21" s="188"/>
+      <c r="V21" s="189"/>
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -14784,18 +14884,18 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="169"/>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="170"/>
-      <c r="R22" s="171"/>
-      <c r="U22" s="184"/>
-      <c r="V22" s="185" t="s">
-        <v>241</v>
+      <c r="O22" s="173"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="175"/>
+      <c r="U22" s="188"/>
+      <c r="V22" s="189" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -14809,16 +14909,16 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="169"/>
-      <c r="P23" s="170"/>
-      <c r="Q23" s="170"/>
-      <c r="R23" s="171"/>
-      <c r="U23" s="184"/>
-      <c r="V23" s="185"/>
+      <c r="O23" s="173"/>
+      <c r="P23" s="174"/>
+      <c r="Q23" s="174"/>
+      <c r="R23" s="175"/>
+      <c r="U23" s="188"/>
+      <c r="V23" s="189"/>
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -14832,18 +14932,18 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="169"/>
-      <c r="P24" s="170"/>
-      <c r="Q24" s="170"/>
-      <c r="R24" s="171"/>
-      <c r="U24" s="184"/>
-      <c r="V24" s="185" t="s">
-        <v>242</v>
+      <c r="O24" s="173"/>
+      <c r="P24" s="174"/>
+      <c r="Q24" s="174"/>
+      <c r="R24" s="175"/>
+      <c r="U24" s="188"/>
+      <c r="V24" s="189" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -14857,16 +14957,16 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="169"/>
-      <c r="P25" s="170"/>
-      <c r="Q25" s="170"/>
-      <c r="R25" s="171"/>
-      <c r="U25" s="184"/>
-      <c r="V25" s="185"/>
+      <c r="O25" s="173"/>
+      <c r="P25" s="174"/>
+      <c r="Q25" s="174"/>
+      <c r="R25" s="175"/>
+      <c r="U25" s="188"/>
+      <c r="V25" s="189"/>
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -14880,18 +14980,18 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="169"/>
-      <c r="P26" s="170"/>
-      <c r="Q26" s="170"/>
-      <c r="R26" s="171"/>
-      <c r="U26" s="184"/>
-      <c r="V26" s="185" t="s">
-        <v>242</v>
+      <c r="O26" s="173"/>
+      <c r="P26" s="174"/>
+      <c r="Q26" s="174"/>
+      <c r="R26" s="175"/>
+      <c r="U26" s="188"/>
+      <c r="V26" s="189" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -14905,16 +15005,16 @@
       <c r="L27" s="29"/>
       <c r="M27" s="29"/>
       <c r="N27" s="29"/>
-      <c r="O27" s="172"/>
-      <c r="P27" s="173"/>
-      <c r="Q27" s="173"/>
-      <c r="R27" s="174"/>
-      <c r="U27" s="184"/>
-      <c r="V27" s="185"/>
+      <c r="O27" s="176"/>
+      <c r="P27" s="177"/>
+      <c r="Q27" s="177"/>
+      <c r="R27" s="178"/>
+      <c r="U27" s="188"/>
+      <c r="V27" s="189"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="119" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C30" s="120"/>
       <c r="D30" s="120"/>
@@ -14934,106 +15034,106 @@
       <c r="R30" s="121"/>
     </row>
     <row r="31" spans="2:25" ht="13.5" customHeight="1">
-      <c r="B31" s="163"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="164"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="164"/>
-      <c r="K31" s="164"/>
-      <c r="L31" s="164"/>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
-      <c r="O31" s="164"/>
-      <c r="P31" s="164"/>
-      <c r="Q31" s="164"/>
-      <c r="R31" s="165"/>
+      <c r="B31" s="167"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="168"/>
+      <c r="H31" s="168"/>
+      <c r="I31" s="168"/>
+      <c r="J31" s="168"/>
+      <c r="K31" s="168"/>
+      <c r="L31" s="168"/>
+      <c r="M31" s="168"/>
+      <c r="N31" s="168"/>
+      <c r="O31" s="168"/>
+      <c r="P31" s="168"/>
+      <c r="Q31" s="168"/>
+      <c r="R31" s="169"/>
       <c r="U31" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="2:25">
       <c r="B32" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F32" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="G32" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="36" t="s">
+      <c r="I32" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="J32" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="K32" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="J32" s="36" t="s">
+      <c r="L32" s="179" t="s">
         <v>222</v>
       </c>
-      <c r="K32" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="L32" s="175" t="s">
-        <v>224</v>
-      </c>
-      <c r="M32" s="176"/>
-      <c r="N32" s="176"/>
-      <c r="O32" s="176"/>
-      <c r="P32" s="176"/>
-      <c r="Q32" s="176"/>
-      <c r="R32" s="177"/>
+      <c r="M32" s="180"/>
+      <c r="N32" s="180"/>
+      <c r="O32" s="180"/>
+      <c r="P32" s="180"/>
+      <c r="Q32" s="180"/>
+      <c r="R32" s="181"/>
       <c r="U32" s="5" t="s">
         <v>5</v>
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -15041,15 +15141,15 @@
       <c r="K33" s="31">
         <v>4</v>
       </c>
-      <c r="L33" s="178"/>
-      <c r="M33" s="179"/>
-      <c r="N33" s="179"/>
-      <c r="O33" s="179"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="179"/>
-      <c r="R33" s="180"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="183"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="183"/>
+      <c r="P33" s="183"/>
+      <c r="Q33" s="183"/>
+      <c r="R33" s="184"/>
       <c r="U33" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -15064,25 +15164,25 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="178"/>
-      <c r="M34" s="179"/>
-      <c r="N34" s="179"/>
-      <c r="O34" s="179"/>
-      <c r="P34" s="179"/>
-      <c r="Q34" s="179"/>
-      <c r="R34" s="180"/>
+      <c r="L34" s="182"/>
+      <c r="M34" s="183"/>
+      <c r="N34" s="183"/>
+      <c r="O34" s="183"/>
+      <c r="P34" s="183"/>
+      <c r="Q34" s="183"/>
+      <c r="R34" s="184"/>
       <c r="U34" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="2:29">
@@ -15096,23 +15196,23 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="178"/>
-      <c r="M35" s="179"/>
-      <c r="N35" s="179"/>
-      <c r="O35" s="179"/>
-      <c r="P35" s="179"/>
-      <c r="Q35" s="179"/>
-      <c r="R35" s="180"/>
+      <c r="L35" s="182"/>
+      <c r="M35" s="183"/>
+      <c r="N35" s="183"/>
+      <c r="O35" s="183"/>
+      <c r="P35" s="183"/>
+      <c r="Q35" s="183"/>
+      <c r="R35" s="184"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="2:29">
@@ -15126,13 +15226,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="178"/>
-      <c r="M36" s="179"/>
-      <c r="N36" s="179"/>
-      <c r="O36" s="179"/>
-      <c r="P36" s="179"/>
-      <c r="Q36" s="179"/>
-      <c r="R36" s="180"/>
+      <c r="L36" s="182"/>
+      <c r="M36" s="183"/>
+      <c r="N36" s="183"/>
+      <c r="O36" s="183"/>
+      <c r="P36" s="183"/>
+      <c r="Q36" s="183"/>
+      <c r="R36" s="184"/>
       <c r="S36" s="7"/>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
@@ -15148,19 +15248,19 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="178"/>
-      <c r="M37" s="179"/>
-      <c r="N37" s="179"/>
-      <c r="O37" s="179"/>
-      <c r="P37" s="179"/>
-      <c r="Q37" s="179"/>
-      <c r="R37" s="180"/>
+      <c r="L37" s="182"/>
+      <c r="M37" s="183"/>
+      <c r="N37" s="183"/>
+      <c r="O37" s="183"/>
+      <c r="P37" s="183"/>
+      <c r="Q37" s="183"/>
+      <c r="R37" s="184"/>
       <c r="U37" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="2:29">
@@ -15174,19 +15274,19 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="178"/>
-      <c r="M38" s="179"/>
-      <c r="N38" s="179"/>
-      <c r="O38" s="179"/>
-      <c r="P38" s="179"/>
-      <c r="Q38" s="179"/>
-      <c r="R38" s="180"/>
+      <c r="L38" s="182"/>
+      <c r="M38" s="183"/>
+      <c r="N38" s="183"/>
+      <c r="O38" s="183"/>
+      <c r="P38" s="183"/>
+      <c r="Q38" s="183"/>
+      <c r="R38" s="184"/>
       <c r="U38" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="2:29">
@@ -15200,34 +15300,34 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="178"/>
-      <c r="M39" s="179"/>
-      <c r="N39" s="179"/>
-      <c r="O39" s="179"/>
-      <c r="P39" s="179"/>
-      <c r="Q39" s="179"/>
-      <c r="R39" s="180"/>
+      <c r="L39" s="182"/>
+      <c r="M39" s="183"/>
+      <c r="N39" s="183"/>
+      <c r="O39" s="183"/>
+      <c r="P39" s="183"/>
+      <c r="Q39" s="183"/>
+      <c r="R39" s="184"/>
       <c r="U39" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AA39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AB39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AC39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -15241,13 +15341,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="178"/>
-      <c r="M40" s="179"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="179"/>
-      <c r="P40" s="179"/>
-      <c r="Q40" s="179"/>
-      <c r="R40" s="180"/>
+      <c r="L40" s="182"/>
+      <c r="M40" s="183"/>
+      <c r="N40" s="183"/>
+      <c r="O40" s="183"/>
+      <c r="P40" s="183"/>
+      <c r="Q40" s="183"/>
+      <c r="R40" s="184"/>
     </row>
     <row r="41" spans="2:29">
       <c r="B41" s="26"/>
@@ -15260,13 +15360,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="178"/>
-      <c r="M41" s="179"/>
-      <c r="N41" s="179"/>
-      <c r="O41" s="179"/>
-      <c r="P41" s="179"/>
-      <c r="Q41" s="179"/>
-      <c r="R41" s="180"/>
+      <c r="L41" s="182"/>
+      <c r="M41" s="183"/>
+      <c r="N41" s="183"/>
+      <c r="O41" s="183"/>
+      <c r="P41" s="183"/>
+      <c r="Q41" s="183"/>
+      <c r="R41" s="184"/>
     </row>
     <row r="42" spans="2:29">
       <c r="B42" s="26"/>
@@ -15279,13 +15379,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="178"/>
-      <c r="M42" s="179"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="179"/>
-      <c r="P42" s="179"/>
-      <c r="Q42" s="179"/>
-      <c r="R42" s="180"/>
+      <c r="L42" s="182"/>
+      <c r="M42" s="183"/>
+      <c r="N42" s="183"/>
+      <c r="O42" s="183"/>
+      <c r="P42" s="183"/>
+      <c r="Q42" s="183"/>
+      <c r="R42" s="184"/>
     </row>
     <row r="43" spans="2:29">
       <c r="B43" s="26"/>
@@ -15298,13 +15398,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="178"/>
-      <c r="M43" s="179"/>
-      <c r="N43" s="179"/>
-      <c r="O43" s="179"/>
-      <c r="P43" s="179"/>
-      <c r="Q43" s="179"/>
-      <c r="R43" s="180"/>
+      <c r="L43" s="182"/>
+      <c r="M43" s="183"/>
+      <c r="N43" s="183"/>
+      <c r="O43" s="183"/>
+      <c r="P43" s="183"/>
+      <c r="Q43" s="183"/>
+      <c r="R43" s="184"/>
     </row>
     <row r="44" spans="2:29">
       <c r="B44" s="26"/>
@@ -15317,13 +15417,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="178"/>
-      <c r="M44" s="179"/>
-      <c r="N44" s="179"/>
-      <c r="O44" s="179"/>
-      <c r="P44" s="179"/>
-      <c r="Q44" s="179"/>
-      <c r="R44" s="180"/>
+      <c r="L44" s="182"/>
+      <c r="M44" s="183"/>
+      <c r="N44" s="183"/>
+      <c r="O44" s="183"/>
+      <c r="P44" s="183"/>
+      <c r="Q44" s="183"/>
+      <c r="R44" s="184"/>
     </row>
     <row r="45" spans="2:29">
       <c r="B45" s="28"/>
@@ -15336,13 +15436,13 @@
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
-      <c r="L45" s="181"/>
-      <c r="M45" s="182"/>
-      <c r="N45" s="182"/>
-      <c r="O45" s="182"/>
-      <c r="P45" s="182"/>
-      <c r="Q45" s="182"/>
-      <c r="R45" s="183"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="186"/>
+      <c r="N45" s="186"/>
+      <c r="O45" s="186"/>
+      <c r="P45" s="186"/>
+      <c r="Q45" s="186"/>
+      <c r="R45" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\13.Asserion TF\2_repository\Assertion-Checker-Generator\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3243D96-EE1E-4504-AF33-B3DF38D725EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABAE76E-9161-4E61-B491-0F46E98D34D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3165" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="handshake" sheetId="16" r:id="rId3"/>
     <sheet name="pulseWidth" sheetId="17" r:id="rId4"/>
     <sheet name="Counter" sheetId="15" r:id="rId5"/>
-    <sheet name="delayCondition" sheetId="20" r:id="rId6"/>
+    <sheet name="delayCondition" sheetId="21" r:id="rId6"/>
     <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId7"/>
     <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId8"/>
     <sheet name="Basic Assertion" sheetId="1" r:id="rId9"/>
@@ -27,6 +27,9 @@
     <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId12"/>
     <sheet name="aw_builder" sheetId="2" r:id="rId13"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId14"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -166,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="326">
   <si>
     <t>Base Information</t>
   </si>
@@ -4972,7 +4975,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5309,6 +5312,39 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5345,39 +5381,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5585,16 +5588,55 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5613,6 +5655,46 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Define"/>
+      <sheetName val="Assertion Sheet"/>
+      <sheetName val="handshake"/>
+      <sheetName val="pulseWidth"/>
+      <sheetName val="Counter"/>
+      <sheetName val="delayCondition"/>
+      <sheetName val="Assertion Sheet(backup)"/>
+      <sheetName val="Assertion System Function Guide"/>
+      <sheetName val="Basic Assertion"/>
+      <sheetName val="Basic Assertion_hsw"/>
+      <sheetName val="Basic Assertion_2"/>
+      <sheetName val="Basic Assertion_개선안"/>
+      <sheetName val="aw_builder"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6260,33 +6342,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="144" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="135"/>
-      <c r="O1" s="133" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="O1" s="144" t="s">
         <v>238</v>
       </c>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="135"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="146"/>
       <c r="Z1" s="188" t="s">
         <v>251</v>
       </c>
@@ -9409,21 +9491,21 @@
       <c r="C2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="145">
+      <c r="D2" s="133">
         <f>Define!C5</f>
         <v>0</v>
       </c>
-      <c r="E2" s="146"/>
+      <c r="E2" s="134"/>
     </row>
     <row r="3" spans="2:42" ht="17.25" thickBot="1">
       <c r="C3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="145">
+      <c r="D3" s="133">
         <f>Define!C6</f>
         <v>0</v>
       </c>
-      <c r="E3" s="146"/>
+      <c r="E3" s="134"/>
     </row>
     <row r="4" spans="2:42">
       <c r="C4"/>
@@ -9436,33 +9518,33 @@
       </c>
       <c r="D5" s="117"/>
       <c r="E5" s="118"/>
-      <c r="H5" s="133" t="s">
+      <c r="H5" s="144" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="135"/>
-      <c r="U5" s="133" t="s">
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="146"/>
+      <c r="U5" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="134"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="135"/>
+      <c r="V5" s="145"/>
+      <c r="W5" s="145"/>
+      <c r="X5" s="145"/>
+      <c r="Y5" s="145"/>
+      <c r="Z5" s="145"/>
+      <c r="AA5" s="145"/>
+      <c r="AB5" s="145"/>
+      <c r="AC5" s="145"/>
+      <c r="AD5" s="145"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="146"/>
       <c r="AG5" s="74"/>
       <c r="AH5" s="74"/>
       <c r="AI5" s="74"/>
@@ -9485,33 +9567,33 @@
       <c r="E6" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="136" t="s">
+      <c r="H6" s="124" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="138"/>
-      <c r="U6" s="124" t="s">
+      <c r="I6" s="125"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="126"/>
+      <c r="U6" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="V6" s="125"/>
-      <c r="W6" s="125"/>
-      <c r="X6" s="125"/>
-      <c r="Y6" s="125"/>
-      <c r="Z6" s="125"/>
-      <c r="AA6" s="125"/>
-      <c r="AB6" s="125"/>
-      <c r="AC6" s="125"/>
-      <c r="AD6" s="125"/>
-      <c r="AE6" s="125"/>
-      <c r="AF6" s="126"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="136"/>
+      <c r="AE6" s="136"/>
+      <c r="AF6" s="137"/>
       <c r="AG6" s="74"/>
       <c r="AH6" s="74"/>
       <c r="AI6" s="74"/>
@@ -9534,29 +9616,29 @@
       <c r="E7" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="139"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="141"/>
-      <c r="U7" s="127"/>
-      <c r="V7" s="128"/>
-      <c r="W7" s="128"/>
-      <c r="X7" s="128"/>
-      <c r="Y7" s="128"/>
-      <c r="Z7" s="128"/>
-      <c r="AA7" s="128"/>
-      <c r="AB7" s="128"/>
-      <c r="AC7" s="128"/>
-      <c r="AD7" s="128"/>
-      <c r="AE7" s="128"/>
-      <c r="AF7" s="129"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="128"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="129"/>
+      <c r="U7" s="138"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="139"/>
+      <c r="Y7" s="139"/>
+      <c r="Z7" s="139"/>
+      <c r="AA7" s="139"/>
+      <c r="AB7" s="139"/>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="139"/>
+      <c r="AE7" s="139"/>
+      <c r="AF7" s="140"/>
       <c r="AG7" s="74"/>
       <c r="AH7" s="74"/>
       <c r="AI7" s="74"/>
@@ -9579,29 +9661,29 @@
       <c r="E8" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="139"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="141"/>
-      <c r="U8" s="127"/>
-      <c r="V8" s="128"/>
-      <c r="W8" s="128"/>
-      <c r="X8" s="128"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="128"/>
-      <c r="AA8" s="128"/>
-      <c r="AB8" s="128"/>
-      <c r="AC8" s="128"/>
-      <c r="AD8" s="128"/>
-      <c r="AE8" s="128"/>
-      <c r="AF8" s="129"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="129"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="139"/>
+      <c r="Y8" s="139"/>
+      <c r="Z8" s="139"/>
+      <c r="AA8" s="139"/>
+      <c r="AB8" s="139"/>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="139"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="140"/>
       <c r="AG8" s="74"/>
       <c r="AH8" s="74"/>
       <c r="AI8" s="74"/>
@@ -9624,29 +9706,29 @@
       <c r="E9" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="139"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="140"/>
-      <c r="O9" s="140"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="141"/>
-      <c r="U9" s="127"/>
-      <c r="V9" s="128"/>
-      <c r="W9" s="128"/>
-      <c r="X9" s="128"/>
-      <c r="Y9" s="128"/>
-      <c r="Z9" s="128"/>
-      <c r="AA9" s="128"/>
-      <c r="AB9" s="128"/>
-      <c r="AC9" s="128"/>
-      <c r="AD9" s="128"/>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="129"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
+      <c r="O9" s="128"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="129"/>
+      <c r="U9" s="138"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="139"/>
+      <c r="AE9" s="139"/>
+      <c r="AF9" s="140"/>
       <c r="AG9" s="74"/>
       <c r="AH9" s="74"/>
       <c r="AI9" s="74"/>
@@ -9662,29 +9744,29 @@
       <c r="C10" s="26"/>
       <c r="D10" s="37"/>
       <c r="E10" s="27"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="141"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="128"/>
-      <c r="W10" s="128"/>
-      <c r="X10" s="128"/>
-      <c r="Y10" s="128"/>
-      <c r="Z10" s="128"/>
-      <c r="AA10" s="128"/>
-      <c r="AB10" s="128"/>
-      <c r="AC10" s="128"/>
-      <c r="AD10" s="128"/>
-      <c r="AE10" s="128"/>
-      <c r="AF10" s="129"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="129"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="139"/>
+      <c r="AB10" s="139"/>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="139"/>
+      <c r="AE10" s="139"/>
+      <c r="AF10" s="140"/>
       <c r="AG10" s="74"/>
       <c r="AH10" s="74"/>
       <c r="AI10" s="74"/>
@@ -9701,29 +9783,29 @@
       <c r="C11" s="26"/>
       <c r="D11" s="1"/>
       <c r="E11" s="27"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="141"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="128"/>
-      <c r="W11" s="128"/>
-      <c r="X11" s="128"/>
-      <c r="Y11" s="128"/>
-      <c r="Z11" s="128"/>
-      <c r="AA11" s="128"/>
-      <c r="AB11" s="128"/>
-      <c r="AC11" s="128"/>
-      <c r="AD11" s="128"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="129"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="129"/>
+      <c r="U11" s="138"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="139"/>
+      <c r="AB11" s="139"/>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="139"/>
+      <c r="AE11" s="139"/>
+      <c r="AF11" s="140"/>
       <c r="AG11" s="74"/>
       <c r="AH11" s="74"/>
       <c r="AI11" s="74"/>
@@ -9737,29 +9819,29 @@
     </row>
     <row r="12" spans="2:42" ht="13.5" customHeight="1">
       <c r="C12" s="26"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="140"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-      <c r="R12" s="141"/>
-      <c r="U12" s="127"/>
-      <c r="V12" s="128"/>
-      <c r="W12" s="128"/>
-      <c r="X12" s="128"/>
-      <c r="Y12" s="128"/>
-      <c r="Z12" s="128"/>
-      <c r="AA12" s="128"/>
-      <c r="AB12" s="128"/>
-      <c r="AC12" s="128"/>
-      <c r="AD12" s="128"/>
-      <c r="AE12" s="128"/>
-      <c r="AF12" s="129"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="128"/>
+      <c r="P12" s="128"/>
+      <c r="Q12" s="128"/>
+      <c r="R12" s="129"/>
+      <c r="U12" s="138"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="139"/>
+      <c r="Y12" s="139"/>
+      <c r="Z12" s="139"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="139"/>
+      <c r="AF12" s="140"/>
       <c r="AG12" s="74"/>
       <c r="AH12" s="74"/>
       <c r="AI12" s="74"/>
@@ -9772,29 +9854,29 @@
       <c r="AP12" s="74"/>
     </row>
     <row r="13" spans="2:42" ht="13.5" customHeight="1">
-      <c r="H13" s="139"/>
-      <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
-      <c r="K13" s="140"/>
-      <c r="L13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="140"/>
-      <c r="O13" s="140"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140"/>
-      <c r="R13" s="141"/>
-      <c r="U13" s="127"/>
-      <c r="V13" s="128"/>
-      <c r="W13" s="128"/>
-      <c r="X13" s="128"/>
-      <c r="Y13" s="128"/>
-      <c r="Z13" s="128"/>
-      <c r="AA13" s="128"/>
-      <c r="AB13" s="128"/>
-      <c r="AC13" s="128"/>
-      <c r="AD13" s="128"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="129"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="129"/>
+      <c r="U13" s="138"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="139"/>
+      <c r="X13" s="139"/>
+      <c r="Y13" s="139"/>
+      <c r="Z13" s="139"/>
+      <c r="AA13" s="139"/>
+      <c r="AB13" s="139"/>
+      <c r="AC13" s="139"/>
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="139"/>
+      <c r="AF13" s="140"/>
       <c r="AG13" s="74"/>
       <c r="AH13" s="74"/>
       <c r="AI13" s="74"/>
@@ -9807,29 +9889,29 @@
       <c r="AP13" s="74"/>
     </row>
     <row r="14" spans="2:42" ht="13.5" customHeight="1">
-      <c r="H14" s="139"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="140"/>
-      <c r="N14" s="140"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="141"/>
-      <c r="U14" s="127"/>
-      <c r="V14" s="128"/>
-      <c r="W14" s="128"/>
-      <c r="X14" s="128"/>
-      <c r="Y14" s="128"/>
-      <c r="Z14" s="128"/>
-      <c r="AA14" s="128"/>
-      <c r="AB14" s="128"/>
-      <c r="AC14" s="128"/>
-      <c r="AD14" s="128"/>
-      <c r="AE14" s="128"/>
-      <c r="AF14" s="129"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="128"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="128"/>
+      <c r="P14" s="128"/>
+      <c r="Q14" s="128"/>
+      <c r="R14" s="129"/>
+      <c r="U14" s="138"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="139"/>
+      <c r="X14" s="139"/>
+      <c r="Y14" s="139"/>
+      <c r="Z14" s="139"/>
+      <c r="AA14" s="139"/>
+      <c r="AB14" s="139"/>
+      <c r="AC14" s="139"/>
+      <c r="AD14" s="139"/>
+      <c r="AE14" s="139"/>
+      <c r="AF14" s="140"/>
       <c r="AG14" s="74"/>
       <c r="AH14" s="74"/>
       <c r="AI14" s="74"/>
@@ -9842,29 +9924,29 @@
       <c r="AP14" s="74"/>
     </row>
     <row r="15" spans="2:42" ht="13.5" customHeight="1">
-      <c r="H15" s="139"/>
-      <c r="I15" s="140"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="140"/>
-      <c r="L15" s="140"/>
-      <c r="M15" s="140"/>
-      <c r="N15" s="140"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="140"/>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="141"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="128"/>
-      <c r="W15" s="128"/>
-      <c r="X15" s="128"/>
-      <c r="Y15" s="128"/>
-      <c r="Z15" s="128"/>
-      <c r="AA15" s="128"/>
-      <c r="AB15" s="128"/>
-      <c r="AC15" s="128"/>
-      <c r="AD15" s="128"/>
-      <c r="AE15" s="128"/>
-      <c r="AF15" s="129"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="128"/>
+      <c r="O15" s="128"/>
+      <c r="P15" s="128"/>
+      <c r="Q15" s="128"/>
+      <c r="R15" s="129"/>
+      <c r="U15" s="138"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="139"/>
+      <c r="AB15" s="139"/>
+      <c r="AC15" s="139"/>
+      <c r="AD15" s="139"/>
+      <c r="AE15" s="139"/>
+      <c r="AF15" s="140"/>
       <c r="AG15" s="74"/>
       <c r="AH15" s="74"/>
       <c r="AI15" s="74"/>
@@ -9877,29 +9959,29 @@
       <c r="AP15" s="74"/>
     </row>
     <row r="16" spans="2:42" ht="13.5" customHeight="1">
-      <c r="H16" s="139"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="140"/>
-      <c r="N16" s="140"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="141"/>
-      <c r="U16" s="127"/>
-      <c r="V16" s="128"/>
-      <c r="W16" s="128"/>
-      <c r="X16" s="128"/>
-      <c r="Y16" s="128"/>
-      <c r="Z16" s="128"/>
-      <c r="AA16" s="128"/>
-      <c r="AB16" s="128"/>
-      <c r="AC16" s="128"/>
-      <c r="AD16" s="128"/>
-      <c r="AE16" s="128"/>
-      <c r="AF16" s="129"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="128"/>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="129"/>
+      <c r="U16" s="138"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139"/>
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="139"/>
+      <c r="AB16" s="139"/>
+      <c r="AC16" s="139"/>
+      <c r="AD16" s="139"/>
+      <c r="AE16" s="139"/>
+      <c r="AF16" s="140"/>
       <c r="AG16" s="74"/>
       <c r="AH16" s="74"/>
       <c r="AI16" s="74"/>
@@ -9912,29 +9994,29 @@
       <c r="AP16" s="74"/>
     </row>
     <row r="17" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H17" s="139"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="140"/>
-      <c r="L17" s="140"/>
-      <c r="M17" s="140"/>
-      <c r="N17" s="140"/>
-      <c r="O17" s="140"/>
-      <c r="P17" s="140"/>
-      <c r="Q17" s="140"/>
-      <c r="R17" s="141"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="128"/>
-      <c r="W17" s="128"/>
-      <c r="X17" s="128"/>
-      <c r="Y17" s="128"/>
-      <c r="Z17" s="128"/>
-      <c r="AA17" s="128"/>
-      <c r="AB17" s="128"/>
-      <c r="AC17" s="128"/>
-      <c r="AD17" s="128"/>
-      <c r="AE17" s="128"/>
-      <c r="AF17" s="129"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128"/>
+      <c r="Q17" s="128"/>
+      <c r="R17" s="129"/>
+      <c r="U17" s="138"/>
+      <c r="V17" s="139"/>
+      <c r="W17" s="139"/>
+      <c r="X17" s="139"/>
+      <c r="Y17" s="139"/>
+      <c r="Z17" s="139"/>
+      <c r="AA17" s="139"/>
+      <c r="AB17" s="139"/>
+      <c r="AC17" s="139"/>
+      <c r="AD17" s="139"/>
+      <c r="AE17" s="139"/>
+      <c r="AF17" s="140"/>
       <c r="AG17" s="74"/>
       <c r="AH17" s="74"/>
       <c r="AI17" s="74"/>
@@ -9947,29 +10029,29 @@
       <c r="AP17" s="74"/>
     </row>
     <row r="18" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H18" s="139"/>
-      <c r="I18" s="140"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="140"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="140"/>
-      <c r="R18" s="141"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="128"/>
-      <c r="W18" s="128"/>
-      <c r="X18" s="128"/>
-      <c r="Y18" s="128"/>
-      <c r="Z18" s="128"/>
-      <c r="AA18" s="128"/>
-      <c r="AB18" s="128"/>
-      <c r="AC18" s="128"/>
-      <c r="AD18" s="128"/>
-      <c r="AE18" s="128"/>
-      <c r="AF18" s="129"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="128"/>
+      <c r="Q18" s="128"/>
+      <c r="R18" s="129"/>
+      <c r="U18" s="138"/>
+      <c r="V18" s="139"/>
+      <c r="W18" s="139"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="139"/>
+      <c r="AA18" s="139"/>
+      <c r="AB18" s="139"/>
+      <c r="AC18" s="139"/>
+      <c r="AD18" s="139"/>
+      <c r="AE18" s="139"/>
+      <c r="AF18" s="140"/>
       <c r="AG18" s="74"/>
       <c r="AH18" s="74"/>
       <c r="AI18" s="74"/>
@@ -9982,29 +10064,29 @@
       <c r="AP18" s="74"/>
     </row>
     <row r="19" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H19" s="139"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="140"/>
-      <c r="M19" s="140"/>
-      <c r="N19" s="140"/>
-      <c r="O19" s="140"/>
-      <c r="P19" s="140"/>
-      <c r="Q19" s="140"/>
-      <c r="R19" s="141"/>
-      <c r="U19" s="127"/>
-      <c r="V19" s="128"/>
-      <c r="W19" s="128"/>
-      <c r="X19" s="128"/>
-      <c r="Y19" s="128"/>
-      <c r="Z19" s="128"/>
-      <c r="AA19" s="128"/>
-      <c r="AB19" s="128"/>
-      <c r="AC19" s="128"/>
-      <c r="AD19" s="128"/>
-      <c r="AE19" s="128"/>
-      <c r="AF19" s="129"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="128"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="129"/>
+      <c r="U19" s="138"/>
+      <c r="V19" s="139"/>
+      <c r="W19" s="139"/>
+      <c r="X19" s="139"/>
+      <c r="Y19" s="139"/>
+      <c r="Z19" s="139"/>
+      <c r="AA19" s="139"/>
+      <c r="AB19" s="139"/>
+      <c r="AC19" s="139"/>
+      <c r="AD19" s="139"/>
+      <c r="AE19" s="139"/>
+      <c r="AF19" s="140"/>
       <c r="AG19" s="74"/>
       <c r="AH19" s="74"/>
       <c r="AI19" s="74"/>
@@ -10017,29 +10099,29 @@
       <c r="AP19" s="74"/>
     </row>
     <row r="20" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H20" s="139"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
-      <c r="U20" s="127"/>
-      <c r="V20" s="128"/>
-      <c r="W20" s="128"/>
-      <c r="X20" s="128"/>
-      <c r="Y20" s="128"/>
-      <c r="Z20" s="128"/>
-      <c r="AA20" s="128"/>
-      <c r="AB20" s="128"/>
-      <c r="AC20" s="128"/>
-      <c r="AD20" s="128"/>
-      <c r="AE20" s="128"/>
-      <c r="AF20" s="129"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="128"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="129"/>
+      <c r="U20" s="138"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="139"/>
+      <c r="X20" s="139"/>
+      <c r="Y20" s="139"/>
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="139"/>
+      <c r="AB20" s="139"/>
+      <c r="AC20" s="139"/>
+      <c r="AD20" s="139"/>
+      <c r="AE20" s="139"/>
+      <c r="AF20" s="140"/>
       <c r="AG20" s="74"/>
       <c r="AH20" s="74"/>
       <c r="AI20" s="74"/>
@@ -10052,29 +10134,29 @@
       <c r="AP20" s="74"/>
     </row>
     <row r="21" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H21" s="139"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="140"/>
-      <c r="O21" s="140"/>
-      <c r="P21" s="140"/>
-      <c r="Q21" s="140"/>
-      <c r="R21" s="141"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="128"/>
-      <c r="W21" s="128"/>
-      <c r="X21" s="128"/>
-      <c r="Y21" s="128"/>
-      <c r="Z21" s="128"/>
-      <c r="AA21" s="128"/>
-      <c r="AB21" s="128"/>
-      <c r="AC21" s="128"/>
-      <c r="AD21" s="128"/>
-      <c r="AE21" s="128"/>
-      <c r="AF21" s="129"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+      <c r="O21" s="128"/>
+      <c r="P21" s="128"/>
+      <c r="Q21" s="128"/>
+      <c r="R21" s="129"/>
+      <c r="U21" s="138"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="139"/>
+      <c r="AB21" s="139"/>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="139"/>
+      <c r="AE21" s="139"/>
+      <c r="AF21" s="140"/>
       <c r="AG21" s="74"/>
       <c r="AH21" s="74"/>
       <c r="AI21" s="74"/>
@@ -10087,29 +10169,29 @@
       <c r="AP21" s="74"/>
     </row>
     <row r="22" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H22" s="139"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="140"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="140"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="140"/>
-      <c r="R22" s="141"/>
-      <c r="U22" s="127"/>
-      <c r="V22" s="128"/>
-      <c r="W22" s="128"/>
-      <c r="X22" s="128"/>
-      <c r="Y22" s="128"/>
-      <c r="Z22" s="128"/>
-      <c r="AA22" s="128"/>
-      <c r="AB22" s="128"/>
-      <c r="AC22" s="128"/>
-      <c r="AD22" s="128"/>
-      <c r="AE22" s="128"/>
-      <c r="AF22" s="129"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="128"/>
+      <c r="N22" s="128"/>
+      <c r="O22" s="128"/>
+      <c r="P22" s="128"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="129"/>
+      <c r="U22" s="138"/>
+      <c r="V22" s="139"/>
+      <c r="W22" s="139"/>
+      <c r="X22" s="139"/>
+      <c r="Y22" s="139"/>
+      <c r="Z22" s="139"/>
+      <c r="AA22" s="139"/>
+      <c r="AB22" s="139"/>
+      <c r="AC22" s="139"/>
+      <c r="AD22" s="139"/>
+      <c r="AE22" s="139"/>
+      <c r="AF22" s="140"/>
       <c r="AG22" s="74"/>
       <c r="AH22" s="74"/>
       <c r="AI22" s="74"/>
@@ -10122,29 +10204,29 @@
       <c r="AP22" s="74"/>
     </row>
     <row r="23" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H23" s="139"/>
-      <c r="I23" s="140"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="140"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="140"/>
-      <c r="Q23" s="140"/>
-      <c r="R23" s="141"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="128"/>
-      <c r="W23" s="128"/>
-      <c r="X23" s="128"/>
-      <c r="Y23" s="128"/>
-      <c r="Z23" s="128"/>
-      <c r="AA23" s="128"/>
-      <c r="AB23" s="128"/>
-      <c r="AC23" s="128"/>
-      <c r="AD23" s="128"/>
-      <c r="AE23" s="128"/>
-      <c r="AF23" s="129"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="129"/>
+      <c r="U23" s="138"/>
+      <c r="V23" s="139"/>
+      <c r="W23" s="139"/>
+      <c r="X23" s="139"/>
+      <c r="Y23" s="139"/>
+      <c r="Z23" s="139"/>
+      <c r="AA23" s="139"/>
+      <c r="AB23" s="139"/>
+      <c r="AC23" s="139"/>
+      <c r="AD23" s="139"/>
+      <c r="AE23" s="139"/>
+      <c r="AF23" s="140"/>
       <c r="AG23" s="74"/>
       <c r="AH23" s="74"/>
       <c r="AI23" s="74"/>
@@ -10157,29 +10239,29 @@
       <c r="AP23" s="74"/>
     </row>
     <row r="24" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H24" s="142"/>
-      <c r="I24" s="143"/>
-      <c r="J24" s="143"/>
-      <c r="K24" s="143"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="143"/>
-      <c r="N24" s="143"/>
-      <c r="O24" s="143"/>
-      <c r="P24" s="143"/>
-      <c r="Q24" s="143"/>
-      <c r="R24" s="144"/>
-      <c r="U24" s="130"/>
-      <c r="V24" s="131"/>
-      <c r="W24" s="131"/>
-      <c r="X24" s="131"/>
-      <c r="Y24" s="131"/>
-      <c r="Z24" s="131"/>
-      <c r="AA24" s="131"/>
-      <c r="AB24" s="131"/>
-      <c r="AC24" s="131"/>
-      <c r="AD24" s="131"/>
-      <c r="AE24" s="131"/>
-      <c r="AF24" s="132"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="132"/>
+      <c r="U24" s="141"/>
+      <c r="V24" s="142"/>
+      <c r="W24" s="142"/>
+      <c r="X24" s="142"/>
+      <c r="Y24" s="142"/>
+      <c r="Z24" s="142"/>
+      <c r="AA24" s="142"/>
+      <c r="AB24" s="142"/>
+      <c r="AC24" s="142"/>
+      <c r="AD24" s="142"/>
+      <c r="AE24" s="142"/>
+      <c r="AF24" s="143"/>
       <c r="AG24" s="74"/>
       <c r="AH24" s="74"/>
       <c r="AI24" s="74"/>
@@ -10262,19 +10344,19 @@
       <c r="AP26" s="74"/>
     </row>
     <row r="27" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H27" s="133" t="s">
+      <c r="H27" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="134"/>
-      <c r="N27" s="134"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="134"/>
-      <c r="Q27" s="134"/>
-      <c r="R27" s="135"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="145"/>
+      <c r="R27" s="146"/>
       <c r="U27" s="74"/>
       <c r="V27" s="74"/>
       <c r="W27" s="74"/>
@@ -10299,19 +10381,19 @@
       <c r="AP27" s="74"/>
     </row>
     <row r="28" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H28" s="136" t="s">
+      <c r="H28" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="137"/>
-      <c r="O28" s="137"/>
-      <c r="P28" s="137"/>
-      <c r="Q28" s="137"/>
-      <c r="R28" s="138"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
+      <c r="L28" s="125"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="125"/>
+      <c r="O28" s="125"/>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="125"/>
+      <c r="R28" s="126"/>
       <c r="U28" s="74"/>
       <c r="V28" s="74"/>
       <c r="W28" s="74"/>
@@ -10336,1171 +10418,1171 @@
       <c r="AP28" s="74"/>
     </row>
     <row r="29" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H29" s="139"/>
-      <c r="I29" s="140"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="140"/>
-      <c r="N29" s="140"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="140"/>
-      <c r="Q29" s="140"/>
-      <c r="R29" s="141"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="128"/>
+      <c r="P29" s="128"/>
+      <c r="Q29" s="128"/>
+      <c r="R29" s="129"/>
     </row>
     <row r="30" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H30" s="139"/>
-      <c r="I30" s="140"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="140"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="140"/>
-      <c r="Q30" s="140"/>
-      <c r="R30" s="141"/>
+      <c r="H30" s="127"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="128"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="128"/>
+      <c r="P30" s="128"/>
+      <c r="Q30" s="128"/>
+      <c r="R30" s="129"/>
     </row>
     <row r="31" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H31" s="139"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="140"/>
-      <c r="N31" s="140"/>
-      <c r="O31" s="140"/>
-      <c r="P31" s="140"/>
-      <c r="Q31" s="140"/>
-      <c r="R31" s="141"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="128"/>
+      <c r="J31" s="128"/>
+      <c r="K31" s="128"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="128"/>
+      <c r="R31" s="129"/>
     </row>
     <row r="32" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H32" s="139"/>
-      <c r="I32" s="140"/>
-      <c r="J32" s="140"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="140"/>
-      <c r="M32" s="140"/>
-      <c r="N32" s="140"/>
-      <c r="O32" s="140"/>
-      <c r="P32" s="140"/>
-      <c r="Q32" s="140"/>
-      <c r="R32" s="141"/>
+      <c r="H32" s="127"/>
+      <c r="I32" s="128"/>
+      <c r="J32" s="128"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="128"/>
+      <c r="M32" s="128"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="128"/>
+      <c r="P32" s="128"/>
+      <c r="Q32" s="128"/>
+      <c r="R32" s="129"/>
     </row>
     <row r="33" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H33" s="139"/>
-      <c r="I33" s="140"/>
-      <c r="J33" s="140"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="140"/>
-      <c r="M33" s="140"/>
-      <c r="N33" s="140"/>
-      <c r="O33" s="140"/>
-      <c r="P33" s="140"/>
-      <c r="Q33" s="140"/>
-      <c r="R33" s="141"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
+      <c r="M33" s="128"/>
+      <c r="N33" s="128"/>
+      <c r="O33" s="128"/>
+      <c r="P33" s="128"/>
+      <c r="Q33" s="128"/>
+      <c r="R33" s="129"/>
     </row>
     <row r="34" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H34" s="139"/>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="140"/>
-      <c r="P34" s="140"/>
-      <c r="Q34" s="140"/>
-      <c r="R34" s="141"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="128"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="128"/>
+      <c r="L34" s="128"/>
+      <c r="M34" s="128"/>
+      <c r="N34" s="128"/>
+      <c r="O34" s="128"/>
+      <c r="P34" s="128"/>
+      <c r="Q34" s="128"/>
+      <c r="R34" s="129"/>
     </row>
     <row r="35" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H35" s="139"/>
-      <c r="I35" s="140"/>
-      <c r="J35" s="140"/>
-      <c r="K35" s="140"/>
-      <c r="L35" s="140"/>
-      <c r="M35" s="140"/>
-      <c r="N35" s="140"/>
-      <c r="O35" s="140"/>
-      <c r="P35" s="140"/>
-      <c r="Q35" s="140"/>
-      <c r="R35" s="141"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="128"/>
+      <c r="J35" s="128"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="129"/>
     </row>
     <row r="36" spans="6:18" ht="13.5" customHeight="1">
       <c r="F36" s="7"/>
-      <c r="H36" s="139"/>
-      <c r="I36" s="140"/>
-      <c r="J36" s="140"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="140"/>
-      <c r="M36" s="140"/>
-      <c r="N36" s="140"/>
-      <c r="O36" s="140"/>
-      <c r="P36" s="140"/>
-      <c r="Q36" s="140"/>
-      <c r="R36" s="141"/>
+      <c r="H36" s="127"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="129"/>
     </row>
     <row r="37" spans="6:18" ht="13.5" customHeight="1">
       <c r="F37" s="7"/>
-      <c r="H37" s="139"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="140"/>
-      <c r="O37" s="140"/>
-      <c r="P37" s="140"/>
-      <c r="Q37" s="140"/>
-      <c r="R37" s="141"/>
+      <c r="H37" s="127"/>
+      <c r="I37" s="128"/>
+      <c r="J37" s="128"/>
+      <c r="K37" s="128"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="128"/>
+      <c r="O37" s="128"/>
+      <c r="P37" s="128"/>
+      <c r="Q37" s="128"/>
+      <c r="R37" s="129"/>
     </row>
     <row r="38" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H38" s="139"/>
-      <c r="I38" s="140"/>
-      <c r="J38" s="140"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="140"/>
-      <c r="M38" s="140"/>
-      <c r="N38" s="140"/>
-      <c r="O38" s="140"/>
-      <c r="P38" s="140"/>
-      <c r="Q38" s="140"/>
-      <c r="R38" s="141"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="128"/>
+      <c r="J38" s="128"/>
+      <c r="K38" s="128"/>
+      <c r="L38" s="128"/>
+      <c r="M38" s="128"/>
+      <c r="N38" s="128"/>
+      <c r="O38" s="128"/>
+      <c r="P38" s="128"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="129"/>
     </row>
     <row r="39" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H39" s="139"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="140"/>
-      <c r="M39" s="140"/>
-      <c r="N39" s="140"/>
-      <c r="O39" s="140"/>
-      <c r="P39" s="140"/>
-      <c r="Q39" s="140"/>
-      <c r="R39" s="141"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="128"/>
+      <c r="J39" s="128"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="128"/>
+      <c r="M39" s="128"/>
+      <c r="N39" s="128"/>
+      <c r="O39" s="128"/>
+      <c r="P39" s="128"/>
+      <c r="Q39" s="128"/>
+      <c r="R39" s="129"/>
     </row>
     <row r="40" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H40" s="139"/>
-      <c r="I40" s="140"/>
-      <c r="J40" s="140"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="140"/>
-      <c r="M40" s="140"/>
-      <c r="N40" s="140"/>
-      <c r="O40" s="140"/>
-      <c r="P40" s="140"/>
-      <c r="Q40" s="140"/>
-      <c r="R40" s="141"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
+      <c r="O40" s="128"/>
+      <c r="P40" s="128"/>
+      <c r="Q40" s="128"/>
+      <c r="R40" s="129"/>
     </row>
     <row r="41" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H41" s="139"/>
-      <c r="I41" s="140"/>
-      <c r="J41" s="140"/>
-      <c r="K41" s="140"/>
-      <c r="L41" s="140"/>
-      <c r="M41" s="140"/>
-      <c r="N41" s="140"/>
-      <c r="O41" s="140"/>
-      <c r="P41" s="140"/>
-      <c r="Q41" s="140"/>
-      <c r="R41" s="141"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
+      <c r="M41" s="128"/>
+      <c r="N41" s="128"/>
+      <c r="O41" s="128"/>
+      <c r="P41" s="128"/>
+      <c r="Q41" s="128"/>
+      <c r="R41" s="129"/>
     </row>
     <row r="42" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H42" s="139"/>
-      <c r="I42" s="140"/>
-      <c r="J42" s="140"/>
-      <c r="K42" s="140"/>
-      <c r="L42" s="140"/>
-      <c r="M42" s="140"/>
-      <c r="N42" s="140"/>
-      <c r="O42" s="140"/>
-      <c r="P42" s="140"/>
-      <c r="Q42" s="140"/>
-      <c r="R42" s="141"/>
+      <c r="H42" s="127"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
+      <c r="M42" s="128"/>
+      <c r="N42" s="128"/>
+      <c r="O42" s="128"/>
+      <c r="P42" s="128"/>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="129"/>
     </row>
     <row r="43" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H43" s="139"/>
-      <c r="I43" s="140"/>
-      <c r="J43" s="140"/>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
-      <c r="M43" s="140"/>
-      <c r="N43" s="140"/>
-      <c r="O43" s="140"/>
-      <c r="P43" s="140"/>
-      <c r="Q43" s="140"/>
-      <c r="R43" s="141"/>
+      <c r="H43" s="127"/>
+      <c r="I43" s="128"/>
+      <c r="J43" s="128"/>
+      <c r="K43" s="128"/>
+      <c r="L43" s="128"/>
+      <c r="M43" s="128"/>
+      <c r="N43" s="128"/>
+      <c r="O43" s="128"/>
+      <c r="P43" s="128"/>
+      <c r="Q43" s="128"/>
+      <c r="R43" s="129"/>
     </row>
     <row r="44" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H44" s="139"/>
-      <c r="I44" s="140"/>
-      <c r="J44" s="140"/>
-      <c r="K44" s="140"/>
-      <c r="L44" s="140"/>
-      <c r="M44" s="140"/>
-      <c r="N44" s="140"/>
-      <c r="O44" s="140"/>
-      <c r="P44" s="140"/>
-      <c r="Q44" s="140"/>
-      <c r="R44" s="141"/>
+      <c r="H44" s="127"/>
+      <c r="I44" s="128"/>
+      <c r="J44" s="128"/>
+      <c r="K44" s="128"/>
+      <c r="L44" s="128"/>
+      <c r="M44" s="128"/>
+      <c r="N44" s="128"/>
+      <c r="O44" s="128"/>
+      <c r="P44" s="128"/>
+      <c r="Q44" s="128"/>
+      <c r="R44" s="129"/>
     </row>
     <row r="45" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H45" s="139"/>
-      <c r="I45" s="140"/>
-      <c r="J45" s="140"/>
-      <c r="K45" s="140"/>
-      <c r="L45" s="140"/>
-      <c r="M45" s="140"/>
-      <c r="N45" s="140"/>
-      <c r="O45" s="140"/>
-      <c r="P45" s="140"/>
-      <c r="Q45" s="140"/>
-      <c r="R45" s="141"/>
+      <c r="H45" s="127"/>
+      <c r="I45" s="128"/>
+      <c r="J45" s="128"/>
+      <c r="K45" s="128"/>
+      <c r="L45" s="128"/>
+      <c r="M45" s="128"/>
+      <c r="N45" s="128"/>
+      <c r="O45" s="128"/>
+      <c r="P45" s="128"/>
+      <c r="Q45" s="128"/>
+      <c r="R45" s="129"/>
     </row>
     <row r="46" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H46" s="139"/>
-      <c r="I46" s="140"/>
-      <c r="J46" s="140"/>
-      <c r="K46" s="140"/>
-      <c r="L46" s="140"/>
-      <c r="M46" s="140"/>
-      <c r="N46" s="140"/>
-      <c r="O46" s="140"/>
-      <c r="P46" s="140"/>
-      <c r="Q46" s="140"/>
-      <c r="R46" s="141"/>
+      <c r="H46" s="127"/>
+      <c r="I46" s="128"/>
+      <c r="J46" s="128"/>
+      <c r="K46" s="128"/>
+      <c r="L46" s="128"/>
+      <c r="M46" s="128"/>
+      <c r="N46" s="128"/>
+      <c r="O46" s="128"/>
+      <c r="P46" s="128"/>
+      <c r="Q46" s="128"/>
+      <c r="R46" s="129"/>
     </row>
     <row r="47" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H47" s="139"/>
-      <c r="I47" s="140"/>
-      <c r="J47" s="140"/>
-      <c r="K47" s="140"/>
-      <c r="L47" s="140"/>
-      <c r="M47" s="140"/>
-      <c r="N47" s="140"/>
-      <c r="O47" s="140"/>
-      <c r="P47" s="140"/>
-      <c r="Q47" s="140"/>
-      <c r="R47" s="141"/>
+      <c r="H47" s="127"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="129"/>
     </row>
     <row r="48" spans="6:18" ht="13.5" customHeight="1">
-      <c r="H48" s="139"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="140"/>
-      <c r="K48" s="140"/>
-      <c r="L48" s="140"/>
-      <c r="M48" s="140"/>
-      <c r="N48" s="140"/>
-      <c r="O48" s="140"/>
-      <c r="P48" s="140"/>
-      <c r="Q48" s="140"/>
-      <c r="R48" s="141"/>
+      <c r="H48" s="127"/>
+      <c r="I48" s="128"/>
+      <c r="J48" s="128"/>
+      <c r="K48" s="128"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="128"/>
+      <c r="N48" s="128"/>
+      <c r="O48" s="128"/>
+      <c r="P48" s="128"/>
+      <c r="Q48" s="128"/>
+      <c r="R48" s="129"/>
     </row>
     <row r="49" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H49" s="139"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="140"/>
-      <c r="K49" s="140"/>
-      <c r="L49" s="140"/>
-      <c r="M49" s="140"/>
-      <c r="N49" s="140"/>
-      <c r="O49" s="140"/>
-      <c r="P49" s="140"/>
-      <c r="Q49" s="140"/>
-      <c r="R49" s="141"/>
+      <c r="H49" s="127"/>
+      <c r="I49" s="128"/>
+      <c r="J49" s="128"/>
+      <c r="K49" s="128"/>
+      <c r="L49" s="128"/>
+      <c r="M49" s="128"/>
+      <c r="N49" s="128"/>
+      <c r="O49" s="128"/>
+      <c r="P49" s="128"/>
+      <c r="Q49" s="128"/>
+      <c r="R49" s="129"/>
     </row>
     <row r="50" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H50" s="139"/>
-      <c r="I50" s="140"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
-      <c r="M50" s="140"/>
-      <c r="N50" s="140"/>
-      <c r="O50" s="140"/>
-      <c r="P50" s="140"/>
-      <c r="Q50" s="140"/>
-      <c r="R50" s="141"/>
+      <c r="H50" s="127"/>
+      <c r="I50" s="128"/>
+      <c r="J50" s="128"/>
+      <c r="K50" s="128"/>
+      <c r="L50" s="128"/>
+      <c r="M50" s="128"/>
+      <c r="N50" s="128"/>
+      <c r="O50" s="128"/>
+      <c r="P50" s="128"/>
+      <c r="Q50" s="128"/>
+      <c r="R50" s="129"/>
     </row>
     <row r="51" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H51" s="139"/>
-      <c r="I51" s="140"/>
-      <c r="J51" s="140"/>
-      <c r="K51" s="140"/>
-      <c r="L51" s="140"/>
-      <c r="M51" s="140"/>
-      <c r="N51" s="140"/>
-      <c r="O51" s="140"/>
-      <c r="P51" s="140"/>
-      <c r="Q51" s="140"/>
-      <c r="R51" s="141"/>
+      <c r="H51" s="127"/>
+      <c r="I51" s="128"/>
+      <c r="J51" s="128"/>
+      <c r="K51" s="128"/>
+      <c r="L51" s="128"/>
+      <c r="M51" s="128"/>
+      <c r="N51" s="128"/>
+      <c r="O51" s="128"/>
+      <c r="P51" s="128"/>
+      <c r="Q51" s="128"/>
+      <c r="R51" s="129"/>
     </row>
     <row r="52" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H52" s="139"/>
-      <c r="I52" s="140"/>
-      <c r="J52" s="140"/>
-      <c r="K52" s="140"/>
-      <c r="L52" s="140"/>
-      <c r="M52" s="140"/>
-      <c r="N52" s="140"/>
-      <c r="O52" s="140"/>
-      <c r="P52" s="140"/>
-      <c r="Q52" s="140"/>
-      <c r="R52" s="141"/>
+      <c r="H52" s="127"/>
+      <c r="I52" s="128"/>
+      <c r="J52" s="128"/>
+      <c r="K52" s="128"/>
+      <c r="L52" s="128"/>
+      <c r="M52" s="128"/>
+      <c r="N52" s="128"/>
+      <c r="O52" s="128"/>
+      <c r="P52" s="128"/>
+      <c r="Q52" s="128"/>
+      <c r="R52" s="129"/>
     </row>
     <row r="53" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H53" s="139"/>
-      <c r="I53" s="140"/>
-      <c r="J53" s="140"/>
-      <c r="K53" s="140"/>
-      <c r="L53" s="140"/>
-      <c r="M53" s="140"/>
-      <c r="N53" s="140"/>
-      <c r="O53" s="140"/>
-      <c r="P53" s="140"/>
-      <c r="Q53" s="140"/>
-      <c r="R53" s="141"/>
+      <c r="H53" s="127"/>
+      <c r="I53" s="128"/>
+      <c r="J53" s="128"/>
+      <c r="K53" s="128"/>
+      <c r="L53" s="128"/>
+      <c r="M53" s="128"/>
+      <c r="N53" s="128"/>
+      <c r="O53" s="128"/>
+      <c r="P53" s="128"/>
+      <c r="Q53" s="128"/>
+      <c r="R53" s="129"/>
     </row>
     <row r="54" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H54" s="139"/>
-      <c r="I54" s="140"/>
-      <c r="J54" s="140"/>
-      <c r="K54" s="140"/>
-      <c r="L54" s="140"/>
-      <c r="M54" s="140"/>
-      <c r="N54" s="140"/>
-      <c r="O54" s="140"/>
-      <c r="P54" s="140"/>
-      <c r="Q54" s="140"/>
-      <c r="R54" s="141"/>
+      <c r="H54" s="127"/>
+      <c r="I54" s="128"/>
+      <c r="J54" s="128"/>
+      <c r="K54" s="128"/>
+      <c r="L54" s="128"/>
+      <c r="M54" s="128"/>
+      <c r="N54" s="128"/>
+      <c r="O54" s="128"/>
+      <c r="P54" s="128"/>
+      <c r="Q54" s="128"/>
+      <c r="R54" s="129"/>
     </row>
     <row r="55" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H55" s="139"/>
-      <c r="I55" s="140"/>
-      <c r="J55" s="140"/>
-      <c r="K55" s="140"/>
-      <c r="L55" s="140"/>
-      <c r="M55" s="140"/>
-      <c r="N55" s="140"/>
-      <c r="O55" s="140"/>
-      <c r="P55" s="140"/>
-      <c r="Q55" s="140"/>
-      <c r="R55" s="141"/>
+      <c r="H55" s="127"/>
+      <c r="I55" s="128"/>
+      <c r="J55" s="128"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
+      <c r="M55" s="128"/>
+      <c r="N55" s="128"/>
+      <c r="O55" s="128"/>
+      <c r="P55" s="128"/>
+      <c r="Q55" s="128"/>
+      <c r="R55" s="129"/>
       <c r="W55" s="75"/>
     </row>
     <row r="56" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H56" s="139"/>
-      <c r="I56" s="140"/>
-      <c r="J56" s="140"/>
-      <c r="K56" s="140"/>
-      <c r="L56" s="140"/>
-      <c r="M56" s="140"/>
-      <c r="N56" s="140"/>
-      <c r="O56" s="140"/>
-      <c r="P56" s="140"/>
-      <c r="Q56" s="140"/>
-      <c r="R56" s="141"/>
+      <c r="H56" s="127"/>
+      <c r="I56" s="128"/>
+      <c r="J56" s="128"/>
+      <c r="K56" s="128"/>
+      <c r="L56" s="128"/>
+      <c r="M56" s="128"/>
+      <c r="N56" s="128"/>
+      <c r="O56" s="128"/>
+      <c r="P56" s="128"/>
+      <c r="Q56" s="128"/>
+      <c r="R56" s="129"/>
     </row>
     <row r="57" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H57" s="139"/>
-      <c r="I57" s="140"/>
-      <c r="J57" s="140"/>
-      <c r="K57" s="140"/>
-      <c r="L57" s="140"/>
-      <c r="M57" s="140"/>
-      <c r="N57" s="140"/>
-      <c r="O57" s="140"/>
-      <c r="P57" s="140"/>
-      <c r="Q57" s="140"/>
-      <c r="R57" s="141"/>
+      <c r="H57" s="127"/>
+      <c r="I57" s="128"/>
+      <c r="J57" s="128"/>
+      <c r="K57" s="128"/>
+      <c r="L57" s="128"/>
+      <c r="M57" s="128"/>
+      <c r="N57" s="128"/>
+      <c r="O57" s="128"/>
+      <c r="P57" s="128"/>
+      <c r="Q57" s="128"/>
+      <c r="R57" s="129"/>
     </row>
     <row r="58" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H58" s="139"/>
-      <c r="I58" s="140"/>
-      <c r="J58" s="140"/>
-      <c r="K58" s="140"/>
-      <c r="L58" s="140"/>
-      <c r="M58" s="140"/>
-      <c r="N58" s="140"/>
-      <c r="O58" s="140"/>
-      <c r="P58" s="140"/>
-      <c r="Q58" s="140"/>
-      <c r="R58" s="141"/>
+      <c r="H58" s="127"/>
+      <c r="I58" s="128"/>
+      <c r="J58" s="128"/>
+      <c r="K58" s="128"/>
+      <c r="L58" s="128"/>
+      <c r="M58" s="128"/>
+      <c r="N58" s="128"/>
+      <c r="O58" s="128"/>
+      <c r="P58" s="128"/>
+      <c r="Q58" s="128"/>
+      <c r="R58" s="129"/>
     </row>
     <row r="59" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H59" s="139"/>
-      <c r="I59" s="140"/>
-      <c r="J59" s="140"/>
-      <c r="K59" s="140"/>
-      <c r="L59" s="140"/>
-      <c r="M59" s="140"/>
-      <c r="N59" s="140"/>
-      <c r="O59" s="140"/>
-      <c r="P59" s="140"/>
-      <c r="Q59" s="140"/>
-      <c r="R59" s="141"/>
+      <c r="H59" s="127"/>
+      <c r="I59" s="128"/>
+      <c r="J59" s="128"/>
+      <c r="K59" s="128"/>
+      <c r="L59" s="128"/>
+      <c r="M59" s="128"/>
+      <c r="N59" s="128"/>
+      <c r="O59" s="128"/>
+      <c r="P59" s="128"/>
+      <c r="Q59" s="128"/>
+      <c r="R59" s="129"/>
     </row>
     <row r="60" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H60" s="139"/>
-      <c r="I60" s="140"/>
-      <c r="J60" s="140"/>
-      <c r="K60" s="140"/>
-      <c r="L60" s="140"/>
-      <c r="M60" s="140"/>
-      <c r="N60" s="140"/>
-      <c r="O60" s="140"/>
-      <c r="P60" s="140"/>
-      <c r="Q60" s="140"/>
-      <c r="R60" s="141"/>
+      <c r="H60" s="127"/>
+      <c r="I60" s="128"/>
+      <c r="J60" s="128"/>
+      <c r="K60" s="128"/>
+      <c r="L60" s="128"/>
+      <c r="M60" s="128"/>
+      <c r="N60" s="128"/>
+      <c r="O60" s="128"/>
+      <c r="P60" s="128"/>
+      <c r="Q60" s="128"/>
+      <c r="R60" s="129"/>
     </row>
     <row r="61" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H61" s="139"/>
-      <c r="I61" s="140"/>
-      <c r="J61" s="140"/>
-      <c r="K61" s="140"/>
-      <c r="L61" s="140"/>
-      <c r="M61" s="140"/>
-      <c r="N61" s="140"/>
-      <c r="O61" s="140"/>
-      <c r="P61" s="140"/>
-      <c r="Q61" s="140"/>
-      <c r="R61" s="141"/>
+      <c r="H61" s="127"/>
+      <c r="I61" s="128"/>
+      <c r="J61" s="128"/>
+      <c r="K61" s="128"/>
+      <c r="L61" s="128"/>
+      <c r="M61" s="128"/>
+      <c r="N61" s="128"/>
+      <c r="O61" s="128"/>
+      <c r="P61" s="128"/>
+      <c r="Q61" s="128"/>
+      <c r="R61" s="129"/>
     </row>
     <row r="62" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H62" s="139"/>
-      <c r="I62" s="140"/>
-      <c r="J62" s="140"/>
-      <c r="K62" s="140"/>
-      <c r="L62" s="140"/>
-      <c r="M62" s="140"/>
-      <c r="N62" s="140"/>
-      <c r="O62" s="140"/>
-      <c r="P62" s="140"/>
-      <c r="Q62" s="140"/>
-      <c r="R62" s="141"/>
+      <c r="H62" s="127"/>
+      <c r="I62" s="128"/>
+      <c r="J62" s="128"/>
+      <c r="K62" s="128"/>
+      <c r="L62" s="128"/>
+      <c r="M62" s="128"/>
+      <c r="N62" s="128"/>
+      <c r="O62" s="128"/>
+      <c r="P62" s="128"/>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="129"/>
     </row>
     <row r="63" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H63" s="139"/>
-      <c r="I63" s="140"/>
-      <c r="J63" s="140"/>
-      <c r="K63" s="140"/>
-      <c r="L63" s="140"/>
-      <c r="M63" s="140"/>
-      <c r="N63" s="140"/>
-      <c r="O63" s="140"/>
-      <c r="P63" s="140"/>
-      <c r="Q63" s="140"/>
-      <c r="R63" s="141"/>
+      <c r="H63" s="127"/>
+      <c r="I63" s="128"/>
+      <c r="J63" s="128"/>
+      <c r="K63" s="128"/>
+      <c r="L63" s="128"/>
+      <c r="M63" s="128"/>
+      <c r="N63" s="128"/>
+      <c r="O63" s="128"/>
+      <c r="P63" s="128"/>
+      <c r="Q63" s="128"/>
+      <c r="R63" s="129"/>
     </row>
     <row r="64" spans="8:23" ht="13.5" customHeight="1">
-      <c r="H64" s="139"/>
-      <c r="I64" s="140"/>
-      <c r="J64" s="140"/>
-      <c r="K64" s="140"/>
-      <c r="L64" s="140"/>
-      <c r="M64" s="140"/>
-      <c r="N64" s="140"/>
-      <c r="O64" s="140"/>
-      <c r="P64" s="140"/>
-      <c r="Q64" s="140"/>
-      <c r="R64" s="141"/>
+      <c r="H64" s="127"/>
+      <c r="I64" s="128"/>
+      <c r="J64" s="128"/>
+      <c r="K64" s="128"/>
+      <c r="L64" s="128"/>
+      <c r="M64" s="128"/>
+      <c r="N64" s="128"/>
+      <c r="O64" s="128"/>
+      <c r="P64" s="128"/>
+      <c r="Q64" s="128"/>
+      <c r="R64" s="129"/>
     </row>
     <row r="65" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H65" s="139"/>
-      <c r="I65" s="140"/>
-      <c r="J65" s="140"/>
-      <c r="K65" s="140"/>
-      <c r="L65" s="140"/>
-      <c r="M65" s="140"/>
-      <c r="N65" s="140"/>
-      <c r="O65" s="140"/>
-      <c r="P65" s="140"/>
-      <c r="Q65" s="140"/>
-      <c r="R65" s="141"/>
+      <c r="H65" s="127"/>
+      <c r="I65" s="128"/>
+      <c r="J65" s="128"/>
+      <c r="K65" s="128"/>
+      <c r="L65" s="128"/>
+      <c r="M65" s="128"/>
+      <c r="N65" s="128"/>
+      <c r="O65" s="128"/>
+      <c r="P65" s="128"/>
+      <c r="Q65" s="128"/>
+      <c r="R65" s="129"/>
     </row>
     <row r="66" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H66" s="139"/>
-      <c r="I66" s="140"/>
-      <c r="J66" s="140"/>
-      <c r="K66" s="140"/>
-      <c r="L66" s="140"/>
-      <c r="M66" s="140"/>
-      <c r="N66" s="140"/>
-      <c r="O66" s="140"/>
-      <c r="P66" s="140"/>
-      <c r="Q66" s="140"/>
-      <c r="R66" s="141"/>
+      <c r="H66" s="127"/>
+      <c r="I66" s="128"/>
+      <c r="J66" s="128"/>
+      <c r="K66" s="128"/>
+      <c r="L66" s="128"/>
+      <c r="M66" s="128"/>
+      <c r="N66" s="128"/>
+      <c r="O66" s="128"/>
+      <c r="P66" s="128"/>
+      <c r="Q66" s="128"/>
+      <c r="R66" s="129"/>
     </row>
     <row r="67" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H67" s="139"/>
-      <c r="I67" s="140"/>
-      <c r="J67" s="140"/>
-      <c r="K67" s="140"/>
-      <c r="L67" s="140"/>
-      <c r="M67" s="140"/>
-      <c r="N67" s="140"/>
-      <c r="O67" s="140"/>
-      <c r="P67" s="140"/>
-      <c r="Q67" s="140"/>
-      <c r="R67" s="141"/>
+      <c r="H67" s="127"/>
+      <c r="I67" s="128"/>
+      <c r="J67" s="128"/>
+      <c r="K67" s="128"/>
+      <c r="L67" s="128"/>
+      <c r="M67" s="128"/>
+      <c r="N67" s="128"/>
+      <c r="O67" s="128"/>
+      <c r="P67" s="128"/>
+      <c r="Q67" s="128"/>
+      <c r="R67" s="129"/>
     </row>
     <row r="68" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H68" s="139"/>
-      <c r="I68" s="140"/>
-      <c r="J68" s="140"/>
-      <c r="K68" s="140"/>
-      <c r="L68" s="140"/>
-      <c r="M68" s="140"/>
-      <c r="N68" s="140"/>
-      <c r="O68" s="140"/>
-      <c r="P68" s="140"/>
-      <c r="Q68" s="140"/>
-      <c r="R68" s="141"/>
+      <c r="H68" s="127"/>
+      <c r="I68" s="128"/>
+      <c r="J68" s="128"/>
+      <c r="K68" s="128"/>
+      <c r="L68" s="128"/>
+      <c r="M68" s="128"/>
+      <c r="N68" s="128"/>
+      <c r="O68" s="128"/>
+      <c r="P68" s="128"/>
+      <c r="Q68" s="128"/>
+      <c r="R68" s="129"/>
     </row>
     <row r="69" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H69" s="139"/>
-      <c r="I69" s="140"/>
-      <c r="J69" s="140"/>
-      <c r="K69" s="140"/>
-      <c r="L69" s="140"/>
-      <c r="M69" s="140"/>
-      <c r="N69" s="140"/>
-      <c r="O69" s="140"/>
-      <c r="P69" s="140"/>
-      <c r="Q69" s="140"/>
-      <c r="R69" s="141"/>
+      <c r="H69" s="127"/>
+      <c r="I69" s="128"/>
+      <c r="J69" s="128"/>
+      <c r="K69" s="128"/>
+      <c r="L69" s="128"/>
+      <c r="M69" s="128"/>
+      <c r="N69" s="128"/>
+      <c r="O69" s="128"/>
+      <c r="P69" s="128"/>
+      <c r="Q69" s="128"/>
+      <c r="R69" s="129"/>
     </row>
     <row r="70" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H70" s="139"/>
-      <c r="I70" s="140"/>
-      <c r="J70" s="140"/>
-      <c r="K70" s="140"/>
-      <c r="L70" s="140"/>
-      <c r="M70" s="140"/>
-      <c r="N70" s="140"/>
-      <c r="O70" s="140"/>
-      <c r="P70" s="140"/>
-      <c r="Q70" s="140"/>
-      <c r="R70" s="141"/>
+      <c r="H70" s="127"/>
+      <c r="I70" s="128"/>
+      <c r="J70" s="128"/>
+      <c r="K70" s="128"/>
+      <c r="L70" s="128"/>
+      <c r="M70" s="128"/>
+      <c r="N70" s="128"/>
+      <c r="O70" s="128"/>
+      <c r="P70" s="128"/>
+      <c r="Q70" s="128"/>
+      <c r="R70" s="129"/>
     </row>
     <row r="71" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H71" s="139"/>
-      <c r="I71" s="140"/>
-      <c r="J71" s="140"/>
-      <c r="K71" s="140"/>
-      <c r="L71" s="140"/>
-      <c r="M71" s="140"/>
-      <c r="N71" s="140"/>
-      <c r="O71" s="140"/>
-      <c r="P71" s="140"/>
-      <c r="Q71" s="140"/>
-      <c r="R71" s="141"/>
+      <c r="H71" s="127"/>
+      <c r="I71" s="128"/>
+      <c r="J71" s="128"/>
+      <c r="K71" s="128"/>
+      <c r="L71" s="128"/>
+      <c r="M71" s="128"/>
+      <c r="N71" s="128"/>
+      <c r="O71" s="128"/>
+      <c r="P71" s="128"/>
+      <c r="Q71" s="128"/>
+      <c r="R71" s="129"/>
     </row>
     <row r="72" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H72" s="142"/>
-      <c r="I72" s="143"/>
-      <c r="J72" s="143"/>
-      <c r="K72" s="143"/>
-      <c r="L72" s="143"/>
-      <c r="M72" s="143"/>
-      <c r="N72" s="143"/>
-      <c r="O72" s="143"/>
-      <c r="P72" s="143"/>
-      <c r="Q72" s="143"/>
-      <c r="R72" s="144"/>
+      <c r="H72" s="130"/>
+      <c r="I72" s="131"/>
+      <c r="J72" s="131"/>
+      <c r="K72" s="131"/>
+      <c r="L72" s="131"/>
+      <c r="M72" s="131"/>
+      <c r="N72" s="131"/>
+      <c r="O72" s="131"/>
+      <c r="P72" s="131"/>
+      <c r="Q72" s="131"/>
+      <c r="R72" s="132"/>
     </row>
     <row r="73" spans="8:18" ht="13.5" customHeight="1"/>
     <row r="74" spans="8:18" ht="13.5" customHeight="1"/>
     <row r="75" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H75" s="133" t="s">
+      <c r="H75" s="144" t="s">
         <v>71</v>
       </c>
-      <c r="I75" s="134"/>
-      <c r="J75" s="134"/>
-      <c r="K75" s="134"/>
-      <c r="L75" s="134"/>
-      <c r="M75" s="134"/>
-      <c r="N75" s="134"/>
-      <c r="O75" s="134"/>
-      <c r="P75" s="134"/>
-      <c r="Q75" s="134"/>
-      <c r="R75" s="135"/>
+      <c r="I75" s="145"/>
+      <c r="J75" s="145"/>
+      <c r="K75" s="145"/>
+      <c r="L75" s="145"/>
+      <c r="M75" s="145"/>
+      <c r="N75" s="145"/>
+      <c r="O75" s="145"/>
+      <c r="P75" s="145"/>
+      <c r="Q75" s="145"/>
+      <c r="R75" s="146"/>
     </row>
     <row r="76" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H76" s="136" t="s">
+      <c r="H76" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="I76" s="137"/>
-      <c r="J76" s="137"/>
-      <c r="K76" s="137"/>
-      <c r="L76" s="137"/>
-      <c r="M76" s="137"/>
-      <c r="N76" s="137"/>
-      <c r="O76" s="137"/>
-      <c r="P76" s="137"/>
-      <c r="Q76" s="137"/>
-      <c r="R76" s="138"/>
+      <c r="I76" s="125"/>
+      <c r="J76" s="125"/>
+      <c r="K76" s="125"/>
+      <c r="L76" s="125"/>
+      <c r="M76" s="125"/>
+      <c r="N76" s="125"/>
+      <c r="O76" s="125"/>
+      <c r="P76" s="125"/>
+      <c r="Q76" s="125"/>
+      <c r="R76" s="126"/>
     </row>
     <row r="77" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H77" s="139"/>
-      <c r="I77" s="140"/>
-      <c r="J77" s="140"/>
-      <c r="K77" s="140"/>
-      <c r="L77" s="140"/>
-      <c r="M77" s="140"/>
-      <c r="N77" s="140"/>
-      <c r="O77" s="140"/>
-      <c r="P77" s="140"/>
-      <c r="Q77" s="140"/>
-      <c r="R77" s="141"/>
+      <c r="H77" s="127"/>
+      <c r="I77" s="128"/>
+      <c r="J77" s="128"/>
+      <c r="K77" s="128"/>
+      <c r="L77" s="128"/>
+      <c r="M77" s="128"/>
+      <c r="N77" s="128"/>
+      <c r="O77" s="128"/>
+      <c r="P77" s="128"/>
+      <c r="Q77" s="128"/>
+      <c r="R77" s="129"/>
     </row>
     <row r="78" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H78" s="139"/>
-      <c r="I78" s="140"/>
-      <c r="J78" s="140"/>
-      <c r="K78" s="140"/>
-      <c r="L78" s="140"/>
-      <c r="M78" s="140"/>
-      <c r="N78" s="140"/>
-      <c r="O78" s="140"/>
-      <c r="P78" s="140"/>
-      <c r="Q78" s="140"/>
-      <c r="R78" s="141"/>
+      <c r="H78" s="127"/>
+      <c r="I78" s="128"/>
+      <c r="J78" s="128"/>
+      <c r="K78" s="128"/>
+      <c r="L78" s="128"/>
+      <c r="M78" s="128"/>
+      <c r="N78" s="128"/>
+      <c r="O78" s="128"/>
+      <c r="P78" s="128"/>
+      <c r="Q78" s="128"/>
+      <c r="R78" s="129"/>
     </row>
     <row r="79" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H79" s="139"/>
-      <c r="I79" s="140"/>
-      <c r="J79" s="140"/>
-      <c r="K79" s="140"/>
-      <c r="L79" s="140"/>
-      <c r="M79" s="140"/>
-      <c r="N79" s="140"/>
-      <c r="O79" s="140"/>
-      <c r="P79" s="140"/>
-      <c r="Q79" s="140"/>
-      <c r="R79" s="141"/>
+      <c r="H79" s="127"/>
+      <c r="I79" s="128"/>
+      <c r="J79" s="128"/>
+      <c r="K79" s="128"/>
+      <c r="L79" s="128"/>
+      <c r="M79" s="128"/>
+      <c r="N79" s="128"/>
+      <c r="O79" s="128"/>
+      <c r="P79" s="128"/>
+      <c r="Q79" s="128"/>
+      <c r="R79" s="129"/>
     </row>
     <row r="80" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H80" s="139"/>
-      <c r="I80" s="140"/>
-      <c r="J80" s="140"/>
-      <c r="K80" s="140"/>
-      <c r="L80" s="140"/>
-      <c r="M80" s="140"/>
-      <c r="N80" s="140"/>
-      <c r="O80" s="140"/>
-      <c r="P80" s="140"/>
-      <c r="Q80" s="140"/>
-      <c r="R80" s="141"/>
+      <c r="H80" s="127"/>
+      <c r="I80" s="128"/>
+      <c r="J80" s="128"/>
+      <c r="K80" s="128"/>
+      <c r="L80" s="128"/>
+      <c r="M80" s="128"/>
+      <c r="N80" s="128"/>
+      <c r="O80" s="128"/>
+      <c r="P80" s="128"/>
+      <c r="Q80" s="128"/>
+      <c r="R80" s="129"/>
     </row>
     <row r="81" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H81" s="139"/>
-      <c r="I81" s="140"/>
-      <c r="J81" s="140"/>
-      <c r="K81" s="140"/>
-      <c r="L81" s="140"/>
-      <c r="M81" s="140"/>
-      <c r="N81" s="140"/>
-      <c r="O81" s="140"/>
-      <c r="P81" s="140"/>
-      <c r="Q81" s="140"/>
-      <c r="R81" s="141"/>
+      <c r="H81" s="127"/>
+      <c r="I81" s="128"/>
+      <c r="J81" s="128"/>
+      <c r="K81" s="128"/>
+      <c r="L81" s="128"/>
+      <c r="M81" s="128"/>
+      <c r="N81" s="128"/>
+      <c r="O81" s="128"/>
+      <c r="P81" s="128"/>
+      <c r="Q81" s="128"/>
+      <c r="R81" s="129"/>
     </row>
     <row r="82" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H82" s="139"/>
-      <c r="I82" s="140"/>
-      <c r="J82" s="140"/>
-      <c r="K82" s="140"/>
-      <c r="L82" s="140"/>
-      <c r="M82" s="140"/>
-      <c r="N82" s="140"/>
-      <c r="O82" s="140"/>
-      <c r="P82" s="140"/>
-      <c r="Q82" s="140"/>
-      <c r="R82" s="141"/>
+      <c r="H82" s="127"/>
+      <c r="I82" s="128"/>
+      <c r="J82" s="128"/>
+      <c r="K82" s="128"/>
+      <c r="L82" s="128"/>
+      <c r="M82" s="128"/>
+      <c r="N82" s="128"/>
+      <c r="O82" s="128"/>
+      <c r="P82" s="128"/>
+      <c r="Q82" s="128"/>
+      <c r="R82" s="129"/>
     </row>
     <row r="83" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H83" s="139"/>
-      <c r="I83" s="140"/>
-      <c r="J83" s="140"/>
-      <c r="K83" s="140"/>
-      <c r="L83" s="140"/>
-      <c r="M83" s="140"/>
-      <c r="N83" s="140"/>
-      <c r="O83" s="140"/>
-      <c r="P83" s="140"/>
-      <c r="Q83" s="140"/>
-      <c r="R83" s="141"/>
+      <c r="H83" s="127"/>
+      <c r="I83" s="128"/>
+      <c r="J83" s="128"/>
+      <c r="K83" s="128"/>
+      <c r="L83" s="128"/>
+      <c r="M83" s="128"/>
+      <c r="N83" s="128"/>
+      <c r="O83" s="128"/>
+      <c r="P83" s="128"/>
+      <c r="Q83" s="128"/>
+      <c r="R83" s="129"/>
     </row>
     <row r="84" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H84" s="139"/>
-      <c r="I84" s="140"/>
-      <c r="J84" s="140"/>
-      <c r="K84" s="140"/>
-      <c r="L84" s="140"/>
-      <c r="M84" s="140"/>
-      <c r="N84" s="140"/>
-      <c r="O84" s="140"/>
-      <c r="P84" s="140"/>
-      <c r="Q84" s="140"/>
-      <c r="R84" s="141"/>
+      <c r="H84" s="127"/>
+      <c r="I84" s="128"/>
+      <c r="J84" s="128"/>
+      <c r="K84" s="128"/>
+      <c r="L84" s="128"/>
+      <c r="M84" s="128"/>
+      <c r="N84" s="128"/>
+      <c r="O84" s="128"/>
+      <c r="P84" s="128"/>
+      <c r="Q84" s="128"/>
+      <c r="R84" s="129"/>
     </row>
     <row r="85" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H85" s="139"/>
-      <c r="I85" s="140"/>
-      <c r="J85" s="140"/>
-      <c r="K85" s="140"/>
-      <c r="L85" s="140"/>
-      <c r="M85" s="140"/>
-      <c r="N85" s="140"/>
-      <c r="O85" s="140"/>
-      <c r="P85" s="140"/>
-      <c r="Q85" s="140"/>
-      <c r="R85" s="141"/>
+      <c r="H85" s="127"/>
+      <c r="I85" s="128"/>
+      <c r="J85" s="128"/>
+      <c r="K85" s="128"/>
+      <c r="L85" s="128"/>
+      <c r="M85" s="128"/>
+      <c r="N85" s="128"/>
+      <c r="O85" s="128"/>
+      <c r="P85" s="128"/>
+      <c r="Q85" s="128"/>
+      <c r="R85" s="129"/>
     </row>
     <row r="86" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H86" s="139"/>
-      <c r="I86" s="140"/>
-      <c r="J86" s="140"/>
-      <c r="K86" s="140"/>
-      <c r="L86" s="140"/>
-      <c r="M86" s="140"/>
-      <c r="N86" s="140"/>
-      <c r="O86" s="140"/>
-      <c r="P86" s="140"/>
-      <c r="Q86" s="140"/>
-      <c r="R86" s="141"/>
+      <c r="H86" s="127"/>
+      <c r="I86" s="128"/>
+      <c r="J86" s="128"/>
+      <c r="K86" s="128"/>
+      <c r="L86" s="128"/>
+      <c r="M86" s="128"/>
+      <c r="N86" s="128"/>
+      <c r="O86" s="128"/>
+      <c r="P86" s="128"/>
+      <c r="Q86" s="128"/>
+      <c r="R86" s="129"/>
     </row>
     <row r="87" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H87" s="139"/>
-      <c r="I87" s="140"/>
-      <c r="J87" s="140"/>
-      <c r="K87" s="140"/>
-      <c r="L87" s="140"/>
-      <c r="M87" s="140"/>
-      <c r="N87" s="140"/>
-      <c r="O87" s="140"/>
-      <c r="P87" s="140"/>
-      <c r="Q87" s="140"/>
-      <c r="R87" s="141"/>
+      <c r="H87" s="127"/>
+      <c r="I87" s="128"/>
+      <c r="J87" s="128"/>
+      <c r="K87" s="128"/>
+      <c r="L87" s="128"/>
+      <c r="M87" s="128"/>
+      <c r="N87" s="128"/>
+      <c r="O87" s="128"/>
+      <c r="P87" s="128"/>
+      <c r="Q87" s="128"/>
+      <c r="R87" s="129"/>
     </row>
     <row r="88" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H88" s="139"/>
-      <c r="I88" s="140"/>
-      <c r="J88" s="140"/>
-      <c r="K88" s="140"/>
-      <c r="L88" s="140"/>
-      <c r="M88" s="140"/>
-      <c r="N88" s="140"/>
-      <c r="O88" s="140"/>
-      <c r="P88" s="140"/>
-      <c r="Q88" s="140"/>
-      <c r="R88" s="141"/>
+      <c r="H88" s="127"/>
+      <c r="I88" s="128"/>
+      <c r="J88" s="128"/>
+      <c r="K88" s="128"/>
+      <c r="L88" s="128"/>
+      <c r="M88" s="128"/>
+      <c r="N88" s="128"/>
+      <c r="O88" s="128"/>
+      <c r="P88" s="128"/>
+      <c r="Q88" s="128"/>
+      <c r="R88" s="129"/>
     </row>
     <row r="89" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H89" s="139"/>
-      <c r="I89" s="140"/>
-      <c r="J89" s="140"/>
-      <c r="K89" s="140"/>
-      <c r="L89" s="140"/>
-      <c r="M89" s="140"/>
-      <c r="N89" s="140"/>
-      <c r="O89" s="140"/>
-      <c r="P89" s="140"/>
-      <c r="Q89" s="140"/>
-      <c r="R89" s="141"/>
+      <c r="H89" s="127"/>
+      <c r="I89" s="128"/>
+      <c r="J89" s="128"/>
+      <c r="K89" s="128"/>
+      <c r="L89" s="128"/>
+      <c r="M89" s="128"/>
+      <c r="N89" s="128"/>
+      <c r="O89" s="128"/>
+      <c r="P89" s="128"/>
+      <c r="Q89" s="128"/>
+      <c r="R89" s="129"/>
     </row>
     <row r="90" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H90" s="139"/>
-      <c r="I90" s="140"/>
-      <c r="J90" s="140"/>
-      <c r="K90" s="140"/>
-      <c r="L90" s="140"/>
-      <c r="M90" s="140"/>
-      <c r="N90" s="140"/>
-      <c r="O90" s="140"/>
-      <c r="P90" s="140"/>
-      <c r="Q90" s="140"/>
-      <c r="R90" s="141"/>
+      <c r="H90" s="127"/>
+      <c r="I90" s="128"/>
+      <c r="J90" s="128"/>
+      <c r="K90" s="128"/>
+      <c r="L90" s="128"/>
+      <c r="M90" s="128"/>
+      <c r="N90" s="128"/>
+      <c r="O90" s="128"/>
+      <c r="P90" s="128"/>
+      <c r="Q90" s="128"/>
+      <c r="R90" s="129"/>
     </row>
     <row r="91" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H91" s="139"/>
-      <c r="I91" s="140"/>
-      <c r="J91" s="140"/>
-      <c r="K91" s="140"/>
-      <c r="L91" s="140"/>
-      <c r="M91" s="140"/>
-      <c r="N91" s="140"/>
-      <c r="O91" s="140"/>
-      <c r="P91" s="140"/>
-      <c r="Q91" s="140"/>
-      <c r="R91" s="141"/>
+      <c r="H91" s="127"/>
+      <c r="I91" s="128"/>
+      <c r="J91" s="128"/>
+      <c r="K91" s="128"/>
+      <c r="L91" s="128"/>
+      <c r="M91" s="128"/>
+      <c r="N91" s="128"/>
+      <c r="O91" s="128"/>
+      <c r="P91" s="128"/>
+      <c r="Q91" s="128"/>
+      <c r="R91" s="129"/>
     </row>
     <row r="92" spans="8:18">
-      <c r="H92" s="139"/>
-      <c r="I92" s="140"/>
-      <c r="J92" s="140"/>
-      <c r="K92" s="140"/>
-      <c r="L92" s="140"/>
-      <c r="M92" s="140"/>
-      <c r="N92" s="140"/>
-      <c r="O92" s="140"/>
-      <c r="P92" s="140"/>
-      <c r="Q92" s="140"/>
-      <c r="R92" s="141"/>
+      <c r="H92" s="127"/>
+      <c r="I92" s="128"/>
+      <c r="J92" s="128"/>
+      <c r="K92" s="128"/>
+      <c r="L92" s="128"/>
+      <c r="M92" s="128"/>
+      <c r="N92" s="128"/>
+      <c r="O92" s="128"/>
+      <c r="P92" s="128"/>
+      <c r="Q92" s="128"/>
+      <c r="R92" s="129"/>
     </row>
     <row r="93" spans="8:18">
-      <c r="H93" s="139"/>
-      <c r="I93" s="140"/>
-      <c r="J93" s="140"/>
-      <c r="K93" s="140"/>
-      <c r="L93" s="140"/>
-      <c r="M93" s="140"/>
-      <c r="N93" s="140"/>
-      <c r="O93" s="140"/>
-      <c r="P93" s="140"/>
-      <c r="Q93" s="140"/>
-      <c r="R93" s="141"/>
+      <c r="H93" s="127"/>
+      <c r="I93" s="128"/>
+      <c r="J93" s="128"/>
+      <c r="K93" s="128"/>
+      <c r="L93" s="128"/>
+      <c r="M93" s="128"/>
+      <c r="N93" s="128"/>
+      <c r="O93" s="128"/>
+      <c r="P93" s="128"/>
+      <c r="Q93" s="128"/>
+      <c r="R93" s="129"/>
     </row>
     <row r="94" spans="8:18">
-      <c r="H94" s="139"/>
-      <c r="I94" s="140"/>
-      <c r="J94" s="140"/>
-      <c r="K94" s="140"/>
-      <c r="L94" s="140"/>
-      <c r="M94" s="140"/>
-      <c r="N94" s="140"/>
-      <c r="O94" s="140"/>
-      <c r="P94" s="140"/>
-      <c r="Q94" s="140"/>
-      <c r="R94" s="141"/>
+      <c r="H94" s="127"/>
+      <c r="I94" s="128"/>
+      <c r="J94" s="128"/>
+      <c r="K94" s="128"/>
+      <c r="L94" s="128"/>
+      <c r="M94" s="128"/>
+      <c r="N94" s="128"/>
+      <c r="O94" s="128"/>
+      <c r="P94" s="128"/>
+      <c r="Q94" s="128"/>
+      <c r="R94" s="129"/>
     </row>
     <row r="95" spans="8:18">
-      <c r="H95" s="139"/>
-      <c r="I95" s="140"/>
-      <c r="J95" s="140"/>
-      <c r="K95" s="140"/>
-      <c r="L95" s="140"/>
-      <c r="M95" s="140"/>
-      <c r="N95" s="140"/>
-      <c r="O95" s="140"/>
-      <c r="P95" s="140"/>
-      <c r="Q95" s="140"/>
-      <c r="R95" s="141"/>
+      <c r="H95" s="127"/>
+      <c r="I95" s="128"/>
+      <c r="J95" s="128"/>
+      <c r="K95" s="128"/>
+      <c r="L95" s="128"/>
+      <c r="M95" s="128"/>
+      <c r="N95" s="128"/>
+      <c r="O95" s="128"/>
+      <c r="P95" s="128"/>
+      <c r="Q95" s="128"/>
+      <c r="R95" s="129"/>
     </row>
     <row r="96" spans="8:18">
-      <c r="H96" s="139"/>
-      <c r="I96" s="140"/>
-      <c r="J96" s="140"/>
-      <c r="K96" s="140"/>
-      <c r="L96" s="140"/>
-      <c r="M96" s="140"/>
-      <c r="N96" s="140"/>
-      <c r="O96" s="140"/>
-      <c r="P96" s="140"/>
-      <c r="Q96" s="140"/>
-      <c r="R96" s="141"/>
+      <c r="H96" s="127"/>
+      <c r="I96" s="128"/>
+      <c r="J96" s="128"/>
+      <c r="K96" s="128"/>
+      <c r="L96" s="128"/>
+      <c r="M96" s="128"/>
+      <c r="N96" s="128"/>
+      <c r="O96" s="128"/>
+      <c r="P96" s="128"/>
+      <c r="Q96" s="128"/>
+      <c r="R96" s="129"/>
     </row>
     <row r="97" spans="8:18">
-      <c r="H97" s="139"/>
-      <c r="I97" s="140"/>
-      <c r="J97" s="140"/>
-      <c r="K97" s="140"/>
-      <c r="L97" s="140"/>
-      <c r="M97" s="140"/>
-      <c r="N97" s="140"/>
-      <c r="O97" s="140"/>
-      <c r="P97" s="140"/>
-      <c r="Q97" s="140"/>
-      <c r="R97" s="141"/>
+      <c r="H97" s="127"/>
+      <c r="I97" s="128"/>
+      <c r="J97" s="128"/>
+      <c r="K97" s="128"/>
+      <c r="L97" s="128"/>
+      <c r="M97" s="128"/>
+      <c r="N97" s="128"/>
+      <c r="O97" s="128"/>
+      <c r="P97" s="128"/>
+      <c r="Q97" s="128"/>
+      <c r="R97" s="129"/>
     </row>
     <row r="98" spans="8:18">
-      <c r="H98" s="139"/>
-      <c r="I98" s="140"/>
-      <c r="J98" s="140"/>
-      <c r="K98" s="140"/>
-      <c r="L98" s="140"/>
-      <c r="M98" s="140"/>
-      <c r="N98" s="140"/>
-      <c r="O98" s="140"/>
-      <c r="P98" s="140"/>
-      <c r="Q98" s="140"/>
-      <c r="R98" s="141"/>
+      <c r="H98" s="127"/>
+      <c r="I98" s="128"/>
+      <c r="J98" s="128"/>
+      <c r="K98" s="128"/>
+      <c r="L98" s="128"/>
+      <c r="M98" s="128"/>
+      <c r="N98" s="128"/>
+      <c r="O98" s="128"/>
+      <c r="P98" s="128"/>
+      <c r="Q98" s="128"/>
+      <c r="R98" s="129"/>
     </row>
     <row r="99" spans="8:18">
-      <c r="H99" s="139"/>
-      <c r="I99" s="140"/>
-      <c r="J99" s="140"/>
-      <c r="K99" s="140"/>
-      <c r="L99" s="140"/>
-      <c r="M99" s="140"/>
-      <c r="N99" s="140"/>
-      <c r="O99" s="140"/>
-      <c r="P99" s="140"/>
-      <c r="Q99" s="140"/>
-      <c r="R99" s="141"/>
+      <c r="H99" s="127"/>
+      <c r="I99" s="128"/>
+      <c r="J99" s="128"/>
+      <c r="K99" s="128"/>
+      <c r="L99" s="128"/>
+      <c r="M99" s="128"/>
+      <c r="N99" s="128"/>
+      <c r="O99" s="128"/>
+      <c r="P99" s="128"/>
+      <c r="Q99" s="128"/>
+      <c r="R99" s="129"/>
     </row>
     <row r="100" spans="8:18">
-      <c r="H100" s="139"/>
-      <c r="I100" s="140"/>
-      <c r="J100" s="140"/>
-      <c r="K100" s="140"/>
-      <c r="L100" s="140"/>
-      <c r="M100" s="140"/>
-      <c r="N100" s="140"/>
-      <c r="O100" s="140"/>
-      <c r="P100" s="140"/>
-      <c r="Q100" s="140"/>
-      <c r="R100" s="141"/>
+      <c r="H100" s="127"/>
+      <c r="I100" s="128"/>
+      <c r="J100" s="128"/>
+      <c r="K100" s="128"/>
+      <c r="L100" s="128"/>
+      <c r="M100" s="128"/>
+      <c r="N100" s="128"/>
+      <c r="O100" s="128"/>
+      <c r="P100" s="128"/>
+      <c r="Q100" s="128"/>
+      <c r="R100" s="129"/>
     </row>
     <row r="101" spans="8:18">
-      <c r="H101" s="139"/>
-      <c r="I101" s="140"/>
-      <c r="J101" s="140"/>
-      <c r="K101" s="140"/>
-      <c r="L101" s="140"/>
-      <c r="M101" s="140"/>
-      <c r="N101" s="140"/>
-      <c r="O101" s="140"/>
-      <c r="P101" s="140"/>
-      <c r="Q101" s="140"/>
-      <c r="R101" s="141"/>
+      <c r="H101" s="127"/>
+      <c r="I101" s="128"/>
+      <c r="J101" s="128"/>
+      <c r="K101" s="128"/>
+      <c r="L101" s="128"/>
+      <c r="M101" s="128"/>
+      <c r="N101" s="128"/>
+      <c r="O101" s="128"/>
+      <c r="P101" s="128"/>
+      <c r="Q101" s="128"/>
+      <c r="R101" s="129"/>
     </row>
     <row r="102" spans="8:18">
-      <c r="H102" s="139"/>
-      <c r="I102" s="140"/>
-      <c r="J102" s="140"/>
-      <c r="K102" s="140"/>
-      <c r="L102" s="140"/>
-      <c r="M102" s="140"/>
-      <c r="N102" s="140"/>
-      <c r="O102" s="140"/>
-      <c r="P102" s="140"/>
-      <c r="Q102" s="140"/>
-      <c r="R102" s="141"/>
+      <c r="H102" s="127"/>
+      <c r="I102" s="128"/>
+      <c r="J102" s="128"/>
+      <c r="K102" s="128"/>
+      <c r="L102" s="128"/>
+      <c r="M102" s="128"/>
+      <c r="N102" s="128"/>
+      <c r="O102" s="128"/>
+      <c r="P102" s="128"/>
+      <c r="Q102" s="128"/>
+      <c r="R102" s="129"/>
     </row>
     <row r="103" spans="8:18">
-      <c r="H103" s="139"/>
-      <c r="I103" s="140"/>
-      <c r="J103" s="140"/>
-      <c r="K103" s="140"/>
-      <c r="L103" s="140"/>
-      <c r="M103" s="140"/>
-      <c r="N103" s="140"/>
-      <c r="O103" s="140"/>
-      <c r="P103" s="140"/>
-      <c r="Q103" s="140"/>
-      <c r="R103" s="141"/>
+      <c r="H103" s="127"/>
+      <c r="I103" s="128"/>
+      <c r="J103" s="128"/>
+      <c r="K103" s="128"/>
+      <c r="L103" s="128"/>
+      <c r="M103" s="128"/>
+      <c r="N103" s="128"/>
+      <c r="O103" s="128"/>
+      <c r="P103" s="128"/>
+      <c r="Q103" s="128"/>
+      <c r="R103" s="129"/>
     </row>
     <row r="104" spans="8:18">
-      <c r="H104" s="139"/>
-      <c r="I104" s="140"/>
-      <c r="J104" s="140"/>
-      <c r="K104" s="140"/>
-      <c r="L104" s="140"/>
-      <c r="M104" s="140"/>
-      <c r="N104" s="140"/>
-      <c r="O104" s="140"/>
-      <c r="P104" s="140"/>
-      <c r="Q104" s="140"/>
-      <c r="R104" s="141"/>
+      <c r="H104" s="127"/>
+      <c r="I104" s="128"/>
+      <c r="J104" s="128"/>
+      <c r="K104" s="128"/>
+      <c r="L104" s="128"/>
+      <c r="M104" s="128"/>
+      <c r="N104" s="128"/>
+      <c r="O104" s="128"/>
+      <c r="P104" s="128"/>
+      <c r="Q104" s="128"/>
+      <c r="R104" s="129"/>
     </row>
     <row r="105" spans="8:18">
-      <c r="H105" s="139"/>
-      <c r="I105" s="140"/>
-      <c r="J105" s="140"/>
-      <c r="K105" s="140"/>
-      <c r="L105" s="140"/>
-      <c r="M105" s="140"/>
-      <c r="N105" s="140"/>
-      <c r="O105" s="140"/>
-      <c r="P105" s="140"/>
-      <c r="Q105" s="140"/>
-      <c r="R105" s="141"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="128"/>
+      <c r="J105" s="128"/>
+      <c r="K105" s="128"/>
+      <c r="L105" s="128"/>
+      <c r="M105" s="128"/>
+      <c r="N105" s="128"/>
+      <c r="O105" s="128"/>
+      <c r="P105" s="128"/>
+      <c r="Q105" s="128"/>
+      <c r="R105" s="129"/>
     </row>
     <row r="106" spans="8:18">
-      <c r="H106" s="139"/>
-      <c r="I106" s="140"/>
-      <c r="J106" s="140"/>
-      <c r="K106" s="140"/>
-      <c r="L106" s="140"/>
-      <c r="M106" s="140"/>
-      <c r="N106" s="140"/>
-      <c r="O106" s="140"/>
-      <c r="P106" s="140"/>
-      <c r="Q106" s="140"/>
-      <c r="R106" s="141"/>
+      <c r="H106" s="127"/>
+      <c r="I106" s="128"/>
+      <c r="J106" s="128"/>
+      <c r="K106" s="128"/>
+      <c r="L106" s="128"/>
+      <c r="M106" s="128"/>
+      <c r="N106" s="128"/>
+      <c r="O106" s="128"/>
+      <c r="P106" s="128"/>
+      <c r="Q106" s="128"/>
+      <c r="R106" s="129"/>
     </row>
     <row r="107" spans="8:18">
-      <c r="H107" s="139"/>
-      <c r="I107" s="140"/>
-      <c r="J107" s="140"/>
-      <c r="K107" s="140"/>
-      <c r="L107" s="140"/>
-      <c r="M107" s="140"/>
-      <c r="N107" s="140"/>
-      <c r="O107" s="140"/>
-      <c r="P107" s="140"/>
-      <c r="Q107" s="140"/>
-      <c r="R107" s="141"/>
+      <c r="H107" s="127"/>
+      <c r="I107" s="128"/>
+      <c r="J107" s="128"/>
+      <c r="K107" s="128"/>
+      <c r="L107" s="128"/>
+      <c r="M107" s="128"/>
+      <c r="N107" s="128"/>
+      <c r="O107" s="128"/>
+      <c r="P107" s="128"/>
+      <c r="Q107" s="128"/>
+      <c r="R107" s="129"/>
     </row>
     <row r="108" spans="8:18">
-      <c r="H108" s="139"/>
-      <c r="I108" s="140"/>
-      <c r="J108" s="140"/>
-      <c r="K108" s="140"/>
-      <c r="L108" s="140"/>
-      <c r="M108" s="140"/>
-      <c r="N108" s="140"/>
-      <c r="O108" s="140"/>
-      <c r="P108" s="140"/>
-      <c r="Q108" s="140"/>
-      <c r="R108" s="141"/>
+      <c r="H108" s="127"/>
+      <c r="I108" s="128"/>
+      <c r="J108" s="128"/>
+      <c r="K108" s="128"/>
+      <c r="L108" s="128"/>
+      <c r="M108" s="128"/>
+      <c r="N108" s="128"/>
+      <c r="O108" s="128"/>
+      <c r="P108" s="128"/>
+      <c r="Q108" s="128"/>
+      <c r="R108" s="129"/>
     </row>
     <row r="109" spans="8:18">
-      <c r="H109" s="139"/>
-      <c r="I109" s="140"/>
-      <c r="J109" s="140"/>
-      <c r="K109" s="140"/>
-      <c r="L109" s="140"/>
-      <c r="M109" s="140"/>
-      <c r="N109" s="140"/>
-      <c r="O109" s="140"/>
-      <c r="P109" s="140"/>
-      <c r="Q109" s="140"/>
-      <c r="R109" s="141"/>
+      <c r="H109" s="127"/>
+      <c r="I109" s="128"/>
+      <c r="J109" s="128"/>
+      <c r="K109" s="128"/>
+      <c r="L109" s="128"/>
+      <c r="M109" s="128"/>
+      <c r="N109" s="128"/>
+      <c r="O109" s="128"/>
+      <c r="P109" s="128"/>
+      <c r="Q109" s="128"/>
+      <c r="R109" s="129"/>
     </row>
     <row r="110" spans="8:18">
-      <c r="H110" s="139"/>
-      <c r="I110" s="140"/>
-      <c r="J110" s="140"/>
-      <c r="K110" s="140"/>
-      <c r="L110" s="140"/>
-      <c r="M110" s="140"/>
-      <c r="N110" s="140"/>
-      <c r="O110" s="140"/>
-      <c r="P110" s="140"/>
-      <c r="Q110" s="140"/>
-      <c r="R110" s="141"/>
+      <c r="H110" s="127"/>
+      <c r="I110" s="128"/>
+      <c r="J110" s="128"/>
+      <c r="K110" s="128"/>
+      <c r="L110" s="128"/>
+      <c r="M110" s="128"/>
+      <c r="N110" s="128"/>
+      <c r="O110" s="128"/>
+      <c r="P110" s="128"/>
+      <c r="Q110" s="128"/>
+      <c r="R110" s="129"/>
     </row>
     <row r="111" spans="8:18">
-      <c r="H111" s="139"/>
-      <c r="I111" s="140"/>
-      <c r="J111" s="140"/>
-      <c r="K111" s="140"/>
-      <c r="L111" s="140"/>
-      <c r="M111" s="140"/>
-      <c r="N111" s="140"/>
-      <c r="O111" s="140"/>
-      <c r="P111" s="140"/>
-      <c r="Q111" s="140"/>
-      <c r="R111" s="141"/>
+      <c r="H111" s="127"/>
+      <c r="I111" s="128"/>
+      <c r="J111" s="128"/>
+      <c r="K111" s="128"/>
+      <c r="L111" s="128"/>
+      <c r="M111" s="128"/>
+      <c r="N111" s="128"/>
+      <c r="O111" s="128"/>
+      <c r="P111" s="128"/>
+      <c r="Q111" s="128"/>
+      <c r="R111" s="129"/>
     </row>
     <row r="112" spans="8:18">
-      <c r="H112" s="139"/>
-      <c r="I112" s="140"/>
-      <c r="J112" s="140"/>
-      <c r="K112" s="140"/>
-      <c r="L112" s="140"/>
-      <c r="M112" s="140"/>
-      <c r="N112" s="140"/>
-      <c r="O112" s="140"/>
-      <c r="P112" s="140"/>
-      <c r="Q112" s="140"/>
-      <c r="R112" s="141"/>
+      <c r="H112" s="127"/>
+      <c r="I112" s="128"/>
+      <c r="J112" s="128"/>
+      <c r="K112" s="128"/>
+      <c r="L112" s="128"/>
+      <c r="M112" s="128"/>
+      <c r="N112" s="128"/>
+      <c r="O112" s="128"/>
+      <c r="P112" s="128"/>
+      <c r="Q112" s="128"/>
+      <c r="R112" s="129"/>
     </row>
     <row r="113" spans="8:18">
-      <c r="H113" s="139"/>
-      <c r="I113" s="140"/>
-      <c r="J113" s="140"/>
-      <c r="K113" s="140"/>
-      <c r="L113" s="140"/>
-      <c r="M113" s="140"/>
-      <c r="N113" s="140"/>
-      <c r="O113" s="140"/>
-      <c r="P113" s="140"/>
-      <c r="Q113" s="140"/>
-      <c r="R113" s="141"/>
+      <c r="H113" s="127"/>
+      <c r="I113" s="128"/>
+      <c r="J113" s="128"/>
+      <c r="K113" s="128"/>
+      <c r="L113" s="128"/>
+      <c r="M113" s="128"/>
+      <c r="N113" s="128"/>
+      <c r="O113" s="128"/>
+      <c r="P113" s="128"/>
+      <c r="Q113" s="128"/>
+      <c r="R113" s="129"/>
     </row>
     <row r="114" spans="8:18">
-      <c r="H114" s="139"/>
-      <c r="I114" s="140"/>
-      <c r="J114" s="140"/>
-      <c r="K114" s="140"/>
-      <c r="L114" s="140"/>
-      <c r="M114" s="140"/>
-      <c r="N114" s="140"/>
-      <c r="O114" s="140"/>
-      <c r="P114" s="140"/>
-      <c r="Q114" s="140"/>
-      <c r="R114" s="141"/>
+      <c r="H114" s="127"/>
+      <c r="I114" s="128"/>
+      <c r="J114" s="128"/>
+      <c r="K114" s="128"/>
+      <c r="L114" s="128"/>
+      <c r="M114" s="128"/>
+      <c r="N114" s="128"/>
+      <c r="O114" s="128"/>
+      <c r="P114" s="128"/>
+      <c r="Q114" s="128"/>
+      <c r="R114" s="129"/>
     </row>
     <row r="115" spans="8:18">
-      <c r="H115" s="139"/>
-      <c r="I115" s="140"/>
-      <c r="J115" s="140"/>
-      <c r="K115" s="140"/>
-      <c r="L115" s="140"/>
-      <c r="M115" s="140"/>
-      <c r="N115" s="140"/>
-      <c r="O115" s="140"/>
-      <c r="P115" s="140"/>
-      <c r="Q115" s="140"/>
-      <c r="R115" s="141"/>
+      <c r="H115" s="127"/>
+      <c r="I115" s="128"/>
+      <c r="J115" s="128"/>
+      <c r="K115" s="128"/>
+      <c r="L115" s="128"/>
+      <c r="M115" s="128"/>
+      <c r="N115" s="128"/>
+      <c r="O115" s="128"/>
+      <c r="P115" s="128"/>
+      <c r="Q115" s="128"/>
+      <c r="R115" s="129"/>
     </row>
     <row r="116" spans="8:18">
-      <c r="H116" s="139"/>
-      <c r="I116" s="140"/>
-      <c r="J116" s="140"/>
-      <c r="K116" s="140"/>
-      <c r="L116" s="140"/>
-      <c r="M116" s="140"/>
-      <c r="N116" s="140"/>
-      <c r="O116" s="140"/>
-      <c r="P116" s="140"/>
-      <c r="Q116" s="140"/>
-      <c r="R116" s="141"/>
+      <c r="H116" s="127"/>
+      <c r="I116" s="128"/>
+      <c r="J116" s="128"/>
+      <c r="K116" s="128"/>
+      <c r="L116" s="128"/>
+      <c r="M116" s="128"/>
+      <c r="N116" s="128"/>
+      <c r="O116" s="128"/>
+      <c r="P116" s="128"/>
+      <c r="Q116" s="128"/>
+      <c r="R116" s="129"/>
     </row>
     <row r="117" spans="8:18">
-      <c r="H117" s="139"/>
-      <c r="I117" s="140"/>
-      <c r="J117" s="140"/>
-      <c r="K117" s="140"/>
-      <c r="L117" s="140"/>
-      <c r="M117" s="140"/>
-      <c r="N117" s="140"/>
-      <c r="O117" s="140"/>
-      <c r="P117" s="140"/>
-      <c r="Q117" s="140"/>
-      <c r="R117" s="141"/>
+      <c r="H117" s="127"/>
+      <c r="I117" s="128"/>
+      <c r="J117" s="128"/>
+      <c r="K117" s="128"/>
+      <c r="L117" s="128"/>
+      <c r="M117" s="128"/>
+      <c r="N117" s="128"/>
+      <c r="O117" s="128"/>
+      <c r="P117" s="128"/>
+      <c r="Q117" s="128"/>
+      <c r="R117" s="129"/>
     </row>
     <row r="118" spans="8:18">
-      <c r="H118" s="142"/>
-      <c r="I118" s="143"/>
-      <c r="J118" s="143"/>
-      <c r="K118" s="143"/>
-      <c r="L118" s="143"/>
-      <c r="M118" s="143"/>
-      <c r="N118" s="143"/>
-      <c r="O118" s="143"/>
-      <c r="P118" s="143"/>
-      <c r="Q118" s="143"/>
-      <c r="R118" s="144"/>
+      <c r="H118" s="130"/>
+      <c r="I118" s="131"/>
+      <c r="J118" s="131"/>
+      <c r="K118" s="131"/>
+      <c r="L118" s="131"/>
+      <c r="M118" s="131"/>
+      <c r="N118" s="131"/>
+      <c r="O118" s="131"/>
+      <c r="P118" s="131"/>
+      <c r="Q118" s="131"/>
+      <c r="R118" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="U6:AF24"/>
+    <mergeCell ref="U5:AF5"/>
+    <mergeCell ref="H75:R75"/>
+    <mergeCell ref="H5:R5"/>
+    <mergeCell ref="H27:R27"/>
     <mergeCell ref="H76:R118"/>
     <mergeCell ref="H6:R24"/>
     <mergeCell ref="H28:R72"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="U6:AF24"/>
-    <mergeCell ref="U5:AF5"/>
-    <mergeCell ref="H75:R75"/>
-    <mergeCell ref="H5:R5"/>
-    <mergeCell ref="H27:R27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="1">
@@ -11611,32 +11693,32 @@
       <c r="G6" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="J6" s="136" t="s">
+      <c r="J6" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="138"/>
-      <c r="V6" s="136" t="s">
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="125"/>
+      <c r="R6" s="125"/>
+      <c r="S6" s="125"/>
+      <c r="T6" s="126"/>
+      <c r="V6" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="W6" s="137"/>
-      <c r="X6" s="137"/>
-      <c r="Y6" s="137"/>
-      <c r="Z6" s="137"/>
-      <c r="AA6" s="137"/>
-      <c r="AB6" s="137"/>
-      <c r="AC6" s="137"/>
-      <c r="AD6" s="137"/>
-      <c r="AE6" s="137"/>
-      <c r="AF6" s="138"/>
+      <c r="W6" s="125"/>
+      <c r="X6" s="125"/>
+      <c r="Y6" s="125"/>
+      <c r="Z6" s="125"/>
+      <c r="AA6" s="125"/>
+      <c r="AB6" s="125"/>
+      <c r="AC6" s="125"/>
+      <c r="AD6" s="125"/>
+      <c r="AE6" s="125"/>
+      <c r="AF6" s="126"/>
     </row>
     <row r="7" spans="3:32" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
@@ -11654,28 +11736,28 @@
       <c r="G7" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="J7" s="139"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="141"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="140"/>
-      <c r="X7" s="140"/>
-      <c r="Y7" s="140"/>
-      <c r="Z7" s="140"/>
-      <c r="AA7" s="140"/>
-      <c r="AB7" s="140"/>
-      <c r="AC7" s="140"/>
-      <c r="AD7" s="140"/>
-      <c r="AE7" s="140"/>
-      <c r="AF7" s="141"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="128"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="128"/>
+      <c r="S7" s="128"/>
+      <c r="T7" s="129"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="128"/>
+      <c r="X7" s="128"/>
+      <c r="Y7" s="128"/>
+      <c r="Z7" s="128"/>
+      <c r="AA7" s="128"/>
+      <c r="AB7" s="128"/>
+      <c r="AC7" s="128"/>
+      <c r="AD7" s="128"/>
+      <c r="AE7" s="128"/>
+      <c r="AF7" s="129"/>
     </row>
     <row r="8" spans="3:32" ht="13.5" customHeight="1">
       <c r="C8" s="26" t="s">
@@ -11693,28 +11775,28 @@
       <c r="G8" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="139"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="140"/>
-      <c r="T8" s="141"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="140"/>
-      <c r="X8" s="140"/>
-      <c r="Y8" s="140"/>
-      <c r="Z8" s="140"/>
-      <c r="AA8" s="140"/>
-      <c r="AB8" s="140"/>
-      <c r="AC8" s="140"/>
-      <c r="AD8" s="140"/>
-      <c r="AE8" s="140"/>
-      <c r="AF8" s="141"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="129"/>
+      <c r="V8" s="127"/>
+      <c r="W8" s="128"/>
+      <c r="X8" s="128"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="128"/>
+      <c r="AA8" s="128"/>
+      <c r="AB8" s="128"/>
+      <c r="AC8" s="128"/>
+      <c r="AD8" s="128"/>
+      <c r="AE8" s="128"/>
+      <c r="AF8" s="129"/>
     </row>
     <row r="9" spans="3:32" ht="13.5" customHeight="1">
       <c r="C9" s="26"/>
@@ -11722,28 +11804,28 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="27"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="140"/>
-      <c r="O9" s="140"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="140"/>
-      <c r="S9" s="140"/>
-      <c r="T9" s="141"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="140"/>
-      <c r="X9" s="140"/>
-      <c r="Y9" s="140"/>
-      <c r="Z9" s="140"/>
-      <c r="AA9" s="140"/>
-      <c r="AB9" s="140"/>
-      <c r="AC9" s="140"/>
-      <c r="AD9" s="140"/>
-      <c r="AE9" s="140"/>
-      <c r="AF9" s="141"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
+      <c r="O9" s="128"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
+      <c r="S9" s="128"/>
+      <c r="T9" s="129"/>
+      <c r="V9" s="127"/>
+      <c r="W9" s="128"/>
+      <c r="X9" s="128"/>
+      <c r="Y9" s="128"/>
+      <c r="Z9" s="128"/>
+      <c r="AA9" s="128"/>
+      <c r="AB9" s="128"/>
+      <c r="AC9" s="128"/>
+      <c r="AD9" s="128"/>
+      <c r="AE9" s="128"/>
+      <c r="AF9" s="129"/>
     </row>
     <row r="10" spans="3:32" ht="13.5" customHeight="1">
       <c r="C10" s="26"/>
@@ -11751,28 +11833,28 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="27"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="140"/>
-      <c r="T10" s="141"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="140"/>
-      <c r="X10" s="140"/>
-      <c r="Y10" s="140"/>
-      <c r="Z10" s="140"/>
-      <c r="AA10" s="140"/>
-      <c r="AB10" s="140"/>
-      <c r="AC10" s="140"/>
-      <c r="AD10" s="140"/>
-      <c r="AE10" s="140"/>
-      <c r="AF10" s="141"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
+      <c r="S10" s="128"/>
+      <c r="T10" s="129"/>
+      <c r="V10" s="127"/>
+      <c r="W10" s="128"/>
+      <c r="X10" s="128"/>
+      <c r="Y10" s="128"/>
+      <c r="Z10" s="128"/>
+      <c r="AA10" s="128"/>
+      <c r="AB10" s="128"/>
+      <c r="AC10" s="128"/>
+      <c r="AD10" s="128"/>
+      <c r="AE10" s="128"/>
+      <c r="AF10" s="129"/>
     </row>
     <row r="11" spans="3:32" ht="13.5" customHeight="1">
       <c r="C11" s="26"/>
@@ -11780,943 +11862,943 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="27"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="140"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="140"/>
-      <c r="R11" s="140"/>
-      <c r="S11" s="140"/>
-      <c r="T11" s="141"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="140"/>
-      <c r="X11" s="140"/>
-      <c r="Y11" s="140"/>
-      <c r="Z11" s="140"/>
-      <c r="AA11" s="140"/>
-      <c r="AB11" s="140"/>
-      <c r="AC11" s="140"/>
-      <c r="AD11" s="140"/>
-      <c r="AE11" s="140"/>
-      <c r="AF11" s="141"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="128"/>
+      <c r="T11" s="129"/>
+      <c r="V11" s="127"/>
+      <c r="W11" s="128"/>
+      <c r="X11" s="128"/>
+      <c r="Y11" s="128"/>
+      <c r="Z11" s="128"/>
+      <c r="AA11" s="128"/>
+      <c r="AB11" s="128"/>
+      <c r="AC11" s="128"/>
+      <c r="AD11" s="128"/>
+      <c r="AE11" s="128"/>
+      <c r="AF11" s="129"/>
     </row>
     <row r="12" spans="3:32" ht="13.5" customHeight="1">
       <c r="C12" s="26"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="J12" s="139"/>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="140"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-      <c r="R12" s="140"/>
-      <c r="S12" s="140"/>
-      <c r="T12" s="141"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="140"/>
-      <c r="X12" s="140"/>
-      <c r="Y12" s="140"/>
-      <c r="Z12" s="140"/>
-      <c r="AA12" s="140"/>
-      <c r="AB12" s="140"/>
-      <c r="AC12" s="140"/>
-      <c r="AD12" s="140"/>
-      <c r="AE12" s="140"/>
-      <c r="AF12" s="141"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="128"/>
+      <c r="P12" s="128"/>
+      <c r="Q12" s="128"/>
+      <c r="R12" s="128"/>
+      <c r="S12" s="128"/>
+      <c r="T12" s="129"/>
+      <c r="V12" s="127"/>
+      <c r="W12" s="128"/>
+      <c r="X12" s="128"/>
+      <c r="Y12" s="128"/>
+      <c r="Z12" s="128"/>
+      <c r="AA12" s="128"/>
+      <c r="AB12" s="128"/>
+      <c r="AC12" s="128"/>
+      <c r="AD12" s="128"/>
+      <c r="AE12" s="128"/>
+      <c r="AF12" s="129"/>
     </row>
     <row r="13" spans="3:32" ht="13.5" customHeight="1">
-      <c r="J13" s="139"/>
-      <c r="K13" s="140"/>
-      <c r="L13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="140"/>
-      <c r="O13" s="140"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140"/>
-      <c r="R13" s="140"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
-      <c r="X13" s="140"/>
-      <c r="Y13" s="140"/>
-      <c r="Z13" s="140"/>
-      <c r="AA13" s="140"/>
-      <c r="AB13" s="140"/>
-      <c r="AC13" s="140"/>
-      <c r="AD13" s="140"/>
-      <c r="AE13" s="140"/>
-      <c r="AF13" s="141"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="129"/>
+      <c r="V13" s="127"/>
+      <c r="W13" s="128"/>
+      <c r="X13" s="128"/>
+      <c r="Y13" s="128"/>
+      <c r="Z13" s="128"/>
+      <c r="AA13" s="128"/>
+      <c r="AB13" s="128"/>
+      <c r="AC13" s="128"/>
+      <c r="AD13" s="128"/>
+      <c r="AE13" s="128"/>
+      <c r="AF13" s="129"/>
     </row>
     <row r="14" spans="3:32" ht="13.5" customHeight="1">
-      <c r="J14" s="139"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="140"/>
-      <c r="N14" s="140"/>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="140"/>
-      <c r="T14" s="141"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="140"/>
-      <c r="X14" s="140"/>
-      <c r="Y14" s="140"/>
-      <c r="Z14" s="140"/>
-      <c r="AA14" s="140"/>
-      <c r="AB14" s="140"/>
-      <c r="AC14" s="140"/>
-      <c r="AD14" s="140"/>
-      <c r="AE14" s="140"/>
-      <c r="AF14" s="141"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="128"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="128"/>
+      <c r="P14" s="128"/>
+      <c r="Q14" s="128"/>
+      <c r="R14" s="128"/>
+      <c r="S14" s="128"/>
+      <c r="T14" s="129"/>
+      <c r="V14" s="127"/>
+      <c r="W14" s="128"/>
+      <c r="X14" s="128"/>
+      <c r="Y14" s="128"/>
+      <c r="Z14" s="128"/>
+      <c r="AA14" s="128"/>
+      <c r="AB14" s="128"/>
+      <c r="AC14" s="128"/>
+      <c r="AD14" s="128"/>
+      <c r="AE14" s="128"/>
+      <c r="AF14" s="129"/>
     </row>
     <row r="15" spans="3:32" ht="13.5" customHeight="1">
-      <c r="J15" s="139"/>
-      <c r="K15" s="140"/>
-      <c r="L15" s="140"/>
-      <c r="M15" s="140"/>
-      <c r="N15" s="140"/>
-      <c r="O15" s="140"/>
-      <c r="P15" s="140"/>
-      <c r="Q15" s="140"/>
-      <c r="R15" s="140"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="141"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="140"/>
-      <c r="X15" s="140"/>
-      <c r="Y15" s="140"/>
-      <c r="Z15" s="140"/>
-      <c r="AA15" s="140"/>
-      <c r="AB15" s="140"/>
-      <c r="AC15" s="140"/>
-      <c r="AD15" s="140"/>
-      <c r="AE15" s="140"/>
-      <c r="AF15" s="141"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="128"/>
+      <c r="O15" s="128"/>
+      <c r="P15" s="128"/>
+      <c r="Q15" s="128"/>
+      <c r="R15" s="128"/>
+      <c r="S15" s="128"/>
+      <c r="T15" s="129"/>
+      <c r="V15" s="127"/>
+      <c r="W15" s="128"/>
+      <c r="X15" s="128"/>
+      <c r="Y15" s="128"/>
+      <c r="Z15" s="128"/>
+      <c r="AA15" s="128"/>
+      <c r="AB15" s="128"/>
+      <c r="AC15" s="128"/>
+      <c r="AD15" s="128"/>
+      <c r="AE15" s="128"/>
+      <c r="AF15" s="129"/>
     </row>
     <row r="16" spans="3:32" ht="13.5" customHeight="1">
-      <c r="J16" s="139"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="140"/>
-      <c r="N16" s="140"/>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="140"/>
-      <c r="T16" s="141"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="140"/>
-      <c r="X16" s="140"/>
-      <c r="Y16" s="140"/>
-      <c r="Z16" s="140"/>
-      <c r="AA16" s="140"/>
-      <c r="AB16" s="140"/>
-      <c r="AC16" s="140"/>
-      <c r="AD16" s="140"/>
-      <c r="AE16" s="140"/>
-      <c r="AF16" s="141"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="128"/>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="128"/>
+      <c r="S16" s="128"/>
+      <c r="T16" s="129"/>
+      <c r="V16" s="127"/>
+      <c r="W16" s="128"/>
+      <c r="X16" s="128"/>
+      <c r="Y16" s="128"/>
+      <c r="Z16" s="128"/>
+      <c r="AA16" s="128"/>
+      <c r="AB16" s="128"/>
+      <c r="AC16" s="128"/>
+      <c r="AD16" s="128"/>
+      <c r="AE16" s="128"/>
+      <c r="AF16" s="129"/>
     </row>
     <row r="17" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J17" s="139"/>
-      <c r="K17" s="140"/>
-      <c r="L17" s="140"/>
-      <c r="M17" s="140"/>
-      <c r="N17" s="140"/>
-      <c r="O17" s="140"/>
-      <c r="P17" s="140"/>
-      <c r="Q17" s="140"/>
-      <c r="R17" s="140"/>
-      <c r="S17" s="140"/>
-      <c r="T17" s="141"/>
-      <c r="V17" s="139"/>
-      <c r="W17" s="140"/>
-      <c r="X17" s="140"/>
-      <c r="Y17" s="140"/>
-      <c r="Z17" s="140"/>
-      <c r="AA17" s="140"/>
-      <c r="AB17" s="140"/>
-      <c r="AC17" s="140"/>
-      <c r="AD17" s="140"/>
-      <c r="AE17" s="140"/>
-      <c r="AF17" s="141"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128"/>
+      <c r="Q17" s="128"/>
+      <c r="R17" s="128"/>
+      <c r="S17" s="128"/>
+      <c r="T17" s="129"/>
+      <c r="V17" s="127"/>
+      <c r="W17" s="128"/>
+      <c r="X17" s="128"/>
+      <c r="Y17" s="128"/>
+      <c r="Z17" s="128"/>
+      <c r="AA17" s="128"/>
+      <c r="AB17" s="128"/>
+      <c r="AC17" s="128"/>
+      <c r="AD17" s="128"/>
+      <c r="AE17" s="128"/>
+      <c r="AF17" s="129"/>
     </row>
     <row r="18" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J18" s="139"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140"/>
-      <c r="M18" s="140"/>
-      <c r="N18" s="140"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="140"/>
-      <c r="R18" s="140"/>
-      <c r="S18" s="140"/>
-      <c r="T18" s="141"/>
-      <c r="V18" s="139"/>
-      <c r="W18" s="140"/>
-      <c r="X18" s="140"/>
-      <c r="Y18" s="140"/>
-      <c r="Z18" s="140"/>
-      <c r="AA18" s="140"/>
-      <c r="AB18" s="140"/>
-      <c r="AC18" s="140"/>
-      <c r="AD18" s="140"/>
-      <c r="AE18" s="140"/>
-      <c r="AF18" s="141"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="128"/>
+      <c r="Q18" s="128"/>
+      <c r="R18" s="128"/>
+      <c r="S18" s="128"/>
+      <c r="T18" s="129"/>
+      <c r="V18" s="127"/>
+      <c r="W18" s="128"/>
+      <c r="X18" s="128"/>
+      <c r="Y18" s="128"/>
+      <c r="Z18" s="128"/>
+      <c r="AA18" s="128"/>
+      <c r="AB18" s="128"/>
+      <c r="AC18" s="128"/>
+      <c r="AD18" s="128"/>
+      <c r="AE18" s="128"/>
+      <c r="AF18" s="129"/>
     </row>
     <row r="19" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J19" s="139"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="140"/>
-      <c r="M19" s="140"/>
-      <c r="N19" s="140"/>
-      <c r="O19" s="140"/>
-      <c r="P19" s="140"/>
-      <c r="Q19" s="140"/>
-      <c r="R19" s="140"/>
-      <c r="S19" s="140"/>
-      <c r="T19" s="141"/>
-      <c r="V19" s="139"/>
-      <c r="W19" s="140"/>
-      <c r="X19" s="140"/>
-      <c r="Y19" s="140"/>
-      <c r="Z19" s="140"/>
-      <c r="AA19" s="140"/>
-      <c r="AB19" s="140"/>
-      <c r="AC19" s="140"/>
-      <c r="AD19" s="140"/>
-      <c r="AE19" s="140"/>
-      <c r="AF19" s="141"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="128"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="128"/>
+      <c r="S19" s="128"/>
+      <c r="T19" s="129"/>
+      <c r="V19" s="127"/>
+      <c r="W19" s="128"/>
+      <c r="X19" s="128"/>
+      <c r="Y19" s="128"/>
+      <c r="Z19" s="128"/>
+      <c r="AA19" s="128"/>
+      <c r="AB19" s="128"/>
+      <c r="AC19" s="128"/>
+      <c r="AD19" s="128"/>
+      <c r="AE19" s="128"/>
+      <c r="AF19" s="129"/>
     </row>
     <row r="20" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J20" s="139"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="140"/>
-      <c r="S20" s="140"/>
-      <c r="T20" s="141"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="140"/>
-      <c r="X20" s="140"/>
-      <c r="Y20" s="140"/>
-      <c r="Z20" s="140"/>
-      <c r="AA20" s="140"/>
-      <c r="AB20" s="140"/>
-      <c r="AC20" s="140"/>
-      <c r="AD20" s="140"/>
-      <c r="AE20" s="140"/>
-      <c r="AF20" s="141"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="128"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="128"/>
+      <c r="S20" s="128"/>
+      <c r="T20" s="129"/>
+      <c r="V20" s="127"/>
+      <c r="W20" s="128"/>
+      <c r="X20" s="128"/>
+      <c r="Y20" s="128"/>
+      <c r="Z20" s="128"/>
+      <c r="AA20" s="128"/>
+      <c r="AB20" s="128"/>
+      <c r="AC20" s="128"/>
+      <c r="AD20" s="128"/>
+      <c r="AE20" s="128"/>
+      <c r="AF20" s="129"/>
     </row>
     <row r="21" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J21" s="139"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="140"/>
-      <c r="O21" s="140"/>
-      <c r="P21" s="140"/>
-      <c r="Q21" s="140"/>
-      <c r="R21" s="140"/>
-      <c r="S21" s="140"/>
-      <c r="T21" s="141"/>
-      <c r="V21" s="139"/>
-      <c r="W21" s="140"/>
-      <c r="X21" s="140"/>
-      <c r="Y21" s="140"/>
-      <c r="Z21" s="140"/>
-      <c r="AA21" s="140"/>
-      <c r="AB21" s="140"/>
-      <c r="AC21" s="140"/>
-      <c r="AD21" s="140"/>
-      <c r="AE21" s="140"/>
-      <c r="AF21" s="141"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+      <c r="O21" s="128"/>
+      <c r="P21" s="128"/>
+      <c r="Q21" s="128"/>
+      <c r="R21" s="128"/>
+      <c r="S21" s="128"/>
+      <c r="T21" s="129"/>
+      <c r="V21" s="127"/>
+      <c r="W21" s="128"/>
+      <c r="X21" s="128"/>
+      <c r="Y21" s="128"/>
+      <c r="Z21" s="128"/>
+      <c r="AA21" s="128"/>
+      <c r="AB21" s="128"/>
+      <c r="AC21" s="128"/>
+      <c r="AD21" s="128"/>
+      <c r="AE21" s="128"/>
+      <c r="AF21" s="129"/>
     </row>
     <row r="22" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J22" s="139"/>
-      <c r="K22" s="140"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="140"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="140"/>
-      <c r="R22" s="140"/>
-      <c r="S22" s="140"/>
-      <c r="T22" s="141"/>
-      <c r="V22" s="139"/>
-      <c r="W22" s="140"/>
-      <c r="X22" s="140"/>
-      <c r="Y22" s="140"/>
-      <c r="Z22" s="140"/>
-      <c r="AA22" s="140"/>
-      <c r="AB22" s="140"/>
-      <c r="AC22" s="140"/>
-      <c r="AD22" s="140"/>
-      <c r="AE22" s="140"/>
-      <c r="AF22" s="141"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="128"/>
+      <c r="N22" s="128"/>
+      <c r="O22" s="128"/>
+      <c r="P22" s="128"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
+      <c r="S22" s="128"/>
+      <c r="T22" s="129"/>
+      <c r="V22" s="127"/>
+      <c r="W22" s="128"/>
+      <c r="X22" s="128"/>
+      <c r="Y22" s="128"/>
+      <c r="Z22" s="128"/>
+      <c r="AA22" s="128"/>
+      <c r="AB22" s="128"/>
+      <c r="AC22" s="128"/>
+      <c r="AD22" s="128"/>
+      <c r="AE22" s="128"/>
+      <c r="AF22" s="129"/>
     </row>
     <row r="23" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J23" s="139"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="140"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="140"/>
-      <c r="Q23" s="140"/>
-      <c r="R23" s="140"/>
-      <c r="S23" s="140"/>
-      <c r="T23" s="141"/>
-      <c r="V23" s="139"/>
-      <c r="W23" s="140"/>
-      <c r="X23" s="140"/>
-      <c r="Y23" s="140"/>
-      <c r="Z23" s="140"/>
-      <c r="AA23" s="140"/>
-      <c r="AB23" s="140"/>
-      <c r="AC23" s="140"/>
-      <c r="AD23" s="140"/>
-      <c r="AE23" s="140"/>
-      <c r="AF23" s="141"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="129"/>
+      <c r="V23" s="127"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
+      <c r="Z23" s="128"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="128"/>
+      <c r="AC23" s="128"/>
+      <c r="AD23" s="128"/>
+      <c r="AE23" s="128"/>
+      <c r="AF23" s="129"/>
     </row>
     <row r="24" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J24" s="139"/>
-      <c r="K24" s="140"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="140"/>
-      <c r="N24" s="140"/>
-      <c r="O24" s="140"/>
-      <c r="P24" s="140"/>
-      <c r="Q24" s="140"/>
-      <c r="R24" s="140"/>
-      <c r="S24" s="140"/>
-      <c r="T24" s="141"/>
-      <c r="V24" s="139"/>
-      <c r="W24" s="140"/>
-      <c r="X24" s="140"/>
-      <c r="Y24" s="140"/>
-      <c r="Z24" s="140"/>
-      <c r="AA24" s="140"/>
-      <c r="AB24" s="140"/>
-      <c r="AC24" s="140"/>
-      <c r="AD24" s="140"/>
-      <c r="AE24" s="140"/>
-      <c r="AF24" s="141"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="129"/>
+      <c r="V24" s="127"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
+      <c r="AD24" s="128"/>
+      <c r="AE24" s="128"/>
+      <c r="AF24" s="129"/>
     </row>
     <row r="25" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J25" s="139"/>
-      <c r="K25" s="140"/>
-      <c r="L25" s="140"/>
-      <c r="M25" s="140"/>
-      <c r="N25" s="140"/>
-      <c r="O25" s="140"/>
-      <c r="P25" s="140"/>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="140"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="141"/>
-      <c r="V25" s="139"/>
-      <c r="W25" s="140"/>
-      <c r="X25" s="140"/>
-      <c r="Y25" s="140"/>
-      <c r="Z25" s="140"/>
-      <c r="AA25" s="140"/>
-      <c r="AB25" s="140"/>
-      <c r="AC25" s="140"/>
-      <c r="AD25" s="140"/>
-      <c r="AE25" s="140"/>
-      <c r="AF25" s="141"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128"/>
+      <c r="S25" s="128"/>
+      <c r="T25" s="129"/>
+      <c r="V25" s="127"/>
+      <c r="W25" s="128"/>
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
+      <c r="Z25" s="128"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="128"/>
+      <c r="AC25" s="128"/>
+      <c r="AD25" s="128"/>
+      <c r="AE25" s="128"/>
+      <c r="AF25" s="129"/>
     </row>
     <row r="26" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J26" s="139"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="140"/>
-      <c r="N26" s="140"/>
-      <c r="O26" s="140"/>
-      <c r="P26" s="140"/>
-      <c r="Q26" s="140"/>
-      <c r="R26" s="140"/>
-      <c r="S26" s="140"/>
-      <c r="T26" s="141"/>
-      <c r="V26" s="139"/>
-      <c r="W26" s="140"/>
-      <c r="X26" s="140"/>
-      <c r="Y26" s="140"/>
-      <c r="Z26" s="140"/>
-      <c r="AA26" s="140"/>
-      <c r="AB26" s="140"/>
-      <c r="AC26" s="140"/>
-      <c r="AD26" s="140"/>
-      <c r="AE26" s="140"/>
-      <c r="AF26" s="141"/>
+      <c r="J26" s="127"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128"/>
+      <c r="Q26" s="128"/>
+      <c r="R26" s="128"/>
+      <c r="S26" s="128"/>
+      <c r="T26" s="129"/>
+      <c r="V26" s="127"/>
+      <c r="W26" s="128"/>
+      <c r="X26" s="128"/>
+      <c r="Y26" s="128"/>
+      <c r="Z26" s="128"/>
+      <c r="AA26" s="128"/>
+      <c r="AB26" s="128"/>
+      <c r="AC26" s="128"/>
+      <c r="AD26" s="128"/>
+      <c r="AE26" s="128"/>
+      <c r="AF26" s="129"/>
     </row>
     <row r="27" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J27" s="139"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="140"/>
-      <c r="M27" s="140"/>
-      <c r="N27" s="140"/>
-      <c r="O27" s="140"/>
-      <c r="P27" s="140"/>
-      <c r="Q27" s="140"/>
-      <c r="R27" s="140"/>
-      <c r="S27" s="140"/>
-      <c r="T27" s="141"/>
-      <c r="V27" s="139"/>
-      <c r="W27" s="140"/>
-      <c r="X27" s="140"/>
-      <c r="Y27" s="140"/>
-      <c r="Z27" s="140"/>
-      <c r="AA27" s="140"/>
-      <c r="AB27" s="140"/>
-      <c r="AC27" s="140"/>
-      <c r="AD27" s="140"/>
-      <c r="AE27" s="140"/>
-      <c r="AF27" s="141"/>
+      <c r="J27" s="127"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="128"/>
+      <c r="P27" s="128"/>
+      <c r="Q27" s="128"/>
+      <c r="R27" s="128"/>
+      <c r="S27" s="128"/>
+      <c r="T27" s="129"/>
+      <c r="V27" s="127"/>
+      <c r="W27" s="128"/>
+      <c r="X27" s="128"/>
+      <c r="Y27" s="128"/>
+      <c r="Z27" s="128"/>
+      <c r="AA27" s="128"/>
+      <c r="AB27" s="128"/>
+      <c r="AC27" s="128"/>
+      <c r="AD27" s="128"/>
+      <c r="AE27" s="128"/>
+      <c r="AF27" s="129"/>
     </row>
     <row r="28" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J28" s="139"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="140"/>
-      <c r="Q28" s="140"/>
-      <c r="R28" s="140"/>
-      <c r="S28" s="140"/>
-      <c r="T28" s="141"/>
-      <c r="V28" s="139"/>
-      <c r="W28" s="140"/>
-      <c r="X28" s="140"/>
-      <c r="Y28" s="140"/>
-      <c r="Z28" s="140"/>
-      <c r="AA28" s="140"/>
-      <c r="AB28" s="140"/>
-      <c r="AC28" s="140"/>
-      <c r="AD28" s="140"/>
-      <c r="AE28" s="140"/>
-      <c r="AF28" s="141"/>
+      <c r="J28" s="127"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="128"/>
+      <c r="Q28" s="128"/>
+      <c r="R28" s="128"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="129"/>
+      <c r="V28" s="127"/>
+      <c r="W28" s="128"/>
+      <c r="X28" s="128"/>
+      <c r="Y28" s="128"/>
+      <c r="Z28" s="128"/>
+      <c r="AA28" s="128"/>
+      <c r="AB28" s="128"/>
+      <c r="AC28" s="128"/>
+      <c r="AD28" s="128"/>
+      <c r="AE28" s="128"/>
+      <c r="AF28" s="129"/>
     </row>
     <row r="29" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J29" s="139"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="140"/>
-      <c r="N29" s="140"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="140"/>
-      <c r="Q29" s="140"/>
-      <c r="R29" s="140"/>
-      <c r="S29" s="140"/>
-      <c r="T29" s="141"/>
-      <c r="V29" s="139"/>
-      <c r="W29" s="140"/>
-      <c r="X29" s="140"/>
-      <c r="Y29" s="140"/>
-      <c r="Z29" s="140"/>
-      <c r="AA29" s="140"/>
-      <c r="AB29" s="140"/>
-      <c r="AC29" s="140"/>
-      <c r="AD29" s="140"/>
-      <c r="AE29" s="140"/>
-      <c r="AF29" s="141"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="128"/>
+      <c r="P29" s="128"/>
+      <c r="Q29" s="128"/>
+      <c r="R29" s="128"/>
+      <c r="S29" s="128"/>
+      <c r="T29" s="129"/>
+      <c r="V29" s="127"/>
+      <c r="W29" s="128"/>
+      <c r="X29" s="128"/>
+      <c r="Y29" s="128"/>
+      <c r="Z29" s="128"/>
+      <c r="AA29" s="128"/>
+      <c r="AB29" s="128"/>
+      <c r="AC29" s="128"/>
+      <c r="AD29" s="128"/>
+      <c r="AE29" s="128"/>
+      <c r="AF29" s="129"/>
     </row>
     <row r="30" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J30" s="139"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="140"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="140"/>
-      <c r="Q30" s="140"/>
-      <c r="R30" s="140"/>
-      <c r="S30" s="140"/>
-      <c r="T30" s="141"/>
-      <c r="V30" s="139"/>
-      <c r="W30" s="140"/>
-      <c r="X30" s="140"/>
-      <c r="Y30" s="140"/>
-      <c r="Z30" s="140"/>
-      <c r="AA30" s="140"/>
-      <c r="AB30" s="140"/>
-      <c r="AC30" s="140"/>
-      <c r="AD30" s="140"/>
-      <c r="AE30" s="140"/>
-      <c r="AF30" s="141"/>
+      <c r="J30" s="127"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="128"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="128"/>
+      <c r="P30" s="128"/>
+      <c r="Q30" s="128"/>
+      <c r="R30" s="128"/>
+      <c r="S30" s="128"/>
+      <c r="T30" s="129"/>
+      <c r="V30" s="127"/>
+      <c r="W30" s="128"/>
+      <c r="X30" s="128"/>
+      <c r="Y30" s="128"/>
+      <c r="Z30" s="128"/>
+      <c r="AA30" s="128"/>
+      <c r="AB30" s="128"/>
+      <c r="AC30" s="128"/>
+      <c r="AD30" s="128"/>
+      <c r="AE30" s="128"/>
+      <c r="AF30" s="129"/>
     </row>
     <row r="31" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J31" s="139"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="140"/>
-      <c r="N31" s="140"/>
-      <c r="O31" s="140"/>
-      <c r="P31" s="140"/>
-      <c r="Q31" s="140"/>
-      <c r="R31" s="140"/>
-      <c r="S31" s="140"/>
-      <c r="T31" s="141"/>
-      <c r="V31" s="139"/>
-      <c r="W31" s="140"/>
-      <c r="X31" s="140"/>
-      <c r="Y31" s="140"/>
-      <c r="Z31" s="140"/>
-      <c r="AA31" s="140"/>
-      <c r="AB31" s="140"/>
-      <c r="AC31" s="140"/>
-      <c r="AD31" s="140"/>
-      <c r="AE31" s="140"/>
-      <c r="AF31" s="141"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="128"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="128"/>
+      <c r="R31" s="128"/>
+      <c r="S31" s="128"/>
+      <c r="T31" s="129"/>
+      <c r="V31" s="127"/>
+      <c r="W31" s="128"/>
+      <c r="X31" s="128"/>
+      <c r="Y31" s="128"/>
+      <c r="Z31" s="128"/>
+      <c r="AA31" s="128"/>
+      <c r="AB31" s="128"/>
+      <c r="AC31" s="128"/>
+      <c r="AD31" s="128"/>
+      <c r="AE31" s="128"/>
+      <c r="AF31" s="129"/>
     </row>
     <row r="32" spans="10:32" ht="13.5" customHeight="1">
-      <c r="J32" s="139"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="140"/>
-      <c r="M32" s="140"/>
-      <c r="N32" s="140"/>
-      <c r="O32" s="140"/>
-      <c r="P32" s="140"/>
-      <c r="Q32" s="140"/>
-      <c r="R32" s="140"/>
-      <c r="S32" s="140"/>
-      <c r="T32" s="141"/>
-      <c r="V32" s="139"/>
-      <c r="W32" s="140"/>
-      <c r="X32" s="140"/>
-      <c r="Y32" s="140"/>
-      <c r="Z32" s="140"/>
-      <c r="AA32" s="140"/>
-      <c r="AB32" s="140"/>
-      <c r="AC32" s="140"/>
-      <c r="AD32" s="140"/>
-      <c r="AE32" s="140"/>
-      <c r="AF32" s="141"/>
+      <c r="J32" s="127"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="128"/>
+      <c r="M32" s="128"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="128"/>
+      <c r="P32" s="128"/>
+      <c r="Q32" s="128"/>
+      <c r="R32" s="128"/>
+      <c r="S32" s="128"/>
+      <c r="T32" s="129"/>
+      <c r="V32" s="127"/>
+      <c r="W32" s="128"/>
+      <c r="X32" s="128"/>
+      <c r="Y32" s="128"/>
+      <c r="Z32" s="128"/>
+      <c r="AA32" s="128"/>
+      <c r="AB32" s="128"/>
+      <c r="AC32" s="128"/>
+      <c r="AD32" s="128"/>
+      <c r="AE32" s="128"/>
+      <c r="AF32" s="129"/>
     </row>
     <row r="33" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J33" s="139"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="140"/>
-      <c r="M33" s="140"/>
-      <c r="N33" s="140"/>
-      <c r="O33" s="140"/>
-      <c r="P33" s="140"/>
-      <c r="Q33" s="140"/>
-      <c r="R33" s="140"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="141"/>
-      <c r="V33" s="139"/>
-      <c r="W33" s="140"/>
-      <c r="X33" s="140"/>
-      <c r="Y33" s="140"/>
-      <c r="Z33" s="140"/>
-      <c r="AA33" s="140"/>
-      <c r="AB33" s="140"/>
-      <c r="AC33" s="140"/>
-      <c r="AD33" s="140"/>
-      <c r="AE33" s="140"/>
-      <c r="AF33" s="141"/>
+      <c r="J33" s="127"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
+      <c r="M33" s="128"/>
+      <c r="N33" s="128"/>
+      <c r="O33" s="128"/>
+      <c r="P33" s="128"/>
+      <c r="Q33" s="128"/>
+      <c r="R33" s="128"/>
+      <c r="S33" s="128"/>
+      <c r="T33" s="129"/>
+      <c r="V33" s="127"/>
+      <c r="W33" s="128"/>
+      <c r="X33" s="128"/>
+      <c r="Y33" s="128"/>
+      <c r="Z33" s="128"/>
+      <c r="AA33" s="128"/>
+      <c r="AB33" s="128"/>
+      <c r="AC33" s="128"/>
+      <c r="AD33" s="128"/>
+      <c r="AE33" s="128"/>
+      <c r="AF33" s="129"/>
     </row>
     <row r="34" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J34" s="139"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="140"/>
-      <c r="P34" s="140"/>
-      <c r="Q34" s="140"/>
-      <c r="R34" s="140"/>
-      <c r="S34" s="140"/>
-      <c r="T34" s="141"/>
-      <c r="V34" s="139"/>
-      <c r="W34" s="140"/>
-      <c r="X34" s="140"/>
-      <c r="Y34" s="140"/>
-      <c r="Z34" s="140"/>
-      <c r="AA34" s="140"/>
-      <c r="AB34" s="140"/>
-      <c r="AC34" s="140"/>
-      <c r="AD34" s="140"/>
-      <c r="AE34" s="140"/>
-      <c r="AF34" s="141"/>
+      <c r="J34" s="127"/>
+      <c r="K34" s="128"/>
+      <c r="L34" s="128"/>
+      <c r="M34" s="128"/>
+      <c r="N34" s="128"/>
+      <c r="O34" s="128"/>
+      <c r="P34" s="128"/>
+      <c r="Q34" s="128"/>
+      <c r="R34" s="128"/>
+      <c r="S34" s="128"/>
+      <c r="T34" s="129"/>
+      <c r="V34" s="127"/>
+      <c r="W34" s="128"/>
+      <c r="X34" s="128"/>
+      <c r="Y34" s="128"/>
+      <c r="Z34" s="128"/>
+      <c r="AA34" s="128"/>
+      <c r="AB34" s="128"/>
+      <c r="AC34" s="128"/>
+      <c r="AD34" s="128"/>
+      <c r="AE34" s="128"/>
+      <c r="AF34" s="129"/>
     </row>
     <row r="35" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J35" s="139"/>
-      <c r="K35" s="140"/>
-      <c r="L35" s="140"/>
-      <c r="M35" s="140"/>
-      <c r="N35" s="140"/>
-      <c r="O35" s="140"/>
-      <c r="P35" s="140"/>
-      <c r="Q35" s="140"/>
-      <c r="R35" s="140"/>
-      <c r="S35" s="140"/>
-      <c r="T35" s="141"/>
-      <c r="V35" s="139"/>
-      <c r="W35" s="140"/>
-      <c r="X35" s="140"/>
-      <c r="Y35" s="140"/>
-      <c r="Z35" s="140"/>
-      <c r="AA35" s="140"/>
-      <c r="AB35" s="140"/>
-      <c r="AC35" s="140"/>
-      <c r="AD35" s="140"/>
-      <c r="AE35" s="140"/>
-      <c r="AF35" s="141"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="128"/>
+      <c r="L35" s="128"/>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
+      <c r="S35" s="128"/>
+      <c r="T35" s="129"/>
+      <c r="V35" s="127"/>
+      <c r="W35" s="128"/>
+      <c r="X35" s="128"/>
+      <c r="Y35" s="128"/>
+      <c r="Z35" s="128"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="128"/>
+      <c r="AC35" s="128"/>
+      <c r="AD35" s="128"/>
+      <c r="AE35" s="128"/>
+      <c r="AF35" s="129"/>
     </row>
     <row r="36" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J36" s="139"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="140"/>
-      <c r="M36" s="140"/>
-      <c r="N36" s="140"/>
-      <c r="O36" s="140"/>
-      <c r="P36" s="140"/>
-      <c r="Q36" s="140"/>
-      <c r="R36" s="140"/>
-      <c r="S36" s="140"/>
-      <c r="T36" s="141"/>
-      <c r="V36" s="139"/>
-      <c r="W36" s="140"/>
-      <c r="X36" s="140"/>
-      <c r="Y36" s="140"/>
-      <c r="Z36" s="140"/>
-      <c r="AA36" s="140"/>
-      <c r="AB36" s="140"/>
-      <c r="AC36" s="140"/>
-      <c r="AD36" s="140"/>
-      <c r="AE36" s="140"/>
-      <c r="AF36" s="141"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="128"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="128"/>
+      <c r="P36" s="128"/>
+      <c r="Q36" s="128"/>
+      <c r="R36" s="128"/>
+      <c r="S36" s="128"/>
+      <c r="T36" s="129"/>
+      <c r="V36" s="127"/>
+      <c r="W36" s="128"/>
+      <c r="X36" s="128"/>
+      <c r="Y36" s="128"/>
+      <c r="Z36" s="128"/>
+      <c r="AA36" s="128"/>
+      <c r="AB36" s="128"/>
+      <c r="AC36" s="128"/>
+      <c r="AD36" s="128"/>
+      <c r="AE36" s="128"/>
+      <c r="AF36" s="129"/>
     </row>
     <row r="37" spans="2:32" ht="13.5" customHeight="1">
       <c r="B37" s="7"/>
-      <c r="J37" s="139"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="140"/>
-      <c r="O37" s="140"/>
-      <c r="P37" s="140"/>
-      <c r="Q37" s="140"/>
-      <c r="R37" s="140"/>
-      <c r="S37" s="140"/>
-      <c r="T37" s="141"/>
-      <c r="V37" s="139"/>
-      <c r="W37" s="140"/>
-      <c r="X37" s="140"/>
-      <c r="Y37" s="140"/>
-      <c r="Z37" s="140"/>
-      <c r="AA37" s="140"/>
-      <c r="AB37" s="140"/>
-      <c r="AC37" s="140"/>
-      <c r="AD37" s="140"/>
-      <c r="AE37" s="140"/>
-      <c r="AF37" s="141"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="128"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="128"/>
+      <c r="O37" s="128"/>
+      <c r="P37" s="128"/>
+      <c r="Q37" s="128"/>
+      <c r="R37" s="128"/>
+      <c r="S37" s="128"/>
+      <c r="T37" s="129"/>
+      <c r="V37" s="127"/>
+      <c r="W37" s="128"/>
+      <c r="X37" s="128"/>
+      <c r="Y37" s="128"/>
+      <c r="Z37" s="128"/>
+      <c r="AA37" s="128"/>
+      <c r="AB37" s="128"/>
+      <c r="AC37" s="128"/>
+      <c r="AD37" s="128"/>
+      <c r="AE37" s="128"/>
+      <c r="AF37" s="129"/>
     </row>
     <row r="38" spans="2:32" ht="13.5" customHeight="1">
       <c r="B38" s="7"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="140"/>
-      <c r="M38" s="140"/>
-      <c r="N38" s="140"/>
-      <c r="O38" s="140"/>
-      <c r="P38" s="140"/>
-      <c r="Q38" s="140"/>
-      <c r="R38" s="140"/>
-      <c r="S38" s="140"/>
-      <c r="T38" s="141"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="140"/>
-      <c r="X38" s="140"/>
-      <c r="Y38" s="140"/>
-      <c r="Z38" s="140"/>
-      <c r="AA38" s="140"/>
-      <c r="AB38" s="140"/>
-      <c r="AC38" s="140"/>
-      <c r="AD38" s="140"/>
-      <c r="AE38" s="140"/>
-      <c r="AF38" s="141"/>
+      <c r="J38" s="127"/>
+      <c r="K38" s="128"/>
+      <c r="L38" s="128"/>
+      <c r="M38" s="128"/>
+      <c r="N38" s="128"/>
+      <c r="O38" s="128"/>
+      <c r="P38" s="128"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="128"/>
+      <c r="S38" s="128"/>
+      <c r="T38" s="129"/>
+      <c r="V38" s="127"/>
+      <c r="W38" s="128"/>
+      <c r="X38" s="128"/>
+      <c r="Y38" s="128"/>
+      <c r="Z38" s="128"/>
+      <c r="AA38" s="128"/>
+      <c r="AB38" s="128"/>
+      <c r="AC38" s="128"/>
+      <c r="AD38" s="128"/>
+      <c r="AE38" s="128"/>
+      <c r="AF38" s="129"/>
     </row>
     <row r="39" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J39" s="139"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="140"/>
-      <c r="M39" s="140"/>
-      <c r="N39" s="140"/>
-      <c r="O39" s="140"/>
-      <c r="P39" s="140"/>
-      <c r="Q39" s="140"/>
-      <c r="R39" s="140"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="141"/>
-      <c r="V39" s="139"/>
-      <c r="W39" s="140"/>
-      <c r="X39" s="140"/>
-      <c r="Y39" s="140"/>
-      <c r="Z39" s="140"/>
-      <c r="AA39" s="140"/>
-      <c r="AB39" s="140"/>
-      <c r="AC39" s="140"/>
-      <c r="AD39" s="140"/>
-      <c r="AE39" s="140"/>
-      <c r="AF39" s="141"/>
+      <c r="J39" s="127"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="128"/>
+      <c r="M39" s="128"/>
+      <c r="N39" s="128"/>
+      <c r="O39" s="128"/>
+      <c r="P39" s="128"/>
+      <c r="Q39" s="128"/>
+      <c r="R39" s="128"/>
+      <c r="S39" s="128"/>
+      <c r="T39" s="129"/>
+      <c r="V39" s="127"/>
+      <c r="W39" s="128"/>
+      <c r="X39" s="128"/>
+      <c r="Y39" s="128"/>
+      <c r="Z39" s="128"/>
+      <c r="AA39" s="128"/>
+      <c r="AB39" s="128"/>
+      <c r="AC39" s="128"/>
+      <c r="AD39" s="128"/>
+      <c r="AE39" s="128"/>
+      <c r="AF39" s="129"/>
     </row>
     <row r="40" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J40" s="139"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="140"/>
-      <c r="M40" s="140"/>
-      <c r="N40" s="140"/>
-      <c r="O40" s="140"/>
-      <c r="P40" s="140"/>
-      <c r="Q40" s="140"/>
-      <c r="R40" s="140"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
-      <c r="V40" s="139"/>
-      <c r="W40" s="140"/>
-      <c r="X40" s="140"/>
-      <c r="Y40" s="140"/>
-      <c r="Z40" s="140"/>
-      <c r="AA40" s="140"/>
-      <c r="AB40" s="140"/>
-      <c r="AC40" s="140"/>
-      <c r="AD40" s="140"/>
-      <c r="AE40" s="140"/>
-      <c r="AF40" s="141"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
+      <c r="O40" s="128"/>
+      <c r="P40" s="128"/>
+      <c r="Q40" s="128"/>
+      <c r="R40" s="128"/>
+      <c r="S40" s="128"/>
+      <c r="T40" s="129"/>
+      <c r="V40" s="127"/>
+      <c r="W40" s="128"/>
+      <c r="X40" s="128"/>
+      <c r="Y40" s="128"/>
+      <c r="Z40" s="128"/>
+      <c r="AA40" s="128"/>
+      <c r="AB40" s="128"/>
+      <c r="AC40" s="128"/>
+      <c r="AD40" s="128"/>
+      <c r="AE40" s="128"/>
+      <c r="AF40" s="129"/>
     </row>
     <row r="41" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J41" s="139"/>
-      <c r="K41" s="140"/>
-      <c r="L41" s="140"/>
-      <c r="M41" s="140"/>
-      <c r="N41" s="140"/>
-      <c r="O41" s="140"/>
-      <c r="P41" s="140"/>
-      <c r="Q41" s="140"/>
-      <c r="R41" s="140"/>
-      <c r="S41" s="140"/>
-      <c r="T41" s="141"/>
-      <c r="V41" s="139"/>
-      <c r="W41" s="140"/>
-      <c r="X41" s="140"/>
-      <c r="Y41" s="140"/>
-      <c r="Z41" s="140"/>
-      <c r="AA41" s="140"/>
-      <c r="AB41" s="140"/>
-      <c r="AC41" s="140"/>
-      <c r="AD41" s="140"/>
-      <c r="AE41" s="140"/>
-      <c r="AF41" s="141"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="128"/>
+      <c r="L41" s="128"/>
+      <c r="M41" s="128"/>
+      <c r="N41" s="128"/>
+      <c r="O41" s="128"/>
+      <c r="P41" s="128"/>
+      <c r="Q41" s="128"/>
+      <c r="R41" s="128"/>
+      <c r="S41" s="128"/>
+      <c r="T41" s="129"/>
+      <c r="V41" s="127"/>
+      <c r="W41" s="128"/>
+      <c r="X41" s="128"/>
+      <c r="Y41" s="128"/>
+      <c r="Z41" s="128"/>
+      <c r="AA41" s="128"/>
+      <c r="AB41" s="128"/>
+      <c r="AC41" s="128"/>
+      <c r="AD41" s="128"/>
+      <c r="AE41" s="128"/>
+      <c r="AF41" s="129"/>
     </row>
     <row r="42" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J42" s="139"/>
-      <c r="K42" s="140"/>
-      <c r="L42" s="140"/>
-      <c r="M42" s="140"/>
-      <c r="N42" s="140"/>
-      <c r="O42" s="140"/>
-      <c r="P42" s="140"/>
-      <c r="Q42" s="140"/>
-      <c r="R42" s="140"/>
-      <c r="S42" s="140"/>
-      <c r="T42" s="141"/>
-      <c r="V42" s="139"/>
-      <c r="W42" s="140"/>
-      <c r="X42" s="140"/>
-      <c r="Y42" s="140"/>
-      <c r="Z42" s="140"/>
-      <c r="AA42" s="140"/>
-      <c r="AB42" s="140"/>
-      <c r="AC42" s="140"/>
-      <c r="AD42" s="140"/>
-      <c r="AE42" s="140"/>
-      <c r="AF42" s="141"/>
+      <c r="J42" s="127"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
+      <c r="M42" s="128"/>
+      <c r="N42" s="128"/>
+      <c r="O42" s="128"/>
+      <c r="P42" s="128"/>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
+      <c r="S42" s="128"/>
+      <c r="T42" s="129"/>
+      <c r="V42" s="127"/>
+      <c r="W42" s="128"/>
+      <c r="X42" s="128"/>
+      <c r="Y42" s="128"/>
+      <c r="Z42" s="128"/>
+      <c r="AA42" s="128"/>
+      <c r="AB42" s="128"/>
+      <c r="AC42" s="128"/>
+      <c r="AD42" s="128"/>
+      <c r="AE42" s="128"/>
+      <c r="AF42" s="129"/>
     </row>
     <row r="43" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J43" s="139"/>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
-      <c r="M43" s="140"/>
-      <c r="N43" s="140"/>
-      <c r="O43" s="140"/>
-      <c r="P43" s="140"/>
-      <c r="Q43" s="140"/>
-      <c r="R43" s="140"/>
-      <c r="S43" s="140"/>
-      <c r="T43" s="141"/>
-      <c r="V43" s="139"/>
-      <c r="W43" s="140"/>
-      <c r="X43" s="140"/>
-      <c r="Y43" s="140"/>
-      <c r="Z43" s="140"/>
-      <c r="AA43" s="140"/>
-      <c r="AB43" s="140"/>
-      <c r="AC43" s="140"/>
-      <c r="AD43" s="140"/>
-      <c r="AE43" s="140"/>
-      <c r="AF43" s="141"/>
+      <c r="J43" s="127"/>
+      <c r="K43" s="128"/>
+      <c r="L43" s="128"/>
+      <c r="M43" s="128"/>
+      <c r="N43" s="128"/>
+      <c r="O43" s="128"/>
+      <c r="P43" s="128"/>
+      <c r="Q43" s="128"/>
+      <c r="R43" s="128"/>
+      <c r="S43" s="128"/>
+      <c r="T43" s="129"/>
+      <c r="V43" s="127"/>
+      <c r="W43" s="128"/>
+      <c r="X43" s="128"/>
+      <c r="Y43" s="128"/>
+      <c r="Z43" s="128"/>
+      <c r="AA43" s="128"/>
+      <c r="AB43" s="128"/>
+      <c r="AC43" s="128"/>
+      <c r="AD43" s="128"/>
+      <c r="AE43" s="128"/>
+      <c r="AF43" s="129"/>
     </row>
     <row r="44" spans="2:32" ht="13.5" customHeight="1">
-      <c r="J44" s="142"/>
-      <c r="K44" s="143"/>
-      <c r="L44" s="143"/>
-      <c r="M44" s="143"/>
-      <c r="N44" s="143"/>
-      <c r="O44" s="143"/>
-      <c r="P44" s="143"/>
-      <c r="Q44" s="143"/>
-      <c r="R44" s="143"/>
-      <c r="S44" s="143"/>
-      <c r="T44" s="144"/>
-      <c r="V44" s="139"/>
-      <c r="W44" s="140"/>
-      <c r="X44" s="140"/>
-      <c r="Y44" s="140"/>
-      <c r="Z44" s="140"/>
-      <c r="AA44" s="140"/>
-      <c r="AB44" s="140"/>
-      <c r="AC44" s="140"/>
-      <c r="AD44" s="140"/>
-      <c r="AE44" s="140"/>
-      <c r="AF44" s="141"/>
+      <c r="J44" s="130"/>
+      <c r="K44" s="131"/>
+      <c r="L44" s="131"/>
+      <c r="M44" s="131"/>
+      <c r="N44" s="131"/>
+      <c r="O44" s="131"/>
+      <c r="P44" s="131"/>
+      <c r="Q44" s="131"/>
+      <c r="R44" s="131"/>
+      <c r="S44" s="131"/>
+      <c r="T44" s="132"/>
+      <c r="V44" s="127"/>
+      <c r="W44" s="128"/>
+      <c r="X44" s="128"/>
+      <c r="Y44" s="128"/>
+      <c r="Z44" s="128"/>
+      <c r="AA44" s="128"/>
+      <c r="AB44" s="128"/>
+      <c r="AC44" s="128"/>
+      <c r="AD44" s="128"/>
+      <c r="AE44" s="128"/>
+      <c r="AF44" s="129"/>
     </row>
     <row r="45" spans="2:32">
-      <c r="V45" s="139"/>
-      <c r="W45" s="140"/>
-      <c r="X45" s="140"/>
-      <c r="Y45" s="140"/>
-      <c r="Z45" s="140"/>
-      <c r="AA45" s="140"/>
-      <c r="AB45" s="140"/>
-      <c r="AC45" s="140"/>
-      <c r="AD45" s="140"/>
-      <c r="AE45" s="140"/>
-      <c r="AF45" s="141"/>
+      <c r="V45" s="127"/>
+      <c r="W45" s="128"/>
+      <c r="X45" s="128"/>
+      <c r="Y45" s="128"/>
+      <c r="Z45" s="128"/>
+      <c r="AA45" s="128"/>
+      <c r="AB45" s="128"/>
+      <c r="AC45" s="128"/>
+      <c r="AD45" s="128"/>
+      <c r="AE45" s="128"/>
+      <c r="AF45" s="129"/>
     </row>
     <row r="46" spans="2:32">
-      <c r="V46" s="139"/>
-      <c r="W46" s="140"/>
-      <c r="X46" s="140"/>
-      <c r="Y46" s="140"/>
-      <c r="Z46" s="140"/>
-      <c r="AA46" s="140"/>
-      <c r="AB46" s="140"/>
-      <c r="AC46" s="140"/>
-      <c r="AD46" s="140"/>
-      <c r="AE46" s="140"/>
-      <c r="AF46" s="141"/>
+      <c r="V46" s="127"/>
+      <c r="W46" s="128"/>
+      <c r="X46" s="128"/>
+      <c r="Y46" s="128"/>
+      <c r="Z46" s="128"/>
+      <c r="AA46" s="128"/>
+      <c r="AB46" s="128"/>
+      <c r="AC46" s="128"/>
+      <c r="AD46" s="128"/>
+      <c r="AE46" s="128"/>
+      <c r="AF46" s="129"/>
     </row>
     <row r="47" spans="2:32">
-      <c r="V47" s="139"/>
-      <c r="W47" s="140"/>
-      <c r="X47" s="140"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
-      <c r="AA47" s="140"/>
-      <c r="AB47" s="140"/>
-      <c r="AC47" s="140"/>
-      <c r="AD47" s="140"/>
-      <c r="AE47" s="140"/>
-      <c r="AF47" s="141"/>
+      <c r="V47" s="127"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="128"/>
+      <c r="Y47" s="128"/>
+      <c r="Z47" s="128"/>
+      <c r="AA47" s="128"/>
+      <c r="AB47" s="128"/>
+      <c r="AC47" s="128"/>
+      <c r="AD47" s="128"/>
+      <c r="AE47" s="128"/>
+      <c r="AF47" s="129"/>
     </row>
     <row r="48" spans="2:32">
-      <c r="V48" s="139"/>
-      <c r="W48" s="140"/>
-      <c r="X48" s="140"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="140"/>
-      <c r="AB48" s="140"/>
-      <c r="AC48" s="140"/>
-      <c r="AD48" s="140"/>
-      <c r="AE48" s="140"/>
-      <c r="AF48" s="141"/>
+      <c r="V48" s="127"/>
+      <c r="W48" s="128"/>
+      <c r="X48" s="128"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
+      <c r="AA48" s="128"/>
+      <c r="AB48" s="128"/>
+      <c r="AC48" s="128"/>
+      <c r="AD48" s="128"/>
+      <c r="AE48" s="128"/>
+      <c r="AF48" s="129"/>
     </row>
     <row r="49" spans="22:32">
-      <c r="V49" s="139"/>
-      <c r="W49" s="140"/>
-      <c r="X49" s="140"/>
-      <c r="Y49" s="140"/>
-      <c r="Z49" s="140"/>
-      <c r="AA49" s="140"/>
-      <c r="AB49" s="140"/>
-      <c r="AC49" s="140"/>
-      <c r="AD49" s="140"/>
-      <c r="AE49" s="140"/>
-      <c r="AF49" s="141"/>
+      <c r="V49" s="127"/>
+      <c r="W49" s="128"/>
+      <c r="X49" s="128"/>
+      <c r="Y49" s="128"/>
+      <c r="Z49" s="128"/>
+      <c r="AA49" s="128"/>
+      <c r="AB49" s="128"/>
+      <c r="AC49" s="128"/>
+      <c r="AD49" s="128"/>
+      <c r="AE49" s="128"/>
+      <c r="AF49" s="129"/>
     </row>
     <row r="50" spans="22:32">
-      <c r="V50" s="139"/>
-      <c r="W50" s="140"/>
-      <c r="X50" s="140"/>
-      <c r="Y50" s="140"/>
-      <c r="Z50" s="140"/>
-      <c r="AA50" s="140"/>
-      <c r="AB50" s="140"/>
-      <c r="AC50" s="140"/>
-      <c r="AD50" s="140"/>
-      <c r="AE50" s="140"/>
-      <c r="AF50" s="141"/>
+      <c r="V50" s="127"/>
+      <c r="W50" s="128"/>
+      <c r="X50" s="128"/>
+      <c r="Y50" s="128"/>
+      <c r="Z50" s="128"/>
+      <c r="AA50" s="128"/>
+      <c r="AB50" s="128"/>
+      <c r="AC50" s="128"/>
+      <c r="AD50" s="128"/>
+      <c r="AE50" s="128"/>
+      <c r="AF50" s="129"/>
     </row>
     <row r="51" spans="22:32">
-      <c r="V51" s="139"/>
-      <c r="W51" s="140"/>
-      <c r="X51" s="140"/>
-      <c r="Y51" s="140"/>
-      <c r="Z51" s="140"/>
-      <c r="AA51" s="140"/>
-      <c r="AB51" s="140"/>
-      <c r="AC51" s="140"/>
-      <c r="AD51" s="140"/>
-      <c r="AE51" s="140"/>
-      <c r="AF51" s="141"/>
+      <c r="V51" s="127"/>
+      <c r="W51" s="128"/>
+      <c r="X51" s="128"/>
+      <c r="Y51" s="128"/>
+      <c r="Z51" s="128"/>
+      <c r="AA51" s="128"/>
+      <c r="AB51" s="128"/>
+      <c r="AC51" s="128"/>
+      <c r="AD51" s="128"/>
+      <c r="AE51" s="128"/>
+      <c r="AF51" s="129"/>
     </row>
     <row r="52" spans="22:32">
-      <c r="V52" s="139"/>
-      <c r="W52" s="140"/>
-      <c r="X52" s="140"/>
-      <c r="Y52" s="140"/>
-      <c r="Z52" s="140"/>
-      <c r="AA52" s="140"/>
-      <c r="AB52" s="140"/>
-      <c r="AC52" s="140"/>
-      <c r="AD52" s="140"/>
-      <c r="AE52" s="140"/>
-      <c r="AF52" s="141"/>
+      <c r="V52" s="127"/>
+      <c r="W52" s="128"/>
+      <c r="X52" s="128"/>
+      <c r="Y52" s="128"/>
+      <c r="Z52" s="128"/>
+      <c r="AA52" s="128"/>
+      <c r="AB52" s="128"/>
+      <c r="AC52" s="128"/>
+      <c r="AD52" s="128"/>
+      <c r="AE52" s="128"/>
+      <c r="AF52" s="129"/>
     </row>
     <row r="53" spans="22:32">
-      <c r="V53" s="142"/>
-      <c r="W53" s="143"/>
-      <c r="X53" s="143"/>
-      <c r="Y53" s="143"/>
-      <c r="Z53" s="143"/>
-      <c r="AA53" s="143"/>
-      <c r="AB53" s="143"/>
-      <c r="AC53" s="143"/>
-      <c r="AD53" s="143"/>
-      <c r="AE53" s="143"/>
-      <c r="AF53" s="144"/>
+      <c r="V53" s="130"/>
+      <c r="W53" s="131"/>
+      <c r="X53" s="131"/>
+      <c r="Y53" s="131"/>
+      <c r="Z53" s="131"/>
+      <c r="AA53" s="131"/>
+      <c r="AB53" s="131"/>
+      <c r="AC53" s="131"/>
+      <c r="AD53" s="131"/>
+      <c r="AE53" s="131"/>
+      <c r="AF53" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -13200,11 +13282,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAAD788-0DFB-41D5-9FAA-1B18A47AD396}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE76D29-8D9B-478E-9216-A1F6F774227C}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="C1:T53"/>
+  <dimension ref="C1:T55"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -13217,814 +13299,840 @@
     <col min="9" max="9" width="3.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:20">
+    <row r="1" spans="3:20" ht="17.25" thickBot="1">
       <c r="C1"/>
       <c r="G1"/>
     </row>
     <row r="2" spans="3:20" ht="17.25" thickBot="1">
-      <c r="C2"/>
-      <c r="G2"/>
-    </row>
-    <row r="3" spans="3:20" ht="19.5" customHeight="1" thickBot="1">
-      <c r="C3" s="116" t="s">
+      <c r="C2" s="216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="217">
+        <f>[1]Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="218"/>
+    </row>
+    <row r="3" spans="3:20" ht="17.25" thickBot="1">
+      <c r="C3" s="219" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="220">
+        <f>[1]Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="220"/>
+      <c r="F3" s="220"/>
+      <c r="G3" s="221"/>
+    </row>
+    <row r="4" spans="3:20" ht="17.25" thickBot="1">
+      <c r="C4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="3:20" ht="19.5" customHeight="1" thickBot="1">
+      <c r="C5" s="116" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118"/>
-      <c r="J3" s="147" t="s">
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="118"/>
+      <c r="J5" s="147" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="148"/>
-      <c r="L3" s="148"/>
-      <c r="M3" s="148"/>
-      <c r="N3" s="148"/>
-      <c r="O3" s="148"/>
-      <c r="P3" s="148"/>
-      <c r="Q3" s="148"/>
-      <c r="R3" s="148"/>
-      <c r="S3" s="148"/>
-      <c r="T3" s="149"/>
-    </row>
-    <row r="4" spans="3:20" ht="13.5" customHeight="1">
-      <c r="C4" s="77" t="s">
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="148"/>
+      <c r="R5" s="148"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="149"/>
+    </row>
+    <row r="6" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C6" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E6" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F6" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G6" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J6" s="222" t="s">
         <v>325</v>
       </c>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-    </row>
-    <row r="5" spans="3:20">
-      <c r="C5" s="78">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="217" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="217" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="218" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="219"/>
-      <c r="K5" s="219"/>
-      <c r="L5" s="219"/>
-      <c r="M5" s="219"/>
-      <c r="N5" s="219"/>
-      <c r="O5" s="219"/>
-      <c r="P5" s="219"/>
-      <c r="Q5" s="219"/>
-      <c r="R5" s="219"/>
-      <c r="S5" s="219"/>
-      <c r="T5" s="219"/>
-    </row>
-    <row r="6" spans="3:20">
-      <c r="C6" s="78">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="217" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="217" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="218" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="219"/>
-      <c r="K6" s="219"/>
-      <c r="L6" s="219"/>
-      <c r="M6" s="219"/>
-      <c r="N6" s="219"/>
-      <c r="O6" s="219"/>
-      <c r="P6" s="219"/>
-      <c r="Q6" s="219"/>
-      <c r="R6" s="219"/>
-      <c r="S6" s="219"/>
-      <c r="T6" s="219"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="223"/>
+      <c r="O6" s="223"/>
+      <c r="P6" s="223"/>
+      <c r="Q6" s="223"/>
+      <c r="R6" s="223"/>
+      <c r="S6" s="223"/>
+      <c r="T6" s="224"/>
     </row>
     <row r="7" spans="3:20">
       <c r="C7" s="78">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="217"/>
-      <c r="F7" s="217"/>
-      <c r="G7" s="218"/>
-      <c r="J7" s="219"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="219"/>
-      <c r="M7" s="219"/>
-      <c r="N7" s="219"/>
-      <c r="O7" s="219"/>
-      <c r="P7" s="219"/>
-      <c r="Q7" s="219"/>
-      <c r="R7" s="219"/>
-      <c r="S7" s="219"/>
-      <c r="T7" s="219"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="225" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="225" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="226" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="227"/>
+      <c r="K7" s="228"/>
+      <c r="L7" s="228"/>
+      <c r="M7" s="228"/>
+      <c r="N7" s="228"/>
+      <c r="O7" s="228"/>
+      <c r="P7" s="228"/>
+      <c r="Q7" s="228"/>
+      <c r="R7" s="228"/>
+      <c r="S7" s="228"/>
+      <c r="T7" s="229"/>
     </row>
     <row r="8" spans="3:20">
       <c r="C8" s="78">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="225" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="225" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="226" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="227"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="228"/>
+      <c r="Q8" s="228"/>
+      <c r="R8" s="228"/>
+      <c r="S8" s="228"/>
+      <c r="T8" s="229"/>
+    </row>
+    <row r="9" spans="3:20">
+      <c r="C9" s="78">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="225"/>
+      <c r="F9" s="225"/>
+      <c r="G9" s="226"/>
+      <c r="J9" s="227"/>
+      <c r="K9" s="228"/>
+      <c r="L9" s="228"/>
+      <c r="M9" s="228"/>
+      <c r="N9" s="228"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="228"/>
+      <c r="Q9" s="228"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+      <c r="T9" s="229"/>
+    </row>
+    <row r="10" spans="3:20">
+      <c r="C10" s="78">
         <v>4</v>
       </c>
-      <c r="D8" s="217"/>
-      <c r="E8" s="217"/>
-      <c r="F8" s="217"/>
-      <c r="G8" s="27"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="219"/>
-      <c r="Q8" s="219"/>
-      <c r="R8" s="219"/>
-      <c r="S8" s="219"/>
-      <c r="T8" s="219"/>
-    </row>
-    <row r="9" spans="3:20" ht="13.5" customHeight="1">
-      <c r="C9" s="78">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="27"/>
-      <c r="J9" s="219"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="219"/>
-      <c r="N9" s="219"/>
-      <c r="O9" s="219"/>
-      <c r="P9" s="219"/>
-      <c r="Q9" s="219"/>
-      <c r="R9" s="219"/>
-      <c r="S9" s="219"/>
-      <c r="T9" s="219"/>
-    </row>
-    <row r="10" spans="3:20" ht="13.5" customHeight="1">
-      <c r="C10" s="78">
-        <v>6</v>
-      </c>
-      <c r="J10" s="219"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="219"/>
-      <c r="N10" s="219"/>
-      <c r="O10" s="219"/>
-      <c r="P10" s="219"/>
-      <c r="Q10" s="219"/>
-      <c r="R10" s="219"/>
-      <c r="S10" s="219"/>
-      <c r="T10" s="219"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="27"/>
+      <c r="J10" s="227"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="228"/>
+      <c r="M10" s="228"/>
+      <c r="N10" s="228"/>
+      <c r="O10" s="228"/>
+      <c r="P10" s="228"/>
+      <c r="Q10" s="228"/>
+      <c r="R10" s="228"/>
+      <c r="S10" s="228"/>
+      <c r="T10" s="229"/>
     </row>
     <row r="11" spans="3:20" ht="13.5" customHeight="1">
       <c r="C11" s="78">
-        <v>7</v>
-      </c>
-      <c r="J11" s="219"/>
-      <c r="K11" s="219"/>
-      <c r="L11" s="219"/>
-      <c r="M11" s="219"/>
-      <c r="N11" s="219"/>
-      <c r="O11" s="219"/>
-      <c r="P11" s="219"/>
-      <c r="Q11" s="219"/>
-      <c r="R11" s="219"/>
-      <c r="S11" s="219"/>
-      <c r="T11" s="219"/>
+        <v>5</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="27"/>
+      <c r="J11" s="227"/>
+      <c r="K11" s="228"/>
+      <c r="L11" s="228"/>
+      <c r="M11" s="228"/>
+      <c r="N11" s="228"/>
+      <c r="O11" s="228"/>
+      <c r="P11" s="228"/>
+      <c r="Q11" s="228"/>
+      <c r="R11" s="228"/>
+      <c r="S11" s="228"/>
+      <c r="T11" s="229"/>
     </row>
     <row r="12" spans="3:20" ht="13.5" customHeight="1">
       <c r="C12" s="78">
-        <v>8</v>
-      </c>
-      <c r="J12" s="219"/>
-      <c r="K12" s="219"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
-      <c r="O12" s="219"/>
-      <c r="P12" s="219"/>
-      <c r="Q12" s="219"/>
-      <c r="R12" s="219"/>
-      <c r="S12" s="219"/>
-      <c r="T12" s="219"/>
+        <v>6</v>
+      </c>
+      <c r="J12" s="227"/>
+      <c r="K12" s="228"/>
+      <c r="L12" s="228"/>
+      <c r="M12" s="228"/>
+      <c r="N12" s="228"/>
+      <c r="O12" s="228"/>
+      <c r="P12" s="228"/>
+      <c r="Q12" s="228"/>
+      <c r="R12" s="228"/>
+      <c r="S12" s="228"/>
+      <c r="T12" s="229"/>
     </row>
     <row r="13" spans="3:20" ht="13.5" customHeight="1">
       <c r="C13" s="78">
-        <v>9</v>
-      </c>
-      <c r="J13" s="219"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="219"/>
-      <c r="Q13" s="219"/>
-      <c r="R13" s="219"/>
-      <c r="S13" s="219"/>
-      <c r="T13" s="219"/>
+        <v>7</v>
+      </c>
+      <c r="J13" s="227"/>
+      <c r="K13" s="228"/>
+      <c r="L13" s="228"/>
+      <c r="M13" s="228"/>
+      <c r="N13" s="228"/>
+      <c r="O13" s="228"/>
+      <c r="P13" s="228"/>
+      <c r="Q13" s="228"/>
+      <c r="R13" s="228"/>
+      <c r="S13" s="228"/>
+      <c r="T13" s="229"/>
     </row>
     <row r="14" spans="3:20" ht="13.5" customHeight="1">
       <c r="C14" s="78">
-        <v>10</v>
-      </c>
-      <c r="J14" s="219"/>
-      <c r="K14" s="219"/>
-      <c r="L14" s="219"/>
-      <c r="M14" s="219"/>
-      <c r="N14" s="219"/>
-      <c r="O14" s="219"/>
-      <c r="P14" s="219"/>
-      <c r="Q14" s="219"/>
-      <c r="R14" s="219"/>
-      <c r="S14" s="219"/>
-      <c r="T14" s="219"/>
+        <v>8</v>
+      </c>
+      <c r="J14" s="227"/>
+      <c r="K14" s="228"/>
+      <c r="L14" s="228"/>
+      <c r="M14" s="228"/>
+      <c r="N14" s="228"/>
+      <c r="O14" s="228"/>
+      <c r="P14" s="228"/>
+      <c r="Q14" s="228"/>
+      <c r="R14" s="228"/>
+      <c r="S14" s="228"/>
+      <c r="T14" s="229"/>
     </row>
     <row r="15" spans="3:20" ht="13.5" customHeight="1">
       <c r="C15" s="78">
-        <v>11</v>
-      </c>
-      <c r="J15" s="219"/>
-      <c r="K15" s="219"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="219"/>
-      <c r="N15" s="219"/>
-      <c r="O15" s="219"/>
-      <c r="P15" s="219"/>
-      <c r="Q15" s="219"/>
-      <c r="R15" s="219"/>
-      <c r="S15" s="219"/>
-      <c r="T15" s="219"/>
+        <v>9</v>
+      </c>
+      <c r="J15" s="227"/>
+      <c r="K15" s="228"/>
+      <c r="L15" s="228"/>
+      <c r="M15" s="228"/>
+      <c r="N15" s="228"/>
+      <c r="O15" s="228"/>
+      <c r="P15" s="228"/>
+      <c r="Q15" s="228"/>
+      <c r="R15" s="228"/>
+      <c r="S15" s="228"/>
+      <c r="T15" s="229"/>
     </row>
     <row r="16" spans="3:20" ht="13.5" customHeight="1">
       <c r="C16" s="78">
-        <v>12</v>
-      </c>
-      <c r="J16" s="219"/>
-      <c r="K16" s="219"/>
-      <c r="L16" s="219"/>
-      <c r="M16" s="219"/>
-      <c r="N16" s="219"/>
-      <c r="O16" s="219"/>
-      <c r="P16" s="219"/>
-      <c r="Q16" s="219"/>
-      <c r="R16" s="219"/>
-      <c r="S16" s="219"/>
-      <c r="T16" s="219"/>
+        <v>10</v>
+      </c>
+      <c r="J16" s="227"/>
+      <c r="K16" s="228"/>
+      <c r="L16" s="228"/>
+      <c r="M16" s="228"/>
+      <c r="N16" s="228"/>
+      <c r="O16" s="228"/>
+      <c r="P16" s="228"/>
+      <c r="Q16" s="228"/>
+      <c r="R16" s="228"/>
+      <c r="S16" s="228"/>
+      <c r="T16" s="229"/>
     </row>
     <row r="17" spans="3:20" ht="13.5" customHeight="1">
       <c r="C17" s="78">
-        <v>13</v>
-      </c>
-      <c r="J17" s="219"/>
-      <c r="K17" s="219"/>
-      <c r="L17" s="219"/>
-      <c r="M17" s="219"/>
-      <c r="N17" s="219"/>
-      <c r="O17" s="219"/>
-      <c r="P17" s="219"/>
-      <c r="Q17" s="219"/>
-      <c r="R17" s="219"/>
-      <c r="S17" s="219"/>
-      <c r="T17" s="219"/>
+        <v>11</v>
+      </c>
+      <c r="J17" s="227"/>
+      <c r="K17" s="228"/>
+      <c r="L17" s="228"/>
+      <c r="M17" s="228"/>
+      <c r="N17" s="228"/>
+      <c r="O17" s="228"/>
+      <c r="P17" s="228"/>
+      <c r="Q17" s="228"/>
+      <c r="R17" s="228"/>
+      <c r="S17" s="228"/>
+      <c r="T17" s="229"/>
     </row>
     <row r="18" spans="3:20" ht="13.5" customHeight="1">
       <c r="C18" s="78">
-        <v>14</v>
-      </c>
-      <c r="J18" s="219"/>
-      <c r="K18" s="219"/>
-      <c r="L18" s="219"/>
-      <c r="M18" s="219"/>
-      <c r="N18" s="219"/>
-      <c r="O18" s="219"/>
-      <c r="P18" s="219"/>
-      <c r="Q18" s="219"/>
-      <c r="R18" s="219"/>
-      <c r="S18" s="219"/>
-      <c r="T18" s="219"/>
+        <v>12</v>
+      </c>
+      <c r="J18" s="227"/>
+      <c r="K18" s="228"/>
+      <c r="L18" s="228"/>
+      <c r="M18" s="228"/>
+      <c r="N18" s="228"/>
+      <c r="O18" s="228"/>
+      <c r="P18" s="228"/>
+      <c r="Q18" s="228"/>
+      <c r="R18" s="228"/>
+      <c r="S18" s="228"/>
+      <c r="T18" s="229"/>
     </row>
     <row r="19" spans="3:20" ht="13.5" customHeight="1">
       <c r="C19" s="78">
-        <v>15</v>
-      </c>
-      <c r="J19" s="219"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="219"/>
-      <c r="M19" s="219"/>
-      <c r="N19" s="219"/>
-      <c r="O19" s="219"/>
-      <c r="P19" s="219"/>
-      <c r="Q19" s="219"/>
-      <c r="R19" s="219"/>
-      <c r="S19" s="219"/>
-      <c r="T19" s="219"/>
+        <v>13</v>
+      </c>
+      <c r="J19" s="227"/>
+      <c r="K19" s="228"/>
+      <c r="L19" s="228"/>
+      <c r="M19" s="228"/>
+      <c r="N19" s="228"/>
+      <c r="O19" s="228"/>
+      <c r="P19" s="228"/>
+      <c r="Q19" s="228"/>
+      <c r="R19" s="228"/>
+      <c r="S19" s="228"/>
+      <c r="T19" s="229"/>
     </row>
     <row r="20" spans="3:20" ht="13.5" customHeight="1">
       <c r="C20" s="78">
-        <v>16</v>
-      </c>
-      <c r="J20" s="219"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="219"/>
-      <c r="M20" s="219"/>
-      <c r="N20" s="219"/>
-      <c r="O20" s="219"/>
-      <c r="P20" s="219"/>
-      <c r="Q20" s="219"/>
-      <c r="R20" s="219"/>
-      <c r="S20" s="219"/>
-      <c r="T20" s="219"/>
+        <v>14</v>
+      </c>
+      <c r="J20" s="227"/>
+      <c r="K20" s="228"/>
+      <c r="L20" s="228"/>
+      <c r="M20" s="228"/>
+      <c r="N20" s="228"/>
+      <c r="O20" s="228"/>
+      <c r="P20" s="228"/>
+      <c r="Q20" s="228"/>
+      <c r="R20" s="228"/>
+      <c r="S20" s="228"/>
+      <c r="T20" s="229"/>
     </row>
     <row r="21" spans="3:20" ht="13.5" customHeight="1">
       <c r="C21" s="78">
-        <v>17</v>
-      </c>
-      <c r="J21" s="219"/>
-      <c r="K21" s="219"/>
-      <c r="L21" s="219"/>
-      <c r="M21" s="219"/>
-      <c r="N21" s="219"/>
-      <c r="O21" s="219"/>
-      <c r="P21" s="219"/>
-      <c r="Q21" s="219"/>
-      <c r="R21" s="219"/>
-      <c r="S21" s="219"/>
-      <c r="T21" s="219"/>
+        <v>15</v>
+      </c>
+      <c r="J21" s="227"/>
+      <c r="K21" s="228"/>
+      <c r="L21" s="228"/>
+      <c r="M21" s="228"/>
+      <c r="N21" s="228"/>
+      <c r="O21" s="228"/>
+      <c r="P21" s="228"/>
+      <c r="Q21" s="228"/>
+      <c r="R21" s="228"/>
+      <c r="S21" s="228"/>
+      <c r="T21" s="229"/>
     </row>
     <row r="22" spans="3:20" ht="13.5" customHeight="1">
       <c r="C22" s="78">
-        <v>18</v>
-      </c>
-      <c r="J22" s="219"/>
-      <c r="K22" s="219"/>
-      <c r="L22" s="219"/>
-      <c r="M22" s="219"/>
-      <c r="N22" s="219"/>
-      <c r="O22" s="219"/>
-      <c r="P22" s="219"/>
-      <c r="Q22" s="219"/>
-      <c r="R22" s="219"/>
-      <c r="S22" s="219"/>
-      <c r="T22" s="219"/>
+        <v>16</v>
+      </c>
+      <c r="J22" s="227"/>
+      <c r="K22" s="228"/>
+      <c r="L22" s="228"/>
+      <c r="M22" s="228"/>
+      <c r="N22" s="228"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="228"/>
+      <c r="Q22" s="228"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="228"/>
+      <c r="T22" s="229"/>
     </row>
     <row r="23" spans="3:20" ht="13.5" customHeight="1">
       <c r="C23" s="78">
-        <v>19</v>
-      </c>
-      <c r="J23" s="219"/>
-      <c r="K23" s="219"/>
-      <c r="L23" s="219"/>
-      <c r="M23" s="219"/>
-      <c r="N23" s="219"/>
-      <c r="O23" s="219"/>
-      <c r="P23" s="219"/>
-      <c r="Q23" s="219"/>
-      <c r="R23" s="219"/>
-      <c r="S23" s="219"/>
-      <c r="T23" s="219"/>
+        <v>17</v>
+      </c>
+      <c r="J23" s="227"/>
+      <c r="K23" s="228"/>
+      <c r="L23" s="228"/>
+      <c r="M23" s="228"/>
+      <c r="N23" s="228"/>
+      <c r="O23" s="228"/>
+      <c r="P23" s="228"/>
+      <c r="Q23" s="228"/>
+      <c r="R23" s="228"/>
+      <c r="S23" s="228"/>
+      <c r="T23" s="229"/>
     </row>
     <row r="24" spans="3:20" ht="13.5" customHeight="1">
       <c r="C24" s="78">
+        <v>18</v>
+      </c>
+      <c r="J24" s="227"/>
+      <c r="K24" s="228"/>
+      <c r="L24" s="228"/>
+      <c r="M24" s="228"/>
+      <c r="N24" s="228"/>
+      <c r="O24" s="228"/>
+      <c r="P24" s="228"/>
+      <c r="Q24" s="228"/>
+      <c r="R24" s="228"/>
+      <c r="S24" s="228"/>
+      <c r="T24" s="229"/>
+    </row>
+    <row r="25" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C25" s="78">
+        <v>19</v>
+      </c>
+      <c r="J25" s="227"/>
+      <c r="K25" s="228"/>
+      <c r="L25" s="228"/>
+      <c r="M25" s="228"/>
+      <c r="N25" s="228"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="228"/>
+      <c r="Q25" s="228"/>
+      <c r="R25" s="228"/>
+      <c r="S25" s="228"/>
+      <c r="T25" s="229"/>
+    </row>
+    <row r="26" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C26" s="78">
         <v>20</v>
       </c>
-      <c r="J24" s="219"/>
-      <c r="K24" s="219"/>
-      <c r="L24" s="219"/>
-      <c r="M24" s="219"/>
-      <c r="N24" s="219"/>
-      <c r="O24" s="219"/>
-      <c r="P24" s="219"/>
-      <c r="Q24" s="219"/>
-      <c r="R24" s="219"/>
-      <c r="S24" s="219"/>
-      <c r="T24" s="219"/>
-    </row>
-    <row r="25" spans="3:20" ht="13.5" customHeight="1">
-      <c r="C25" s="78" t="s">
+      <c r="J26" s="227"/>
+      <c r="K26" s="228"/>
+      <c r="L26" s="228"/>
+      <c r="M26" s="228"/>
+      <c r="N26" s="228"/>
+      <c r="O26" s="228"/>
+      <c r="P26" s="228"/>
+      <c r="Q26" s="228"/>
+      <c r="R26" s="228"/>
+      <c r="S26" s="228"/>
+      <c r="T26" s="229"/>
+    </row>
+    <row r="27" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C27" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="J25" s="219"/>
-      <c r="K25" s="219"/>
-      <c r="L25" s="219"/>
-      <c r="M25" s="219"/>
-      <c r="N25" s="219"/>
-      <c r="O25" s="219"/>
-      <c r="P25" s="219"/>
-      <c r="Q25" s="219"/>
-      <c r="R25" s="219"/>
-      <c r="S25" s="219"/>
-      <c r="T25" s="219"/>
-    </row>
-    <row r="26" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J26" s="219"/>
-      <c r="K26" s="219"/>
-      <c r="L26" s="219"/>
-      <c r="M26" s="219"/>
-      <c r="N26" s="219"/>
-      <c r="O26" s="219"/>
-      <c r="P26" s="219"/>
-      <c r="Q26" s="219"/>
-      <c r="R26" s="219"/>
-      <c r="S26" s="219"/>
-      <c r="T26" s="219"/>
-    </row>
-    <row r="27" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J27" s="219"/>
-      <c r="K27" s="219"/>
-      <c r="L27" s="219"/>
-      <c r="M27" s="219"/>
-      <c r="N27" s="219"/>
-      <c r="O27" s="219"/>
-      <c r="P27" s="219"/>
-      <c r="Q27" s="219"/>
-      <c r="R27" s="219"/>
-      <c r="S27" s="219"/>
-      <c r="T27" s="219"/>
+      <c r="J27" s="227"/>
+      <c r="K27" s="228"/>
+      <c r="L27" s="228"/>
+      <c r="M27" s="228"/>
+      <c r="N27" s="228"/>
+      <c r="O27" s="228"/>
+      <c r="P27" s="228"/>
+      <c r="Q27" s="228"/>
+      <c r="R27" s="228"/>
+      <c r="S27" s="228"/>
+      <c r="T27" s="229"/>
     </row>
     <row r="28" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J28" s="219"/>
-      <c r="K28" s="219"/>
-      <c r="L28" s="219"/>
-      <c r="M28" s="219"/>
-      <c r="N28" s="219"/>
-      <c r="O28" s="219"/>
-      <c r="P28" s="219"/>
-      <c r="Q28" s="219"/>
-      <c r="R28" s="219"/>
-      <c r="S28" s="219"/>
-      <c r="T28" s="219"/>
+      <c r="J28" s="227"/>
+      <c r="K28" s="228"/>
+      <c r="L28" s="228"/>
+      <c r="M28" s="228"/>
+      <c r="N28" s="228"/>
+      <c r="O28" s="228"/>
+      <c r="P28" s="228"/>
+      <c r="Q28" s="228"/>
+      <c r="R28" s="228"/>
+      <c r="S28" s="228"/>
+      <c r="T28" s="229"/>
     </row>
     <row r="29" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J29" s="219"/>
-      <c r="K29" s="219"/>
-      <c r="L29" s="219"/>
-      <c r="M29" s="219"/>
-      <c r="N29" s="219"/>
-      <c r="O29" s="219"/>
-      <c r="P29" s="219"/>
-      <c r="Q29" s="219"/>
-      <c r="R29" s="219"/>
-      <c r="S29" s="219"/>
-      <c r="T29" s="219"/>
+      <c r="J29" s="227"/>
+      <c r="K29" s="228"/>
+      <c r="L29" s="228"/>
+      <c r="M29" s="228"/>
+      <c r="N29" s="228"/>
+      <c r="O29" s="228"/>
+      <c r="P29" s="228"/>
+      <c r="Q29" s="228"/>
+      <c r="R29" s="228"/>
+      <c r="S29" s="228"/>
+      <c r="T29" s="229"/>
     </row>
     <row r="30" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J30" s="219"/>
-      <c r="K30" s="219"/>
-      <c r="L30" s="219"/>
-      <c r="M30" s="219"/>
-      <c r="N30" s="219"/>
-      <c r="O30" s="219"/>
-      <c r="P30" s="219"/>
-      <c r="Q30" s="219"/>
-      <c r="R30" s="219"/>
-      <c r="S30" s="219"/>
-      <c r="T30" s="219"/>
+      <c r="J30" s="227"/>
+      <c r="K30" s="228"/>
+      <c r="L30" s="228"/>
+      <c r="M30" s="228"/>
+      <c r="N30" s="228"/>
+      <c r="O30" s="228"/>
+      <c r="P30" s="228"/>
+      <c r="Q30" s="228"/>
+      <c r="R30" s="228"/>
+      <c r="S30" s="228"/>
+      <c r="T30" s="229"/>
     </row>
     <row r="31" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J31" s="219"/>
-      <c r="K31" s="219"/>
-      <c r="L31" s="219"/>
-      <c r="M31" s="219"/>
-      <c r="N31" s="219"/>
-      <c r="O31" s="219"/>
-      <c r="P31" s="219"/>
-      <c r="Q31" s="219"/>
-      <c r="R31" s="219"/>
-      <c r="S31" s="219"/>
-      <c r="T31" s="219"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="228"/>
+      <c r="L31" s="228"/>
+      <c r="M31" s="228"/>
+      <c r="N31" s="228"/>
+      <c r="O31" s="228"/>
+      <c r="P31" s="228"/>
+      <c r="Q31" s="228"/>
+      <c r="R31" s="228"/>
+      <c r="S31" s="228"/>
+      <c r="T31" s="229"/>
     </row>
     <row r="32" spans="3:20" ht="13.5" customHeight="1">
-      <c r="J32" s="219"/>
-      <c r="K32" s="219"/>
-      <c r="L32" s="219"/>
-      <c r="M32" s="219"/>
-      <c r="N32" s="219"/>
-      <c r="O32" s="219"/>
-      <c r="P32" s="219"/>
-      <c r="Q32" s="219"/>
-      <c r="R32" s="219"/>
-      <c r="S32" s="219"/>
-      <c r="T32" s="219"/>
+      <c r="J32" s="227"/>
+      <c r="K32" s="228"/>
+      <c r="L32" s="228"/>
+      <c r="M32" s="228"/>
+      <c r="N32" s="228"/>
+      <c r="O32" s="228"/>
+      <c r="P32" s="228"/>
+      <c r="Q32" s="228"/>
+      <c r="R32" s="228"/>
+      <c r="S32" s="228"/>
+      <c r="T32" s="229"/>
     </row>
     <row r="33" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J33" s="219"/>
-      <c r="K33" s="219"/>
-      <c r="L33" s="219"/>
-      <c r="M33" s="219"/>
-      <c r="N33" s="219"/>
-      <c r="O33" s="219"/>
-      <c r="P33" s="219"/>
-      <c r="Q33" s="219"/>
-      <c r="R33" s="219"/>
-      <c r="S33" s="219"/>
-      <c r="T33" s="219"/>
+      <c r="J33" s="227"/>
+      <c r="K33" s="228"/>
+      <c r="L33" s="228"/>
+      <c r="M33" s="228"/>
+      <c r="N33" s="228"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="228"/>
+      <c r="Q33" s="228"/>
+      <c r="R33" s="228"/>
+      <c r="S33" s="228"/>
+      <c r="T33" s="229"/>
     </row>
     <row r="34" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J34" s="219"/>
-      <c r="K34" s="219"/>
-      <c r="L34" s="219"/>
-      <c r="M34" s="219"/>
-      <c r="N34" s="219"/>
-      <c r="O34" s="219"/>
-      <c r="P34" s="219"/>
-      <c r="Q34" s="219"/>
-      <c r="R34" s="219"/>
-      <c r="S34" s="219"/>
-      <c r="T34" s="219"/>
+      <c r="J34" s="227"/>
+      <c r="K34" s="228"/>
+      <c r="L34" s="228"/>
+      <c r="M34" s="228"/>
+      <c r="N34" s="228"/>
+      <c r="O34" s="228"/>
+      <c r="P34" s="228"/>
+      <c r="Q34" s="228"/>
+      <c r="R34" s="228"/>
+      <c r="S34" s="228"/>
+      <c r="T34" s="229"/>
     </row>
     <row r="35" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
-      <c r="M35" s="219"/>
-      <c r="N35" s="219"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="219"/>
-      <c r="Q35" s="219"/>
-      <c r="R35" s="219"/>
-      <c r="S35" s="219"/>
-      <c r="T35" s="219"/>
+      <c r="J35" s="227"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
+      <c r="O35" s="228"/>
+      <c r="P35" s="228"/>
+      <c r="Q35" s="228"/>
+      <c r="R35" s="228"/>
+      <c r="S35" s="228"/>
+      <c r="T35" s="229"/>
     </row>
     <row r="36" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J36" s="219"/>
-      <c r="K36" s="219"/>
-      <c r="L36" s="219"/>
-      <c r="M36" s="219"/>
-      <c r="N36" s="219"/>
-      <c r="O36" s="219"/>
-      <c r="P36" s="219"/>
-      <c r="Q36" s="219"/>
-      <c r="R36" s="219"/>
-      <c r="S36" s="219"/>
-      <c r="T36" s="219"/>
+      <c r="J36" s="227"/>
+      <c r="K36" s="228"/>
+      <c r="L36" s="228"/>
+      <c r="M36" s="228"/>
+      <c r="N36" s="228"/>
+      <c r="O36" s="228"/>
+      <c r="P36" s="228"/>
+      <c r="Q36" s="228"/>
+      <c r="R36" s="228"/>
+      <c r="S36" s="228"/>
+      <c r="T36" s="229"/>
     </row>
     <row r="37" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J37" s="219"/>
-      <c r="K37" s="219"/>
-      <c r="L37" s="219"/>
-      <c r="M37" s="219"/>
-      <c r="N37" s="219"/>
-      <c r="O37" s="219"/>
-      <c r="P37" s="219"/>
-      <c r="Q37" s="219"/>
-      <c r="R37" s="219"/>
-      <c r="S37" s="219"/>
-      <c r="T37" s="219"/>
+      <c r="J37" s="227"/>
+      <c r="K37" s="228"/>
+      <c r="L37" s="228"/>
+      <c r="M37" s="228"/>
+      <c r="N37" s="228"/>
+      <c r="O37" s="228"/>
+      <c r="P37" s="228"/>
+      <c r="Q37" s="228"/>
+      <c r="R37" s="228"/>
+      <c r="S37" s="228"/>
+      <c r="T37" s="229"/>
     </row>
     <row r="38" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J38" s="219"/>
-      <c r="K38" s="219"/>
-      <c r="L38" s="219"/>
-      <c r="M38" s="219"/>
-      <c r="N38" s="219"/>
-      <c r="O38" s="219"/>
-      <c r="P38" s="219"/>
-      <c r="Q38" s="219"/>
-      <c r="R38" s="219"/>
-      <c r="S38" s="219"/>
-      <c r="T38" s="219"/>
+      <c r="J38" s="227"/>
+      <c r="K38" s="228"/>
+      <c r="L38" s="228"/>
+      <c r="M38" s="228"/>
+      <c r="N38" s="228"/>
+      <c r="O38" s="228"/>
+      <c r="P38" s="228"/>
+      <c r="Q38" s="228"/>
+      <c r="R38" s="228"/>
+      <c r="S38" s="228"/>
+      <c r="T38" s="229"/>
     </row>
     <row r="39" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J39" s="219"/>
-      <c r="K39" s="219"/>
-      <c r="L39" s="219"/>
-      <c r="M39" s="219"/>
-      <c r="N39" s="219"/>
-      <c r="O39" s="219"/>
-      <c r="P39" s="219"/>
-      <c r="Q39" s="219"/>
-      <c r="R39" s="219"/>
-      <c r="S39" s="219"/>
-      <c r="T39" s="219"/>
+      <c r="J39" s="227"/>
+      <c r="K39" s="228"/>
+      <c r="L39" s="228"/>
+      <c r="M39" s="228"/>
+      <c r="N39" s="228"/>
+      <c r="O39" s="228"/>
+      <c r="P39" s="228"/>
+      <c r="Q39" s="228"/>
+      <c r="R39" s="228"/>
+      <c r="S39" s="228"/>
+      <c r="T39" s="229"/>
     </row>
     <row r="40" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
-      <c r="M40" s="219"/>
-      <c r="N40" s="219"/>
-      <c r="O40" s="219"/>
-      <c r="P40" s="219"/>
-      <c r="Q40" s="219"/>
-      <c r="R40" s="219"/>
-      <c r="S40" s="219"/>
-      <c r="T40" s="219"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="228"/>
+      <c r="L40" s="228"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="228"/>
+      <c r="O40" s="228"/>
+      <c r="P40" s="228"/>
+      <c r="Q40" s="228"/>
+      <c r="R40" s="228"/>
+      <c r="S40" s="228"/>
+      <c r="T40" s="229"/>
     </row>
     <row r="41" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J41" s="219"/>
-      <c r="K41" s="219"/>
-      <c r="L41" s="219"/>
-      <c r="M41" s="219"/>
-      <c r="N41" s="219"/>
-      <c r="O41" s="219"/>
-      <c r="P41" s="219"/>
-      <c r="Q41" s="219"/>
-      <c r="R41" s="219"/>
-      <c r="S41" s="219"/>
-      <c r="T41" s="219"/>
+      <c r="J41" s="227"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="228"/>
+      <c r="Q41" s="228"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="228"/>
+      <c r="T41" s="229"/>
     </row>
     <row r="42" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J42" s="219"/>
-      <c r="K42" s="219"/>
-      <c r="L42" s="219"/>
-      <c r="M42" s="219"/>
-      <c r="N42" s="219"/>
-      <c r="O42" s="219"/>
-      <c r="P42" s="219"/>
-      <c r="Q42" s="219"/>
-      <c r="R42" s="219"/>
-      <c r="S42" s="219"/>
-      <c r="T42" s="219"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="228"/>
+      <c r="L42" s="228"/>
+      <c r="M42" s="228"/>
+      <c r="N42" s="228"/>
+      <c r="O42" s="228"/>
+      <c r="P42" s="228"/>
+      <c r="Q42" s="228"/>
+      <c r="R42" s="228"/>
+      <c r="S42" s="228"/>
+      <c r="T42" s="229"/>
     </row>
     <row r="43" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J43" s="219"/>
-      <c r="K43" s="219"/>
-      <c r="L43" s="219"/>
-      <c r="M43" s="219"/>
-      <c r="N43" s="219"/>
-      <c r="O43" s="219"/>
-      <c r="P43" s="219"/>
-      <c r="Q43" s="219"/>
-      <c r="R43" s="219"/>
-      <c r="S43" s="219"/>
-      <c r="T43" s="219"/>
+      <c r="J43" s="227"/>
+      <c r="K43" s="228"/>
+      <c r="L43" s="228"/>
+      <c r="M43" s="228"/>
+      <c r="N43" s="228"/>
+      <c r="O43" s="228"/>
+      <c r="P43" s="228"/>
+      <c r="Q43" s="228"/>
+      <c r="R43" s="228"/>
+      <c r="S43" s="228"/>
+      <c r="T43" s="229"/>
     </row>
     <row r="44" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J44" s="219"/>
-      <c r="K44" s="219"/>
-      <c r="L44" s="219"/>
-      <c r="M44" s="219"/>
-      <c r="N44" s="219"/>
-      <c r="O44" s="219"/>
-      <c r="P44" s="219"/>
-      <c r="Q44" s="219"/>
-      <c r="R44" s="219"/>
-      <c r="S44" s="219"/>
-      <c r="T44" s="219"/>
+      <c r="J44" s="227"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="228"/>
+      <c r="N44" s="228"/>
+      <c r="O44" s="228"/>
+      <c r="P44" s="228"/>
+      <c r="Q44" s="228"/>
+      <c r="R44" s="228"/>
+      <c r="S44" s="228"/>
+      <c r="T44" s="229"/>
     </row>
     <row r="45" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J45" s="219"/>
-      <c r="K45" s="219"/>
-      <c r="L45" s="219"/>
-      <c r="M45" s="219"/>
-      <c r="N45" s="219"/>
-      <c r="O45" s="219"/>
-      <c r="P45" s="219"/>
-      <c r="Q45" s="219"/>
-      <c r="R45" s="219"/>
-      <c r="S45" s="219"/>
-      <c r="T45" s="219"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="228"/>
+      <c r="L45" s="228"/>
+      <c r="M45" s="228"/>
+      <c r="N45" s="228"/>
+      <c r="O45" s="228"/>
+      <c r="P45" s="228"/>
+      <c r="Q45" s="228"/>
+      <c r="R45" s="228"/>
+      <c r="S45" s="228"/>
+      <c r="T45" s="229"/>
     </row>
     <row r="46" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J46" s="219"/>
-      <c r="K46" s="219"/>
-      <c r="L46" s="219"/>
-      <c r="M46" s="219"/>
-      <c r="N46" s="219"/>
-      <c r="O46" s="219"/>
-      <c r="P46" s="219"/>
-      <c r="Q46" s="219"/>
-      <c r="R46" s="219"/>
-      <c r="S46" s="219"/>
-      <c r="T46" s="219"/>
+      <c r="J46" s="227"/>
+      <c r="K46" s="228"/>
+      <c r="L46" s="228"/>
+      <c r="M46" s="228"/>
+      <c r="N46" s="228"/>
+      <c r="O46" s="228"/>
+      <c r="P46" s="228"/>
+      <c r="Q46" s="228"/>
+      <c r="R46" s="228"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
     </row>
     <row r="47" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J47" s="219"/>
-      <c r="K47" s="219"/>
-      <c r="L47" s="219"/>
-      <c r="M47" s="219"/>
-      <c r="N47" s="219"/>
-      <c r="O47" s="219"/>
-      <c r="P47" s="219"/>
-      <c r="Q47" s="219"/>
-      <c r="R47" s="219"/>
-      <c r="S47" s="219"/>
-      <c r="T47" s="219"/>
+      <c r="J47" s="227"/>
+      <c r="K47" s="228"/>
+      <c r="L47" s="228"/>
+      <c r="M47" s="228"/>
+      <c r="N47" s="228"/>
+      <c r="O47" s="228"/>
+      <c r="P47" s="228"/>
+      <c r="Q47" s="228"/>
+      <c r="R47" s="228"/>
+      <c r="S47" s="228"/>
+      <c r="T47" s="229"/>
     </row>
     <row r="48" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J48" s="219"/>
-      <c r="K48" s="219"/>
-      <c r="L48" s="219"/>
-      <c r="M48" s="219"/>
-      <c r="N48" s="219"/>
-      <c r="O48" s="219"/>
-      <c r="P48" s="219"/>
-      <c r="Q48" s="219"/>
-      <c r="R48" s="219"/>
-      <c r="S48" s="219"/>
-      <c r="T48" s="219"/>
+      <c r="J48" s="227"/>
+      <c r="K48" s="228"/>
+      <c r="L48" s="228"/>
+      <c r="M48" s="228"/>
+      <c r="N48" s="228"/>
+      <c r="O48" s="228"/>
+      <c r="P48" s="228"/>
+      <c r="Q48" s="228"/>
+      <c r="R48" s="228"/>
+      <c r="S48" s="228"/>
+      <c r="T48" s="229"/>
     </row>
     <row r="49" spans="10:20" ht="13.5" customHeight="1">
-      <c r="J49" s="219"/>
-      <c r="K49" s="219"/>
-      <c r="L49" s="219"/>
-      <c r="M49" s="219"/>
-      <c r="N49" s="219"/>
-      <c r="O49" s="219"/>
-      <c r="P49" s="219"/>
-      <c r="Q49" s="219"/>
-      <c r="R49" s="219"/>
-      <c r="S49" s="219"/>
-      <c r="T49" s="219"/>
-    </row>
-    <row r="50" spans="10:20">
-      <c r="J50" s="219"/>
-      <c r="K50" s="219"/>
-      <c r="L50" s="219"/>
-      <c r="M50" s="219"/>
-      <c r="N50" s="219"/>
-      <c r="O50" s="219"/>
-      <c r="P50" s="219"/>
-      <c r="Q50" s="219"/>
-      <c r="R50" s="219"/>
-      <c r="S50" s="219"/>
-      <c r="T50" s="219"/>
-    </row>
-    <row r="51" spans="10:20">
-      <c r="J51" s="219"/>
-      <c r="K51" s="219"/>
-      <c r="L51" s="219"/>
-      <c r="M51" s="219"/>
-      <c r="N51" s="219"/>
-      <c r="O51" s="219"/>
-      <c r="P51" s="219"/>
-      <c r="Q51" s="219"/>
-      <c r="R51" s="219"/>
-      <c r="S51" s="219"/>
-      <c r="T51" s="219"/>
+      <c r="J49" s="227"/>
+      <c r="K49" s="228"/>
+      <c r="L49" s="228"/>
+      <c r="M49" s="228"/>
+      <c r="N49" s="228"/>
+      <c r="O49" s="228"/>
+      <c r="P49" s="228"/>
+      <c r="Q49" s="228"/>
+      <c r="R49" s="228"/>
+      <c r="S49" s="228"/>
+      <c r="T49" s="229"/>
+    </row>
+    <row r="50" spans="10:20" ht="13.5" customHeight="1">
+      <c r="J50" s="227"/>
+      <c r="K50" s="228"/>
+      <c r="L50" s="228"/>
+      <c r="M50" s="228"/>
+      <c r="N50" s="228"/>
+      <c r="O50" s="228"/>
+      <c r="P50" s="228"/>
+      <c r="Q50" s="228"/>
+      <c r="R50" s="228"/>
+      <c r="S50" s="228"/>
+      <c r="T50" s="229"/>
+    </row>
+    <row r="51" spans="10:20" ht="13.5" customHeight="1">
+      <c r="J51" s="227"/>
+      <c r="K51" s="228"/>
+      <c r="L51" s="228"/>
+      <c r="M51" s="228"/>
+      <c r="N51" s="228"/>
+      <c r="O51" s="228"/>
+      <c r="P51" s="228"/>
+      <c r="Q51" s="228"/>
+      <c r="R51" s="228"/>
+      <c r="S51" s="228"/>
+      <c r="T51" s="229"/>
     </row>
     <row r="52" spans="10:20">
-      <c r="J52" s="219"/>
-      <c r="K52" s="219"/>
-      <c r="L52" s="219"/>
-      <c r="M52" s="219"/>
-      <c r="N52" s="219"/>
-      <c r="O52" s="219"/>
-      <c r="P52" s="219"/>
-      <c r="Q52" s="219"/>
-      <c r="R52" s="219"/>
-      <c r="S52" s="219"/>
-      <c r="T52" s="219"/>
+      <c r="J52" s="227"/>
+      <c r="K52" s="228"/>
+      <c r="L52" s="228"/>
+      <c r="M52" s="228"/>
+      <c r="N52" s="228"/>
+      <c r="O52" s="228"/>
+      <c r="P52" s="228"/>
+      <c r="Q52" s="228"/>
+      <c r="R52" s="228"/>
+      <c r="S52" s="228"/>
+      <c r="T52" s="229"/>
     </row>
     <row r="53" spans="10:20">
-      <c r="J53" s="219"/>
-      <c r="K53" s="219"/>
-      <c r="L53" s="219"/>
-      <c r="M53" s="219"/>
-      <c r="N53" s="219"/>
-      <c r="O53" s="219"/>
-      <c r="P53" s="219"/>
-      <c r="Q53" s="219"/>
-      <c r="R53" s="219"/>
-      <c r="S53" s="219"/>
-      <c r="T53" s="219"/>
+      <c r="J53" s="227"/>
+      <c r="K53" s="228"/>
+      <c r="L53" s="228"/>
+      <c r="M53" s="228"/>
+      <c r="N53" s="228"/>
+      <c r="O53" s="228"/>
+      <c r="P53" s="228"/>
+      <c r="Q53" s="228"/>
+      <c r="R53" s="228"/>
+      <c r="S53" s="228"/>
+      <c r="T53" s="229"/>
+    </row>
+    <row r="54" spans="10:20">
+      <c r="J54" s="227"/>
+      <c r="K54" s="228"/>
+      <c r="L54" s="228"/>
+      <c r="M54" s="228"/>
+      <c r="N54" s="228"/>
+      <c r="O54" s="228"/>
+      <c r="P54" s="228"/>
+      <c r="Q54" s="228"/>
+      <c r="R54" s="228"/>
+      <c r="S54" s="228"/>
+      <c r="T54" s="229"/>
+    </row>
+    <row r="55" spans="10:20" ht="17.25" thickBot="1">
+      <c r="J55" s="230"/>
+      <c r="K55" s="231"/>
+      <c r="L55" s="231"/>
+      <c r="M55" s="231"/>
+      <c r="N55" s="231"/>
+      <c r="O55" s="231"/>
+      <c r="P55" s="231"/>
+      <c r="Q55" s="231"/>
+      <c r="R55" s="231"/>
+      <c r="S55" s="231"/>
+      <c r="T55" s="232"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="J3:T3"/>
-    <mergeCell ref="J4:T53"/>
+  <mergeCells count="5">
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J5:T5"/>
+    <mergeCell ref="J6:T55"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8" xr:uid="{59EA53C9-6879-4885-A1C1-68FDECBD0170}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10" xr:uid="{E0CEA177-B541-4BC0-9525-1C2FDE47B6DF}">
       <formula1>"$rose,$fell,$changed,Data"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D7 C5:C25" xr:uid="{4AE29D8C-379A-4D69-88D6-BD5C27E94A9A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D9 C7:C27" xr:uid="{875603AE-6ADF-42ED-BCD3-3B147BF0E379}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA2F007D-683A-4B23-8B1E-2D5B4C6E8AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FEF86C2-F6C7-4FBB-9C9C-896AF184EF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="4" activeTab="2" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -18,16 +18,17 @@
     <sheet name="handshake" sheetId="16" r:id="rId3"/>
     <sheet name="HSW" sheetId="17" r:id="rId4"/>
     <sheet name="HBP" sheetId="21" r:id="rId5"/>
-    <sheet name="VSW" sheetId="20" r:id="rId6"/>
-    <sheet name="Counter" sheetId="15" r:id="rId7"/>
-    <sheet name="delayCondition" sheetId="18" r:id="rId8"/>
-    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId9"/>
-    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId10"/>
-    <sheet name="Basic Assertion" sheetId="1" r:id="rId11"/>
-    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId12"/>
-    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId13"/>
-    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId14"/>
-    <sheet name="aw_builder" sheetId="2" r:id="rId15"/>
+    <sheet name="VFP" sheetId="22" r:id="rId6"/>
+    <sheet name="VSW" sheetId="20" r:id="rId7"/>
+    <sheet name="Counter" sheetId="15" r:id="rId8"/>
+    <sheet name="delayCondition" sheetId="18" r:id="rId9"/>
+    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId10"/>
+    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId11"/>
+    <sheet name="Basic Assertion" sheetId="1" r:id="rId12"/>
+    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId13"/>
+    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId14"/>
+    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId15"/>
+    <sheet name="aw_builder" sheetId="2" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -168,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="344">
   <si>
     <t>Base Information</t>
   </si>
@@ -1836,12 +1837,6 @@
     </r>
   </si>
   <si>
-    <t>='Define'!C5</t>
-  </si>
-  <si>
-    <t>='Define'!C6</t>
-  </si>
-  <si>
     <t>HSW</t>
   </si>
   <si>
@@ -2204,6 +2199,24 @@
   </si>
   <si>
     <t>data_enable_signal</t>
+  </si>
+  <si>
+    <t>VFP</t>
+  </si>
+  <si>
+    <t>Expected Preset(VFP)</t>
+  </si>
+  <si>
+    <t>Sync Signal</t>
+  </si>
+  <si>
+    <t>sync_signal</t>
+  </si>
+  <si>
+    <t>='Define'!C5</t>
+  </si>
+  <si>
+    <t>='Define'!C6</t>
   </si>
   <si>
     <t>Expected Preset(vpulse)</t>
@@ -5476,7 +5489,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5856,9 +5869,6 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5910,27 +5920,15 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5946,15 +5944,9 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6125,6 +6117,39 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6750,6 +6775,312 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632C17C5-59B7-41E9-805B-4B36986E2251}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="B1:V36"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="5" max="5" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" style="43" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
+    <col min="8" max="8" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="44" customWidth="1"/>
+    <col min="10" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="15.875" style="43" customWidth="1"/>
+    <col min="12" max="12" width="21.5" style="44" customWidth="1"/>
+    <col min="13" max="13" width="3.375" customWidth="1"/>
+    <col min="14" max="14" width="15.875" style="43" customWidth="1"/>
+    <col min="15" max="15" width="40.375" customWidth="1"/>
+    <col min="16" max="17" width="17.375" customWidth="1"/>
+    <col min="18" max="18" width="21.5" style="44" customWidth="1"/>
+    <col min="19" max="19" width="4.5" customWidth="1"/>
+    <col min="20" max="20" width="15.875" style="43" customWidth="1"/>
+    <col min="21" max="21" width="17.375" customWidth="1"/>
+    <col min="22" max="22" width="21.5" style="44" customWidth="1"/>
+    <col min="23" max="23" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="I1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="N1"/>
+      <c r="R1"/>
+      <c r="T1"/>
+      <c r="V1"/>
+    </row>
+    <row r="2" spans="2:22">
+      <c r="B2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="I2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="N2"/>
+      <c r="R2"/>
+      <c r="T2"/>
+      <c r="V2"/>
+    </row>
+    <row r="3" spans="2:22" ht="19.5" customHeight="1">
+      <c r="B3" s="121" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="122"/>
+      <c r="I3" s="123"/>
+      <c r="K3" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="123"/>
+      <c r="N3" s="121" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="123"/>
+      <c r="T3" s="121" t="s">
+        <v>117</v>
+      </c>
+      <c r="U3" s="122"/>
+      <c r="V3" s="123"/>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="71"/>
+      <c r="G4" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="L4" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="N4" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="T4" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="V4" s="42" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" ht="15">
+      <c r="B5" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="37"/>
+      <c r="I5" s="27"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="27"/>
+      <c r="N5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="O5" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="P5" s="37">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="U5" s="37">
+        <v>2</v>
+      </c>
+      <c r="V5" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="15">
+      <c r="B6" s="26"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="27"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="27"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="27"/>
+    </row>
+    <row r="7" spans="2:22" ht="15">
+      <c r="B7" s="26"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="27"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="27"/>
+      <c r="N7" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="O7" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="P7" s="37">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="37">
+        <v>1</v>
+      </c>
+      <c r="R7" s="27">
+        <v>0</v>
+      </c>
+      <c r="T7" s="26"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="27"/>
+    </row>
+    <row r="8" spans="2:22" ht="15">
+      <c r="B8" s="26"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="27"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="27"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="27"/>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="G9" s="26"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="27"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="27"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="27"/>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="B10" s="26"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="T10" s="26"/>
+    </row>
+    <row r="35" spans="10:10">
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="10:10">
+      <c r="J36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="T3:V3"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B5:B8" xr:uid="{8DDDB7D8-EE11-47B5-B588-8A4BD8C3CC68}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G10 K5:K10 N5:N10 R5:R7 T5:T10 V5:V7" xr:uid="{6619C4EF-A22E-45EF-94C7-8C8EE7B88B38}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I8 D5:D8 L5:L8 R8 V8" xr:uid="{E08CDC7A-9ECD-4DCD-A610-26787C899834}">
+      <formula1>"$rose,$fell,$changed,Data"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52C9A5D-390C-4EB4-8E0E-6218D55EFC0C}">
   <dimension ref="C4:I26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6765,348 +7096,348 @@
     <row r="4" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="5" spans="3:9" ht="16.5" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G10" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="3:9" ht="17.25">
       <c r="C14" s="17" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -7114,7 +7445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713538E3-68C7-46EF-9BF7-7D86C6D2932B}">
   <dimension ref="B2:AC45"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7142,7 +7473,7 @@
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="124" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C2" s="125"/>
       <c r="D2" s="125"/>
@@ -7162,109 +7493,109 @@
       <c r="R2" s="126"/>
     </row>
     <row r="3" spans="2:22" ht="13.5" customHeight="1">
-      <c r="B3" s="172"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="174"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="167"/>
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="O4" s="175" t="s">
-        <v>240</v>
-      </c>
-      <c r="P4" s="176"/>
-      <c r="Q4" s="176"/>
-      <c r="R4" s="177"/>
+        <v>243</v>
+      </c>
+      <c r="O4" s="168" t="s">
+        <v>244</v>
+      </c>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="170"/>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="178"/>
-      <c r="P5" s="179"/>
-      <c r="Q5" s="179"/>
-      <c r="R5" s="180"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="172"/>
+      <c r="R5" s="173"/>
     </row>
     <row r="6" spans="2:22" ht="15">
       <c r="B6" s="25" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -7277,10 +7608,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -7288,14 +7619,14 @@
       <c r="N6" s="31">
         <v>4</v>
       </c>
-      <c r="O6" s="178"/>
-      <c r="P6" s="179"/>
-      <c r="Q6" s="179"/>
-      <c r="R6" s="180"/>
+      <c r="O6" s="171"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="173"/>
     </row>
     <row r="7" spans="2:22" ht="15">
       <c r="B7" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -7308,10 +7639,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -7319,14 +7650,14 @@
       <c r="N7" s="31">
         <v>4</v>
       </c>
-      <c r="O7" s="178"/>
-      <c r="P7" s="179"/>
-      <c r="Q7" s="179"/>
-      <c r="R7" s="180"/>
+      <c r="O7" s="171"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="173"/>
     </row>
     <row r="8" spans="2:22" ht="15">
       <c r="B8" s="25" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -7339,10 +7670,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -7350,49 +7681,49 @@
       <c r="N8" s="31">
         <v>4</v>
       </c>
-      <c r="O8" s="178"/>
-      <c r="P8" s="179"/>
-      <c r="Q8" s="179"/>
-      <c r="R8" s="180"/>
+      <c r="O8" s="171"/>
+      <c r="P8" s="172"/>
+      <c r="Q8" s="172"/>
+      <c r="R8" s="173"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="179"/>
-      <c r="Q9" s="179"/>
-      <c r="R9" s="180"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="172"/>
+      <c r="R9" s="173"/>
     </row>
     <row r="10" spans="2:22" ht="15">
       <c r="B10" s="25" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -7405,10 +7736,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -7416,14 +7747,14 @@
       <c r="N10" s="31">
         <v>4</v>
       </c>
-      <c r="O10" s="178"/>
-      <c r="P10" s="179"/>
-      <c r="Q10" s="179"/>
-      <c r="R10" s="180"/>
+      <c r="O10" s="171"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="173"/>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -7437,14 +7768,14 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="178"/>
-      <c r="P11" s="179"/>
-      <c r="Q11" s="179"/>
-      <c r="R11" s="180"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="172"/>
+      <c r="R11" s="173"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -7458,14 +7789,14 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="179"/>
-      <c r="Q12" s="179"/>
-      <c r="R12" s="180"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="172"/>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="173"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -7479,14 +7810,14 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="179"/>
-      <c r="Q13" s="179"/>
-      <c r="R13" s="180"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="172"/>
+      <c r="Q13" s="172"/>
+      <c r="R13" s="173"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -7500,18 +7831,18 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="178"/>
-      <c r="P14" s="179"/>
-      <c r="Q14" s="179"/>
-      <c r="R14" s="180"/>
-      <c r="U14" s="193" t="s">
-        <v>252</v>
-      </c>
-      <c r="V14" s="193"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="172"/>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="173"/>
+      <c r="U14" s="186" t="s">
+        <v>256</v>
+      </c>
+      <c r="V14" s="186"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -7525,16 +7856,16 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="179"/>
-      <c r="Q15" s="179"/>
-      <c r="R15" s="180"/>
-      <c r="U15" s="193"/>
-      <c r="V15" s="193"/>
+      <c r="O15" s="171"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="172"/>
+      <c r="R15" s="173"/>
+      <c r="U15" s="186"/>
+      <c r="V15" s="186"/>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -7548,20 +7879,20 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16" s="178"/>
-      <c r="P16" s="179"/>
-      <c r="Q16" s="179"/>
-      <c r="R16" s="180"/>
-      <c r="U16" s="193" t="s">
-        <v>253</v>
-      </c>
-      <c r="V16" s="194" t="s">
-        <v>254</v>
+      <c r="O16" s="171"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="172"/>
+      <c r="R16" s="173"/>
+      <c r="U16" s="186" t="s">
+        <v>257</v>
+      </c>
+      <c r="V16" s="187" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -7575,16 +7906,16 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="179"/>
-      <c r="Q17" s="179"/>
-      <c r="R17" s="180"/>
-      <c r="U17" s="193"/>
-      <c r="V17" s="194"/>
+      <c r="O17" s="171"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="172"/>
+      <c r="R17" s="173"/>
+      <c r="U17" s="186"/>
+      <c r="V17" s="187"/>
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -7598,18 +7929,18 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="179"/>
-      <c r="Q18" s="179"/>
-      <c r="R18" s="180"/>
-      <c r="U18" s="193"/>
-      <c r="V18" s="194" t="s">
-        <v>255</v>
+      <c r="O18" s="171"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="173"/>
+      <c r="U18" s="186"/>
+      <c r="V18" s="187" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -7623,16 +7954,16 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="179"/>
-      <c r="R19" s="180"/>
-      <c r="U19" s="193"/>
-      <c r="V19" s="194"/>
+      <c r="O19" s="171"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="172"/>
+      <c r="R19" s="173"/>
+      <c r="U19" s="186"/>
+      <c r="V19" s="187"/>
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -7646,18 +7977,18 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="179"/>
-      <c r="Q20" s="179"/>
-      <c r="R20" s="180"/>
-      <c r="U20" s="193"/>
-      <c r="V20" s="194" t="s">
-        <v>256</v>
+      <c r="O20" s="171"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="173"/>
+      <c r="U20" s="186"/>
+      <c r="V20" s="187" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -7671,16 +8002,16 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="179"/>
-      <c r="Q21" s="179"/>
-      <c r="R21" s="180"/>
-      <c r="U21" s="193"/>
-      <c r="V21" s="194"/>
+      <c r="O21" s="171"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="173"/>
+      <c r="U21" s="186"/>
+      <c r="V21" s="187"/>
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -7694,18 +8025,18 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="179"/>
-      <c r="Q22" s="179"/>
-      <c r="R22" s="180"/>
-      <c r="U22" s="193"/>
-      <c r="V22" s="194" t="s">
-        <v>257</v>
+      <c r="O22" s="171"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="172"/>
+      <c r="R22" s="173"/>
+      <c r="U22" s="186"/>
+      <c r="V22" s="187" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -7719,16 +8050,16 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="179"/>
-      <c r="R23" s="180"/>
-      <c r="U23" s="193"/>
-      <c r="V23" s="194"/>
+      <c r="O23" s="171"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="172"/>
+      <c r="R23" s="173"/>
+      <c r="U23" s="186"/>
+      <c r="V23" s="187"/>
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -7742,18 +8073,18 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="179"/>
-      <c r="Q24" s="179"/>
-      <c r="R24" s="180"/>
-      <c r="U24" s="193"/>
-      <c r="V24" s="194" t="s">
-        <v>258</v>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="172"/>
+      <c r="R24" s="173"/>
+      <c r="U24" s="186"/>
+      <c r="V24" s="187" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -7767,16 +8098,16 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="179"/>
-      <c r="R25" s="180"/>
-      <c r="U25" s="193"/>
-      <c r="V25" s="194"/>
+      <c r="O25" s="171"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="172"/>
+      <c r="R25" s="173"/>
+      <c r="U25" s="186"/>
+      <c r="V25" s="187"/>
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -7790,18 +8121,18 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="179"/>
-      <c r="Q26" s="179"/>
-      <c r="R26" s="180"/>
-      <c r="U26" s="193"/>
-      <c r="V26" s="194" t="s">
-        <v>258</v>
+      <c r="O26" s="171"/>
+      <c r="P26" s="172"/>
+      <c r="Q26" s="172"/>
+      <c r="R26" s="173"/>
+      <c r="U26" s="186"/>
+      <c r="V26" s="187" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -7815,16 +8146,16 @@
       <c r="L27" s="29"/>
       <c r="M27" s="29"/>
       <c r="N27" s="29"/>
-      <c r="O27" s="181"/>
-      <c r="P27" s="182"/>
-      <c r="Q27" s="182"/>
-      <c r="R27" s="183"/>
-      <c r="U27" s="193"/>
-      <c r="V27" s="194"/>
+      <c r="O27" s="174"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="175"/>
+      <c r="R27" s="176"/>
+      <c r="U27" s="186"/>
+      <c r="V27" s="187"/>
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C30" s="125"/>
       <c r="D30" s="125"/>
@@ -7844,106 +8175,106 @@
       <c r="R30" s="126"/>
     </row>
     <row r="31" spans="2:25" ht="13.5" customHeight="1">
-      <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="173"/>
-      <c r="J31" s="173"/>
-      <c r="K31" s="173"/>
-      <c r="L31" s="173"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
-      <c r="O31" s="173"/>
-      <c r="P31" s="173"/>
-      <c r="Q31" s="173"/>
-      <c r="R31" s="174"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="166"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="166"/>
+      <c r="K31" s="166"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="166"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="166"/>
+      <c r="P31" s="166"/>
+      <c r="Q31" s="166"/>
+      <c r="R31" s="167"/>
       <c r="U31" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="15">
       <c r="B32" s="38" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H32" s="36" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="L32" s="184" t="s">
-        <v>240</v>
-      </c>
-      <c r="M32" s="185"/>
-      <c r="N32" s="185"/>
-      <c r="O32" s="185"/>
-      <c r="P32" s="185"/>
-      <c r="Q32" s="185"/>
-      <c r="R32" s="186"/>
+        <v>243</v>
+      </c>
+      <c r="L32" s="177" t="s">
+        <v>244</v>
+      </c>
+      <c r="M32" s="178"/>
+      <c r="N32" s="178"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="178"/>
+      <c r="Q32" s="178"/>
+      <c r="R32" s="179"/>
       <c r="U32" s="5" t="s">
         <v>5</v>
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Y32" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="2:29" ht="15">
       <c r="B33" s="26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -7951,15 +8282,15 @@
       <c r="K33" s="31">
         <v>4</v>
       </c>
-      <c r="L33" s="187"/>
-      <c r="M33" s="188"/>
-      <c r="N33" s="188"/>
-      <c r="O33" s="188"/>
-      <c r="P33" s="188"/>
-      <c r="Q33" s="188"/>
-      <c r="R33" s="189"/>
+      <c r="L33" s="180"/>
+      <c r="M33" s="181"/>
+      <c r="N33" s="181"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="181"/>
+      <c r="Q33" s="181"/>
+      <c r="R33" s="182"/>
       <c r="U33" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -7974,25 +8305,25 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="187"/>
-      <c r="M34" s="188"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="188"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="188"/>
-      <c r="R34" s="189"/>
+      <c r="L34" s="180"/>
+      <c r="M34" s="181"/>
+      <c r="N34" s="181"/>
+      <c r="O34" s="181"/>
+      <c r="P34" s="181"/>
+      <c r="Q34" s="181"/>
+      <c r="R34" s="182"/>
       <c r="U34" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Y34" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Z34" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="2:29" ht="15">
@@ -8006,23 +8337,23 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="187"/>
-      <c r="M35" s="188"/>
-      <c r="N35" s="188"/>
-      <c r="O35" s="188"/>
-      <c r="P35" s="188"/>
-      <c r="Q35" s="188"/>
-      <c r="R35" s="189"/>
+      <c r="L35" s="180"/>
+      <c r="M35" s="181"/>
+      <c r="N35" s="181"/>
+      <c r="O35" s="181"/>
+      <c r="P35" s="181"/>
+      <c r="Q35" s="181"/>
+      <c r="R35" s="182"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y35" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="2:29" ht="15">
@@ -8036,13 +8367,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="187"/>
-      <c r="M36" s="188"/>
-      <c r="N36" s="188"/>
-      <c r="O36" s="188"/>
-      <c r="P36" s="188"/>
-      <c r="Q36" s="188"/>
-      <c r="R36" s="189"/>
+      <c r="L36" s="180"/>
+      <c r="M36" s="181"/>
+      <c r="N36" s="181"/>
+      <c r="O36" s="181"/>
+      <c r="P36" s="181"/>
+      <c r="Q36" s="181"/>
+      <c r="R36" s="182"/>
       <c r="S36" s="7"/>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
@@ -8058,19 +8389,19 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="187"/>
-      <c r="M37" s="188"/>
-      <c r="N37" s="188"/>
-      <c r="O37" s="188"/>
-      <c r="P37" s="188"/>
-      <c r="Q37" s="188"/>
-      <c r="R37" s="189"/>
+      <c r="L37" s="180"/>
+      <c r="M37" s="181"/>
+      <c r="N37" s="181"/>
+      <c r="O37" s="181"/>
+      <c r="P37" s="181"/>
+      <c r="Q37" s="181"/>
+      <c r="R37" s="182"/>
       <c r="U37" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="2:29" ht="15">
@@ -8084,19 +8415,19 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="187"/>
-      <c r="M38" s="188"/>
-      <c r="N38" s="188"/>
-      <c r="O38" s="188"/>
-      <c r="P38" s="188"/>
-      <c r="Q38" s="188"/>
-      <c r="R38" s="189"/>
+      <c r="L38" s="180"/>
+      <c r="M38" s="181"/>
+      <c r="N38" s="181"/>
+      <c r="O38" s="181"/>
+      <c r="P38" s="181"/>
+      <c r="Q38" s="181"/>
+      <c r="R38" s="182"/>
       <c r="U38" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="2:29" ht="15">
@@ -8110,34 +8441,34 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="187"/>
-      <c r="M39" s="188"/>
-      <c r="N39" s="188"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="188"/>
-      <c r="Q39" s="188"/>
-      <c r="R39" s="189"/>
+      <c r="L39" s="180"/>
+      <c r="M39" s="181"/>
+      <c r="N39" s="181"/>
+      <c r="O39" s="181"/>
+      <c r="P39" s="181"/>
+      <c r="Q39" s="181"/>
+      <c r="R39" s="182"/>
       <c r="U39" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Y39" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Z39" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA39" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AB39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AC39" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -8151,13 +8482,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="187"/>
-      <c r="M40" s="188"/>
-      <c r="N40" s="188"/>
-      <c r="O40" s="188"/>
-      <c r="P40" s="188"/>
-      <c r="Q40" s="188"/>
-      <c r="R40" s="189"/>
+      <c r="L40" s="180"/>
+      <c r="M40" s="181"/>
+      <c r="N40" s="181"/>
+      <c r="O40" s="181"/>
+      <c r="P40" s="181"/>
+      <c r="Q40" s="181"/>
+      <c r="R40" s="182"/>
     </row>
     <row r="41" spans="2:29">
       <c r="B41" s="26"/>
@@ -8170,13 +8501,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="187"/>
-      <c r="M41" s="188"/>
-      <c r="N41" s="188"/>
-      <c r="O41" s="188"/>
-      <c r="P41" s="188"/>
-      <c r="Q41" s="188"/>
-      <c r="R41" s="189"/>
+      <c r="L41" s="180"/>
+      <c r="M41" s="181"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="181"/>
+      <c r="P41" s="181"/>
+      <c r="Q41" s="181"/>
+      <c r="R41" s="182"/>
     </row>
     <row r="42" spans="2:29">
       <c r="B42" s="26"/>
@@ -8189,13 +8520,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="187"/>
-      <c r="M42" s="188"/>
-      <c r="N42" s="188"/>
-      <c r="O42" s="188"/>
-      <c r="P42" s="188"/>
-      <c r="Q42" s="188"/>
-      <c r="R42" s="189"/>
+      <c r="L42" s="180"/>
+      <c r="M42" s="181"/>
+      <c r="N42" s="181"/>
+      <c r="O42" s="181"/>
+      <c r="P42" s="181"/>
+      <c r="Q42" s="181"/>
+      <c r="R42" s="182"/>
     </row>
     <row r="43" spans="2:29">
       <c r="B43" s="26"/>
@@ -8208,13 +8539,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="187"/>
-      <c r="M43" s="188"/>
-      <c r="N43" s="188"/>
-      <c r="O43" s="188"/>
-      <c r="P43" s="188"/>
-      <c r="Q43" s="188"/>
-      <c r="R43" s="189"/>
+      <c r="L43" s="180"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="182"/>
     </row>
     <row r="44" spans="2:29">
       <c r="B44" s="26"/>
@@ -8227,13 +8558,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="187"/>
-      <c r="M44" s="188"/>
-      <c r="N44" s="188"/>
-      <c r="O44" s="188"/>
-      <c r="P44" s="188"/>
-      <c r="Q44" s="188"/>
-      <c r="R44" s="189"/>
+      <c r="L44" s="180"/>
+      <c r="M44" s="181"/>
+      <c r="N44" s="181"/>
+      <c r="O44" s="181"/>
+      <c r="P44" s="181"/>
+      <c r="Q44" s="181"/>
+      <c r="R44" s="182"/>
     </row>
     <row r="45" spans="2:29">
       <c r="B45" s="28"/>
@@ -8246,13 +8577,13 @@
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
-      <c r="L45" s="190"/>
-      <c r="M45" s="191"/>
-      <c r="N45" s="191"/>
-      <c r="O45" s="191"/>
-      <c r="P45" s="191"/>
-      <c r="Q45" s="191"/>
-      <c r="R45" s="192"/>
+      <c r="L45" s="183"/>
+      <c r="M45" s="184"/>
+      <c r="N45" s="184"/>
+      <c r="O45" s="184"/>
+      <c r="P45" s="184"/>
+      <c r="Q45" s="184"/>
+      <c r="R45" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -8308,7 +8639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D35609-775E-4A26-9091-D70AA658E418}">
   <dimension ref="A1:AH37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -8347,248 +8678,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
-      <c r="A1" s="149" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="151"/>
-      <c r="O1" s="149" t="s">
-        <v>259</v>
-      </c>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="151"/>
-      <c r="Z1" s="201" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA1" s="202"/>
-      <c r="AB1" s="202"/>
-      <c r="AC1" s="202"/>
-      <c r="AD1" s="202"/>
-      <c r="AE1" s="202"/>
-      <c r="AF1" s="202"/>
-      <c r="AG1" s="202"/>
-      <c r="AH1" s="203"/>
+      <c r="A1" s="148" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="150"/>
+      <c r="O1" s="148" t="s">
+        <v>263</v>
+      </c>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="150"/>
+      <c r="Z1" s="194" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA1" s="195"/>
+      <c r="AB1" s="195"/>
+      <c r="AC1" s="195"/>
+      <c r="AD1" s="195"/>
+      <c r="AE1" s="195"/>
+      <c r="AF1" s="195"/>
+      <c r="AG1" s="195"/>
+      <c r="AH1" s="196"/>
     </row>
     <row r="2" spans="1:34" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A2" s="195"/>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="197"/>
-      <c r="O2" s="195"/>
-      <c r="P2" s="196"/>
-      <c r="Q2" s="196"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="196"/>
-      <c r="T2" s="196"/>
-      <c r="U2" s="196"/>
-      <c r="V2" s="196"/>
-      <c r="W2" s="196"/>
-      <c r="X2" s="197"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="205"/>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="205"/>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="206"/>
+      <c r="A2" s="188"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="189"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="190"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="189"/>
+      <c r="Q2" s="189"/>
+      <c r="R2" s="189"/>
+      <c r="S2" s="189"/>
+      <c r="T2" s="189"/>
+      <c r="U2" s="189"/>
+      <c r="V2" s="189"/>
+      <c r="W2" s="189"/>
+      <c r="X2" s="190"/>
+      <c r="Z2" s="197"/>
+      <c r="AA2" s="198"/>
+      <c r="AB2" s="198"/>
+      <c r="AC2" s="198"/>
+      <c r="AD2" s="198"/>
+      <c r="AE2" s="198"/>
+      <c r="AF2" s="198"/>
+      <c r="AG2" s="198"/>
+      <c r="AH2" s="199"/>
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A3" s="207" t="s">
-        <v>273</v>
-      </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="207" t="s">
-        <v>274</v>
-      </c>
-      <c r="I3" s="208"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="208"/>
-      <c r="L3" s="208"/>
-      <c r="M3" s="209"/>
-      <c r="O3" s="198"/>
-      <c r="P3" s="199"/>
-      <c r="Q3" s="199"/>
-      <c r="R3" s="199"/>
-      <c r="S3" s="199"/>
-      <c r="T3" s="199"/>
-      <c r="U3" s="199"/>
-      <c r="V3" s="199"/>
-      <c r="W3" s="199"/>
-      <c r="X3" s="200"/>
-      <c r="Z3" s="210" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA3" s="211"/>
-      <c r="AB3" s="211"/>
-      <c r="AC3" s="211"/>
-      <c r="AD3" s="212"/>
-      <c r="AE3" s="210" t="s">
-        <v>275</v>
-      </c>
-      <c r="AF3" s="213"/>
-      <c r="AG3" s="213"/>
-      <c r="AH3" s="214"/>
+      <c r="A3" s="200" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="201"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="201"/>
+      <c r="G3" s="201"/>
+      <c r="H3" s="200" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" s="201"/>
+      <c r="J3" s="201"/>
+      <c r="K3" s="201"/>
+      <c r="L3" s="201"/>
+      <c r="M3" s="202"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="192"/>
+      <c r="Q3" s="192"/>
+      <c r="R3" s="192"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
+      <c r="X3" s="193"/>
+      <c r="Z3" s="203" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA3" s="204"/>
+      <c r="AB3" s="204"/>
+      <c r="AC3" s="204"/>
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="203" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF3" s="206"/>
+      <c r="AG3" s="206"/>
+      <c r="AH3" s="207"/>
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="S4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="W4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AF4" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>278</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -8603,54 +8934,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AA5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AB5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AC5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AF5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -8669,39 +9000,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AF6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -8720,36 +9051,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AF7" t="s">
+        <v>294</v>
+      </c>
+      <c r="AH7" s="44" t="s">
         <v>290</v>
-      </c>
-      <c r="AH7" s="44" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -9094,7 +9425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A12CEB-23C8-48B1-A30D-D9BBB9DB2391}">
   <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9134,7 +9465,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="124" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -9149,7 +9480,7 @@
       <c r="L1" s="125"/>
       <c r="M1" s="126"/>
       <c r="O1" s="124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="P1" s="125"/>
       <c r="Q1" s="125"/>
@@ -9160,55 +9491,55 @@
       <c r="V1" s="125"/>
       <c r="W1" s="125"/>
       <c r="X1" s="126"/>
-      <c r="Z1" s="216" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA1" s="217"/>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="217"/>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="217"/>
-      <c r="AH1" s="218"/>
+      <c r="Z1" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA1" s="210"/>
+      <c r="AB1" s="210"/>
+      <c r="AC1" s="210"/>
+      <c r="AD1" s="210"/>
+      <c r="AE1" s="210"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="210"/>
+      <c r="AH1" s="211"/>
     </row>
     <row r="2" spans="1:34" ht="13.5" customHeight="1">
-      <c r="A2" s="172"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="174"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="173"/>
-      <c r="Q2" s="173"/>
-      <c r="R2" s="173"/>
-      <c r="S2" s="173"/>
-      <c r="T2" s="173"/>
-      <c r="U2" s="173"/>
-      <c r="V2" s="173"/>
-      <c r="W2" s="173"/>
-      <c r="X2" s="174"/>
-      <c r="Z2" s="219"/>
-      <c r="AA2" s="220"/>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="220"/>
-      <c r="AD2" s="220"/>
-      <c r="AE2" s="220"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="220"/>
-      <c r="AH2" s="221"/>
+      <c r="A2" s="165"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="167"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="166"/>
+      <c r="Q2" s="166"/>
+      <c r="R2" s="166"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="166"/>
+      <c r="U2" s="166"/>
+      <c r="V2" s="166"/>
+      <c r="W2" s="166"/>
+      <c r="X2" s="167"/>
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="213"/>
+      <c r="AB2" s="213"/>
+      <c r="AC2" s="213"/>
+      <c r="AD2" s="213"/>
+      <c r="AE2" s="213"/>
+      <c r="AF2" s="213"/>
+      <c r="AG2" s="213"/>
+      <c r="AH2" s="214"/>
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="121" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="122"/>
       <c r="C3" s="122"/>
@@ -9217,194 +9548,194 @@
       <c r="F3" s="122"/>
       <c r="G3" s="122"/>
       <c r="H3" s="121" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I3" s="122"/>
       <c r="J3" s="122"/>
       <c r="K3" s="122"/>
       <c r="L3" s="122"/>
       <c r="M3" s="123"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
-      <c r="R3" s="225"/>
-      <c r="S3" s="225"/>
-      <c r="T3" s="225"/>
-      <c r="U3" s="225"/>
-      <c r="V3" s="225"/>
-      <c r="W3" s="225"/>
-      <c r="X3" s="226"/>
-      <c r="Z3" s="215" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA3" s="211"/>
-      <c r="AB3" s="211"/>
-      <c r="AC3" s="211"/>
-      <c r="AD3" s="212"/>
-      <c r="AE3" s="215" t="s">
-        <v>275</v>
-      </c>
-      <c r="AF3" s="222"/>
-      <c r="AG3" s="222"/>
-      <c r="AH3" s="223"/>
+      <c r="O3" s="217"/>
+      <c r="P3" s="218"/>
+      <c r="Q3" s="218"/>
+      <c r="R3" s="218"/>
+      <c r="S3" s="218"/>
+      <c r="T3" s="218"/>
+      <c r="U3" s="218"/>
+      <c r="V3" s="218"/>
+      <c r="W3" s="218"/>
+      <c r="X3" s="219"/>
+      <c r="Z3" s="208" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA3" s="204"/>
+      <c r="AB3" s="204"/>
+      <c r="AC3" s="204"/>
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="208" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF3" s="215"/>
+      <c r="AG3" s="215"/>
+      <c r="AH3" s="216"/>
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="S4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="W4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AF4" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG4" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="AH4" s="51" t="s">
         <v>278</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH4" s="51" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -9413,66 +9744,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AA5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AB5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AC5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AF5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -9491,13 +9822,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -9509,16 +9840,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -9537,7 +9868,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -9549,16 +9880,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -9661,7 +9992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8D5FDC-1119-4995-AFF6-CB9868EEC023}">
   <dimension ref="A1:AE36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9698,7 +10029,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="124" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -9710,7 +10041,7 @@
       <c r="I1" s="125"/>
       <c r="J1" s="126"/>
       <c r="L1" s="124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M1" s="125"/>
       <c r="N1" s="125"/>
@@ -9721,227 +10052,227 @@
       <c r="S1" s="125"/>
       <c r="T1" s="125"/>
       <c r="U1" s="126"/>
-      <c r="W1" s="216" t="s">
-        <v>272</v>
-      </c>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="217"/>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="217"/>
-      <c r="AE1" s="218"/>
+      <c r="W1" s="209" t="s">
+        <v>276</v>
+      </c>
+      <c r="X1" s="210"/>
+      <c r="Y1" s="210"/>
+      <c r="Z1" s="210"/>
+      <c r="AA1" s="210"/>
+      <c r="AB1" s="210"/>
+      <c r="AC1" s="210"/>
+      <c r="AD1" s="210"/>
+      <c r="AE1" s="211"/>
     </row>
     <row r="2" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A2" s="172"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="174"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="173"/>
-      <c r="Q2" s="173"/>
-      <c r="R2" s="173"/>
-      <c r="S2" s="173"/>
-      <c r="T2" s="173"/>
-      <c r="U2" s="174"/>
-      <c r="W2" s="219"/>
-      <c r="X2" s="220"/>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="220"/>
-      <c r="AA2" s="220"/>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="220"/>
-      <c r="AD2" s="220"/>
-      <c r="AE2" s="221"/>
+      <c r="A2" s="165"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="167"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="166"/>
+      <c r="Q2" s="166"/>
+      <c r="R2" s="166"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="166"/>
+      <c r="U2" s="167"/>
+      <c r="W2" s="212"/>
+      <c r="X2" s="213"/>
+      <c r="Y2" s="213"/>
+      <c r="Z2" s="213"/>
+      <c r="AA2" s="213"/>
+      <c r="AB2" s="213"/>
+      <c r="AC2" s="213"/>
+      <c r="AD2" s="213"/>
+      <c r="AE2" s="214"/>
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="121" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="122"/>
       <c r="C3" s="122"/>
       <c r="D3" s="122"/>
       <c r="E3" s="121" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F3" s="122"/>
       <c r="G3" s="122"/>
       <c r="H3" s="122"/>
       <c r="I3" s="122"/>
       <c r="J3" s="123"/>
-      <c r="L3" s="224"/>
-      <c r="M3" s="225"/>
-      <c r="N3" s="225"/>
-      <c r="O3" s="225"/>
-      <c r="P3" s="225"/>
-      <c r="Q3" s="225"/>
-      <c r="R3" s="225"/>
-      <c r="S3" s="225"/>
-      <c r="T3" s="225"/>
-      <c r="U3" s="226"/>
-      <c r="W3" s="215" t="s">
-        <v>272</v>
-      </c>
-      <c r="X3" s="211"/>
-      <c r="Y3" s="211"/>
-      <c r="Z3" s="211"/>
-      <c r="AA3" s="212"/>
-      <c r="AB3" s="215" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC3" s="222"/>
-      <c r="AD3" s="222"/>
-      <c r="AE3" s="223"/>
+      <c r="L3" s="217"/>
+      <c r="M3" s="218"/>
+      <c r="N3" s="218"/>
+      <c r="O3" s="218"/>
+      <c r="P3" s="218"/>
+      <c r="Q3" s="218"/>
+      <c r="R3" s="218"/>
+      <c r="S3" s="218"/>
+      <c r="T3" s="218"/>
+      <c r="U3" s="219"/>
+      <c r="W3" s="208" t="s">
+        <v>276</v>
+      </c>
+      <c r="X3" s="204"/>
+      <c r="Y3" s="204"/>
+      <c r="Z3" s="204"/>
+      <c r="AA3" s="205"/>
+      <c r="AB3" s="208" t="s">
+        <v>279</v>
+      </c>
+      <c r="AC3" s="215"/>
+      <c r="AD3" s="215"/>
+      <c r="AE3" s="216"/>
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L4" s="41" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="R4" s="40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="S4" s="40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="U4" s="42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="W4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -9950,57 +10281,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="X5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Y5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Z5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AC5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AD5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>246</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -10025,16 +10356,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -10059,16 +10390,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -10164,7 +10495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD588F34-D77B-42F6-9174-CC0FF762963C}">
   <dimension ref="B2:H37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -10178,26 +10509,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="21">
-      <c r="B2" s="227" t="s">
-        <v>300</v>
-      </c>
-      <c r="C2" s="227"/>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="227"/>
-      <c r="H2" s="227"/>
+      <c r="B2" s="220" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
     </row>
     <row r="3" spans="2:8" ht="17.25" customHeight="1">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="228" t="s">
-        <v>302</v>
-      </c>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
+        <v>305</v>
+      </c>
+      <c r="D3" s="221" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
       <c r="G3" s="47"/>
       <c r="H3" s="45"/>
     </row>
@@ -10205,12 +10536,12 @@
       <c r="B4" s="46"/>
       <c r="C4" s="47"/>
       <c r="D4" s="52" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="228" t="s">
-        <v>304</v>
-      </c>
-      <c r="F4" s="228"/>
+        <v>307</v>
+      </c>
+      <c r="E4" s="221" t="s">
+        <v>308</v>
+      </c>
+      <c r="F4" s="221"/>
       <c r="G4" s="47"/>
       <c r="H4" s="45"/>
     </row>
@@ -10218,12 +10549,12 @@
       <c r="B5" s="46"/>
       <c r="C5" s="47"/>
       <c r="D5" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="E5" s="228" t="s">
-        <v>306</v>
-      </c>
-      <c r="F5" s="228"/>
+        <v>309</v>
+      </c>
+      <c r="E5" s="221" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5" s="221"/>
       <c r="G5" s="47"/>
       <c r="H5" s="45"/>
     </row>
@@ -10283,339 +10614,339 @@
     </row>
     <row r="13" spans="2:8" ht="15">
       <c r="B13" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="2:8" ht="15">
       <c r="B14" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15">
       <c r="B16" s="24" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="23" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="23" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="23" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15">
       <c r="B26" s="24" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="23" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="23" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="23" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D35" s="1">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -11496,7 +11827,7 @@
         <f>Define!C5</f>
         <v>0</v>
       </c>
-      <c r="E2" s="139"/>
+      <c r="E2" s="232"/>
     </row>
     <row r="3" spans="2:42">
       <c r="C3" s="87" t="s">
@@ -11506,7 +11837,7 @@
         <f>Define!C6</f>
         <v>0</v>
       </c>
-      <c r="E3" s="139"/>
+      <c r="E3" s="232"/>
     </row>
     <row r="4" spans="2:42">
       <c r="C4"/>
@@ -11519,33 +11850,33 @@
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="123"/>
-      <c r="H5" s="149" t="s">
+      <c r="H5" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
-      <c r="O5" s="150"/>
-      <c r="P5" s="150"/>
-      <c r="Q5" s="150"/>
-      <c r="R5" s="151"/>
-      <c r="U5" s="149" t="s">
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="149"/>
+      <c r="R5" s="150"/>
+      <c r="U5" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="V5" s="150"/>
-      <c r="W5" s="150"/>
-      <c r="X5" s="150"/>
-      <c r="Y5" s="150"/>
-      <c r="Z5" s="150"/>
-      <c r="AA5" s="150"/>
-      <c r="AB5" s="150"/>
-      <c r="AC5" s="150"/>
-      <c r="AD5" s="150"/>
-      <c r="AE5" s="150"/>
-      <c r="AF5" s="151"/>
+      <c r="V5" s="149"/>
+      <c r="W5" s="149"/>
+      <c r="X5" s="149"/>
+      <c r="Y5" s="149"/>
+      <c r="Z5" s="149"/>
+      <c r="AA5" s="149"/>
+      <c r="AB5" s="149"/>
+      <c r="AC5" s="149"/>
+      <c r="AD5" s="149"/>
+      <c r="AE5" s="149"/>
+      <c r="AF5" s="150"/>
       <c r="AG5" s="74"/>
       <c r="AH5" s="74"/>
       <c r="AI5" s="74"/>
@@ -11581,20 +11912,20 @@
       <c r="P6" s="130"/>
       <c r="Q6" s="130"/>
       <c r="R6" s="131"/>
-      <c r="U6" s="140" t="s">
+      <c r="U6" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="V6" s="141"/>
-      <c r="W6" s="141"/>
-      <c r="X6" s="141"/>
-      <c r="Y6" s="141"/>
-      <c r="Z6" s="141"/>
-      <c r="AA6" s="141"/>
-      <c r="AB6" s="141"/>
-      <c r="AC6" s="141"/>
-      <c r="AD6" s="141"/>
-      <c r="AE6" s="141"/>
-      <c r="AF6" s="142"/>
+      <c r="V6" s="140"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="140"/>
+      <c r="Z6" s="140"/>
+      <c r="AA6" s="140"/>
+      <c r="AB6" s="140"/>
+      <c r="AC6" s="140"/>
+      <c r="AD6" s="140"/>
+      <c r="AE6" s="140"/>
+      <c r="AF6" s="141"/>
       <c r="AG6" s="74"/>
       <c r="AH6" s="74"/>
       <c r="AI6" s="74"/>
@@ -11628,18 +11959,18 @@
       <c r="P7" s="133"/>
       <c r="Q7" s="133"/>
       <c r="R7" s="134"/>
-      <c r="U7" s="143"/>
-      <c r="V7" s="144"/>
-      <c r="W7" s="144"/>
-      <c r="X7" s="144"/>
-      <c r="Y7" s="144"/>
-      <c r="Z7" s="144"/>
-      <c r="AA7" s="144"/>
-      <c r="AB7" s="144"/>
-      <c r="AC7" s="144"/>
-      <c r="AD7" s="144"/>
-      <c r="AE7" s="144"/>
-      <c r="AF7" s="145"/>
+      <c r="U7" s="142"/>
+      <c r="V7" s="143"/>
+      <c r="W7" s="143"/>
+      <c r="X7" s="143"/>
+      <c r="Y7" s="143"/>
+      <c r="Z7" s="143"/>
+      <c r="AA7" s="143"/>
+      <c r="AB7" s="143"/>
+      <c r="AC7" s="143"/>
+      <c r="AD7" s="143"/>
+      <c r="AE7" s="143"/>
+      <c r="AF7" s="144"/>
       <c r="AG7" s="74"/>
       <c r="AH7" s="74"/>
       <c r="AI7" s="74"/>
@@ -11673,18 +12004,18 @@
       <c r="P8" s="133"/>
       <c r="Q8" s="133"/>
       <c r="R8" s="134"/>
-      <c r="U8" s="143"/>
-      <c r="V8" s="144"/>
-      <c r="W8" s="144"/>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="144"/>
-      <c r="Z8" s="144"/>
-      <c r="AA8" s="144"/>
-      <c r="AB8" s="144"/>
-      <c r="AC8" s="144"/>
-      <c r="AD8" s="144"/>
-      <c r="AE8" s="144"/>
-      <c r="AF8" s="145"/>
+      <c r="U8" s="142"/>
+      <c r="V8" s="143"/>
+      <c r="W8" s="143"/>
+      <c r="X8" s="143"/>
+      <c r="Y8" s="143"/>
+      <c r="Z8" s="143"/>
+      <c r="AA8" s="143"/>
+      <c r="AB8" s="143"/>
+      <c r="AC8" s="143"/>
+      <c r="AD8" s="143"/>
+      <c r="AE8" s="143"/>
+      <c r="AF8" s="144"/>
       <c r="AG8" s="74"/>
       <c r="AH8" s="74"/>
       <c r="AI8" s="74"/>
@@ -11718,18 +12049,18 @@
       <c r="P9" s="133"/>
       <c r="Q9" s="133"/>
       <c r="R9" s="134"/>
-      <c r="U9" s="143"/>
-      <c r="V9" s="144"/>
-      <c r="W9" s="144"/>
-      <c r="X9" s="144"/>
-      <c r="Y9" s="144"/>
-      <c r="Z9" s="144"/>
-      <c r="AA9" s="144"/>
-      <c r="AB9" s="144"/>
-      <c r="AC9" s="144"/>
-      <c r="AD9" s="144"/>
-      <c r="AE9" s="144"/>
-      <c r="AF9" s="145"/>
+      <c r="U9" s="142"/>
+      <c r="V9" s="143"/>
+      <c r="W9" s="143"/>
+      <c r="X9" s="143"/>
+      <c r="Y9" s="143"/>
+      <c r="Z9" s="143"/>
+      <c r="AA9" s="143"/>
+      <c r="AB9" s="143"/>
+      <c r="AC9" s="143"/>
+      <c r="AD9" s="143"/>
+      <c r="AE9" s="143"/>
+      <c r="AF9" s="144"/>
       <c r="AG9" s="74"/>
       <c r="AH9" s="74"/>
       <c r="AI9" s="74"/>
@@ -11756,18 +12087,18 @@
       <c r="P10" s="133"/>
       <c r="Q10" s="133"/>
       <c r="R10" s="134"/>
-      <c r="U10" s="143"/>
-      <c r="V10" s="144"/>
-      <c r="W10" s="144"/>
-      <c r="X10" s="144"/>
-      <c r="Y10" s="144"/>
-      <c r="Z10" s="144"/>
-      <c r="AA10" s="144"/>
-      <c r="AB10" s="144"/>
-      <c r="AC10" s="144"/>
-      <c r="AD10" s="144"/>
-      <c r="AE10" s="144"/>
-      <c r="AF10" s="145"/>
+      <c r="U10" s="142"/>
+      <c r="V10" s="143"/>
+      <c r="W10" s="143"/>
+      <c r="X10" s="143"/>
+      <c r="Y10" s="143"/>
+      <c r="Z10" s="143"/>
+      <c r="AA10" s="143"/>
+      <c r="AB10" s="143"/>
+      <c r="AC10" s="143"/>
+      <c r="AD10" s="143"/>
+      <c r="AE10" s="143"/>
+      <c r="AF10" s="144"/>
       <c r="AG10" s="74"/>
       <c r="AH10" s="74"/>
       <c r="AI10" s="74"/>
@@ -11795,18 +12126,18 @@
       <c r="P11" s="133"/>
       <c r="Q11" s="133"/>
       <c r="R11" s="134"/>
-      <c r="U11" s="143"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="144"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="144"/>
-      <c r="AC11" s="144"/>
-      <c r="AD11" s="144"/>
-      <c r="AE11" s="144"/>
-      <c r="AF11" s="145"/>
+      <c r="U11" s="142"/>
+      <c r="V11" s="143"/>
+      <c r="W11" s="143"/>
+      <c r="X11" s="143"/>
+      <c r="Y11" s="143"/>
+      <c r="Z11" s="143"/>
+      <c r="AA11" s="143"/>
+      <c r="AB11" s="143"/>
+      <c r="AC11" s="143"/>
+      <c r="AD11" s="143"/>
+      <c r="AE11" s="143"/>
+      <c r="AF11" s="144"/>
       <c r="AG11" s="74"/>
       <c r="AH11" s="74"/>
       <c r="AI11" s="74"/>
@@ -11831,18 +12162,18 @@
       <c r="P12" s="133"/>
       <c r="Q12" s="133"/>
       <c r="R12" s="134"/>
-      <c r="U12" s="143"/>
-      <c r="V12" s="144"/>
-      <c r="W12" s="144"/>
-      <c r="X12" s="144"/>
-      <c r="Y12" s="144"/>
-      <c r="Z12" s="144"/>
-      <c r="AA12" s="144"/>
-      <c r="AB12" s="144"/>
-      <c r="AC12" s="144"/>
-      <c r="AD12" s="144"/>
-      <c r="AE12" s="144"/>
-      <c r="AF12" s="145"/>
+      <c r="U12" s="142"/>
+      <c r="V12" s="143"/>
+      <c r="W12" s="143"/>
+      <c r="X12" s="143"/>
+      <c r="Y12" s="143"/>
+      <c r="Z12" s="143"/>
+      <c r="AA12" s="143"/>
+      <c r="AB12" s="143"/>
+      <c r="AC12" s="143"/>
+      <c r="AD12" s="143"/>
+      <c r="AE12" s="143"/>
+      <c r="AF12" s="144"/>
       <c r="AG12" s="74"/>
       <c r="AH12" s="74"/>
       <c r="AI12" s="74"/>
@@ -11866,18 +12197,18 @@
       <c r="P13" s="133"/>
       <c r="Q13" s="133"/>
       <c r="R13" s="134"/>
-      <c r="U13" s="143"/>
-      <c r="V13" s="144"/>
-      <c r="W13" s="144"/>
-      <c r="X13" s="144"/>
-      <c r="Y13" s="144"/>
-      <c r="Z13" s="144"/>
-      <c r="AA13" s="144"/>
-      <c r="AB13" s="144"/>
-      <c r="AC13" s="144"/>
-      <c r="AD13" s="144"/>
-      <c r="AE13" s="144"/>
-      <c r="AF13" s="145"/>
+      <c r="U13" s="142"/>
+      <c r="V13" s="143"/>
+      <c r="W13" s="143"/>
+      <c r="X13" s="143"/>
+      <c r="Y13" s="143"/>
+      <c r="Z13" s="143"/>
+      <c r="AA13" s="143"/>
+      <c r="AB13" s="143"/>
+      <c r="AC13" s="143"/>
+      <c r="AD13" s="143"/>
+      <c r="AE13" s="143"/>
+      <c r="AF13" s="144"/>
       <c r="AG13" s="74"/>
       <c r="AH13" s="74"/>
       <c r="AI13" s="74"/>
@@ -11901,18 +12232,18 @@
       <c r="P14" s="133"/>
       <c r="Q14" s="133"/>
       <c r="R14" s="134"/>
-      <c r="U14" s="143"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="144"/>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="145"/>
+      <c r="U14" s="142"/>
+      <c r="V14" s="143"/>
+      <c r="W14" s="143"/>
+      <c r="X14" s="143"/>
+      <c r="Y14" s="143"/>
+      <c r="Z14" s="143"/>
+      <c r="AA14" s="143"/>
+      <c r="AB14" s="143"/>
+      <c r="AC14" s="143"/>
+      <c r="AD14" s="143"/>
+      <c r="AE14" s="143"/>
+      <c r="AF14" s="144"/>
       <c r="AG14" s="74"/>
       <c r="AH14" s="74"/>
       <c r="AI14" s="74"/>
@@ -11936,18 +12267,18 @@
       <c r="P15" s="133"/>
       <c r="Q15" s="133"/>
       <c r="R15" s="134"/>
-      <c r="U15" s="143"/>
-      <c r="V15" s="144"/>
-      <c r="W15" s="144"/>
-      <c r="X15" s="144"/>
-      <c r="Y15" s="144"/>
-      <c r="Z15" s="144"/>
-      <c r="AA15" s="144"/>
-      <c r="AB15" s="144"/>
-      <c r="AC15" s="144"/>
-      <c r="AD15" s="144"/>
-      <c r="AE15" s="144"/>
-      <c r="AF15" s="145"/>
+      <c r="U15" s="142"/>
+      <c r="V15" s="143"/>
+      <c r="W15" s="143"/>
+      <c r="X15" s="143"/>
+      <c r="Y15" s="143"/>
+      <c r="Z15" s="143"/>
+      <c r="AA15" s="143"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="143"/>
+      <c r="AD15" s="143"/>
+      <c r="AE15" s="143"/>
+      <c r="AF15" s="144"/>
       <c r="AG15" s="74"/>
       <c r="AH15" s="74"/>
       <c r="AI15" s="74"/>
@@ -11971,18 +12302,18 @@
       <c r="P16" s="133"/>
       <c r="Q16" s="133"/>
       <c r="R16" s="134"/>
-      <c r="U16" s="143"/>
-      <c r="V16" s="144"/>
-      <c r="W16" s="144"/>
-      <c r="X16" s="144"/>
-      <c r="Y16" s="144"/>
-      <c r="Z16" s="144"/>
-      <c r="AA16" s="144"/>
-      <c r="AB16" s="144"/>
-      <c r="AC16" s="144"/>
-      <c r="AD16" s="144"/>
-      <c r="AE16" s="144"/>
-      <c r="AF16" s="145"/>
+      <c r="U16" s="142"/>
+      <c r="V16" s="143"/>
+      <c r="W16" s="143"/>
+      <c r="X16" s="143"/>
+      <c r="Y16" s="143"/>
+      <c r="Z16" s="143"/>
+      <c r="AA16" s="143"/>
+      <c r="AB16" s="143"/>
+      <c r="AC16" s="143"/>
+      <c r="AD16" s="143"/>
+      <c r="AE16" s="143"/>
+      <c r="AF16" s="144"/>
       <c r="AG16" s="74"/>
       <c r="AH16" s="74"/>
       <c r="AI16" s="74"/>
@@ -12006,18 +12337,18 @@
       <c r="P17" s="133"/>
       <c r="Q17" s="133"/>
       <c r="R17" s="134"/>
-      <c r="U17" s="143"/>
-      <c r="V17" s="144"/>
-      <c r="W17" s="144"/>
-      <c r="X17" s="144"/>
-      <c r="Y17" s="144"/>
-      <c r="Z17" s="144"/>
-      <c r="AA17" s="144"/>
-      <c r="AB17" s="144"/>
-      <c r="AC17" s="144"/>
-      <c r="AD17" s="144"/>
-      <c r="AE17" s="144"/>
-      <c r="AF17" s="145"/>
+      <c r="U17" s="142"/>
+      <c r="V17" s="143"/>
+      <c r="W17" s="143"/>
+      <c r="X17" s="143"/>
+      <c r="Y17" s="143"/>
+      <c r="Z17" s="143"/>
+      <c r="AA17" s="143"/>
+      <c r="AB17" s="143"/>
+      <c r="AC17" s="143"/>
+      <c r="AD17" s="143"/>
+      <c r="AE17" s="143"/>
+      <c r="AF17" s="144"/>
       <c r="AG17" s="74"/>
       <c r="AH17" s="74"/>
       <c r="AI17" s="74"/>
@@ -12041,18 +12372,18 @@
       <c r="P18" s="133"/>
       <c r="Q18" s="133"/>
       <c r="R18" s="134"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="144"/>
-      <c r="W18" s="144"/>
-      <c r="X18" s="144"/>
-      <c r="Y18" s="144"/>
-      <c r="Z18" s="144"/>
-      <c r="AA18" s="144"/>
-      <c r="AB18" s="144"/>
-      <c r="AC18" s="144"/>
-      <c r="AD18" s="144"/>
-      <c r="AE18" s="144"/>
-      <c r="AF18" s="145"/>
+      <c r="U18" s="142"/>
+      <c r="V18" s="143"/>
+      <c r="W18" s="143"/>
+      <c r="X18" s="143"/>
+      <c r="Y18" s="143"/>
+      <c r="Z18" s="143"/>
+      <c r="AA18" s="143"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="143"/>
+      <c r="AD18" s="143"/>
+      <c r="AE18" s="143"/>
+      <c r="AF18" s="144"/>
       <c r="AG18" s="74"/>
       <c r="AH18" s="74"/>
       <c r="AI18" s="74"/>
@@ -12076,18 +12407,18 @@
       <c r="P19" s="133"/>
       <c r="Q19" s="133"/>
       <c r="R19" s="134"/>
-      <c r="U19" s="143"/>
-      <c r="V19" s="144"/>
-      <c r="W19" s="144"/>
-      <c r="X19" s="144"/>
-      <c r="Y19" s="144"/>
-      <c r="Z19" s="144"/>
-      <c r="AA19" s="144"/>
-      <c r="AB19" s="144"/>
-      <c r="AC19" s="144"/>
-      <c r="AD19" s="144"/>
-      <c r="AE19" s="144"/>
-      <c r="AF19" s="145"/>
+      <c r="U19" s="142"/>
+      <c r="V19" s="143"/>
+      <c r="W19" s="143"/>
+      <c r="X19" s="143"/>
+      <c r="Y19" s="143"/>
+      <c r="Z19" s="143"/>
+      <c r="AA19" s="143"/>
+      <c r="AB19" s="143"/>
+      <c r="AC19" s="143"/>
+      <c r="AD19" s="143"/>
+      <c r="AE19" s="143"/>
+      <c r="AF19" s="144"/>
       <c r="AG19" s="74"/>
       <c r="AH19" s="74"/>
       <c r="AI19" s="74"/>
@@ -12111,18 +12442,18 @@
       <c r="P20" s="133"/>
       <c r="Q20" s="133"/>
       <c r="R20" s="134"/>
-      <c r="U20" s="143"/>
-      <c r="V20" s="144"/>
-      <c r="W20" s="144"/>
-      <c r="X20" s="144"/>
-      <c r="Y20" s="144"/>
-      <c r="Z20" s="144"/>
-      <c r="AA20" s="144"/>
-      <c r="AB20" s="144"/>
-      <c r="AC20" s="144"/>
-      <c r="AD20" s="144"/>
-      <c r="AE20" s="144"/>
-      <c r="AF20" s="145"/>
+      <c r="U20" s="142"/>
+      <c r="V20" s="143"/>
+      <c r="W20" s="143"/>
+      <c r="X20" s="143"/>
+      <c r="Y20" s="143"/>
+      <c r="Z20" s="143"/>
+      <c r="AA20" s="143"/>
+      <c r="AB20" s="143"/>
+      <c r="AC20" s="143"/>
+      <c r="AD20" s="143"/>
+      <c r="AE20" s="143"/>
+      <c r="AF20" s="144"/>
       <c r="AG20" s="74"/>
       <c r="AH20" s="74"/>
       <c r="AI20" s="74"/>
@@ -12146,18 +12477,18 @@
       <c r="P21" s="133"/>
       <c r="Q21" s="133"/>
       <c r="R21" s="134"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="144"/>
-      <c r="W21" s="144"/>
-      <c r="X21" s="144"/>
-      <c r="Y21" s="144"/>
-      <c r="Z21" s="144"/>
-      <c r="AA21" s="144"/>
-      <c r="AB21" s="144"/>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="145"/>
+      <c r="U21" s="142"/>
+      <c r="V21" s="143"/>
+      <c r="W21" s="143"/>
+      <c r="X21" s="143"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="143"/>
+      <c r="AA21" s="143"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="143"/>
+      <c r="AD21" s="143"/>
+      <c r="AE21" s="143"/>
+      <c r="AF21" s="144"/>
       <c r="AG21" s="74"/>
       <c r="AH21" s="74"/>
       <c r="AI21" s="74"/>
@@ -12181,18 +12512,18 @@
       <c r="P22" s="133"/>
       <c r="Q22" s="133"/>
       <c r="R22" s="134"/>
-      <c r="U22" s="143"/>
-      <c r="V22" s="144"/>
-      <c r="W22" s="144"/>
-      <c r="X22" s="144"/>
-      <c r="Y22" s="144"/>
-      <c r="Z22" s="144"/>
-      <c r="AA22" s="144"/>
-      <c r="AB22" s="144"/>
-      <c r="AC22" s="144"/>
-      <c r="AD22" s="144"/>
-      <c r="AE22" s="144"/>
-      <c r="AF22" s="145"/>
+      <c r="U22" s="142"/>
+      <c r="V22" s="143"/>
+      <c r="W22" s="143"/>
+      <c r="X22" s="143"/>
+      <c r="Y22" s="143"/>
+      <c r="Z22" s="143"/>
+      <c r="AA22" s="143"/>
+      <c r="AB22" s="143"/>
+      <c r="AC22" s="143"/>
+      <c r="AD22" s="143"/>
+      <c r="AE22" s="143"/>
+      <c r="AF22" s="144"/>
       <c r="AG22" s="74"/>
       <c r="AH22" s="74"/>
       <c r="AI22" s="74"/>
@@ -12216,18 +12547,18 @@
       <c r="P23" s="133"/>
       <c r="Q23" s="133"/>
       <c r="R23" s="134"/>
-      <c r="U23" s="143"/>
-      <c r="V23" s="144"/>
-      <c r="W23" s="144"/>
-      <c r="X23" s="144"/>
-      <c r="Y23" s="144"/>
-      <c r="Z23" s="144"/>
-      <c r="AA23" s="144"/>
-      <c r="AB23" s="144"/>
-      <c r="AC23" s="144"/>
-      <c r="AD23" s="144"/>
-      <c r="AE23" s="144"/>
-      <c r="AF23" s="145"/>
+      <c r="U23" s="142"/>
+      <c r="V23" s="143"/>
+      <c r="W23" s="143"/>
+      <c r="X23" s="143"/>
+      <c r="Y23" s="143"/>
+      <c r="Z23" s="143"/>
+      <c r="AA23" s="143"/>
+      <c r="AB23" s="143"/>
+      <c r="AC23" s="143"/>
+      <c r="AD23" s="143"/>
+      <c r="AE23" s="143"/>
+      <c r="AF23" s="144"/>
       <c r="AG23" s="74"/>
       <c r="AH23" s="74"/>
       <c r="AI23" s="74"/>
@@ -12251,18 +12582,18 @@
       <c r="P24" s="136"/>
       <c r="Q24" s="136"/>
       <c r="R24" s="137"/>
-      <c r="U24" s="146"/>
-      <c r="V24" s="147"/>
-      <c r="W24" s="147"/>
-      <c r="X24" s="147"/>
-      <c r="Y24" s="147"/>
-      <c r="Z24" s="147"/>
-      <c r="AA24" s="147"/>
-      <c r="AB24" s="147"/>
-      <c r="AC24" s="147"/>
-      <c r="AD24" s="147"/>
-      <c r="AE24" s="147"/>
-      <c r="AF24" s="148"/>
+      <c r="U24" s="145"/>
+      <c r="V24" s="146"/>
+      <c r="W24" s="146"/>
+      <c r="X24" s="146"/>
+      <c r="Y24" s="146"/>
+      <c r="Z24" s="146"/>
+      <c r="AA24" s="146"/>
+      <c r="AB24" s="146"/>
+      <c r="AC24" s="146"/>
+      <c r="AD24" s="146"/>
+      <c r="AE24" s="146"/>
+      <c r="AF24" s="147"/>
       <c r="AG24" s="74"/>
       <c r="AH24" s="74"/>
       <c r="AI24" s="74"/>
@@ -12345,19 +12676,19 @@
       <c r="AP26" s="74"/>
     </row>
     <row r="27" spans="8:42" ht="13.5" customHeight="1">
-      <c r="H27" s="149" t="s">
+      <c r="H27" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="150"/>
-      <c r="J27" s="150"/>
-      <c r="K27" s="150"/>
-      <c r="L27" s="150"/>
-      <c r="M27" s="150"/>
-      <c r="N27" s="150"/>
-      <c r="O27" s="150"/>
-      <c r="P27" s="150"/>
-      <c r="Q27" s="150"/>
-      <c r="R27" s="151"/>
+      <c r="I27" s="149"/>
+      <c r="J27" s="149"/>
+      <c r="K27" s="149"/>
+      <c r="L27" s="149"/>
+      <c r="M27" s="149"/>
+      <c r="N27" s="149"/>
+      <c r="O27" s="149"/>
+      <c r="P27" s="149"/>
+      <c r="Q27" s="149"/>
+      <c r="R27" s="150"/>
       <c r="U27" s="74"/>
       <c r="V27" s="74"/>
       <c r="W27" s="74"/>
@@ -12996,19 +13327,19 @@
     <row r="73" spans="8:18" ht="13.5" customHeight="1"/>
     <row r="74" spans="8:18" ht="13.5" customHeight="1"/>
     <row r="75" spans="8:18" ht="13.5" customHeight="1">
-      <c r="H75" s="149" t="s">
+      <c r="H75" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="I75" s="150"/>
-      <c r="J75" s="150"/>
-      <c r="K75" s="150"/>
-      <c r="L75" s="150"/>
-      <c r="M75" s="150"/>
-      <c r="N75" s="150"/>
-      <c r="O75" s="150"/>
-      <c r="P75" s="150"/>
-      <c r="Q75" s="150"/>
-      <c r="R75" s="151"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="149"/>
+      <c r="K75" s="149"/>
+      <c r="L75" s="149"/>
+      <c r="M75" s="149"/>
+      <c r="N75" s="149"/>
+      <c r="O75" s="149"/>
+      <c r="P75" s="149"/>
+      <c r="Q75" s="149"/>
+      <c r="R75" s="150"/>
     </row>
     <row r="76" spans="8:18" ht="13.5" customHeight="1">
       <c r="H76" s="129" t="s">
@@ -13618,22 +13949,24 @@
       <c r="C2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="155" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="156"/>
-      <c r="F2" s="157"/>
+      <c r="D2" s="154">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="222"/>
+      <c r="F2" s="223"/>
       <c r="G2"/>
     </row>
     <row r="3" spans="3:19">
       <c r="C3" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="158" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
+      <c r="D3" s="156">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="224"/>
+      <c r="F3" s="225"/>
       <c r="G3"/>
     </row>
     <row r="4" spans="3:19">
@@ -13642,42 +13975,42 @@
     </row>
     <row r="5" spans="3:19" ht="19.5" customHeight="1">
       <c r="C5" s="121" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="123"/>
       <c r="G5"/>
-      <c r="I5" s="152" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="154"/>
+      <c r="I5" s="151" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="153"/>
     </row>
     <row r="6" spans="3:19" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="F6" s="42" t="s">
         <v>78</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>80</v>
       </c>
       <c r="G6"/>
       <c r="I6" s="129" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J6" s="130"/>
       <c r="K6" s="130"/>
@@ -13692,16 +14025,16 @@
     </row>
     <row r="7" spans="3:19" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>85</v>
       </c>
       <c r="G7"/>
       <c r="I7" s="132"/>
@@ -14500,24 +14833,26 @@
       <c r="C2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="161" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="163"/>
+      <c r="D2" s="158">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
       <c r="H2"/>
     </row>
     <row r="3" spans="3:20">
       <c r="C3" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="158" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="160"/>
+      <c r="D3" s="156">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="225"/>
       <c r="H3"/>
     </row>
     <row r="4" spans="3:20">
@@ -14526,46 +14861,46 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="121" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="122"/>
       <c r="G5" s="123"/>
       <c r="H5"/>
-      <c r="J5" s="152" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="154"/>
+      <c r="J5" s="151" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="153"/>
     </row>
     <row r="6" spans="3:20" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="G6" s="42" t="s">
         <v>78</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>80</v>
       </c>
       <c r="H6"/>
       <c r="J6" s="129" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K6" s="130"/>
       <c r="L6" s="130"/>
@@ -14580,19 +14915,19 @@
     </row>
     <row r="7" spans="3:20" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>85</v>
       </c>
       <c r="H7"/>
       <c r="J7" s="132"/>
@@ -15372,6 +15707,904 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385F985E-2870-4308-82B2-23D8BBD3D2EC}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:T84"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="3.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="43" customWidth="1"/>
+    <col min="4" max="7" width="15.875" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="44" customWidth="1"/>
+    <col min="9" max="9" width="3.375" customWidth="1"/>
+    <col min="10" max="10" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:20">
+      <c r="C1" s="83"/>
+      <c r="H1"/>
+    </row>
+    <row r="2" spans="3:20">
+      <c r="C2" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="158">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2"/>
+    </row>
+    <row r="3" spans="3:20">
+      <c r="C3" s="91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="156">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="225"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="3:20">
+      <c r="C4"/>
+      <c r="H4" s="90"/>
+    </row>
+    <row r="5" spans="3:20" ht="19.5" customHeight="1">
+      <c r="C5" s="121" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="123"/>
+      <c r="H5"/>
+      <c r="J5" s="151" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="153"/>
+    </row>
+    <row r="6" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C6" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6"/>
+      <c r="J6" s="129" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
+      <c r="S6" s="130"/>
+      <c r="T6" s="131"/>
+    </row>
+    <row r="7" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="133"/>
+      <c r="T7" s="134"/>
+    </row>
+    <row r="8" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C8" s="26"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="27"/>
+      <c r="H8"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="134"/>
+    </row>
+    <row r="9" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C9" s="26"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="27"/>
+      <c r="H9"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="134"/>
+    </row>
+    <row r="10" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C10" s="26"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="27"/>
+      <c r="H10"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="133"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="133"/>
+      <c r="T10" s="134"/>
+    </row>
+    <row r="11" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C11" s="26"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="27"/>
+      <c r="H11"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="134"/>
+    </row>
+    <row r="12" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C12" s="26"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="44"/>
+      <c r="H12"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="134"/>
+    </row>
+    <row r="13" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G13" s="44"/>
+      <c r="H13"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="134"/>
+    </row>
+    <row r="14" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G14" s="44"/>
+      <c r="H14"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="134"/>
+    </row>
+    <row r="15" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G15" s="44"/>
+      <c r="H15"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="134"/>
+    </row>
+    <row r="16" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G16" s="44"/>
+      <c r="H16"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="133"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="133"/>
+      <c r="T16" s="134"/>
+    </row>
+    <row r="17" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G17" s="44"/>
+      <c r="H17"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="133"/>
+      <c r="P17" s="133"/>
+      <c r="Q17" s="133"/>
+      <c r="R17" s="133"/>
+      <c r="S17" s="133"/>
+      <c r="T17" s="134"/>
+    </row>
+    <row r="18" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G18" s="44"/>
+      <c r="H18"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
+      <c r="N18" s="133"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="133"/>
+      <c r="Q18" s="133"/>
+      <c r="R18" s="133"/>
+      <c r="S18" s="133"/>
+      <c r="T18" s="134"/>
+    </row>
+    <row r="19" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G19" s="44"/>
+      <c r="H19"/>
+      <c r="J19" s="132"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="133"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="133"/>
+      <c r="Q19" s="133"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="133"/>
+      <c r="T19" s="134"/>
+    </row>
+    <row r="20" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G20" s="44"/>
+      <c r="H20"/>
+      <c r="J20" s="132"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="133"/>
+      <c r="R20" s="133"/>
+      <c r="S20" s="133"/>
+      <c r="T20" s="134"/>
+    </row>
+    <row r="21" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G21" s="44"/>
+      <c r="H21"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="133"/>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="133"/>
+      <c r="S21" s="133"/>
+      <c r="T21" s="134"/>
+    </row>
+    <row r="22" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G22" s="44"/>
+      <c r="H22"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="133"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="133"/>
+      <c r="Q22" s="133"/>
+      <c r="R22" s="133"/>
+      <c r="S22" s="133"/>
+      <c r="T22" s="134"/>
+    </row>
+    <row r="23" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G23" s="44"/>
+      <c r="H23"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="133"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="133"/>
+      <c r="Q23" s="133"/>
+      <c r="R23" s="133"/>
+      <c r="S23" s="133"/>
+      <c r="T23" s="134"/>
+    </row>
+    <row r="24" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G24" s="44"/>
+      <c r="H24"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="133"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="133"/>
+      <c r="Q24" s="133"/>
+      <c r="R24" s="133"/>
+      <c r="S24" s="133"/>
+      <c r="T24" s="134"/>
+    </row>
+    <row r="25" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G25" s="44"/>
+      <c r="H25"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="133"/>
+      <c r="T25" s="134"/>
+    </row>
+    <row r="26" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G26" s="44"/>
+      <c r="H26"/>
+      <c r="J26" s="132"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
+      <c r="N26" s="133"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="133"/>
+      <c r="Q26" s="133"/>
+      <c r="R26" s="133"/>
+      <c r="S26" s="133"/>
+      <c r="T26" s="134"/>
+    </row>
+    <row r="27" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G27" s="44"/>
+      <c r="H27"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="133"/>
+      <c r="Q27" s="133"/>
+      <c r="R27" s="133"/>
+      <c r="S27" s="133"/>
+      <c r="T27" s="134"/>
+    </row>
+    <row r="28" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G28" s="44"/>
+      <c r="H28"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="133"/>
+      <c r="S28" s="133"/>
+      <c r="T28" s="134"/>
+    </row>
+    <row r="29" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G29" s="44"/>
+      <c r="H29"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="133"/>
+      <c r="N29" s="133"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="133"/>
+      <c r="Q29" s="133"/>
+      <c r="R29" s="133"/>
+      <c r="S29" s="133"/>
+      <c r="T29" s="134"/>
+    </row>
+    <row r="30" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G30" s="44"/>
+      <c r="H30"/>
+      <c r="J30" s="132"/>
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="133"/>
+      <c r="N30" s="133"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="133"/>
+      <c r="Q30" s="133"/>
+      <c r="R30" s="133"/>
+      <c r="S30" s="133"/>
+      <c r="T30" s="134"/>
+    </row>
+    <row r="31" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G31" s="44"/>
+      <c r="H31"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="133"/>
+      <c r="N31" s="133"/>
+      <c r="O31" s="133"/>
+      <c r="P31" s="133"/>
+      <c r="Q31" s="133"/>
+      <c r="R31" s="133"/>
+      <c r="S31" s="133"/>
+      <c r="T31" s="134"/>
+    </row>
+    <row r="32" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G32" s="44"/>
+      <c r="H32"/>
+      <c r="J32" s="132"/>
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="133"/>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="133"/>
+      <c r="R32" s="133"/>
+      <c r="S32" s="133"/>
+      <c r="T32" s="134"/>
+    </row>
+    <row r="33" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G33" s="44"/>
+      <c r="H33"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
+      <c r="M33" s="133"/>
+      <c r="N33" s="133"/>
+      <c r="O33" s="133"/>
+      <c r="P33" s="133"/>
+      <c r="Q33" s="133"/>
+      <c r="R33" s="133"/>
+      <c r="S33" s="133"/>
+      <c r="T33" s="134"/>
+    </row>
+    <row r="34" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G34" s="44"/>
+      <c r="H34"/>
+      <c r="J34" s="132"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="133"/>
+      <c r="M34" s="133"/>
+      <c r="N34" s="133"/>
+      <c r="O34" s="133"/>
+      <c r="P34" s="133"/>
+      <c r="Q34" s="133"/>
+      <c r="R34" s="133"/>
+      <c r="S34" s="133"/>
+      <c r="T34" s="134"/>
+    </row>
+    <row r="35" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G35" s="44"/>
+      <c r="H35"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
+      <c r="M35" s="133"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="133"/>
+      <c r="R35" s="133"/>
+      <c r="S35" s="133"/>
+      <c r="T35" s="134"/>
+    </row>
+    <row r="36" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G36" s="44"/>
+      <c r="H36"/>
+      <c r="J36" s="132"/>
+      <c r="K36" s="133"/>
+      <c r="L36" s="133"/>
+      <c r="M36" s="133"/>
+      <c r="N36" s="133"/>
+      <c r="O36" s="133"/>
+      <c r="P36" s="133"/>
+      <c r="Q36" s="133"/>
+      <c r="R36" s="133"/>
+      <c r="S36" s="133"/>
+      <c r="T36" s="134"/>
+    </row>
+    <row r="37" spans="2:20" ht="13.5" customHeight="1">
+      <c r="B37" s="7"/>
+      <c r="G37" s="44"/>
+      <c r="H37"/>
+      <c r="J37" s="132"/>
+      <c r="K37" s="133"/>
+      <c r="L37" s="133"/>
+      <c r="M37" s="133"/>
+      <c r="N37" s="133"/>
+      <c r="O37" s="133"/>
+      <c r="P37" s="133"/>
+      <c r="Q37" s="133"/>
+      <c r="R37" s="133"/>
+      <c r="S37" s="133"/>
+      <c r="T37" s="134"/>
+    </row>
+    <row r="38" spans="2:20" ht="13.5" customHeight="1">
+      <c r="B38" s="7"/>
+      <c r="G38" s="44"/>
+      <c r="H38"/>
+      <c r="J38" s="132"/>
+      <c r="K38" s="133"/>
+      <c r="L38" s="133"/>
+      <c r="M38" s="133"/>
+      <c r="N38" s="133"/>
+      <c r="O38" s="133"/>
+      <c r="P38" s="133"/>
+      <c r="Q38" s="133"/>
+      <c r="R38" s="133"/>
+      <c r="S38" s="133"/>
+      <c r="T38" s="134"/>
+    </row>
+    <row r="39" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G39" s="44"/>
+      <c r="H39"/>
+      <c r="J39" s="132"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133"/>
+      <c r="M39" s="133"/>
+      <c r="N39" s="133"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="133"/>
+      <c r="Q39" s="133"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="133"/>
+      <c r="T39" s="134"/>
+    </row>
+    <row r="40" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G40" s="44"/>
+      <c r="H40"/>
+      <c r="J40" s="132"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="133"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="133"/>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="133"/>
+      <c r="R40" s="133"/>
+      <c r="S40" s="133"/>
+      <c r="T40" s="134"/>
+    </row>
+    <row r="41" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G41" s="44"/>
+      <c r="H41"/>
+      <c r="J41" s="132"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133"/>
+      <c r="M41" s="133"/>
+      <c r="N41" s="133"/>
+      <c r="O41" s="133"/>
+      <c r="P41" s="133"/>
+      <c r="Q41" s="133"/>
+      <c r="R41" s="133"/>
+      <c r="S41" s="133"/>
+      <c r="T41" s="134"/>
+    </row>
+    <row r="42" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G42" s="44"/>
+      <c r="H42"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="133"/>
+      <c r="L42" s="133"/>
+      <c r="M42" s="133"/>
+      <c r="N42" s="133"/>
+      <c r="O42" s="133"/>
+      <c r="P42" s="133"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="133"/>
+      <c r="S42" s="133"/>
+      <c r="T42" s="134"/>
+    </row>
+    <row r="43" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G43" s="44"/>
+      <c r="H43"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="133"/>
+      <c r="L43" s="133"/>
+      <c r="M43" s="133"/>
+      <c r="N43" s="133"/>
+      <c r="O43" s="133"/>
+      <c r="P43" s="133"/>
+      <c r="Q43" s="133"/>
+      <c r="R43" s="133"/>
+      <c r="S43" s="133"/>
+      <c r="T43" s="134"/>
+    </row>
+    <row r="44" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G44" s="44"/>
+      <c r="H44"/>
+      <c r="J44" s="132"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="133"/>
+      <c r="M44" s="133"/>
+      <c r="N44" s="133"/>
+      <c r="O44" s="133"/>
+      <c r="P44" s="133"/>
+      <c r="Q44" s="133"/>
+      <c r="R44" s="133"/>
+      <c r="S44" s="133"/>
+      <c r="T44" s="134"/>
+    </row>
+    <row r="45" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G45" s="44"/>
+      <c r="H45"/>
+      <c r="J45" s="135"/>
+      <c r="K45" s="136"/>
+      <c r="L45" s="136"/>
+      <c r="M45" s="136"/>
+      <c r="N45" s="136"/>
+      <c r="O45" s="136"/>
+      <c r="P45" s="136"/>
+      <c r="Q45" s="136"/>
+      <c r="R45" s="136"/>
+      <c r="S45" s="136"/>
+      <c r="T45" s="137"/>
+    </row>
+    <row r="46" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G46" s="44"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G47" s="44"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G48" s="44"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G49" s="44"/>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G50" s="44"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G51" s="44"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G52" s="44"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G53" s="44"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="7:8" ht="13.5" customHeight="1">
+      <c r="G54" s="44"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="7:8">
+      <c r="G55" s="44"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="7:8">
+      <c r="G56" s="44"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="7:8">
+      <c r="G57" s="44"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="7:8">
+      <c r="G58" s="44"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="7:8">
+      <c r="G59" s="44"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="7:8">
+      <c r="G60" s="44"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="7:8">
+      <c r="G61" s="44"/>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="7:8">
+      <c r="G62" s="44"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="7:8">
+      <c r="G63" s="44"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="7:8">
+      <c r="G64" s="44"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="7:8">
+      <c r="G65" s="44"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="7:8">
+      <c r="G66" s="44"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="7:8">
+      <c r="G67" s="44"/>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="7:8">
+      <c r="G68" s="44"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="7:8">
+      <c r="G69" s="44"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="7:8">
+      <c r="G70" s="44"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="7:8">
+      <c r="G71" s="44"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="7:8">
+      <c r="G72" s="44"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="7:8">
+      <c r="G73" s="44"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="7:8">
+      <c r="G74" s="44"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="7:8">
+      <c r="G75" s="44"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="7:8">
+      <c r="G76" s="44"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="7:8">
+      <c r="G77" s="44"/>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="7:8">
+      <c r="G78" s="44"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="7:8">
+      <c r="G79" s="44"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="7:8">
+      <c r="G80" s="44"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="7:8">
+      <c r="G81" s="44"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="7:8">
+      <c r="G82" s="44"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="7:8">
+      <c r="G83" s="44"/>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="7:8">
+      <c r="G84" s="44"/>
+      <c r="H84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J5:T5"/>
+    <mergeCell ref="J6:T45"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F12 H1 G6:G84 H85:H1048576 C7:E12" xr:uid="{2635B342-CCA0-4B12-B53B-58CAE3AE7567}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66394428-CC81-4B04-9434-EDC45C3B131C}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -15396,23 +16629,23 @@
       <c r="C2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="155" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="164"/>
+      <c r="D2" s="154" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="159"/>
     </row>
     <row r="3" spans="3:32">
       <c r="C3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="158" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="165"/>
+      <c r="D3" s="156" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="160"/>
     </row>
     <row r="4" spans="3:32">
       <c r="C4"/>
@@ -15426,51 +16659,51 @@
       <c r="E5" s="122"/>
       <c r="F5" s="125"/>
       <c r="G5" s="123"/>
-      <c r="J5" s="152" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="154"/>
-      <c r="V5" s="152" t="s">
-        <v>91</v>
-      </c>
-      <c r="W5" s="153"/>
-      <c r="X5" s="153"/>
-      <c r="Y5" s="153"/>
-      <c r="Z5" s="153"/>
-      <c r="AA5" s="153"/>
-      <c r="AB5" s="153"/>
-      <c r="AC5" s="153"/>
-      <c r="AD5" s="153"/>
-      <c r="AE5" s="153"/>
-      <c r="AF5" s="154"/>
+      <c r="J5" s="151" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="153"/>
+      <c r="V5" s="151" t="s">
+        <v>95</v>
+      </c>
+      <c r="W5" s="152"/>
+      <c r="X5" s="152"/>
+      <c r="Y5" s="152"/>
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="152"/>
+      <c r="AE5" s="152"/>
+      <c r="AF5" s="153"/>
     </row>
     <row r="6" spans="3:32" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J6" s="129" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K6" s="130"/>
       <c r="L6" s="130"/>
@@ -15483,7 +16716,7 @@
       <c r="S6" s="130"/>
       <c r="T6" s="131"/>
       <c r="V6" s="129" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="W6" s="130"/>
       <c r="X6" s="130"/>
@@ -15498,19 +16731,19 @@
     </row>
     <row r="7" spans="3:32" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>85</v>
       </c>
       <c r="J7" s="132"/>
       <c r="K7" s="133"/>
@@ -15537,19 +16770,19 @@
     </row>
     <row r="8" spans="3:32" ht="13.5" customHeight="1">
       <c r="C8" s="26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>85</v>
       </c>
       <c r="J8" s="132"/>
       <c r="K8" s="133"/>
@@ -16618,7 +17851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0A1BC2-AD1F-4F40-B462-EAC4DD963BF3}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -16667,15 +17900,15 @@
       <c r="E5" s="125"/>
       <c r="F5" s="125"/>
       <c r="G5" s="70"/>
-      <c r="I5" s="167" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="167"/>
-      <c r="K5" s="167"/>
-      <c r="L5" s="167"/>
-      <c r="M5" s="167"/>
-      <c r="N5" s="167"/>
-      <c r="O5" s="167"/>
+      <c r="I5" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
     </row>
     <row r="6" spans="2:15" ht="13.5" customHeight="1">
       <c r="B6" s="85" t="s">
@@ -16690,15 +17923,15 @@
       </c>
       <c r="F6" s="128"/>
       <c r="G6" s="72"/>
-      <c r="I6" s="166" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="166"/>
-      <c r="K6" s="166"/>
-      <c r="L6" s="166"/>
-      <c r="M6" s="166"/>
-      <c r="N6" s="166"/>
-      <c r="O6" s="166"/>
+      <c r="I6" s="161" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="161"/>
+      <c r="O6" s="161"/>
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="41" t="s">
@@ -16717,13 +17950,13 @@
         <v>39</v>
       </c>
       <c r="G7" s="26"/>
-      <c r="I7" s="166"/>
-      <c r="J7" s="166"/>
-      <c r="K7" s="166"/>
-      <c r="L7" s="166"/>
-      <c r="M7" s="166"/>
-      <c r="N7" s="166"/>
-      <c r="O7" s="166"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
     </row>
     <row r="8" spans="2:15">
       <c r="B8" s="26" t="s">
@@ -16742,13 +17975,13 @@
         <v>52</v>
       </c>
       <c r="G8" s="26"/>
-      <c r="I8" s="166"/>
-      <c r="J8" s="166"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
+      <c r="I8" s="161"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="161"/>
+      <c r="L8" s="161"/>
+      <c r="M8" s="161"/>
+      <c r="N8" s="161"/>
+      <c r="O8" s="161"/>
     </row>
     <row r="9" spans="2:15">
       <c r="B9" s="26"/>
@@ -16757,13 +17990,13 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="26"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="166"/>
-      <c r="L9" s="166"/>
-      <c r="M9" s="166"/>
-      <c r="N9" s="166"/>
-      <c r="O9" s="166"/>
+      <c r="I9" s="161"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="161"/>
+      <c r="L9" s="161"/>
+      <c r="M9" s="161"/>
+      <c r="N9" s="161"/>
+      <c r="O9" s="161"/>
     </row>
     <row r="10" spans="2:15">
       <c r="B10" s="26"/>
@@ -16772,13 +18005,13 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="26"/>
-      <c r="I10" s="166"/>
-      <c r="J10" s="166"/>
-      <c r="K10" s="166"/>
-      <c r="L10" s="166"/>
-      <c r="M10" s="166"/>
-      <c r="N10" s="166"/>
-      <c r="O10" s="166"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="161"/>
+      <c r="L10" s="161"/>
+      <c r="M10" s="161"/>
+      <c r="N10" s="161"/>
+      <c r="O10" s="161"/>
     </row>
     <row r="11" spans="2:15">
       <c r="B11" s="26"/>
@@ -16786,23 +18019,23 @@
       <c r="D11" s="27"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="I11" s="166"/>
-      <c r="J11" s="166"/>
-      <c r="K11" s="166"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="166"/>
-      <c r="O11" s="166"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="161"/>
+      <c r="L11" s="161"/>
+      <c r="M11" s="161"/>
+      <c r="N11" s="161"/>
+      <c r="O11" s="161"/>
     </row>
     <row r="12" spans="2:15">
       <c r="G12" s="26"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-      <c r="M12" s="166"/>
-      <c r="N12" s="166"/>
-      <c r="O12" s="166"/>
+      <c r="I12" s="161"/>
+      <c r="J12" s="161"/>
+      <c r="K12" s="161"/>
+      <c r="L12" s="161"/>
+      <c r="M12" s="161"/>
+      <c r="N12" s="161"/>
+      <c r="O12" s="161"/>
     </row>
     <row r="13" spans="2:15">
       <c r="B13" s="26"/>
@@ -16810,242 +18043,242 @@
       <c r="D13" s="27"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
+      <c r="I13" s="161"/>
+      <c r="J13" s="161"/>
+      <c r="K13" s="161"/>
+      <c r="L13" s="161"/>
+      <c r="M13" s="161"/>
+      <c r="N13" s="161"/>
+      <c r="O13" s="161"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
-      <c r="L14" s="166"/>
-      <c r="M14" s="166"/>
-      <c r="N14" s="166"/>
-      <c r="O14" s="166"/>
+      <c r="I14" s="161"/>
+      <c r="J14" s="161"/>
+      <c r="K14" s="161"/>
+      <c r="L14" s="161"/>
+      <c r="M14" s="161"/>
+      <c r="N14" s="161"/>
+      <c r="O14" s="161"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="166"/>
-      <c r="L15" s="166"/>
-      <c r="M15" s="166"/>
-      <c r="N15" s="166"/>
-      <c r="O15" s="166"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="161"/>
+      <c r="K15" s="161"/>
+      <c r="L15" s="161"/>
+      <c r="M15" s="161"/>
+      <c r="N15" s="161"/>
+      <c r="O15" s="161"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="166"/>
-      <c r="L16" s="166"/>
-      <c r="M16" s="166"/>
-      <c r="N16" s="166"/>
-      <c r="O16" s="166"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
+      <c r="M16" s="161"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="161"/>
     </row>
     <row r="17" spans="9:15">
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="166"/>
-      <c r="M17" s="166"/>
-      <c r="N17" s="166"/>
-      <c r="O17" s="166"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="161"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="161"/>
+      <c r="M17" s="161"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="161"/>
     </row>
     <row r="18" spans="9:15">
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="166"/>
-      <c r="O18" s="166"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="161"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="161"/>
+      <c r="M18" s="161"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="161"/>
     </row>
     <row r="19" spans="9:15">
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="166"/>
-      <c r="N19" s="166"/>
-      <c r="O19" s="166"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="161"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="161"/>
+      <c r="M19" s="161"/>
+      <c r="N19" s="161"/>
+      <c r="O19" s="161"/>
     </row>
     <row r="20" spans="9:15">
-      <c r="I20" s="166"/>
-      <c r="J20" s="166"/>
-      <c r="K20" s="166"/>
-      <c r="L20" s="166"/>
-      <c r="M20" s="166"/>
-      <c r="N20" s="166"/>
-      <c r="O20" s="166"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="161"/>
     </row>
     <row r="21" spans="9:15">
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161"/>
+      <c r="L21" s="161"/>
+      <c r="M21" s="161"/>
+      <c r="N21" s="161"/>
+      <c r="O21" s="161"/>
     </row>
     <row r="23" spans="9:15" ht="21">
-      <c r="I23" s="167" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" s="167"/>
-      <c r="K23" s="167"/>
-      <c r="L23" s="167"/>
-      <c r="M23" s="167"/>
-      <c r="N23" s="167"/>
-      <c r="O23" s="167"/>
+      <c r="I23" s="162" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="162"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="162"/>
     </row>
     <row r="24" spans="9:15" ht="13.5" customHeight="1">
-      <c r="I24" s="166" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="166"/>
-      <c r="K24" s="166"/>
-      <c r="L24" s="166"/>
-      <c r="M24" s="166"/>
-      <c r="N24" s="166"/>
-      <c r="O24" s="166"/>
+      <c r="I24" s="161" t="s">
+        <v>108</v>
+      </c>
+      <c r="J24" s="161"/>
+      <c r="K24" s="161"/>
+      <c r="L24" s="161"/>
+      <c r="M24" s="161"/>
+      <c r="N24" s="161"/>
+      <c r="O24" s="161"/>
     </row>
     <row r="25" spans="9:15">
-      <c r="I25" s="166"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="166"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="166"/>
-      <c r="N25" s="166"/>
-      <c r="O25" s="166"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="161"/>
+      <c r="K25" s="161"/>
+      <c r="L25" s="161"/>
+      <c r="M25" s="161"/>
+      <c r="N25" s="161"/>
+      <c r="O25" s="161"/>
     </row>
     <row r="26" spans="9:15">
-      <c r="I26" s="166"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="166"/>
-      <c r="L26" s="166"/>
-      <c r="M26" s="166"/>
-      <c r="N26" s="166"/>
-      <c r="O26" s="166"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="161"/>
+      <c r="K26" s="161"/>
+      <c r="L26" s="161"/>
+      <c r="M26" s="161"/>
+      <c r="N26" s="161"/>
+      <c r="O26" s="161"/>
     </row>
     <row r="27" spans="9:15">
-      <c r="I27" s="166"/>
-      <c r="J27" s="166"/>
-      <c r="K27" s="166"/>
-      <c r="L27" s="166"/>
-      <c r="M27" s="166"/>
-      <c r="N27" s="166"/>
-      <c r="O27" s="166"/>
+      <c r="I27" s="161"/>
+      <c r="J27" s="161"/>
+      <c r="K27" s="161"/>
+      <c r="L27" s="161"/>
+      <c r="M27" s="161"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="161"/>
     </row>
     <row r="28" spans="9:15">
-      <c r="I28" s="166"/>
-      <c r="J28" s="166"/>
-      <c r="K28" s="166"/>
-      <c r="L28" s="166"/>
-      <c r="M28" s="166"/>
-      <c r="N28" s="166"/>
-      <c r="O28" s="166"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="161"/>
+      <c r="K28" s="161"/>
+      <c r="L28" s="161"/>
+      <c r="M28" s="161"/>
+      <c r="N28" s="161"/>
+      <c r="O28" s="161"/>
     </row>
     <row r="29" spans="9:15">
-      <c r="I29" s="166"/>
-      <c r="J29" s="166"/>
-      <c r="K29" s="166"/>
-      <c r="L29" s="166"/>
-      <c r="M29" s="166"/>
-      <c r="N29" s="166"/>
-      <c r="O29" s="166"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="161"/>
     </row>
     <row r="30" spans="9:15">
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="166"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
-      <c r="O30" s="166"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
+      <c r="M30" s="161"/>
+      <c r="N30" s="161"/>
+      <c r="O30" s="161"/>
     </row>
     <row r="31" spans="9:15">
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
-      <c r="K31" s="166"/>
-      <c r="L31" s="166"/>
-      <c r="M31" s="166"/>
-      <c r="N31" s="166"/>
-      <c r="O31" s="166"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="161"/>
+      <c r="M31" s="161"/>
+      <c r="N31" s="161"/>
+      <c r="O31" s="161"/>
     </row>
     <row r="32" spans="9:15">
-      <c r="I32" s="166"/>
-      <c r="J32" s="166"/>
-      <c r="K32" s="166"/>
-      <c r="L32" s="166"/>
-      <c r="M32" s="166"/>
-      <c r="N32" s="166"/>
-      <c r="O32" s="166"/>
+      <c r="I32" s="161"/>
+      <c r="J32" s="161"/>
+      <c r="K32" s="161"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="161"/>
+      <c r="N32" s="161"/>
+      <c r="O32" s="161"/>
     </row>
     <row r="33" spans="9:15">
-      <c r="I33" s="166"/>
-      <c r="J33" s="166"/>
-      <c r="K33" s="166"/>
-      <c r="L33" s="166"/>
-      <c r="M33" s="166"/>
-      <c r="N33" s="166"/>
-      <c r="O33" s="166"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="161"/>
+      <c r="K33" s="161"/>
+      <c r="L33" s="161"/>
+      <c r="M33" s="161"/>
+      <c r="N33" s="161"/>
+      <c r="O33" s="161"/>
     </row>
     <row r="34" spans="9:15">
-      <c r="I34" s="166"/>
-      <c r="J34" s="166"/>
-      <c r="K34" s="166"/>
-      <c r="L34" s="166"/>
-      <c r="M34" s="166"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="166"/>
+      <c r="I34" s="161"/>
+      <c r="J34" s="161"/>
+      <c r="K34" s="161"/>
+      <c r="L34" s="161"/>
+      <c r="M34" s="161"/>
+      <c r="N34" s="161"/>
+      <c r="O34" s="161"/>
     </row>
     <row r="35" spans="9:15">
-      <c r="I35" s="166"/>
-      <c r="J35" s="166"/>
-      <c r="K35" s="166"/>
-      <c r="L35" s="166"/>
-      <c r="M35" s="166"/>
-      <c r="N35" s="166"/>
-      <c r="O35" s="166"/>
+      <c r="I35" s="161"/>
+      <c r="J35" s="161"/>
+      <c r="K35" s="161"/>
+      <c r="L35" s="161"/>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161"/>
+      <c r="O35" s="161"/>
     </row>
     <row r="36" spans="9:15">
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="166"/>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
-      <c r="O36" s="166"/>
+      <c r="I36" s="161"/>
+      <c r="J36" s="161"/>
+      <c r="K36" s="161"/>
+      <c r="L36" s="161"/>
+      <c r="M36" s="161"/>
+      <c r="N36" s="161"/>
+      <c r="O36" s="161"/>
     </row>
     <row r="37" spans="9:15">
-      <c r="I37" s="166"/>
-      <c r="J37" s="166"/>
-      <c r="K37" s="166"/>
-      <c r="L37" s="166"/>
-      <c r="M37" s="166"/>
-      <c r="N37" s="166"/>
-      <c r="O37" s="166"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="161"/>
     </row>
     <row r="38" spans="9:15">
-      <c r="I38" s="166"/>
-      <c r="J38" s="166"/>
-      <c r="K38" s="166"/>
-      <c r="L38" s="166"/>
-      <c r="M38" s="166"/>
-      <c r="N38" s="166"/>
-      <c r="O38" s="166"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
     </row>
     <row r="39" spans="9:15">
-      <c r="I39" s="166"/>
-      <c r="J39" s="166"/>
-      <c r="K39" s="166"/>
-      <c r="L39" s="166"/>
-      <c r="M39" s="166"/>
-      <c r="N39" s="166"/>
-      <c r="O39" s="166"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="161"/>
+      <c r="K39" s="161"/>
+      <c r="L39" s="161"/>
+      <c r="M39" s="161"/>
+      <c r="N39" s="161"/>
+      <c r="O39" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -17066,7 +18299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD90D1D-3345-4EDC-9CC4-2BE02D44AE19}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -17092,25 +18325,25 @@
       <c r="C2" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="168">
+      <c r="D2" s="163">
         <f>Define!C5</f>
         <v>0</v>
       </c>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="229"/>
     </row>
     <row r="3" spans="3:32">
       <c r="C3" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="170">
+      <c r="D3" s="164">
         <f>Define!C6</f>
         <v>0</v>
       </c>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="171"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="231"/>
     </row>
     <row r="4" spans="3:32">
       <c r="C4"/>
@@ -17118,38 +18351,38 @@
     </row>
     <row r="5" spans="3:32" ht="19.5" customHeight="1">
       <c r="C5" s="121" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122"/>
       <c r="F5" s="122"/>
       <c r="G5" s="123"/>
-      <c r="J5" s="152" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="154"/>
-      <c r="V5" s="152" t="s">
-        <v>107</v>
-      </c>
-      <c r="W5" s="153"/>
-      <c r="X5" s="153"/>
-      <c r="Y5" s="153"/>
-      <c r="Z5" s="153"/>
-      <c r="AA5" s="153"/>
-      <c r="AB5" s="153"/>
-      <c r="AC5" s="153"/>
-      <c r="AD5" s="153"/>
-      <c r="AE5" s="153"/>
-      <c r="AF5" s="154"/>
+      <c r="J5" s="151" t="s">
+        <v>110</v>
+      </c>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="153"/>
+      <c r="V5" s="151" t="s">
+        <v>111</v>
+      </c>
+      <c r="W5" s="152"/>
+      <c r="X5" s="152"/>
+      <c r="Y5" s="152"/>
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="152"/>
+      <c r="AE5" s="152"/>
+      <c r="AF5" s="153"/>
     </row>
     <row r="6" spans="3:32" ht="13.5" customHeight="1">
       <c r="C6" s="77" t="s">
@@ -17159,16 +18392,16 @@
         <v>31</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J6" s="129" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K6" s="130"/>
       <c r="L6" s="130"/>
@@ -17181,7 +18414,7 @@
       <c r="S6" s="130"/>
       <c r="T6" s="131"/>
       <c r="V6" s="129" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="W6" s="130"/>
       <c r="X6" s="130"/>
@@ -18488,310 +19721,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632C17C5-59B7-41E9-805B-4B36986E2251}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="B1:V36"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="4" width="17.25" customWidth="1"/>
-    <col min="5" max="5" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4" style="43" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="44" customWidth="1"/>
-    <col min="10" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="15.875" style="43" customWidth="1"/>
-    <col min="12" max="12" width="21.5" style="44" customWidth="1"/>
-    <col min="13" max="13" width="3.375" customWidth="1"/>
-    <col min="14" max="14" width="15.875" style="43" customWidth="1"/>
-    <col min="15" max="15" width="40.375" customWidth="1"/>
-    <col min="16" max="17" width="17.375" customWidth="1"/>
-    <col min="18" max="18" width="21.5" style="44" customWidth="1"/>
-    <col min="19" max="19" width="4.5" customWidth="1"/>
-    <col min="20" max="20" width="15.875" style="43" customWidth="1"/>
-    <col min="21" max="21" width="17.375" customWidth="1"/>
-    <col min="22" max="22" width="21.5" style="44" customWidth="1"/>
-    <col min="23" max="23" width="3.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:22">
-      <c r="B1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="I1"/>
-      <c r="K1"/>
-      <c r="L1"/>
-      <c r="N1"/>
-      <c r="R1"/>
-      <c r="T1"/>
-      <c r="V1"/>
-    </row>
-    <row r="2" spans="2:22">
-      <c r="B2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="I2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="N2"/>
-      <c r="R2"/>
-      <c r="T2"/>
-      <c r="V2"/>
-    </row>
-    <row r="3" spans="2:22" ht="19.5" customHeight="1">
-      <c r="B3" s="121" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="121" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="122"/>
-      <c r="I3" s="123"/>
-      <c r="K3" s="121" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="123"/>
-      <c r="N3" s="121" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="123"/>
-      <c r="T3" s="121" t="s">
-        <v>113</v>
-      </c>
-      <c r="U3" s="122"/>
-      <c r="V3" s="123"/>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="71"/>
-      <c r="G4" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="L4" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="N4" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q4" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="R4" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="T4" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="V4" s="42" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" ht="15">
-      <c r="B5" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="27"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="27"/>
-      <c r="N5" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="O5" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="P5" s="37">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="T5" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="U5" s="37">
-        <v>2</v>
-      </c>
-      <c r="V5" s="27" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="15">
-      <c r="B6" s="26"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="27"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="27"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="27"/>
-    </row>
-    <row r="7" spans="2:22" ht="15">
-      <c r="B7" s="26"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="27"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="27"/>
-      <c r="N7" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="O7" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="P7" s="37">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="37">
-        <v>1</v>
-      </c>
-      <c r="R7" s="27">
-        <v>0</v>
-      </c>
-      <c r="T7" s="26"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="27"/>
-    </row>
-    <row r="8" spans="2:22" ht="15">
-      <c r="B8" s="26"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="27"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="27"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="27"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="27"/>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="G9" s="26"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="27"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="27"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="27"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="27"/>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="26"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="T10" s="26"/>
-    </row>
-    <row r="35" spans="10:10">
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="10:10">
-      <c r="J36" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="T3:V3"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B5:B8" xr:uid="{8DDDB7D8-EE11-47B5-B588-8A4BD8C3CC68}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G10 K5:K10 N5:N10 R5:R7 T5:T10 V5:V7" xr:uid="{6619C4EF-A22E-45EF-94C7-8C8EE7B88B38}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I8 D5:D8 L5:L8 R8 V8" xr:uid="{E08CDC7A-9ECD-4DCD-A610-26787C899834}">
-      <formula1>"$rose,$fell,$changed,Data"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
 </file>
--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76922DF8-EE1D-4AEB-9839-E046F1D79A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5138DCF-3972-4597-9C33-DE4B42177915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="5" activeTab="6" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
@@ -19,17 +19,18 @@
     <sheet name="HSW" sheetId="17" r:id="rId4"/>
     <sheet name="HBP" sheetId="21" r:id="rId5"/>
     <sheet name="HACT" sheetId="23" r:id="rId6"/>
-    <sheet name="VFP" sheetId="22" r:id="rId7"/>
-    <sheet name="VSW" sheetId="20" r:id="rId8"/>
-    <sheet name="Counter" sheetId="15" r:id="rId9"/>
-    <sheet name="delayCondition" sheetId="18" r:id="rId10"/>
-    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId11"/>
-    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId12"/>
-    <sheet name="Basic Assertion" sheetId="1" r:id="rId13"/>
-    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId14"/>
-    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId15"/>
-    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId16"/>
-    <sheet name="aw_builder" sheetId="2" r:id="rId17"/>
+    <sheet name="HFP" sheetId="24" r:id="rId7"/>
+    <sheet name="VFP" sheetId="22" r:id="rId8"/>
+    <sheet name="VSW" sheetId="20" r:id="rId9"/>
+    <sheet name="Counter" sheetId="15" r:id="rId10"/>
+    <sheet name="delayCondition" sheetId="18" r:id="rId11"/>
+    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId12"/>
+    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId13"/>
+    <sheet name="Basic Assertion" sheetId="1" r:id="rId14"/>
+    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId15"/>
+    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId16"/>
+    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId17"/>
+    <sheet name="aw_builder" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -170,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="349">
   <si>
     <t>Base Information</t>
   </si>
@@ -2245,6 +2246,72 @@
     $rose(&lt;Data Enable Signal&gt;) |=&gt; s_hact;
 endproperty
 assert property (p_hact) $display("[%0t] Assertion PASS", $time);
+else $display ("[%0t] Assertion FAIL", $time);
+endinterface
+// 윗부분까지가 생성되는 assertion_gen.sv 입니다. 아래부터는 assertion_gen_inst.sv 입니다.
+assertion_intf
+u_assertion_intf();
+assign u_assertion_intf.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
+assign u_assertion_intf.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
+assign u_assertion_intf.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
+assign u_assertion_intf.&lt;Data Enable  Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;
+</t>
+  </si>
+  <si>
+    <t>HFP</t>
+  </si>
+  <si>
+    <t>Expected Preset(HFP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`include "uvm_marcros.svh"
+import uvm_pkg::*;
+interface assertion_intf()
+(
+    input &lt;Base Clock&gt;,
+    input &lt;Base Reset&gt;,
+    input &lt;Hsync Signal&gt;,
+    input &lt;Data Enable Signal&gt;
+)
+int clk_cnt;
+logic l_hfp;
+always @(posedge &lt;Base Clock&gt; or negedge &lt;Base Reset&gt;) begin
+    if(!&lt;Base Reset&gt;) begin
+        l_hfp &lt;= 0;
+    end
+    else begin
+        if($fell(&lt;Data Enable Signal&gt;)) begin
+            l_hfp &lt;= 1;
+        end
+        else if(&lt;Hsync Signal&gt;) begin
+            l_hfp &lt;= 0;
+        end
+        else begin
+            l_hfp &lt;= l_hfp;
+        end
+    end
+end
+always @(posedge &lt;Base Clock&gt; or negedge &lt;Base Reset&gt;) begin
+    if(!&lt;Base Reset) begin
+        clk_cnt &lt;= 0;
+    end
+    else begin
+        if(l_hfp) begin
+            clk_cnt &lt;= clk_cnt + 1;
+        end
+        else if(!&lt;Hsync Signal&gt;) begin
+            clk_cnt &lt;= 0;
+        end
+        else begin
+            clk_cnt &lt;= clk_cnt;
+        end
+    end
+end
+property p_hfp;
+    @(posedge &lt;Base Clock&gt;) disable iff(!&lt;Base Reset&gt;)
+    $fell(l_hfp) |-&gt; ((&lt;Expected_Min_Value&gt; &lt;= clk_cnt) &amp;&amp; (clk_cnt &lt;= &lt;Expected_Max_Value&gt;));
+endproperty
+assert property (p_hfp) $display("[%0t] Assertion PASS", $time);
 else $display ("[%0t] Assertion FAIL", $time);
 endinterface
 // 윗부분까지가 생성되는 assertion_gen.sv 입니다. 아래부터는 assertion_gen_inst.sv 입니다.
@@ -6879,6 +6946,454 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0A1BC2-AD1F-4F40-B462-EAC4DD963BF3}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:O39"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="3" width="18.125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="44" customWidth="1"/>
+    <col min="5" max="5" width="17.25" customWidth="1"/>
+    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" style="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="2:15">
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="2:15" ht="21">
+      <c r="B5" s="125" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="70"/>
+      <c r="I5" s="170" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="170"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="170"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="170"/>
+    </row>
+    <row r="6" spans="2:15" ht="13.5" customHeight="1">
+      <c r="B6" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="128" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="128"/>
+      <c r="E6" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="129"/>
+      <c r="G6" s="72"/>
+      <c r="I6" s="169" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="I8" s="169"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="26"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="26"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="G12" s="26"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="169"/>
+      <c r="J13" s="169"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="I14" s="169"/>
+      <c r="J14" s="169"/>
+      <c r="K14" s="169"/>
+      <c r="L14" s="169"/>
+      <c r="M14" s="169"/>
+      <c r="N14" s="169"/>
+      <c r="O14" s="169"/>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="I15" s="169"/>
+      <c r="J15" s="169"/>
+      <c r="K15" s="169"/>
+      <c r="L15" s="169"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="I16" s="169"/>
+      <c r="J16" s="169"/>
+      <c r="K16" s="169"/>
+      <c r="L16" s="169"/>
+      <c r="M16" s="169"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="169"/>
+    </row>
+    <row r="17" spans="9:15">
+      <c r="I17" s="169"/>
+      <c r="J17" s="169"/>
+      <c r="K17" s="169"/>
+      <c r="L17" s="169"/>
+      <c r="M17" s="169"/>
+      <c r="N17" s="169"/>
+      <c r="O17" s="169"/>
+    </row>
+    <row r="18" spans="9:15">
+      <c r="I18" s="169"/>
+      <c r="J18" s="169"/>
+      <c r="K18" s="169"/>
+      <c r="L18" s="169"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="169"/>
+      <c r="O18" s="169"/>
+    </row>
+    <row r="19" spans="9:15">
+      <c r="I19" s="169"/>
+      <c r="J19" s="169"/>
+      <c r="K19" s="169"/>
+      <c r="L19" s="169"/>
+      <c r="M19" s="169"/>
+      <c r="N19" s="169"/>
+      <c r="O19" s="169"/>
+    </row>
+    <row r="20" spans="9:15">
+      <c r="I20" s="169"/>
+      <c r="J20" s="169"/>
+      <c r="K20" s="169"/>
+      <c r="L20" s="169"/>
+      <c r="M20" s="169"/>
+      <c r="N20" s="169"/>
+      <c r="O20" s="169"/>
+    </row>
+    <row r="21" spans="9:15">
+      <c r="I21" s="169"/>
+      <c r="J21" s="169"/>
+      <c r="K21" s="169"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="169"/>
+      <c r="O21" s="169"/>
+    </row>
+    <row r="23" spans="9:15" ht="21">
+      <c r="I23" s="170" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="170"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="170"/>
+      <c r="M23" s="170"/>
+      <c r="N23" s="170"/>
+      <c r="O23" s="170"/>
+    </row>
+    <row r="24" spans="9:15" ht="13.5" customHeight="1">
+      <c r="I24" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" s="169"/>
+      <c r="K24" s="169"/>
+      <c r="L24" s="169"/>
+      <c r="M24" s="169"/>
+      <c r="N24" s="169"/>
+      <c r="O24" s="169"/>
+    </row>
+    <row r="25" spans="9:15">
+      <c r="I25" s="169"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="169"/>
+    </row>
+    <row r="26" spans="9:15">
+      <c r="I26" s="169"/>
+      <c r="J26" s="169"/>
+      <c r="K26" s="169"/>
+      <c r="L26" s="169"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="169"/>
+      <c r="O26" s="169"/>
+    </row>
+    <row r="27" spans="9:15">
+      <c r="I27" s="169"/>
+      <c r="J27" s="169"/>
+      <c r="K27" s="169"/>
+      <c r="L27" s="169"/>
+      <c r="M27" s="169"/>
+      <c r="N27" s="169"/>
+      <c r="O27" s="169"/>
+    </row>
+    <row r="28" spans="9:15">
+      <c r="I28" s="169"/>
+      <c r="J28" s="169"/>
+      <c r="K28" s="169"/>
+      <c r="L28" s="169"/>
+      <c r="M28" s="169"/>
+      <c r="N28" s="169"/>
+      <c r="O28" s="169"/>
+    </row>
+    <row r="29" spans="9:15">
+      <c r="I29" s="169"/>
+      <c r="J29" s="169"/>
+      <c r="K29" s="169"/>
+      <c r="L29" s="169"/>
+      <c r="M29" s="169"/>
+      <c r="N29" s="169"/>
+      <c r="O29" s="169"/>
+    </row>
+    <row r="30" spans="9:15">
+      <c r="I30" s="169"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="169"/>
+    </row>
+    <row r="31" spans="9:15">
+      <c r="I31" s="169"/>
+      <c r="J31" s="169"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="169"/>
+      <c r="M31" s="169"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="169"/>
+    </row>
+    <row r="32" spans="9:15">
+      <c r="I32" s="169"/>
+      <c r="J32" s="169"/>
+      <c r="K32" s="169"/>
+      <c r="L32" s="169"/>
+      <c r="M32" s="169"/>
+      <c r="N32" s="169"/>
+      <c r="O32" s="169"/>
+    </row>
+    <row r="33" spans="9:15">
+      <c r="I33" s="169"/>
+      <c r="J33" s="169"/>
+      <c r="K33" s="169"/>
+      <c r="L33" s="169"/>
+      <c r="M33" s="169"/>
+      <c r="N33" s="169"/>
+      <c r="O33" s="169"/>
+    </row>
+    <row r="34" spans="9:15">
+      <c r="I34" s="169"/>
+      <c r="J34" s="169"/>
+      <c r="K34" s="169"/>
+      <c r="L34" s="169"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="169"/>
+    </row>
+    <row r="35" spans="9:15">
+      <c r="I35" s="169"/>
+      <c r="J35" s="169"/>
+      <c r="K35" s="169"/>
+      <c r="L35" s="169"/>
+      <c r="M35" s="169"/>
+      <c r="N35" s="169"/>
+      <c r="O35" s="169"/>
+    </row>
+    <row r="36" spans="9:15">
+      <c r="I36" s="169"/>
+      <c r="J36" s="169"/>
+      <c r="K36" s="169"/>
+      <c r="L36" s="169"/>
+      <c r="M36" s="169"/>
+      <c r="N36" s="169"/>
+      <c r="O36" s="169"/>
+    </row>
+    <row r="37" spans="9:15">
+      <c r="I37" s="169"/>
+      <c r="J37" s="169"/>
+      <c r="K37" s="169"/>
+      <c r="L37" s="169"/>
+      <c r="M37" s="169"/>
+      <c r="N37" s="169"/>
+      <c r="O37" s="169"/>
+    </row>
+    <row r="38" spans="9:15">
+      <c r="I38" s="169"/>
+      <c r="J38" s="169"/>
+      <c r="K38" s="169"/>
+      <c r="L38" s="169"/>
+      <c r="M38" s="169"/>
+      <c r="N38" s="169"/>
+      <c r="O38" s="169"/>
+    </row>
+    <row r="39" spans="9:15">
+      <c r="I39" s="169"/>
+      <c r="J39" s="169"/>
+      <c r="K39" s="169"/>
+      <c r="L39" s="169"/>
+      <c r="M39" s="169"/>
+      <c r="N39" s="169"/>
+      <c r="O39" s="169"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="I24:O39"/>
+    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="I6:O21"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B8:C11" xr:uid="{F0C12A19-5B7C-43E6-878B-953093678A31}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 D1:D5 D7:D1048576" xr:uid="{8EE0318C-3A2F-4D03-8AC3-17A868D0D886}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD90D1D-3345-4EDC-9CC4-2BE02D44AE19}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -6930,14 +7445,14 @@
     </row>
     <row r="5" spans="3:32" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -6950,7 +7465,7 @@
       <c r="S5" s="154"/>
       <c r="T5" s="155"/>
       <c r="V5" s="153" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="W5" s="154"/>
       <c r="X5" s="154"/>
@@ -6971,16 +7486,16 @@
         <v>31</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -6993,7 +7508,7 @@
       <c r="S6" s="131"/>
       <c r="T6" s="132"/>
       <c r="V6" s="130" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W6" s="131"/>
       <c r="X6" s="131"/>
@@ -8302,7 +8817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632C17C5-59B7-41E9-805B-4B36986E2251}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8383,7 +8898,7 @@
       <c r="Q3" s="123"/>
       <c r="R3" s="124"/>
       <c r="T3" s="122" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="U3" s="123"/>
       <c r="V3" s="124"/>
@@ -8393,10 +8908,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>39</v>
@@ -8412,10 +8927,10 @@
         <v>27</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N4" s="41" t="s">
         <v>35</v>
@@ -8424,27 +8939,27 @@
         <v>21</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>31</v>
       </c>
       <c r="U4" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="V4" s="42" t="s">
         <v>119</v>
-      </c>
-      <c r="V4" s="42" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="15">
       <c r="B5" s="26" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -8458,28 +8973,28 @@
       <c r="K5" s="26"/>
       <c r="L5" s="27"/>
       <c r="N5" s="26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O5" s="37" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="P5" s="37">
         <v>3</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="T5" s="26" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="U5" s="37">
         <v>2</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="15">
@@ -8489,7 +9004,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="27"/>
@@ -8511,17 +9026,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="27"/>
       <c r="K7" s="26"/>
       <c r="L7" s="27"/>
       <c r="N7" s="26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="P7" s="37">
         <v>5</v>
@@ -8608,7 +9123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52C9A5D-390C-4EB4-8E0E-6218D55EFC0C}">
   <dimension ref="C4:I26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -8624,348 +9139,348 @@
     <row r="4" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="5" spans="3:9" ht="16.5" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E10" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="3:9" ht="17.25">
       <c r="C14" s="17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -8973,7 +9488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713538E3-68C7-46EF-9BF7-7D86C6D2932B}">
   <dimension ref="B2:AC45"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9001,7 +9516,7 @@
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="125" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
@@ -9041,46 +9556,46 @@
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="O4" s="178" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P4" s="179"/>
       <c r="Q4" s="179"/>
@@ -9088,28 +9603,28 @@
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -9123,7 +9638,7 @@
     </row>
     <row r="6" spans="2:22" ht="15">
       <c r="B6" s="25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -9136,10 +9651,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -9154,7 +9669,7 @@
     </row>
     <row r="7" spans="2:22" ht="15">
       <c r="B7" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -9167,10 +9682,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -9185,7 +9700,7 @@
     </row>
     <row r="8" spans="2:22" ht="15">
       <c r="B8" s="25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -9198,10 +9713,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -9216,28 +9731,28 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -9251,7 +9766,7 @@
     </row>
     <row r="10" spans="2:22" ht="15">
       <c r="B10" s="25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -9264,10 +9779,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -9282,7 +9797,7 @@
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -9303,7 +9818,7 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -9324,7 +9839,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -9345,7 +9860,7 @@
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -9364,13 +9879,13 @@
       <c r="Q14" s="182"/>
       <c r="R14" s="183"/>
       <c r="U14" s="196" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V14" s="196"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -9393,7 +9908,7 @@
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -9412,15 +9927,15 @@
       <c r="Q16" s="182"/>
       <c r="R16" s="183"/>
       <c r="U16" s="196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="V16" s="197" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -9443,7 +9958,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -9463,12 +9978,12 @@
       <c r="R18" s="183"/>
       <c r="U18" s="196"/>
       <c r="V18" s="197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -9491,7 +10006,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -9511,12 +10026,12 @@
       <c r="R20" s="183"/>
       <c r="U20" s="196"/>
       <c r="V20" s="197" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -9539,7 +10054,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -9559,12 +10074,12 @@
       <c r="R22" s="183"/>
       <c r="U22" s="196"/>
       <c r="V22" s="197" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -9587,7 +10102,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -9607,12 +10122,12 @@
       <c r="R24" s="183"/>
       <c r="U24" s="196"/>
       <c r="V24" s="197" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -9635,7 +10150,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -9655,12 +10170,12 @@
       <c r="R26" s="183"/>
       <c r="U26" s="196"/>
       <c r="V26" s="197" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -9683,7 +10198,7 @@
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="125" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C30" s="126"/>
       <c r="D30" s="126"/>
@@ -9721,46 +10236,46 @@
       <c r="Q31" s="176"/>
       <c r="R31" s="177"/>
       <c r="U31" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="15">
       <c r="B32" s="38" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H32" s="36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L32" s="187" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M32" s="188"/>
       <c r="N32" s="188"/>
@@ -9773,36 +10288,36 @@
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Y32" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="2:29" ht="15">
       <c r="B33" s="26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -9818,7 +10333,7 @@
       <c r="Q33" s="191"/>
       <c r="R33" s="192"/>
       <c r="U33" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -9841,17 +10356,17 @@
       <c r="Q34" s="191"/>
       <c r="R34" s="192"/>
       <c r="U34" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Y34" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Z34" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="2:29" ht="15">
@@ -9874,14 +10389,14 @@
       <c r="R35" s="192"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Y35" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="2:29" ht="15">
@@ -9925,11 +10440,11 @@
       <c r="Q37" s="191"/>
       <c r="R37" s="192"/>
       <c r="U37" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="2:29" ht="15">
@@ -9951,11 +10466,11 @@
       <c r="Q38" s="191"/>
       <c r="R38" s="192"/>
       <c r="U38" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="2:29" ht="15">
@@ -9977,26 +10492,26 @@
       <c r="Q39" s="191"/>
       <c r="R39" s="192"/>
       <c r="U39" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Y39" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Z39" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AA39" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AB39" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AC39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -10167,7 +10682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D35609-775E-4A26-9091-D70AA658E418}">
   <dimension ref="A1:AH37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -10207,7 +10722,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="150" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B1" s="151"/>
       <c r="C1" s="151"/>
@@ -10222,7 +10737,7 @@
       <c r="L1" s="151"/>
       <c r="M1" s="152"/>
       <c r="O1" s="150" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P1" s="151"/>
       <c r="Q1" s="151"/>
@@ -10234,7 +10749,7 @@
       <c r="W1" s="151"/>
       <c r="X1" s="152"/>
       <c r="Z1" s="204" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AA1" s="205"/>
       <c r="AB1" s="205"/>
@@ -10281,7 +10796,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="210" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B3" s="211"/>
       <c r="C3" s="211"/>
@@ -10290,7 +10805,7 @@
       <c r="F3" s="211"/>
       <c r="G3" s="211"/>
       <c r="H3" s="210" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I3" s="211"/>
       <c r="J3" s="211"/>
@@ -10308,14 +10823,14 @@
       <c r="W3" s="202"/>
       <c r="X3" s="203"/>
       <c r="Z3" s="213" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AA3" s="214"/>
       <c r="AB3" s="214"/>
       <c r="AC3" s="214"/>
       <c r="AD3" s="215"/>
       <c r="AE3" s="213" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AF3" s="216"/>
       <c r="AG3" s="216"/>
@@ -10323,131 +10838,131 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="W4" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z4" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA4" s="23" t="s">
         <v>240</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="U4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="V4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="W4" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z4" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>237</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AF4" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG4" s="23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AH4" s="51" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>248</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -10462,54 +10977,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AA5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AB5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AC5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AF5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -10528,39 +11043,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>296</v>
+      </c>
+      <c r="AG6" t="s">
         <v>289</v>
       </c>
-      <c r="AF6" t="s">
-        <v>293</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>286</v>
-      </c>
       <c r="AH6" s="44" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -10579,36 +11094,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AF7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AH7" s="44" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -10953,7 +11468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A12CEB-23C8-48B1-A30D-D9BBB9DB2391}">
   <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -10993,7 +11508,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -11008,7 +11523,7 @@
       <c r="L1" s="126"/>
       <c r="M1" s="127"/>
       <c r="O1" s="125" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P1" s="126"/>
       <c r="Q1" s="126"/>
@@ -11020,7 +11535,7 @@
       <c r="W1" s="126"/>
       <c r="X1" s="127"/>
       <c r="Z1" s="219" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AA1" s="220"/>
       <c r="AB1" s="220"/>
@@ -11067,7 +11582,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
@@ -11076,7 +11591,7 @@
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
       <c r="H3" s="122" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I3" s="123"/>
       <c r="J3" s="123"/>
@@ -11094,14 +11609,14 @@
       <c r="W3" s="228"/>
       <c r="X3" s="229"/>
       <c r="Z3" s="218" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AA3" s="214"/>
       <c r="AB3" s="214"/>
       <c r="AC3" s="214"/>
       <c r="AD3" s="215"/>
       <c r="AE3" s="218" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AF3" s="225"/>
       <c r="AG3" s="225"/>
@@ -11109,161 +11624,161 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="W4" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z4" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA4" s="23" t="s">
         <v>240</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="U4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="V4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="W4" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z4" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>237</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AF4" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG4" s="23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AH4" s="51" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>248</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -11272,66 +11787,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AA5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AB5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AC5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AF5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>248</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -11350,13 +11865,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -11368,16 +11883,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -11396,7 +11911,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -11408,16 +11923,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -11520,7 +12035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8D5FDC-1119-4995-AFF6-CB9868EEC023}">
   <dimension ref="A1:AE36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -11557,7 +12072,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -11569,7 +12084,7 @@
       <c r="I1" s="126"/>
       <c r="J1" s="127"/>
       <c r="L1" s="125" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M1" s="126"/>
       <c r="N1" s="126"/>
@@ -11581,7 +12096,7 @@
       <c r="T1" s="126"/>
       <c r="U1" s="127"/>
       <c r="W1" s="219" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="X1" s="220"/>
       <c r="Y1" s="220"/>
@@ -11625,13 +12140,13 @@
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
       <c r="E3" s="122" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
@@ -11649,14 +12164,14 @@
       <c r="T3" s="228"/>
       <c r="U3" s="229"/>
       <c r="W3" s="218" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="X3" s="214"/>
       <c r="Y3" s="214"/>
       <c r="Z3" s="214"/>
       <c r="AA3" s="215"/>
       <c r="AB3" s="218" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AC3" s="225"/>
       <c r="AD3" s="225"/>
@@ -11664,143 +12179,143 @@
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L4" s="41" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P4" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="R4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="S4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="U4" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="W4" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="X4" s="23" t="s">
         <v>240</v>
-      </c>
-      <c r="Q4" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="R4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="S4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="U4" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="W4" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="X4" s="23" t="s">
-        <v>237</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>248</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -11809,57 +12324,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="X5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Y5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Z5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AC5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AD5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>248</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -11884,16 +12399,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -11918,16 +12433,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -12023,7 +12538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD588F34-D77B-42F6-9174-CC0FF762963C}">
   <dimension ref="B2:H37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12038,7 +12553,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="21">
       <c r="B2" s="230" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C2" s="230"/>
       <c r="D2" s="230"/>
@@ -12050,10 +12565,10 @@
     <row r="3" spans="2:8" ht="17.25" customHeight="1">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D3" s="231" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E3" s="231"/>
       <c r="F3" s="231"/>
@@ -12064,10 +12579,10 @@
       <c r="B4" s="46"/>
       <c r="C4" s="47"/>
       <c r="D4" s="52" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E4" s="231" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F4" s="231"/>
       <c r="G4" s="47"/>
@@ -12077,10 +12592,10 @@
       <c r="B5" s="46"/>
       <c r="C5" s="47"/>
       <c r="D5" s="52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E5" s="231" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F5" s="231"/>
       <c r="G5" s="47"/>
@@ -12142,339 +12657,339 @@
     </row>
     <row r="13" spans="2:8" ht="15">
       <c r="B13" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="2:8" ht="15">
       <c r="B14" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15">
       <c r="B16" s="24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="23" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="23" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15">
       <c r="B26" s="24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="23" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="23" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D35" s="1">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -18364,6 +18879,1135 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B800AF-18CA-4CA9-9CF2-9F3EFB84734C}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:S84"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="3.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="43" customWidth="1"/>
+    <col min="4" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="44" customWidth="1"/>
+    <col min="8" max="8" width="3.375" customWidth="1"/>
+    <col min="9" max="9" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:19">
+      <c r="C1" s="83"/>
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="3:19">
+      <c r="C2" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="156">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="157"/>
+      <c r="F2" s="158"/>
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="3:19">
+      <c r="C3" s="91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="159">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="160"/>
+      <c r="F3" s="161"/>
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="3:19">
+      <c r="C4"/>
+      <c r="G4" s="90"/>
+    </row>
+    <row r="5" spans="3:19" ht="19.5" customHeight="1">
+      <c r="C5" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="124"/>
+      <c r="G5"/>
+      <c r="I5" s="153" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="154"/>
+      <c r="S5" s="155"/>
+    </row>
+    <row r="6" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C6" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6"/>
+      <c r="I6" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="131"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131"/>
+      <c r="N6" s="131"/>
+      <c r="O6" s="131"/>
+      <c r="P6" s="131"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="132"/>
+    </row>
+    <row r="7" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C7" s="26"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="27"/>
+      <c r="G7"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="232"/>
+      <c r="O7" s="232"/>
+      <c r="P7" s="232"/>
+      <c r="Q7" s="232"/>
+      <c r="R7" s="232"/>
+      <c r="S7" s="135"/>
+    </row>
+    <row r="8" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C8" s="26"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="27"/>
+      <c r="G8"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="232"/>
+      <c r="Q8" s="232"/>
+      <c r="R8" s="232"/>
+      <c r="S8" s="135"/>
+    </row>
+    <row r="9" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C9" s="26"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="27"/>
+      <c r="G9"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="232"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="232"/>
+      <c r="P9" s="232"/>
+      <c r="Q9" s="232"/>
+      <c r="R9" s="232"/>
+      <c r="S9" s="135"/>
+    </row>
+    <row r="10" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C10" s="26"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="27"/>
+      <c r="G10"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="232"/>
+      <c r="K10" s="232"/>
+      <c r="L10" s="232"/>
+      <c r="M10" s="232"/>
+      <c r="N10" s="232"/>
+      <c r="O10" s="232"/>
+      <c r="P10" s="232"/>
+      <c r="Q10" s="232"/>
+      <c r="R10" s="232"/>
+      <c r="S10" s="135"/>
+    </row>
+    <row r="11" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C11" s="26"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="27"/>
+      <c r="G11"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232"/>
+      <c r="L11" s="232"/>
+      <c r="M11" s="232"/>
+      <c r="N11" s="232"/>
+      <c r="O11" s="232"/>
+      <c r="P11" s="232"/>
+      <c r="Q11" s="232"/>
+      <c r="R11" s="232"/>
+      <c r="S11" s="135"/>
+    </row>
+    <row r="12" spans="3:19" ht="13.5" customHeight="1">
+      <c r="C12" s="26"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="44"/>
+      <c r="G12"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="232"/>
+      <c r="O12" s="232"/>
+      <c r="P12" s="232"/>
+      <c r="Q12" s="232"/>
+      <c r="R12" s="232"/>
+      <c r="S12" s="135"/>
+    </row>
+    <row r="13" spans="3:19" ht="13.5" customHeight="1">
+      <c r="F13" s="44"/>
+      <c r="G13"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="232"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="232"/>
+      <c r="O13" s="232"/>
+      <c r="P13" s="232"/>
+      <c r="Q13" s="232"/>
+      <c r="R13" s="232"/>
+      <c r="S13" s="135"/>
+    </row>
+    <row r="14" spans="3:19" ht="13.5" customHeight="1">
+      <c r="F14" s="44"/>
+      <c r="G14"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="232"/>
+      <c r="K14" s="232"/>
+      <c r="L14" s="232"/>
+      <c r="M14" s="232"/>
+      <c r="N14" s="232"/>
+      <c r="O14" s="232"/>
+      <c r="P14" s="232"/>
+      <c r="Q14" s="232"/>
+      <c r="R14" s="232"/>
+      <c r="S14" s="135"/>
+    </row>
+    <row r="15" spans="3:19" ht="13.5" customHeight="1">
+      <c r="F15" s="44"/>
+      <c r="G15"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="232"/>
+      <c r="K15" s="232"/>
+      <c r="L15" s="232"/>
+      <c r="M15" s="232"/>
+      <c r="N15" s="232"/>
+      <c r="O15" s="232"/>
+      <c r="P15" s="232"/>
+      <c r="Q15" s="232"/>
+      <c r="R15" s="232"/>
+      <c r="S15" s="135"/>
+    </row>
+    <row r="16" spans="3:19" ht="13.5" customHeight="1">
+      <c r="F16" s="44"/>
+      <c r="G16"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="232"/>
+      <c r="K16" s="232"/>
+      <c r="L16" s="232"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="232"/>
+      <c r="O16" s="232"/>
+      <c r="P16" s="232"/>
+      <c r="Q16" s="232"/>
+      <c r="R16" s="232"/>
+      <c r="S16" s="135"/>
+    </row>
+    <row r="17" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F17" s="44"/>
+      <c r="G17"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="232"/>
+      <c r="L17" s="232"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="232"/>
+      <c r="O17" s="232"/>
+      <c r="P17" s="232"/>
+      <c r="Q17" s="232"/>
+      <c r="R17" s="232"/>
+      <c r="S17" s="135"/>
+    </row>
+    <row r="18" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F18" s="44"/>
+      <c r="G18"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="232"/>
+      <c r="O18" s="232"/>
+      <c r="P18" s="232"/>
+      <c r="Q18" s="232"/>
+      <c r="R18" s="232"/>
+      <c r="S18" s="135"/>
+    </row>
+    <row r="19" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F19" s="44"/>
+      <c r="G19"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="232"/>
+      <c r="L19" s="232"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="232"/>
+      <c r="O19" s="232"/>
+      <c r="P19" s="232"/>
+      <c r="Q19" s="232"/>
+      <c r="R19" s="232"/>
+      <c r="S19" s="135"/>
+    </row>
+    <row r="20" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F20" s="44"/>
+      <c r="G20"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="232"/>
+      <c r="K20" s="232"/>
+      <c r="L20" s="232"/>
+      <c r="M20" s="232"/>
+      <c r="N20" s="232"/>
+      <c r="O20" s="232"/>
+      <c r="P20" s="232"/>
+      <c r="Q20" s="232"/>
+      <c r="R20" s="232"/>
+      <c r="S20" s="135"/>
+    </row>
+    <row r="21" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F21" s="44"/>
+      <c r="G21"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="232"/>
+      <c r="K21" s="232"/>
+      <c r="L21" s="232"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="232"/>
+      <c r="O21" s="232"/>
+      <c r="P21" s="232"/>
+      <c r="Q21" s="232"/>
+      <c r="R21" s="232"/>
+      <c r="S21" s="135"/>
+    </row>
+    <row r="22" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F22" s="44"/>
+      <c r="G22"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="232"/>
+      <c r="K22" s="232"/>
+      <c r="L22" s="232"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="232"/>
+      <c r="P22" s="232"/>
+      <c r="Q22" s="232"/>
+      <c r="R22" s="232"/>
+      <c r="S22" s="135"/>
+    </row>
+    <row r="23" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F23" s="44"/>
+      <c r="G23"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="232"/>
+      <c r="K23" s="232"/>
+      <c r="L23" s="232"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="232"/>
+      <c r="O23" s="232"/>
+      <c r="P23" s="232"/>
+      <c r="Q23" s="232"/>
+      <c r="R23" s="232"/>
+      <c r="S23" s="135"/>
+    </row>
+    <row r="24" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F24" s="44"/>
+      <c r="G24"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="232"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="232"/>
+      <c r="O24" s="232"/>
+      <c r="P24" s="232"/>
+      <c r="Q24" s="232"/>
+      <c r="R24" s="232"/>
+      <c r="S24" s="135"/>
+    </row>
+    <row r="25" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F25" s="44"/>
+      <c r="G25"/>
+      <c r="I25" s="133"/>
+      <c r="J25" s="232"/>
+      <c r="K25" s="232"/>
+      <c r="L25" s="232"/>
+      <c r="M25" s="232"/>
+      <c r="N25" s="232"/>
+      <c r="O25" s="232"/>
+      <c r="P25" s="232"/>
+      <c r="Q25" s="232"/>
+      <c r="R25" s="232"/>
+      <c r="S25" s="135"/>
+    </row>
+    <row r="26" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F26" s="44"/>
+      <c r="G26"/>
+      <c r="I26" s="133"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="232"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="232"/>
+      <c r="O26" s="232"/>
+      <c r="P26" s="232"/>
+      <c r="Q26" s="232"/>
+      <c r="R26" s="232"/>
+      <c r="S26" s="135"/>
+    </row>
+    <row r="27" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F27" s="44"/>
+      <c r="G27"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="232"/>
+      <c r="K27" s="232"/>
+      <c r="L27" s="232"/>
+      <c r="M27" s="232"/>
+      <c r="N27" s="232"/>
+      <c r="O27" s="232"/>
+      <c r="P27" s="232"/>
+      <c r="Q27" s="232"/>
+      <c r="R27" s="232"/>
+      <c r="S27" s="135"/>
+    </row>
+    <row r="28" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F28" s="44"/>
+      <c r="G28"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="232"/>
+      <c r="K28" s="232"/>
+      <c r="L28" s="232"/>
+      <c r="M28" s="232"/>
+      <c r="N28" s="232"/>
+      <c r="O28" s="232"/>
+      <c r="P28" s="232"/>
+      <c r="Q28" s="232"/>
+      <c r="R28" s="232"/>
+      <c r="S28" s="135"/>
+    </row>
+    <row r="29" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F29" s="44"/>
+      <c r="G29"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="232"/>
+      <c r="K29" s="232"/>
+      <c r="L29" s="232"/>
+      <c r="M29" s="232"/>
+      <c r="N29" s="232"/>
+      <c r="O29" s="232"/>
+      <c r="P29" s="232"/>
+      <c r="Q29" s="232"/>
+      <c r="R29" s="232"/>
+      <c r="S29" s="135"/>
+    </row>
+    <row r="30" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F30" s="44"/>
+      <c r="G30"/>
+      <c r="I30" s="133"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="232"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="232"/>
+      <c r="O30" s="232"/>
+      <c r="P30" s="232"/>
+      <c r="Q30" s="232"/>
+      <c r="R30" s="232"/>
+      <c r="S30" s="135"/>
+    </row>
+    <row r="31" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F31" s="44"/>
+      <c r="G31"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="232"/>
+      <c r="O31" s="232"/>
+      <c r="P31" s="232"/>
+      <c r="Q31" s="232"/>
+      <c r="R31" s="232"/>
+      <c r="S31" s="135"/>
+    </row>
+    <row r="32" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F32" s="44"/>
+      <c r="G32"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="232"/>
+      <c r="P32" s="232"/>
+      <c r="Q32" s="232"/>
+      <c r="R32" s="232"/>
+      <c r="S32" s="135"/>
+    </row>
+    <row r="33" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F33" s="44"/>
+      <c r="G33"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="232"/>
+      <c r="O33" s="232"/>
+      <c r="P33" s="232"/>
+      <c r="Q33" s="232"/>
+      <c r="R33" s="232"/>
+      <c r="S33" s="135"/>
+    </row>
+    <row r="34" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F34" s="44"/>
+      <c r="G34"/>
+      <c r="I34" s="133"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="232"/>
+      <c r="O34" s="232"/>
+      <c r="P34" s="232"/>
+      <c r="Q34" s="232"/>
+      <c r="R34" s="232"/>
+      <c r="S34" s="135"/>
+    </row>
+    <row r="35" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F35" s="44"/>
+      <c r="G35"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="232"/>
+      <c r="O35" s="232"/>
+      <c r="P35" s="232"/>
+      <c r="Q35" s="232"/>
+      <c r="R35" s="232"/>
+      <c r="S35" s="135"/>
+    </row>
+    <row r="36" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F36" s="44"/>
+      <c r="G36"/>
+      <c r="I36" s="133"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="232"/>
+      <c r="O36" s="232"/>
+      <c r="P36" s="232"/>
+      <c r="Q36" s="232"/>
+      <c r="R36" s="232"/>
+      <c r="S36" s="135"/>
+    </row>
+    <row r="37" spans="2:19" ht="13.5" customHeight="1">
+      <c r="B37" s="7"/>
+      <c r="F37" s="44"/>
+      <c r="G37"/>
+      <c r="I37" s="133"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="232"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="232"/>
+      <c r="O37" s="232"/>
+      <c r="P37" s="232"/>
+      <c r="Q37" s="232"/>
+      <c r="R37" s="232"/>
+      <c r="S37" s="135"/>
+    </row>
+    <row r="38" spans="2:19" ht="13.5" customHeight="1">
+      <c r="B38" s="7"/>
+      <c r="F38" s="44"/>
+      <c r="G38"/>
+      <c r="I38" s="133"/>
+      <c r="J38" s="232"/>
+      <c r="K38" s="232"/>
+      <c r="L38" s="232"/>
+      <c r="M38" s="232"/>
+      <c r="N38" s="232"/>
+      <c r="O38" s="232"/>
+      <c r="P38" s="232"/>
+      <c r="Q38" s="232"/>
+      <c r="R38" s="232"/>
+      <c r="S38" s="135"/>
+    </row>
+    <row r="39" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F39" s="44"/>
+      <c r="G39"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="232"/>
+      <c r="K39" s="232"/>
+      <c r="L39" s="232"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="232"/>
+      <c r="O39" s="232"/>
+      <c r="P39" s="232"/>
+      <c r="Q39" s="232"/>
+      <c r="R39" s="232"/>
+      <c r="S39" s="135"/>
+    </row>
+    <row r="40" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F40" s="44"/>
+      <c r="G40"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="135"/>
+    </row>
+    <row r="41" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F41" s="44"/>
+      <c r="G41"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="232"/>
+      <c r="M41" s="232"/>
+      <c r="N41" s="232"/>
+      <c r="O41" s="232"/>
+      <c r="P41" s="232"/>
+      <c r="Q41" s="232"/>
+      <c r="R41" s="232"/>
+      <c r="S41" s="135"/>
+    </row>
+    <row r="42" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F42" s="44"/>
+      <c r="G42"/>
+      <c r="I42" s="133"/>
+      <c r="J42" s="232"/>
+      <c r="K42" s="232"/>
+      <c r="L42" s="232"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="232"/>
+      <c r="O42" s="232"/>
+      <c r="P42" s="232"/>
+      <c r="Q42" s="232"/>
+      <c r="R42" s="232"/>
+      <c r="S42" s="135"/>
+    </row>
+    <row r="43" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F43" s="44"/>
+      <c r="G43"/>
+      <c r="I43" s="133"/>
+      <c r="J43" s="232"/>
+      <c r="K43" s="232"/>
+      <c r="L43" s="232"/>
+      <c r="M43" s="232"/>
+      <c r="N43" s="232"/>
+      <c r="O43" s="232"/>
+      <c r="P43" s="232"/>
+      <c r="Q43" s="232"/>
+      <c r="R43" s="232"/>
+      <c r="S43" s="135"/>
+    </row>
+    <row r="44" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F44" s="44"/>
+      <c r="G44"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="232"/>
+      <c r="K44" s="232"/>
+      <c r="L44" s="232"/>
+      <c r="M44" s="232"/>
+      <c r="N44" s="232"/>
+      <c r="O44" s="232"/>
+      <c r="P44" s="232"/>
+      <c r="Q44" s="232"/>
+      <c r="R44" s="232"/>
+      <c r="S44" s="135"/>
+    </row>
+    <row r="45" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F45" s="44"/>
+      <c r="G45"/>
+      <c r="I45" s="133"/>
+      <c r="J45" s="232"/>
+      <c r="K45" s="232"/>
+      <c r="L45" s="232"/>
+      <c r="M45" s="232"/>
+      <c r="N45" s="232"/>
+      <c r="O45" s="232"/>
+      <c r="P45" s="232"/>
+      <c r="Q45" s="232"/>
+      <c r="R45" s="232"/>
+      <c r="S45" s="135"/>
+    </row>
+    <row r="46" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F46" s="44"/>
+      <c r="G46"/>
+      <c r="I46" s="133"/>
+      <c r="J46" s="232"/>
+      <c r="K46" s="232"/>
+      <c r="L46" s="232"/>
+      <c r="M46" s="232"/>
+      <c r="N46" s="232"/>
+      <c r="O46" s="232"/>
+      <c r="P46" s="232"/>
+      <c r="Q46" s="232"/>
+      <c r="R46" s="232"/>
+      <c r="S46" s="135"/>
+    </row>
+    <row r="47" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F47" s="44"/>
+      <c r="G47"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="232"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="232"/>
+      <c r="M47" s="232"/>
+      <c r="N47" s="232"/>
+      <c r="O47" s="232"/>
+      <c r="P47" s="232"/>
+      <c r="Q47" s="232"/>
+      <c r="R47" s="232"/>
+      <c r="S47" s="135"/>
+    </row>
+    <row r="48" spans="2:19" ht="13.5" customHeight="1">
+      <c r="F48" s="44"/>
+      <c r="G48"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="232"/>
+      <c r="L48" s="232"/>
+      <c r="M48" s="232"/>
+      <c r="N48" s="232"/>
+      <c r="O48" s="232"/>
+      <c r="P48" s="232"/>
+      <c r="Q48" s="232"/>
+      <c r="R48" s="232"/>
+      <c r="S48" s="135"/>
+    </row>
+    <row r="49" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F49" s="44"/>
+      <c r="G49"/>
+      <c r="I49" s="133"/>
+      <c r="J49" s="232"/>
+      <c r="K49" s="232"/>
+      <c r="L49" s="232"/>
+      <c r="M49" s="232"/>
+      <c r="N49" s="232"/>
+      <c r="O49" s="232"/>
+      <c r="P49" s="232"/>
+      <c r="Q49" s="232"/>
+      <c r="R49" s="232"/>
+      <c r="S49" s="135"/>
+    </row>
+    <row r="50" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F50" s="44"/>
+      <c r="G50"/>
+      <c r="I50" s="133"/>
+      <c r="J50" s="232"/>
+      <c r="K50" s="232"/>
+      <c r="L50" s="232"/>
+      <c r="M50" s="232"/>
+      <c r="N50" s="232"/>
+      <c r="O50" s="232"/>
+      <c r="P50" s="232"/>
+      <c r="Q50" s="232"/>
+      <c r="R50" s="232"/>
+      <c r="S50" s="135"/>
+    </row>
+    <row r="51" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F51" s="44"/>
+      <c r="G51"/>
+      <c r="I51" s="133"/>
+      <c r="J51" s="232"/>
+      <c r="K51" s="232"/>
+      <c r="L51" s="232"/>
+      <c r="M51" s="232"/>
+      <c r="N51" s="232"/>
+      <c r="O51" s="232"/>
+      <c r="P51" s="232"/>
+      <c r="Q51" s="232"/>
+      <c r="R51" s="232"/>
+      <c r="S51" s="135"/>
+    </row>
+    <row r="52" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F52" s="44"/>
+      <c r="G52"/>
+      <c r="I52" s="133"/>
+      <c r="J52" s="232"/>
+      <c r="K52" s="232"/>
+      <c r="L52" s="232"/>
+      <c r="M52" s="232"/>
+      <c r="N52" s="232"/>
+      <c r="O52" s="232"/>
+      <c r="P52" s="232"/>
+      <c r="Q52" s="232"/>
+      <c r="R52" s="232"/>
+      <c r="S52" s="135"/>
+    </row>
+    <row r="53" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F53" s="44"/>
+      <c r="G53"/>
+      <c r="I53" s="133"/>
+      <c r="J53" s="232"/>
+      <c r="K53" s="232"/>
+      <c r="L53" s="232"/>
+      <c r="M53" s="232"/>
+      <c r="N53" s="232"/>
+      <c r="O53" s="232"/>
+      <c r="P53" s="232"/>
+      <c r="Q53" s="232"/>
+      <c r="R53" s="232"/>
+      <c r="S53" s="135"/>
+    </row>
+    <row r="54" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F54" s="44"/>
+      <c r="G54"/>
+      <c r="I54" s="133"/>
+      <c r="J54" s="232"/>
+      <c r="K54" s="232"/>
+      <c r="L54" s="232"/>
+      <c r="M54" s="232"/>
+      <c r="N54" s="232"/>
+      <c r="O54" s="232"/>
+      <c r="P54" s="232"/>
+      <c r="Q54" s="232"/>
+      <c r="R54" s="232"/>
+      <c r="S54" s="135"/>
+    </row>
+    <row r="55" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F55" s="44"/>
+      <c r="G55"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="232"/>
+      <c r="K55" s="232"/>
+      <c r="L55" s="232"/>
+      <c r="M55" s="232"/>
+      <c r="N55" s="232"/>
+      <c r="O55" s="232"/>
+      <c r="P55" s="232"/>
+      <c r="Q55" s="232"/>
+      <c r="R55" s="232"/>
+      <c r="S55" s="135"/>
+    </row>
+    <row r="56" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F56" s="44"/>
+      <c r="G56"/>
+      <c r="I56" s="133"/>
+      <c r="J56" s="232"/>
+      <c r="K56" s="232"/>
+      <c r="L56" s="232"/>
+      <c r="M56" s="232"/>
+      <c r="N56" s="232"/>
+      <c r="O56" s="232"/>
+      <c r="P56" s="232"/>
+      <c r="Q56" s="232"/>
+      <c r="R56" s="232"/>
+      <c r="S56" s="135"/>
+    </row>
+    <row r="57" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F57" s="44"/>
+      <c r="G57"/>
+      <c r="I57" s="133"/>
+      <c r="J57" s="232"/>
+      <c r="K57" s="232"/>
+      <c r="L57" s="232"/>
+      <c r="M57" s="232"/>
+      <c r="N57" s="232"/>
+      <c r="O57" s="232"/>
+      <c r="P57" s="232"/>
+      <c r="Q57" s="232"/>
+      <c r="R57" s="232"/>
+      <c r="S57" s="135"/>
+    </row>
+    <row r="58" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F58" s="44"/>
+      <c r="G58"/>
+      <c r="I58" s="133"/>
+      <c r="J58" s="232"/>
+      <c r="K58" s="232"/>
+      <c r="L58" s="232"/>
+      <c r="M58" s="232"/>
+      <c r="N58" s="232"/>
+      <c r="O58" s="232"/>
+      <c r="P58" s="232"/>
+      <c r="Q58" s="232"/>
+      <c r="R58" s="232"/>
+      <c r="S58" s="135"/>
+    </row>
+    <row r="59" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F59" s="44"/>
+      <c r="G59"/>
+      <c r="I59" s="133"/>
+      <c r="J59" s="232"/>
+      <c r="K59" s="232"/>
+      <c r="L59" s="232"/>
+      <c r="M59" s="232"/>
+      <c r="N59" s="232"/>
+      <c r="O59" s="232"/>
+      <c r="P59" s="232"/>
+      <c r="Q59" s="232"/>
+      <c r="R59" s="232"/>
+      <c r="S59" s="135"/>
+    </row>
+    <row r="60" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F60" s="44"/>
+      <c r="G60"/>
+      <c r="I60" s="133"/>
+      <c r="J60" s="232"/>
+      <c r="K60" s="232"/>
+      <c r="L60" s="232"/>
+      <c r="M60" s="232"/>
+      <c r="N60" s="232"/>
+      <c r="O60" s="232"/>
+      <c r="P60" s="232"/>
+      <c r="Q60" s="232"/>
+      <c r="R60" s="232"/>
+      <c r="S60" s="135"/>
+    </row>
+    <row r="61" spans="6:19" ht="13.5" customHeight="1">
+      <c r="F61" s="44"/>
+      <c r="G61"/>
+      <c r="I61" s="133"/>
+      <c r="J61" s="232"/>
+      <c r="K61" s="232"/>
+      <c r="L61" s="232"/>
+      <c r="M61" s="232"/>
+      <c r="N61" s="232"/>
+      <c r="O61" s="232"/>
+      <c r="P61" s="232"/>
+      <c r="Q61" s="232"/>
+      <c r="R61" s="232"/>
+      <c r="S61" s="135"/>
+    </row>
+    <row r="62" spans="6:19">
+      <c r="F62" s="44"/>
+      <c r="G62"/>
+      <c r="I62" s="133"/>
+      <c r="J62" s="232"/>
+      <c r="K62" s="232"/>
+      <c r="L62" s="232"/>
+      <c r="M62" s="232"/>
+      <c r="N62" s="232"/>
+      <c r="O62" s="232"/>
+      <c r="P62" s="232"/>
+      <c r="Q62" s="232"/>
+      <c r="R62" s="232"/>
+      <c r="S62" s="135"/>
+    </row>
+    <row r="63" spans="6:19">
+      <c r="F63" s="44"/>
+      <c r="G63"/>
+      <c r="I63" s="133"/>
+      <c r="J63" s="232"/>
+      <c r="K63" s="232"/>
+      <c r="L63" s="232"/>
+      <c r="M63" s="232"/>
+      <c r="N63" s="232"/>
+      <c r="O63" s="232"/>
+      <c r="P63" s="232"/>
+      <c r="Q63" s="232"/>
+      <c r="R63" s="232"/>
+      <c r="S63" s="135"/>
+    </row>
+    <row r="64" spans="6:19">
+      <c r="F64" s="44"/>
+      <c r="G64"/>
+      <c r="I64" s="133"/>
+      <c r="J64" s="232"/>
+      <c r="K64" s="232"/>
+      <c r="L64" s="232"/>
+      <c r="M64" s="232"/>
+      <c r="N64" s="232"/>
+      <c r="O64" s="232"/>
+      <c r="P64" s="232"/>
+      <c r="Q64" s="232"/>
+      <c r="R64" s="232"/>
+      <c r="S64" s="135"/>
+    </row>
+    <row r="65" spans="6:19">
+      <c r="F65" s="44"/>
+      <c r="G65"/>
+      <c r="I65" s="133"/>
+      <c r="J65" s="232"/>
+      <c r="K65" s="232"/>
+      <c r="L65" s="232"/>
+      <c r="M65" s="232"/>
+      <c r="N65" s="232"/>
+      <c r="O65" s="232"/>
+      <c r="P65" s="232"/>
+      <c r="Q65" s="232"/>
+      <c r="R65" s="232"/>
+      <c r="S65" s="135"/>
+    </row>
+    <row r="66" spans="6:19">
+      <c r="F66" s="44"/>
+      <c r="G66"/>
+      <c r="I66" s="133"/>
+      <c r="J66" s="232"/>
+      <c r="K66" s="232"/>
+      <c r="L66" s="232"/>
+      <c r="M66" s="232"/>
+      <c r="N66" s="232"/>
+      <c r="O66" s="232"/>
+      <c r="P66" s="232"/>
+      <c r="Q66" s="232"/>
+      <c r="R66" s="232"/>
+      <c r="S66" s="135"/>
+    </row>
+    <row r="67" spans="6:19">
+      <c r="F67" s="44"/>
+      <c r="G67"/>
+      <c r="I67" s="133"/>
+      <c r="J67" s="232"/>
+      <c r="K67" s="232"/>
+      <c r="L67" s="232"/>
+      <c r="M67" s="232"/>
+      <c r="N67" s="232"/>
+      <c r="O67" s="232"/>
+      <c r="P67" s="232"/>
+      <c r="Q67" s="232"/>
+      <c r="R67" s="232"/>
+      <c r="S67" s="135"/>
+    </row>
+    <row r="68" spans="6:19">
+      <c r="F68" s="44"/>
+      <c r="G68"/>
+      <c r="I68" s="136"/>
+      <c r="J68" s="137"/>
+      <c r="K68" s="137"/>
+      <c r="L68" s="137"/>
+      <c r="M68" s="137"/>
+      <c r="N68" s="137"/>
+      <c r="O68" s="137"/>
+      <c r="P68" s="137"/>
+      <c r="Q68" s="137"/>
+      <c r="R68" s="137"/>
+      <c r="S68" s="138"/>
+    </row>
+    <row r="69" spans="6:19">
+      <c r="F69" s="44"/>
+      <c r="G69"/>
+    </row>
+    <row r="70" spans="6:19">
+      <c r="F70" s="44"/>
+      <c r="G70"/>
+    </row>
+    <row r="71" spans="6:19">
+      <c r="F71" s="44"/>
+      <c r="G71"/>
+    </row>
+    <row r="72" spans="6:19">
+      <c r="F72" s="44"/>
+      <c r="G72"/>
+    </row>
+    <row r="73" spans="6:19">
+      <c r="F73" s="44"/>
+      <c r="G73"/>
+    </row>
+    <row r="74" spans="6:19">
+      <c r="F74" s="44"/>
+      <c r="G74"/>
+    </row>
+    <row r="75" spans="6:19">
+      <c r="F75" s="44"/>
+      <c r="G75"/>
+    </row>
+    <row r="76" spans="6:19">
+      <c r="F76" s="44"/>
+      <c r="G76"/>
+    </row>
+    <row r="77" spans="6:19">
+      <c r="F77" s="44"/>
+      <c r="G77"/>
+    </row>
+    <row r="78" spans="6:19">
+      <c r="F78" s="44"/>
+      <c r="G78"/>
+    </row>
+    <row r="79" spans="6:19">
+      <c r="F79" s="44"/>
+      <c r="G79"/>
+    </row>
+    <row r="80" spans="6:19">
+      <c r="F80" s="44"/>
+      <c r="G80"/>
+    </row>
+    <row r="81" spans="6:7">
+      <c r="F81" s="44"/>
+      <c r="G81"/>
+    </row>
+    <row r="82" spans="6:7">
+      <c r="F82" s="44"/>
+      <c r="G82"/>
+    </row>
+    <row r="83" spans="6:7">
+      <c r="F83" s="44"/>
+      <c r="G83"/>
+    </row>
+    <row r="84" spans="6:7">
+      <c r="F84" s="44"/>
+      <c r="G84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="I5:S5"/>
+    <mergeCell ref="I6:S68"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E12 G1 F6:F84 G85:G1048576 C7:D12" xr:uid="{FDF74671-6EE0-48D7-9EBF-0F66C0E6C0B9}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385F985E-2870-4308-82B2-23D8BBD3D2EC}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -18415,14 +20059,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -18440,7 +20084,7 @@
         <v>91</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>86</v>
@@ -18452,7 +20096,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -19577,7 +21221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66394428-CC81-4B04-9434-EDC45C3B131C}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -19648,7 +21292,7 @@
       <c r="S5" s="154"/>
       <c r="T5" s="155"/>
       <c r="V5" s="153" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W5" s="154"/>
       <c r="X5" s="154"/>
@@ -19666,19 +21310,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -19691,7 +21335,7 @@
       <c r="S6" s="131"/>
       <c r="T6" s="132"/>
       <c r="V6" s="130" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="W6" s="131"/>
       <c r="X6" s="131"/>
@@ -19706,7 +21350,7 @@
     </row>
     <row r="7" spans="3:32" ht="13.5" customHeight="1">
       <c r="C7" s="26" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>80</v>
@@ -19745,10 +21389,10 @@
     </row>
     <row r="8" spans="3:32" ht="13.5" customHeight="1">
       <c r="C8" s="26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>81</v>
@@ -20824,452 +22468,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0A1BC2-AD1F-4F40-B462-EAC4DD963BF3}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="B1:O39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="3" width="18.125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="44" customWidth="1"/>
-    <col min="5" max="5" width="17.25" customWidth="1"/>
-    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" style="43" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15">
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="G1"/>
-    </row>
-    <row r="2" spans="2:15">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="G2"/>
-    </row>
-    <row r="3" spans="2:15">
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="G3"/>
-    </row>
-    <row r="4" spans="2:15">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="G4"/>
-    </row>
-    <row r="5" spans="2:15" ht="21">
-      <c r="B5" s="125" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="70"/>
-      <c r="I5" s="170" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" s="170"/>
-      <c r="K5" s="170"/>
-      <c r="L5" s="170"/>
-      <c r="M5" s="170"/>
-      <c r="N5" s="170"/>
-      <c r="O5" s="170"/>
-    </row>
-    <row r="6" spans="2:15" ht="13.5" customHeight="1">
-      <c r="B6" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="128" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="128"/>
-      <c r="E6" s="129" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="129"/>
-      <c r="G6" s="72"/>
-      <c r="I6" s="169" t="s">
-        <v>108</v>
-      </c>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-    </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="26"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="26"/>
-      <c r="I8" s="169"/>
-      <c r="J8" s="169"/>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="26"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-    </row>
-    <row r="10" spans="2:15">
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="26"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-    </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="I11" s="169"/>
-      <c r="J11" s="169"/>
-      <c r="K11" s="169"/>
-      <c r="L11" s="169"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-    </row>
-    <row r="12" spans="2:15">
-      <c r="G12" s="26"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-    </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="I13" s="169"/>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-    </row>
-    <row r="14" spans="2:15">
-      <c r="I14" s="169"/>
-      <c r="J14" s="169"/>
-      <c r="K14" s="169"/>
-      <c r="L14" s="169"/>
-      <c r="M14" s="169"/>
-      <c r="N14" s="169"/>
-      <c r="O14" s="169"/>
-    </row>
-    <row r="15" spans="2:15">
-      <c r="I15" s="169"/>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
-      <c r="L15" s="169"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-    </row>
-    <row r="16" spans="2:15">
-      <c r="I16" s="169"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="169"/>
-      <c r="M16" s="169"/>
-      <c r="N16" s="169"/>
-      <c r="O16" s="169"/>
-    </row>
-    <row r="17" spans="9:15">
-      <c r="I17" s="169"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="169"/>
-      <c r="M17" s="169"/>
-      <c r="N17" s="169"/>
-      <c r="O17" s="169"/>
-    </row>
-    <row r="18" spans="9:15">
-      <c r="I18" s="169"/>
-      <c r="J18" s="169"/>
-      <c r="K18" s="169"/>
-      <c r="L18" s="169"/>
-      <c r="M18" s="169"/>
-      <c r="N18" s="169"/>
-      <c r="O18" s="169"/>
-    </row>
-    <row r="19" spans="9:15">
-      <c r="I19" s="169"/>
-      <c r="J19" s="169"/>
-      <c r="K19" s="169"/>
-      <c r="L19" s="169"/>
-      <c r="M19" s="169"/>
-      <c r="N19" s="169"/>
-      <c r="O19" s="169"/>
-    </row>
-    <row r="20" spans="9:15">
-      <c r="I20" s="169"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="169"/>
-      <c r="L20" s="169"/>
-      <c r="M20" s="169"/>
-      <c r="N20" s="169"/>
-      <c r="O20" s="169"/>
-    </row>
-    <row r="21" spans="9:15">
-      <c r="I21" s="169"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="169"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-      <c r="O21" s="169"/>
-    </row>
-    <row r="23" spans="9:15" ht="21">
-      <c r="I23" s="170" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="170"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="170"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="170"/>
-      <c r="O23" s="170"/>
-    </row>
-    <row r="24" spans="9:15" ht="13.5" customHeight="1">
-      <c r="I24" s="169" t="s">
-        <v>110</v>
-      </c>
-      <c r="J24" s="169"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="169"/>
-      <c r="M24" s="169"/>
-      <c r="N24" s="169"/>
-      <c r="O24" s="169"/>
-    </row>
-    <row r="25" spans="9:15">
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="169"/>
-      <c r="L25" s="169"/>
-      <c r="M25" s="169"/>
-      <c r="N25" s="169"/>
-      <c r="O25" s="169"/>
-    </row>
-    <row r="26" spans="9:15">
-      <c r="I26" s="169"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="169"/>
-      <c r="L26" s="169"/>
-      <c r="M26" s="169"/>
-      <c r="N26" s="169"/>
-      <c r="O26" s="169"/>
-    </row>
-    <row r="27" spans="9:15">
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="169"/>
-      <c r="L27" s="169"/>
-      <c r="M27" s="169"/>
-      <c r="N27" s="169"/>
-      <c r="O27" s="169"/>
-    </row>
-    <row r="28" spans="9:15">
-      <c r="I28" s="169"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="169"/>
-      <c r="L28" s="169"/>
-      <c r="M28" s="169"/>
-      <c r="N28" s="169"/>
-      <c r="O28" s="169"/>
-    </row>
-    <row r="29" spans="9:15">
-      <c r="I29" s="169"/>
-      <c r="J29" s="169"/>
-      <c r="K29" s="169"/>
-      <c r="L29" s="169"/>
-      <c r="M29" s="169"/>
-      <c r="N29" s="169"/>
-      <c r="O29" s="169"/>
-    </row>
-    <row r="30" spans="9:15">
-      <c r="I30" s="169"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="169"/>
-      <c r="M30" s="169"/>
-      <c r="N30" s="169"/>
-      <c r="O30" s="169"/>
-    </row>
-    <row r="31" spans="9:15">
-      <c r="I31" s="169"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="169"/>
-      <c r="L31" s="169"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="169"/>
-      <c r="O31" s="169"/>
-    </row>
-    <row r="32" spans="9:15">
-      <c r="I32" s="169"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="169"/>
-      <c r="L32" s="169"/>
-      <c r="M32" s="169"/>
-      <c r="N32" s="169"/>
-      <c r="O32" s="169"/>
-    </row>
-    <row r="33" spans="9:15">
-      <c r="I33" s="169"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="169"/>
-      <c r="M33" s="169"/>
-      <c r="N33" s="169"/>
-      <c r="O33" s="169"/>
-    </row>
-    <row r="34" spans="9:15">
-      <c r="I34" s="169"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="169"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="169"/>
-      <c r="O34" s="169"/>
-    </row>
-    <row r="35" spans="9:15">
-      <c r="I35" s="169"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="169"/>
-      <c r="L35" s="169"/>
-      <c r="M35" s="169"/>
-      <c r="N35" s="169"/>
-      <c r="O35" s="169"/>
-    </row>
-    <row r="36" spans="9:15">
-      <c r="I36" s="169"/>
-      <c r="J36" s="169"/>
-      <c r="K36" s="169"/>
-      <c r="L36" s="169"/>
-      <c r="M36" s="169"/>
-      <c r="N36" s="169"/>
-      <c r="O36" s="169"/>
-    </row>
-    <row r="37" spans="9:15">
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
-      <c r="M37" s="169"/>
-      <c r="N37" s="169"/>
-      <c r="O37" s="169"/>
-    </row>
-    <row r="38" spans="9:15">
-      <c r="I38" s="169"/>
-      <c r="J38" s="169"/>
-      <c r="K38" s="169"/>
-      <c r="L38" s="169"/>
-      <c r="M38" s="169"/>
-      <c r="N38" s="169"/>
-      <c r="O38" s="169"/>
-    </row>
-    <row r="39" spans="9:15">
-      <c r="I39" s="169"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="169"/>
-      <c r="L39" s="169"/>
-      <c r="M39" s="169"/>
-      <c r="N39" s="169"/>
-      <c r="O39" s="169"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="I24:O39"/>
-    <mergeCell ref="I23:O23"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="I6:O21"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="You can only enter a value when B6 is &quot;Property&quot;." sqref="B8:C11" xr:uid="{F0C12A19-5B7C-43E6-878B-953093678A31}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 D1:D5 D7:D1048576" xr:uid="{8EE0318C-3A2F-4D03-8AC3-17A868D0D886}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82E7A9A6-D311-4A4B-BA7A-2A72C0D7A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CADDA5E-8B12-44BE-861D-0B54AA9B3FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="8" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="9" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -22,16 +22,17 @@
     <sheet name="HFP" sheetId="24" r:id="rId7"/>
     <sheet name="VSW" sheetId="26" r:id="rId8"/>
     <sheet name="VBP" sheetId="27" r:id="rId9"/>
-    <sheet name="VFP" sheetId="22" r:id="rId10"/>
-    <sheet name="Counter" sheetId="15" r:id="rId11"/>
-    <sheet name="delayCondition" sheetId="18" r:id="rId12"/>
-    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId13"/>
-    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId14"/>
-    <sheet name="Basic Assertion" sheetId="1" r:id="rId15"/>
-    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId16"/>
-    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId17"/>
-    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId18"/>
-    <sheet name="aw_builder" sheetId="2" r:id="rId19"/>
+    <sheet name="VACT" sheetId="28" r:id="rId10"/>
+    <sheet name="VFP" sheetId="22" r:id="rId11"/>
+    <sheet name="Counter" sheetId="15" r:id="rId12"/>
+    <sheet name="delayCondition" sheetId="18" r:id="rId13"/>
+    <sheet name="Assertion Sheet(backup)" sheetId="19" r:id="rId14"/>
+    <sheet name="Assertion System Function Guide" sheetId="3" r:id="rId15"/>
+    <sheet name="Basic Assertion" sheetId="1" r:id="rId16"/>
+    <sheet name="Basic Assertion_hsw" sheetId="7" r:id="rId17"/>
+    <sheet name="Basic Assertion_2" sheetId="4" r:id="rId18"/>
+    <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId19"/>
+    <sheet name="aw_builder" sheetId="2" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -172,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="348">
   <si>
     <t>Base Information</t>
   </si>
@@ -2433,6 +2434,73 @@
     $fell(l_vbp) |-&gt; ((&lt;Expected Min Value&gt; &lt;= hsync_cnt) &amp;&amp; (hsync_cnt &lt;= &lt;Expected Max Value&gt;));
 endproperty
 assert property (p_vbp) $display("[%0t] Assertion PASS", $time);
+else $display ("[%0t] Assertion FAIL", $time);
+endinterface
+// 윗부분까지가 생성되는 assertion_intf.sv 입니다. 아래부터는 assertion_intf_inst.sv 입니다.
+assertion_intf
+u_assertion_intf();
+assign u_assertion_inst.&lt;Base Clock&gt; = top.dut.&lt;Base Clock&gt;;
+assign u_assertion_inst.&lt;Base Reset&gt; = top.dut.&lt;Base Reset&gt;;
+assign u_assertion_inst.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
+assign u_assertion_inst.&lt;Vsync Signal&gt; = top.dut.&lt;Vsync Signal&gt;;
+assign u_assertion_inst.&lt;Data Enable Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;</t>
+  </si>
+  <si>
+    <t>VACT</t>
+  </si>
+  <si>
+    <t>Expected Preset(VACT)</t>
+  </si>
+  <si>
+    <t>`include "uvm_marcros.svh"
+import uvm_pkg::*;
+interface assertion_intf()
+(
+    input &lt;Base Clock&gt;,
+    input &lt;Base Reset&gt;,
+    input &lt;Hsync Signal&gt;,
+    input &lt;Vsync Signal&gt;,
+    input &lt;Data Enable Signal&gt;
+)
+int de_cnt;
+logic l_vbp_vact_vfp;
+always @(posedge &lt;Base Clock&gt; or negedge &lt;Base Reset&gt;) begin
+    if(!&lt;Base Reset&gt;) begin
+        l_vbp_vact_vfp &lt;= 0;
+    end
+    else begin
+        if($fell(&lt;Vsync Signal&gt;)) begin
+            l_vbp_vact_vfp &lt;= 1;
+        end
+        else if($rose(&lt;Vsync Signal&gt;) ) begin
+            l_vbp_vact_vfp &lt;= 0;
+        end
+        else begin
+            l_vbp_vact_vfp &lt;= l_vbp_vact_vfp;
+        end
+    end
+end
+always @(posedge &lt;Base Clock&gt; or negedge &lt;Base Reset&gt;) begin
+    if(!&lt;Base Reset&gt;) begin
+        de_cnt &lt;= 0;
+    end
+    else begin
+        if($rose(&lt;Data Enable Signal&gt;)) begin
+            de_cnt &lt;= de_cnt + 1;
+        end
+        else if($fell&lt;Data Enable Signal&gt;)) begin
+            de_cnt &lt;= 0;
+        end
+        else begin
+            de_cnt &lt;= de_cnt;
+        end
+    end
+end
+property p_vact;
+    @(posedge &lt;Base Clock&gt;) disable iff (!&lt;Base Reset&gt;)
+    $fell(l_vbp_vact_vfp) |-&gt; ((&lt;Expected Min Value&gt; &lt;= de_cnt) &amp;&amp; (de_cnt &lt;= &lt;Expected Max Value&gt;));
+endproperty
+assert property (p_vact) $display("[%0t] Assertion PASS", $time);
 else $display ("[%0t] Assertion FAIL", $time);
 endinterface
 // 윗부분까지가 생성되는 assertion_intf.sv 입니다. 아래부터는 assertion_intf_inst.sv 입니다.
@@ -6612,6 +6680,1220 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3A08B0-C20D-4512-BE9E-44E986E14AEF}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:T84"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="3.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="43" customWidth="1"/>
+    <col min="4" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="21.5" customWidth="1"/>
+    <col min="10" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:20">
+      <c r="C1" s="83"/>
+    </row>
+    <row r="2" spans="3:20">
+      <c r="C2" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="162">
+        <f>Define!C5</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="43"/>
+    </row>
+    <row r="3" spans="3:20">
+      <c r="C3" s="91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="159">
+        <f>Define!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="93"/>
+    </row>
+    <row r="4" spans="3:20">
+      <c r="C4"/>
+      <c r="I4" s="90"/>
+    </row>
+    <row r="5" spans="3:20" ht="19.5" customHeight="1">
+      <c r="C5" s="122" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="124"/>
+      <c r="J5" s="153" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="154"/>
+      <c r="S5" s="154"/>
+      <c r="T5" s="155"/>
+    </row>
+    <row r="6" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C6" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="130" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131"/>
+      <c r="N6" s="131"/>
+      <c r="O6" s="131"/>
+      <c r="P6" s="131"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="131"/>
+      <c r="T6" s="132"/>
+    </row>
+    <row r="7" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C7" s="26"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="27"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="134"/>
+      <c r="N7" s="134"/>
+      <c r="O7" s="134"/>
+      <c r="P7" s="134"/>
+      <c r="Q7" s="134"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="134"/>
+      <c r="T7" s="135"/>
+    </row>
+    <row r="8" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C8" s="26"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="27"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="134"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
+      <c r="N8" s="134"/>
+      <c r="O8" s="134"/>
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="135"/>
+    </row>
+    <row r="9" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C9" s="26"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="27"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="134"/>
+      <c r="N9" s="134"/>
+      <c r="O9" s="134"/>
+      <c r="P9" s="134"/>
+      <c r="Q9" s="134"/>
+      <c r="R9" s="134"/>
+      <c r="S9" s="134"/>
+      <c r="T9" s="135"/>
+    </row>
+    <row r="10" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C10" s="26"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="27"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="134"/>
+      <c r="N10" s="134"/>
+      <c r="O10" s="134"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
+      <c r="R10" s="134"/>
+      <c r="S10" s="134"/>
+      <c r="T10" s="135"/>
+    </row>
+    <row r="11" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C11" s="26"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="27"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="134"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="135"/>
+    </row>
+    <row r="12" spans="3:20" ht="13.5" customHeight="1">
+      <c r="C12" s="26"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="44"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="134"/>
+      <c r="N12" s="134"/>
+      <c r="O12" s="134"/>
+      <c r="P12" s="134"/>
+      <c r="Q12" s="134"/>
+      <c r="R12" s="134"/>
+      <c r="S12" s="134"/>
+      <c r="T12" s="135"/>
+    </row>
+    <row r="13" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G13" s="44"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="134"/>
+      <c r="P13" s="134"/>
+      <c r="Q13" s="134"/>
+      <c r="R13" s="134"/>
+      <c r="S13" s="134"/>
+      <c r="T13" s="135"/>
+    </row>
+    <row r="14" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G14" s="44"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="134"/>
+      <c r="O14" s="134"/>
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="135"/>
+    </row>
+    <row r="15" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G15" s="44"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="134"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="135"/>
+    </row>
+    <row r="16" spans="3:20" ht="13.5" customHeight="1">
+      <c r="G16" s="44"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="134"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="134"/>
+      <c r="P16" s="134"/>
+      <c r="Q16" s="134"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="134"/>
+      <c r="T16" s="135"/>
+    </row>
+    <row r="17" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G17" s="44"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="135"/>
+    </row>
+    <row r="18" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G18" s="44"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="134"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="134"/>
+      <c r="Q18" s="134"/>
+      <c r="R18" s="134"/>
+      <c r="S18" s="134"/>
+      <c r="T18" s="135"/>
+    </row>
+    <row r="19" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G19" s="44"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="134"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="134"/>
+      <c r="T19" s="135"/>
+    </row>
+    <row r="20" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G20" s="44"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="134"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="135"/>
+    </row>
+    <row r="21" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G21" s="44"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="134"/>
+      <c r="N21" s="134"/>
+      <c r="O21" s="134"/>
+      <c r="P21" s="134"/>
+      <c r="Q21" s="134"/>
+      <c r="R21" s="134"/>
+      <c r="S21" s="134"/>
+      <c r="T21" s="135"/>
+    </row>
+    <row r="22" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G22" s="44"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="134"/>
+      <c r="N22" s="134"/>
+      <c r="O22" s="134"/>
+      <c r="P22" s="134"/>
+      <c r="Q22" s="134"/>
+      <c r="R22" s="134"/>
+      <c r="S22" s="134"/>
+      <c r="T22" s="135"/>
+    </row>
+    <row r="23" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G23" s="44"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="134"/>
+      <c r="N23" s="134"/>
+      <c r="O23" s="134"/>
+      <c r="P23" s="134"/>
+      <c r="Q23" s="134"/>
+      <c r="R23" s="134"/>
+      <c r="S23" s="134"/>
+      <c r="T23" s="135"/>
+    </row>
+    <row r="24" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G24" s="44"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="134"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134"/>
+      <c r="Q24" s="134"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="135"/>
+    </row>
+    <row r="25" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G25" s="44"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="134"/>
+      <c r="N25" s="134"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="134"/>
+      <c r="Q25" s="134"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="134"/>
+      <c r="T25" s="135"/>
+    </row>
+    <row r="26" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G26" s="44"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="134"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="134"/>
+      <c r="N26" s="134"/>
+      <c r="O26" s="134"/>
+      <c r="P26" s="134"/>
+      <c r="Q26" s="134"/>
+      <c r="R26" s="134"/>
+      <c r="S26" s="134"/>
+      <c r="T26" s="135"/>
+    </row>
+    <row r="27" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G27" s="44"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="134"/>
+      <c r="M27" s="134"/>
+      <c r="N27" s="134"/>
+      <c r="O27" s="134"/>
+      <c r="P27" s="134"/>
+      <c r="Q27" s="134"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="134"/>
+      <c r="T27" s="135"/>
+    </row>
+    <row r="28" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G28" s="44"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="134"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="134"/>
+      <c r="N28" s="134"/>
+      <c r="O28" s="134"/>
+      <c r="P28" s="134"/>
+      <c r="Q28" s="134"/>
+      <c r="R28" s="134"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="135"/>
+    </row>
+    <row r="29" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G29" s="44"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="134"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="134"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="134"/>
+      <c r="T29" s="135"/>
+    </row>
+    <row r="30" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G30" s="44"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="134"/>
+      <c r="N30" s="134"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="134"/>
+      <c r="Q30" s="134"/>
+      <c r="R30" s="134"/>
+      <c r="S30" s="134"/>
+      <c r="T30" s="135"/>
+    </row>
+    <row r="31" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G31" s="44"/>
+      <c r="J31" s="133"/>
+      <c r="K31" s="134"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="134"/>
+      <c r="N31" s="134"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="134"/>
+      <c r="Q31" s="134"/>
+      <c r="R31" s="134"/>
+      <c r="S31" s="134"/>
+      <c r="T31" s="135"/>
+    </row>
+    <row r="32" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G32" s="44"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="134"/>
+      <c r="L32" s="134"/>
+      <c r="M32" s="134"/>
+      <c r="N32" s="134"/>
+      <c r="O32" s="134"/>
+      <c r="P32" s="134"/>
+      <c r="Q32" s="134"/>
+      <c r="R32" s="134"/>
+      <c r="S32" s="134"/>
+      <c r="T32" s="135"/>
+    </row>
+    <row r="33" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G33" s="44"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="134"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="134"/>
+      <c r="S33" s="134"/>
+      <c r="T33" s="135"/>
+    </row>
+    <row r="34" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G34" s="44"/>
+      <c r="J34" s="133"/>
+      <c r="K34" s="134"/>
+      <c r="L34" s="134"/>
+      <c r="M34" s="134"/>
+      <c r="N34" s="134"/>
+      <c r="O34" s="134"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="134"/>
+      <c r="R34" s="134"/>
+      <c r="S34" s="134"/>
+      <c r="T34" s="135"/>
+    </row>
+    <row r="35" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G35" s="44"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="134"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="134"/>
+      <c r="Q35" s="134"/>
+      <c r="R35" s="134"/>
+      <c r="S35" s="134"/>
+      <c r="T35" s="135"/>
+    </row>
+    <row r="36" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G36" s="44"/>
+      <c r="J36" s="133"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="134"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="134"/>
+      <c r="S36" s="134"/>
+      <c r="T36" s="135"/>
+    </row>
+    <row r="37" spans="2:20" ht="13.5" customHeight="1">
+      <c r="B37" s="7"/>
+      <c r="G37" s="44"/>
+      <c r="J37" s="133"/>
+      <c r="K37" s="134"/>
+      <c r="L37" s="134"/>
+      <c r="M37" s="134"/>
+      <c r="N37" s="134"/>
+      <c r="O37" s="134"/>
+      <c r="P37" s="134"/>
+      <c r="Q37" s="134"/>
+      <c r="R37" s="134"/>
+      <c r="S37" s="134"/>
+      <c r="T37" s="135"/>
+    </row>
+    <row r="38" spans="2:20" ht="13.5" customHeight="1">
+      <c r="B38" s="7"/>
+      <c r="G38" s="44"/>
+      <c r="J38" s="133"/>
+      <c r="K38" s="134"/>
+      <c r="L38" s="134"/>
+      <c r="M38" s="134"/>
+      <c r="N38" s="134"/>
+      <c r="O38" s="134"/>
+      <c r="P38" s="134"/>
+      <c r="Q38" s="134"/>
+      <c r="R38" s="134"/>
+      <c r="S38" s="134"/>
+      <c r="T38" s="135"/>
+    </row>
+    <row r="39" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G39" s="44"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="134"/>
+      <c r="L39" s="134"/>
+      <c r="M39" s="134"/>
+      <c r="N39" s="134"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="134"/>
+      <c r="S39" s="134"/>
+      <c r="T39" s="135"/>
+    </row>
+    <row r="40" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G40" s="44"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134"/>
+      <c r="L40" s="134"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="134"/>
+      <c r="O40" s="134"/>
+      <c r="P40" s="134"/>
+      <c r="Q40" s="134"/>
+      <c r="R40" s="134"/>
+      <c r="S40" s="134"/>
+      <c r="T40" s="135"/>
+    </row>
+    <row r="41" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G41" s="44"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="134"/>
+      <c r="L41" s="134"/>
+      <c r="M41" s="134"/>
+      <c r="N41" s="134"/>
+      <c r="O41" s="134"/>
+      <c r="P41" s="134"/>
+      <c r="Q41" s="134"/>
+      <c r="R41" s="134"/>
+      <c r="S41" s="134"/>
+      <c r="T41" s="135"/>
+    </row>
+    <row r="42" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G42" s="44"/>
+      <c r="J42" s="133"/>
+      <c r="K42" s="134"/>
+      <c r="L42" s="134"/>
+      <c r="M42" s="134"/>
+      <c r="N42" s="134"/>
+      <c r="O42" s="134"/>
+      <c r="P42" s="134"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="134"/>
+      <c r="S42" s="134"/>
+      <c r="T42" s="135"/>
+    </row>
+    <row r="43" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G43" s="44"/>
+      <c r="J43" s="133"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134"/>
+      <c r="M43" s="134"/>
+      <c r="N43" s="134"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
+      <c r="R43" s="134"/>
+      <c r="S43" s="134"/>
+      <c r="T43" s="135"/>
+    </row>
+    <row r="44" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G44" s="44"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="134"/>
+      <c r="M44" s="134"/>
+      <c r="N44" s="134"/>
+      <c r="O44" s="134"/>
+      <c r="P44" s="134"/>
+      <c r="Q44" s="134"/>
+      <c r="R44" s="134"/>
+      <c r="S44" s="134"/>
+      <c r="T44" s="135"/>
+    </row>
+    <row r="45" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G45" s="44"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="134"/>
+      <c r="L45" s="134"/>
+      <c r="M45" s="134"/>
+      <c r="N45" s="134"/>
+      <c r="O45" s="134"/>
+      <c r="P45" s="134"/>
+      <c r="Q45" s="134"/>
+      <c r="R45" s="134"/>
+      <c r="S45" s="134"/>
+      <c r="T45" s="135"/>
+    </row>
+    <row r="46" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G46" s="44"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="134"/>
+      <c r="L46" s="134"/>
+      <c r="M46" s="134"/>
+      <c r="N46" s="134"/>
+      <c r="O46" s="134"/>
+      <c r="P46" s="134"/>
+      <c r="Q46" s="134"/>
+      <c r="R46" s="134"/>
+      <c r="S46" s="134"/>
+      <c r="T46" s="135"/>
+    </row>
+    <row r="47" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G47" s="44"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="134"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="134"/>
+      <c r="O47" s="134"/>
+      <c r="P47" s="134"/>
+      <c r="Q47" s="134"/>
+      <c r="R47" s="134"/>
+      <c r="S47" s="134"/>
+      <c r="T47" s="135"/>
+    </row>
+    <row r="48" spans="2:20" ht="13.5" customHeight="1">
+      <c r="G48" s="44"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="134"/>
+      <c r="M48" s="134"/>
+      <c r="N48" s="134"/>
+      <c r="O48" s="134"/>
+      <c r="P48" s="134"/>
+      <c r="Q48" s="134"/>
+      <c r="R48" s="134"/>
+      <c r="S48" s="134"/>
+      <c r="T48" s="135"/>
+    </row>
+    <row r="49" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G49" s="44"/>
+      <c r="J49" s="133"/>
+      <c r="K49" s="134"/>
+      <c r="L49" s="134"/>
+      <c r="M49" s="134"/>
+      <c r="N49" s="134"/>
+      <c r="O49" s="134"/>
+      <c r="P49" s="134"/>
+      <c r="Q49" s="134"/>
+      <c r="R49" s="134"/>
+      <c r="S49" s="134"/>
+      <c r="T49" s="135"/>
+    </row>
+    <row r="50" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G50" s="44"/>
+      <c r="J50" s="133"/>
+      <c r="K50" s="134"/>
+      <c r="L50" s="134"/>
+      <c r="M50" s="134"/>
+      <c r="N50" s="134"/>
+      <c r="O50" s="134"/>
+      <c r="P50" s="134"/>
+      <c r="Q50" s="134"/>
+      <c r="R50" s="134"/>
+      <c r="S50" s="134"/>
+      <c r="T50" s="135"/>
+    </row>
+    <row r="51" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G51" s="44"/>
+      <c r="J51" s="133"/>
+      <c r="K51" s="134"/>
+      <c r="L51" s="134"/>
+      <c r="M51" s="134"/>
+      <c r="N51" s="134"/>
+      <c r="O51" s="134"/>
+      <c r="P51" s="134"/>
+      <c r="Q51" s="134"/>
+      <c r="R51" s="134"/>
+      <c r="S51" s="134"/>
+      <c r="T51" s="135"/>
+    </row>
+    <row r="52" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G52" s="44"/>
+      <c r="J52" s="133"/>
+      <c r="K52" s="134"/>
+      <c r="L52" s="134"/>
+      <c r="M52" s="134"/>
+      <c r="N52" s="134"/>
+      <c r="O52" s="134"/>
+      <c r="P52" s="134"/>
+      <c r="Q52" s="134"/>
+      <c r="R52" s="134"/>
+      <c r="S52" s="134"/>
+      <c r="T52" s="135"/>
+    </row>
+    <row r="53" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G53" s="44"/>
+      <c r="J53" s="133"/>
+      <c r="K53" s="134"/>
+      <c r="L53" s="134"/>
+      <c r="M53" s="134"/>
+      <c r="N53" s="134"/>
+      <c r="O53" s="134"/>
+      <c r="P53" s="134"/>
+      <c r="Q53" s="134"/>
+      <c r="R53" s="134"/>
+      <c r="S53" s="134"/>
+      <c r="T53" s="135"/>
+    </row>
+    <row r="54" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G54" s="44"/>
+      <c r="J54" s="133"/>
+      <c r="K54" s="134"/>
+      <c r="L54" s="134"/>
+      <c r="M54" s="134"/>
+      <c r="N54" s="134"/>
+      <c r="O54" s="134"/>
+      <c r="P54" s="134"/>
+      <c r="Q54" s="134"/>
+      <c r="R54" s="134"/>
+      <c r="S54" s="134"/>
+      <c r="T54" s="135"/>
+    </row>
+    <row r="55" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G55" s="44"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="134"/>
+      <c r="L55" s="134"/>
+      <c r="M55" s="134"/>
+      <c r="N55" s="134"/>
+      <c r="O55" s="134"/>
+      <c r="P55" s="134"/>
+      <c r="Q55" s="134"/>
+      <c r="R55" s="134"/>
+      <c r="S55" s="134"/>
+      <c r="T55" s="135"/>
+    </row>
+    <row r="56" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G56" s="44"/>
+      <c r="J56" s="133"/>
+      <c r="K56" s="134"/>
+      <c r="L56" s="134"/>
+      <c r="M56" s="134"/>
+      <c r="N56" s="134"/>
+      <c r="O56" s="134"/>
+      <c r="P56" s="134"/>
+      <c r="Q56" s="134"/>
+      <c r="R56" s="134"/>
+      <c r="S56" s="134"/>
+      <c r="T56" s="135"/>
+    </row>
+    <row r="57" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G57" s="44"/>
+      <c r="J57" s="133"/>
+      <c r="K57" s="134"/>
+      <c r="L57" s="134"/>
+      <c r="M57" s="134"/>
+      <c r="N57" s="134"/>
+      <c r="O57" s="134"/>
+      <c r="P57" s="134"/>
+      <c r="Q57" s="134"/>
+      <c r="R57" s="134"/>
+      <c r="S57" s="134"/>
+      <c r="T57" s="135"/>
+    </row>
+    <row r="58" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G58" s="44"/>
+      <c r="J58" s="133"/>
+      <c r="K58" s="134"/>
+      <c r="L58" s="134"/>
+      <c r="M58" s="134"/>
+      <c r="N58" s="134"/>
+      <c r="O58" s="134"/>
+      <c r="P58" s="134"/>
+      <c r="Q58" s="134"/>
+      <c r="R58" s="134"/>
+      <c r="S58" s="134"/>
+      <c r="T58" s="135"/>
+    </row>
+    <row r="59" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G59" s="44"/>
+      <c r="J59" s="133"/>
+      <c r="K59" s="134"/>
+      <c r="L59" s="134"/>
+      <c r="M59" s="134"/>
+      <c r="N59" s="134"/>
+      <c r="O59" s="134"/>
+      <c r="P59" s="134"/>
+      <c r="Q59" s="134"/>
+      <c r="R59" s="134"/>
+      <c r="S59" s="134"/>
+      <c r="T59" s="135"/>
+    </row>
+    <row r="60" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G60" s="44"/>
+      <c r="J60" s="133"/>
+      <c r="K60" s="134"/>
+      <c r="L60" s="134"/>
+      <c r="M60" s="134"/>
+      <c r="N60" s="134"/>
+      <c r="O60" s="134"/>
+      <c r="P60" s="134"/>
+      <c r="Q60" s="134"/>
+      <c r="R60" s="134"/>
+      <c r="S60" s="134"/>
+      <c r="T60" s="135"/>
+    </row>
+    <row r="61" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G61" s="44"/>
+      <c r="J61" s="133"/>
+      <c r="K61" s="134"/>
+      <c r="L61" s="134"/>
+      <c r="M61" s="134"/>
+      <c r="N61" s="134"/>
+      <c r="O61" s="134"/>
+      <c r="P61" s="134"/>
+      <c r="Q61" s="134"/>
+      <c r="R61" s="134"/>
+      <c r="S61" s="134"/>
+      <c r="T61" s="135"/>
+    </row>
+    <row r="62" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G62" s="44"/>
+      <c r="J62" s="133"/>
+      <c r="K62" s="134"/>
+      <c r="L62" s="134"/>
+      <c r="M62" s="134"/>
+      <c r="N62" s="134"/>
+      <c r="O62" s="134"/>
+      <c r="P62" s="134"/>
+      <c r="Q62" s="134"/>
+      <c r="R62" s="134"/>
+      <c r="S62" s="134"/>
+      <c r="T62" s="135"/>
+    </row>
+    <row r="63" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G63" s="44"/>
+      <c r="J63" s="133"/>
+      <c r="K63" s="134"/>
+      <c r="L63" s="134"/>
+      <c r="M63" s="134"/>
+      <c r="N63" s="134"/>
+      <c r="O63" s="134"/>
+      <c r="P63" s="134"/>
+      <c r="Q63" s="134"/>
+      <c r="R63" s="134"/>
+      <c r="S63" s="134"/>
+      <c r="T63" s="135"/>
+    </row>
+    <row r="64" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G64" s="44"/>
+      <c r="J64" s="133"/>
+      <c r="K64" s="134"/>
+      <c r="L64" s="134"/>
+      <c r="M64" s="134"/>
+      <c r="N64" s="134"/>
+      <c r="O64" s="134"/>
+      <c r="P64" s="134"/>
+      <c r="Q64" s="134"/>
+      <c r="R64" s="134"/>
+      <c r="S64" s="134"/>
+      <c r="T64" s="135"/>
+    </row>
+    <row r="65" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G65" s="44"/>
+      <c r="J65" s="133"/>
+      <c r="K65" s="134"/>
+      <c r="L65" s="134"/>
+      <c r="M65" s="134"/>
+      <c r="N65" s="134"/>
+      <c r="O65" s="134"/>
+      <c r="P65" s="134"/>
+      <c r="Q65" s="134"/>
+      <c r="R65" s="134"/>
+      <c r="S65" s="134"/>
+      <c r="T65" s="135"/>
+    </row>
+    <row r="66" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G66" s="44"/>
+      <c r="J66" s="133"/>
+      <c r="K66" s="134"/>
+      <c r="L66" s="134"/>
+      <c r="M66" s="134"/>
+      <c r="N66" s="134"/>
+      <c r="O66" s="134"/>
+      <c r="P66" s="134"/>
+      <c r="Q66" s="134"/>
+      <c r="R66" s="134"/>
+      <c r="S66" s="134"/>
+      <c r="T66" s="135"/>
+    </row>
+    <row r="67" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G67" s="44"/>
+      <c r="J67" s="133"/>
+      <c r="K67" s="134"/>
+      <c r="L67" s="134"/>
+      <c r="M67" s="134"/>
+      <c r="N67" s="134"/>
+      <c r="O67" s="134"/>
+      <c r="P67" s="134"/>
+      <c r="Q67" s="134"/>
+      <c r="R67" s="134"/>
+      <c r="S67" s="134"/>
+      <c r="T67" s="135"/>
+    </row>
+    <row r="68" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G68" s="44"/>
+      <c r="J68" s="133"/>
+      <c r="K68" s="134"/>
+      <c r="L68" s="134"/>
+      <c r="M68" s="134"/>
+      <c r="N68" s="134"/>
+      <c r="O68" s="134"/>
+      <c r="P68" s="134"/>
+      <c r="Q68" s="134"/>
+      <c r="R68" s="134"/>
+      <c r="S68" s="134"/>
+      <c r="T68" s="135"/>
+    </row>
+    <row r="69" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G69" s="44"/>
+      <c r="J69" s="133"/>
+      <c r="K69" s="134"/>
+      <c r="L69" s="134"/>
+      <c r="M69" s="134"/>
+      <c r="N69" s="134"/>
+      <c r="O69" s="134"/>
+      <c r="P69" s="134"/>
+      <c r="Q69" s="134"/>
+      <c r="R69" s="134"/>
+      <c r="S69" s="134"/>
+      <c r="T69" s="135"/>
+    </row>
+    <row r="70" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G70" s="44"/>
+      <c r="J70" s="133"/>
+      <c r="K70" s="134"/>
+      <c r="L70" s="134"/>
+      <c r="M70" s="134"/>
+      <c r="N70" s="134"/>
+      <c r="O70" s="134"/>
+      <c r="P70" s="134"/>
+      <c r="Q70" s="134"/>
+      <c r="R70" s="134"/>
+      <c r="S70" s="134"/>
+      <c r="T70" s="135"/>
+    </row>
+    <row r="71" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G71" s="44"/>
+      <c r="J71" s="133"/>
+      <c r="K71" s="134"/>
+      <c r="L71" s="134"/>
+      <c r="M71" s="134"/>
+      <c r="N71" s="134"/>
+      <c r="O71" s="134"/>
+      <c r="P71" s="134"/>
+      <c r="Q71" s="134"/>
+      <c r="R71" s="134"/>
+      <c r="S71" s="134"/>
+      <c r="T71" s="135"/>
+    </row>
+    <row r="72" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G72" s="44"/>
+      <c r="J72" s="133"/>
+      <c r="K72" s="134"/>
+      <c r="L72" s="134"/>
+      <c r="M72" s="134"/>
+      <c r="N72" s="134"/>
+      <c r="O72" s="134"/>
+      <c r="P72" s="134"/>
+      <c r="Q72" s="134"/>
+      <c r="R72" s="134"/>
+      <c r="S72" s="134"/>
+      <c r="T72" s="135"/>
+    </row>
+    <row r="73" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G73" s="44"/>
+      <c r="J73" s="133"/>
+      <c r="K73" s="134"/>
+      <c r="L73" s="134"/>
+      <c r="M73" s="134"/>
+      <c r="N73" s="134"/>
+      <c r="O73" s="134"/>
+      <c r="P73" s="134"/>
+      <c r="Q73" s="134"/>
+      <c r="R73" s="134"/>
+      <c r="S73" s="134"/>
+      <c r="T73" s="135"/>
+    </row>
+    <row r="74" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G74" s="44"/>
+      <c r="J74" s="133"/>
+      <c r="K74" s="134"/>
+      <c r="L74" s="134"/>
+      <c r="M74" s="134"/>
+      <c r="N74" s="134"/>
+      <c r="O74" s="134"/>
+      <c r="P74" s="134"/>
+      <c r="Q74" s="134"/>
+      <c r="R74" s="134"/>
+      <c r="S74" s="134"/>
+      <c r="T74" s="135"/>
+    </row>
+    <row r="75" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G75" s="44"/>
+      <c r="J75" s="133"/>
+      <c r="K75" s="134"/>
+      <c r="L75" s="134"/>
+      <c r="M75" s="134"/>
+      <c r="N75" s="134"/>
+      <c r="O75" s="134"/>
+      <c r="P75" s="134"/>
+      <c r="Q75" s="134"/>
+      <c r="R75" s="134"/>
+      <c r="S75" s="134"/>
+      <c r="T75" s="135"/>
+    </row>
+    <row r="76" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G76" s="44"/>
+      <c r="J76" s="133"/>
+      <c r="K76" s="134"/>
+      <c r="L76" s="134"/>
+      <c r="M76" s="134"/>
+      <c r="N76" s="134"/>
+      <c r="O76" s="134"/>
+      <c r="P76" s="134"/>
+      <c r="Q76" s="134"/>
+      <c r="R76" s="134"/>
+      <c r="S76" s="134"/>
+      <c r="T76" s="135"/>
+    </row>
+    <row r="77" spans="7:20" ht="13.5" customHeight="1">
+      <c r="G77" s="44"/>
+      <c r="J77" s="133"/>
+      <c r="K77" s="134"/>
+      <c r="L77" s="134"/>
+      <c r="M77" s="134"/>
+      <c r="N77" s="134"/>
+      <c r="O77" s="134"/>
+      <c r="P77" s="134"/>
+      <c r="Q77" s="134"/>
+      <c r="R77" s="134"/>
+      <c r="S77" s="134"/>
+      <c r="T77" s="135"/>
+    </row>
+    <row r="78" spans="7:20">
+      <c r="G78" s="44"/>
+      <c r="J78" s="133"/>
+      <c r="K78" s="134"/>
+      <c r="L78" s="134"/>
+      <c r="M78" s="134"/>
+      <c r="N78" s="134"/>
+      <c r="O78" s="134"/>
+      <c r="P78" s="134"/>
+      <c r="Q78" s="134"/>
+      <c r="R78" s="134"/>
+      <c r="S78" s="134"/>
+      <c r="T78" s="135"/>
+    </row>
+    <row r="79" spans="7:20">
+      <c r="G79" s="44"/>
+      <c r="J79" s="133"/>
+      <c r="K79" s="134"/>
+      <c r="L79" s="134"/>
+      <c r="M79" s="134"/>
+      <c r="N79" s="134"/>
+      <c r="O79" s="134"/>
+      <c r="P79" s="134"/>
+      <c r="Q79" s="134"/>
+      <c r="R79" s="134"/>
+      <c r="S79" s="134"/>
+      <c r="T79" s="135"/>
+    </row>
+    <row r="80" spans="7:20">
+      <c r="G80" s="44"/>
+      <c r="J80" s="133"/>
+      <c r="K80" s="134"/>
+      <c r="L80" s="134"/>
+      <c r="M80" s="134"/>
+      <c r="N80" s="134"/>
+      <c r="O80" s="134"/>
+      <c r="P80" s="134"/>
+      <c r="Q80" s="134"/>
+      <c r="R80" s="134"/>
+      <c r="S80" s="134"/>
+      <c r="T80" s="135"/>
+    </row>
+    <row r="81" spans="7:20">
+      <c r="G81" s="44"/>
+      <c r="J81" s="133"/>
+      <c r="K81" s="134"/>
+      <c r="L81" s="134"/>
+      <c r="M81" s="134"/>
+      <c r="N81" s="134"/>
+      <c r="O81" s="134"/>
+      <c r="P81" s="134"/>
+      <c r="Q81" s="134"/>
+      <c r="R81" s="134"/>
+      <c r="S81" s="134"/>
+      <c r="T81" s="135"/>
+    </row>
+    <row r="82" spans="7:20">
+      <c r="G82" s="44"/>
+      <c r="J82" s="136"/>
+      <c r="K82" s="137"/>
+      <c r="L82" s="137"/>
+      <c r="M82" s="137"/>
+      <c r="N82" s="137"/>
+      <c r="O82" s="137"/>
+      <c r="P82" s="137"/>
+      <c r="Q82" s="137"/>
+      <c r="R82" s="137"/>
+      <c r="S82" s="137"/>
+      <c r="T82" s="138"/>
+    </row>
+    <row r="83" spans="7:20">
+      <c r="G83" s="44"/>
+    </row>
+    <row r="84" spans="7:20">
+      <c r="G84" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J5:T5"/>
+    <mergeCell ref="J6:T82"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F12 I1 G6:G84 I85:I1048576 C7:E12" xr:uid="{D5EC765B-43EF-4E2D-B40B-4501E648FF14}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385F985E-2870-4308-82B2-23D8BBD3D2EC}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -6663,14 +7945,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -6700,7 +7982,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -7825,7 +9107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0A1BC2-AD1F-4F40-B462-EAC4DD963BF3}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -7875,7 +9157,7 @@
       <c r="F5" s="126"/>
       <c r="G5" s="70"/>
       <c r="I5" s="166" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J5" s="166"/>
       <c r="K5" s="166"/>
@@ -7898,7 +9180,7 @@
       <c r="F6" s="129"/>
       <c r="G6" s="72"/>
       <c r="I6" s="165" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J6" s="165"/>
       <c r="K6" s="165"/>
@@ -8099,7 +9381,7 @@
     </row>
     <row r="23" spans="9:15" ht="21">
       <c r="I23" s="166" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J23" s="166"/>
       <c r="K23" s="166"/>
@@ -8110,7 +9392,7 @@
     </row>
     <row r="24" spans="9:15" ht="13.5" customHeight="1">
       <c r="I24" s="165" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J24" s="165"/>
       <c r="K24" s="165"/>
@@ -8273,7 +9555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD90D1D-3345-4EDC-9CC4-2BE02D44AE19}">
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
@@ -8325,14 +9607,14 @@
     </row>
     <row r="5" spans="3:32" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -8345,7 +9627,7 @@
       <c r="S5" s="154"/>
       <c r="T5" s="155"/>
       <c r="V5" s="153" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="W5" s="154"/>
       <c r="X5" s="154"/>
@@ -8366,16 +9648,16 @@
         <v>31</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -8388,7 +9670,7 @@
       <c r="S6" s="131"/>
       <c r="T6" s="132"/>
       <c r="V6" s="130" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="W6" s="131"/>
       <c r="X6" s="131"/>
@@ -9697,7 +10979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632C17C5-59B7-41E9-805B-4B36986E2251}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9778,7 +11060,7 @@
       <c r="Q3" s="123"/>
       <c r="R3" s="124"/>
       <c r="T3" s="122" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U3" s="123"/>
       <c r="V3" s="124"/>
@@ -9788,10 +11070,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>39</v>
@@ -9807,10 +11089,10 @@
         <v>27</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N4" s="41" t="s">
         <v>35</v>
@@ -9819,27 +11101,27 @@
         <v>21</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>31</v>
       </c>
       <c r="U4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="V4" s="42" t="s">
         <v>118</v>
-      </c>
-      <c r="V4" s="42" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="15">
       <c r="B5" s="26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -9853,28 +11135,28 @@
       <c r="K5" s="26"/>
       <c r="L5" s="27"/>
       <c r="N5" s="26" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O5" s="37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P5" s="37">
         <v>3</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="T5" s="26" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="U5" s="37">
         <v>2</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="15">
@@ -9884,7 +11166,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="27"/>
@@ -9906,17 +11188,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="27"/>
       <c r="K7" s="26"/>
       <c r="L7" s="27"/>
       <c r="N7" s="26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="P7" s="37">
         <v>5</v>
@@ -10003,7 +11285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52C9A5D-390C-4EB4-8E0E-6218D55EFC0C}">
   <dimension ref="C4:I26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -10019,348 +11301,348 @@
     <row r="4" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="5" spans="3:9" ht="16.5" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>156</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="3:9" ht="17.25">
       <c r="C14" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -10368,7 +11650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713538E3-68C7-46EF-9BF7-7D86C6D2932B}">
   <dimension ref="B2:AC45"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -10396,7 +11678,7 @@
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="125" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
@@ -10436,46 +11718,46 @@
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O4" s="174" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P4" s="175"/>
       <c r="Q4" s="175"/>
@@ -10483,28 +11765,28 @@
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -10518,7 +11800,7 @@
     </row>
     <row r="6" spans="2:22" ht="15">
       <c r="B6" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -10531,10 +11813,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -10549,7 +11831,7 @@
     </row>
     <row r="7" spans="2:22" ht="15">
       <c r="B7" s="25" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -10562,10 +11844,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -10580,7 +11862,7 @@
     </row>
     <row r="8" spans="2:22" ht="15">
       <c r="B8" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -10593,10 +11875,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -10611,28 +11893,28 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -10646,7 +11928,7 @@
     </row>
     <row r="10" spans="2:22" ht="15">
       <c r="B10" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -10659,10 +11941,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -10677,7 +11959,7 @@
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -10698,7 +11980,7 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -10719,7 +12001,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -10740,7 +12022,7 @@
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -10759,13 +12041,13 @@
       <c r="Q14" s="178"/>
       <c r="R14" s="179"/>
       <c r="U14" s="192" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="V14" s="192"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -10788,7 +12070,7 @@
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -10807,15 +12089,15 @@
       <c r="Q16" s="178"/>
       <c r="R16" s="179"/>
       <c r="U16" s="192" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V16" s="193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -10838,7 +12120,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -10858,12 +12140,12 @@
       <c r="R18" s="179"/>
       <c r="U18" s="192"/>
       <c r="V18" s="193" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -10886,7 +12168,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -10906,12 +12188,12 @@
       <c r="R20" s="179"/>
       <c r="U20" s="192"/>
       <c r="V20" s="193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -10934,7 +12216,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -10954,12 +12236,12 @@
       <c r="R22" s="179"/>
       <c r="U22" s="192"/>
       <c r="V22" s="193" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -10982,7 +12264,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -11002,12 +12284,12 @@
       <c r="R24" s="179"/>
       <c r="U24" s="192"/>
       <c r="V24" s="193" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -11030,7 +12312,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -11050,12 +12332,12 @@
       <c r="R26" s="179"/>
       <c r="U26" s="192"/>
       <c r="V26" s="193" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -11078,7 +12360,7 @@
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="125" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C30" s="126"/>
       <c r="D30" s="126"/>
@@ -11116,46 +12398,46 @@
       <c r="Q31" s="172"/>
       <c r="R31" s="173"/>
       <c r="U31" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="15">
       <c r="B32" s="38" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H32" s="36" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L32" s="183" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M32" s="184"/>
       <c r="N32" s="184"/>
@@ -11168,36 +12450,36 @@
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="2:29" ht="15">
       <c r="B33" s="26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -11213,7 +12495,7 @@
       <c r="Q33" s="187"/>
       <c r="R33" s="188"/>
       <c r="U33" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -11236,17 +12518,17 @@
       <c r="Q34" s="187"/>
       <c r="R34" s="188"/>
       <c r="U34" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Y34" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Z34" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="2:29" ht="15">
@@ -11269,14 +12551,14 @@
       <c r="R35" s="188"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Y35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="2:29" ht="15">
@@ -11320,11 +12602,11 @@
       <c r="Q37" s="187"/>
       <c r="R37" s="188"/>
       <c r="U37" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="2:29" ht="15">
@@ -11346,11 +12628,11 @@
       <c r="Q38" s="187"/>
       <c r="R38" s="188"/>
       <c r="U38" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="2:29" ht="15">
@@ -11372,26 +12654,26 @@
       <c r="Q39" s="187"/>
       <c r="R39" s="188"/>
       <c r="U39" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Y39" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AA39" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AB39" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AC39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -11562,7 +12844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D35609-775E-4A26-9091-D70AA658E418}">
   <dimension ref="A1:AH37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -11602,7 +12884,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="150" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B1" s="151"/>
       <c r="C1" s="151"/>
@@ -11617,7 +12899,7 @@
       <c r="L1" s="151"/>
       <c r="M1" s="152"/>
       <c r="O1" s="150" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P1" s="151"/>
       <c r="Q1" s="151"/>
@@ -11629,7 +12911,7 @@
       <c r="W1" s="151"/>
       <c r="X1" s="152"/>
       <c r="Z1" s="200" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AA1" s="201"/>
       <c r="AB1" s="201"/>
@@ -11676,7 +12958,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="206" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B3" s="207"/>
       <c r="C3" s="207"/>
@@ -11685,7 +12967,7 @@
       <c r="F3" s="207"/>
       <c r="G3" s="207"/>
       <c r="H3" s="206" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I3" s="207"/>
       <c r="J3" s="207"/>
@@ -11703,14 +12985,14 @@
       <c r="W3" s="198"/>
       <c r="X3" s="199"/>
       <c r="Z3" s="209" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AA3" s="210"/>
       <c r="AB3" s="210"/>
       <c r="AC3" s="210"/>
       <c r="AD3" s="211"/>
       <c r="AE3" s="209" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AF3" s="212"/>
       <c r="AG3" s="212"/>
@@ -11718,131 +13000,131 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="W4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z4" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA4" s="23" t="s">
         <v>239</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="U4" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="V4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="W4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="Z4" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>236</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AF4" s="23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG4" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AH4" s="51" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -11857,54 +13139,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AA5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AB5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AC5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AF5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -11923,39 +13205,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG6" t="s">
         <v>288</v>
       </c>
-      <c r="AF6" t="s">
-        <v>292</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>285</v>
-      </c>
       <c r="AH6" s="44" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -11974,36 +13256,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AF7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AH7" s="44" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -12348,7 +13630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A12CEB-23C8-48B1-A30D-D9BBB9DB2391}">
   <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12388,7 +13670,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -12403,7 +13685,7 @@
       <c r="L1" s="126"/>
       <c r="M1" s="127"/>
       <c r="O1" s="125" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P1" s="126"/>
       <c r="Q1" s="126"/>
@@ -12415,7 +13697,7 @@
       <c r="W1" s="126"/>
       <c r="X1" s="127"/>
       <c r="Z1" s="215" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AA1" s="216"/>
       <c r="AB1" s="216"/>
@@ -12462,7 +13744,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="122" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
@@ -12471,7 +13753,7 @@
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
       <c r="H3" s="122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I3" s="123"/>
       <c r="J3" s="123"/>
@@ -12489,14 +13771,14 @@
       <c r="W3" s="224"/>
       <c r="X3" s="225"/>
       <c r="Z3" s="214" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AA3" s="210"/>
       <c r="AB3" s="210"/>
       <c r="AC3" s="210"/>
       <c r="AD3" s="211"/>
       <c r="AE3" s="214" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AF3" s="221"/>
       <c r="AG3" s="221"/>
@@ -12504,161 +13786,161 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="V4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="W4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="X4" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z4" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA4" s="23" t="s">
         <v>239</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="U4" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="V4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="W4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="X4" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="Z4" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>236</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AF4" s="23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG4" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AH4" s="51" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -12667,66 +13949,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AA5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AB5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AC5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AF5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -12745,13 +14027,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -12763,16 +14045,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -12791,7 +14073,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -12803,16 +14085,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -12915,7 +14197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8D5FDC-1119-4995-AFF6-CB9868EEC023}">
   <dimension ref="A1:AE36"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -12952,7 +14234,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -12964,7 +14246,7 @@
       <c r="I1" s="126"/>
       <c r="J1" s="127"/>
       <c r="L1" s="125" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M1" s="126"/>
       <c r="N1" s="126"/>
@@ -12976,7 +14258,7 @@
       <c r="T1" s="126"/>
       <c r="U1" s="127"/>
       <c r="W1" s="215" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="X1" s="216"/>
       <c r="Y1" s="216"/>
@@ -13020,13 +14302,13 @@
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="122" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
       <c r="E3" s="122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
@@ -13044,14 +14326,14 @@
       <c r="T3" s="224"/>
       <c r="U3" s="225"/>
       <c r="W3" s="214" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="X3" s="210"/>
       <c r="Y3" s="210"/>
       <c r="Z3" s="210"/>
       <c r="AA3" s="211"/>
       <c r="AB3" s="214" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AC3" s="221"/>
       <c r="AD3" s="221"/>
@@ -13059,143 +14341,143 @@
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L4" s="41" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P4" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="S4" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="U4" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="W4" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="X4" s="23" t="s">
         <v>239</v>
-      </c>
-      <c r="Q4" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="R4" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="S4" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="T4" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="U4" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="W4" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="X4" s="23" t="s">
-        <v>236</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -13204,57 +14486,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="X5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Y5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Z5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AC5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AD5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>247</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -13279,16 +14561,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -13313,16 +14595,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -13415,498 +14697,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD588F34-D77B-42F6-9174-CC0FF762963C}">
-  <dimension ref="B2:H37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="2.75" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="4" width="26.25" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="6" width="72.5" customWidth="1"/>
-    <col min="7" max="7" width="43.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" ht="21">
-      <c r="B2" s="226" t="s">
-        <v>305</v>
-      </c>
-      <c r="C2" s="226"/>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-    </row>
-    <row r="3" spans="2:8" ht="17.25" customHeight="1">
-      <c r="B3" s="46"/>
-      <c r="C3" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="D3" s="227" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="45"/>
-    </row>
-    <row r="4" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="52" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" s="227" t="s">
-        <v>309</v>
-      </c>
-      <c r="F4" s="227"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="45"/>
-    </row>
-    <row r="5" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B5" s="46"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="52" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="227" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" s="227"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="45"/>
-    </row>
-    <row r="6" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="45"/>
-    </row>
-    <row r="7" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="45"/>
-    </row>
-    <row r="8" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="45"/>
-    </row>
-    <row r="9" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="45"/>
-    </row>
-    <row r="10" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B10" s="46"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="45"/>
-    </row>
-    <row r="11" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B11" s="46"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="45"/>
-    </row>
-    <row r="13" spans="2:8" ht="15">
-      <c r="B13" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="2:8" ht="15">
-      <c r="B14" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="15">
-      <c r="B16" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="15">
-      <c r="B26" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D35" s="1">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E4:F4"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E21 E33:E37 E25:E29" xr:uid="{3F491861-09B2-4965-8997-8FA73292F9AF}">
-      <formula1>"Wait, Posedge, Negedge, Parameter, Test Argument"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="────────────────────────────────" prompt="On Event      : Sim Start - Assertion Off - Event - Assertion On_x000a_Off Event      : Sim Start - Event - Assertion Off_x000a_Forever Loop : Loop ( Event1 - Assertion Off - Event2 - Assertion On )_x000a_Off Event      : Loop ( Event - Assertion Kill )" sqref="B27:B29 B17:B21 B15 B25 B33 B35:B37" xr:uid="{E30D744A-FABA-4402-B47F-419DA2C7DE3E}">
-      <formula1>"On Event, Off Event, Forever Loop, Kill Event, └ +On Event, └ +Off Event, None"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="────────────────────────────────" prompt="On Event      : Sim Start - Assertion Off - Event - Assertion On_x000a_Off Event      : Sim Start - Event - Assertion Off_x000a_Forever Loop : Loop ( Event1 - Assertion Off - Event2 - Assertion On )_x000a_Off Event      : Loop ( Event - Assertion Kill )" sqref="B34" xr:uid="{6CA08298-7170-482C-A47B-F6F86A398E2E}">
-      <formula1>"On Event, Off Event, always begin, Kill Event, └ +On Event, └ +Off Event, None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -14721,6 +15511,498 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD588F34-D77B-42F6-9174-CC0FF762963C}">
+  <dimension ref="B2:H37"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="2.75" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="3" max="4" width="26.25" customWidth="1"/>
+    <col min="5" max="5" width="17.375" customWidth="1"/>
+    <col min="6" max="6" width="72.5" customWidth="1"/>
+    <col min="7" max="7" width="43.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="21">
+      <c r="B2" s="226" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="226"/>
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+    </row>
+    <row r="3" spans="2:8" ht="17.25" customHeight="1">
+      <c r="B3" s="46"/>
+      <c r="C3" s="47" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="227" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="45"/>
+    </row>
+    <row r="4" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="227" t="s">
+        <v>312</v>
+      </c>
+      <c r="F4" s="227"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="45"/>
+    </row>
+    <row r="5" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B5" s="46"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="227" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5" s="227"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="45"/>
+    </row>
+    <row r="6" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="45"/>
+    </row>
+    <row r="8" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B8" s="46"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="45"/>
+    </row>
+    <row r="9" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="45"/>
+    </row>
+    <row r="10" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B10" s="46"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="45"/>
+    </row>
+    <row r="11" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="45"/>
+    </row>
+    <row r="13" spans="2:8" ht="15">
+      <c r="B13" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="2:8" ht="15">
+      <c r="B14" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="15">
+      <c r="B16" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="15">
+      <c r="B26" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E4:F4"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E21 E33:E37 E25:E29" xr:uid="{3F491861-09B2-4965-8997-8FA73292F9AF}">
+      <formula1>"Wait, Posedge, Negedge, Parameter, Test Argument"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="────────────────────────────────" prompt="On Event      : Sim Start - Assertion Off - Event - Assertion On_x000a_Off Event      : Sim Start - Event - Assertion Off_x000a_Forever Loop : Loop ( Event1 - Assertion Off - Event2 - Assertion On )_x000a_Off Event      : Loop ( Event - Assertion Kill )" sqref="B27:B29 B17:B21 B15 B25 B33 B35:B37" xr:uid="{E30D744A-FABA-4402-B47F-419DA2C7DE3E}">
+      <formula1>"On Event, Off Event, Forever Loop, Kill Event, └ +On Event, └ +Off Event, None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="────────────────────────────────" prompt="On Event      : Sim Start - Assertion Off - Event - Assertion On_x000a_Off Event      : Sim Start - Event - Assertion Off_x000a_Forever Loop : Loop ( Event1 - Assertion Off - Event2 - Assertion On )_x000a_Off Event      : Loop ( Event - Assertion Kill )" sqref="B34" xr:uid="{6CA08298-7170-482C-A47B-F6F86A398E2E}">
+      <formula1>"On Event, Off Event, always begin, Kill Event, └ +On Event, └ +Off Event, None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB7CBB2-7D65-4367-9539-203D43D673CC}">
   <sheetPr>

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CADDA5E-8B12-44BE-861D-0B54AA9B3FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8448669B-7E55-44BF-B15D-E1103A3CE73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="9" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="3" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="341">
   <si>
     <t>Base Information</t>
   </si>
@@ -1847,10 +1847,10 @@
     <t>Expected Preset(hpulse)</t>
   </si>
   <si>
-    <t>Count Trigger</t>
-  </si>
-  <si>
-    <t>Target Pulse</t>
+    <t>Hsync Signal</t>
+  </si>
+  <si>
+    <t>Data Enable Signal</t>
   </si>
   <si>
     <t>Expected Min Value</t>
@@ -1859,154 +1859,22 @@
     <t>Expected Max Value</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">`include "uvm_marcros.svh"
+    <t>`include "uvm_marcros.svh"
 import uvm_pkg::*;
 interface assertion_intf()
 (
     input &lt;Base Clock&gt;,
     input &lt;Base Reset&gt;,
-    input &lt;Target_pulse&gt;,
+    input &lt;Hsync Signal&gt;,
+    input &lt;Data Enable Signal&gt;
 )
 property p_hsw;
     int value_count;
-    @(posedge </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Base Clock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) disable iff(!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Base Reset</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)
-    $rose(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>target_pulse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) |-&gt; (1, value_count  = 0)
-    ##1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF215C98"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>target_pulse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, value_count = value_count + 1)[*0:$]
-    ##1 (!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>target_pulse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, value_count = value_count + 1)
-    ##0 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>expected_min_value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;= value_count &amp;&amp; value_count &lt;= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>expected_max_value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);
+    @(posedge &lt;Base Clock&gt;) disable iff(!&lt;Base Reset&gt;)
+    $rose(&lt;Hsync Signal&gt;) |-&gt; (1, value_count  = 0)
+    ##1 (&lt;Hsync Signal&gt;, value_count = value_count + 1)[*0:$]
+    ##1 (!&lt;Hsync Signal&gt;, value_count = value_count + 1)
+    ##0 (&lt;expected_min_value&gt; &lt;= value_count &amp;&amp; value_count &lt;= &lt;expected_max_value&gt;);
 endproperty
 assert property (p_hsw)  else $error("failed at %t", $time");
 endinterface
@@ -2015,20 +1883,8 @@
 u_assertion_intf();
 assign u_assertion_hpulse.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
 assign u_assertion_hpulse.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
-assign u_assertion_hpulse.&lt;Target_Pulse&gt; = top.dut.&lt;Target_Pulse&gt;;</t>
-    </r>
-  </si>
-  <si>
-    <t>&lt;Base Clock&gt;</t>
-  </si>
-  <si>
-    <t>target_pulse</t>
-  </si>
-  <si>
-    <t>expect_min_value</t>
-  </si>
-  <si>
-    <t>expect_max_value</t>
+assign u_assertion_hpulse.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
+assign u_assertion_hpulse.&lt;Data Enable Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;</t>
   </si>
   <si>
     <t>HBP</t>
@@ -2037,7 +1893,7 @@
     <t>Expected Preset(HBP)</t>
   </si>
   <si>
-    <t>Data Enable Signal</t>
+    <t>Vsync Signal</t>
   </si>
   <si>
     <r>
@@ -2202,16 +2058,10 @@
     </r>
   </si>
   <si>
-    <t>data_enable_signal</t>
-  </si>
-  <si>
     <t>HACT</t>
   </si>
   <si>
     <t>Expected Preset(HACT)</t>
-  </si>
-  <si>
-    <t>Hsync Signal</t>
   </si>
   <si>
     <t xml:space="preserve">`include "uvm_marcros.svh"
@@ -2330,9 +2180,6 @@
   </si>
   <si>
     <t>Expected Preset(VSW)</t>
-  </si>
-  <si>
-    <t>Vsync Signal</t>
   </si>
   <si>
     <t>`include "uvm_marcros.svh"
@@ -5411,7 +5258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6056,6 +5903,15 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6731,14 +6587,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -6753,13 +6609,13 @@
     </row>
     <row r="6" spans="3:20" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>77</v>
@@ -6768,7 +6624,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -7945,14 +7801,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -7967,13 +7823,13 @@
     </row>
     <row r="6" spans="3:20" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>77</v>
@@ -7982,7 +7838,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -9157,7 +9013,7 @@
       <c r="F5" s="126"/>
       <c r="G5" s="70"/>
       <c r="I5" s="166" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J5" s="166"/>
       <c r="K5" s="166"/>
@@ -9180,7 +9036,7 @@
       <c r="F6" s="129"/>
       <c r="G6" s="72"/>
       <c r="I6" s="165" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J6" s="165"/>
       <c r="K6" s="165"/>
@@ -9381,7 +9237,7 @@
     </row>
     <row r="23" spans="9:15" ht="21">
       <c r="I23" s="166" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J23" s="166"/>
       <c r="K23" s="166"/>
@@ -9392,7 +9248,7 @@
     </row>
     <row r="24" spans="9:15" ht="13.5" customHeight="1">
       <c r="I24" s="165" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="J24" s="165"/>
       <c r="K24" s="165"/>
@@ -9607,14 +9463,14 @@
     </row>
     <row r="5" spans="3:32" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -9627,7 +9483,7 @@
       <c r="S5" s="154"/>
       <c r="T5" s="155"/>
       <c r="V5" s="153" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W5" s="154"/>
       <c r="X5" s="154"/>
@@ -9648,16 +9504,16 @@
         <v>31</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -9670,7 +9526,7 @@
       <c r="S6" s="131"/>
       <c r="T6" s="132"/>
       <c r="V6" s="130" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="W6" s="131"/>
       <c r="X6" s="131"/>
@@ -11060,7 +10916,7 @@
       <c r="Q3" s="123"/>
       <c r="R3" s="124"/>
       <c r="T3" s="122" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="U3" s="123"/>
       <c r="V3" s="124"/>
@@ -11070,10 +10926,10 @@
         <v>35</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>39</v>
@@ -11089,10 +10945,10 @@
         <v>27</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="N4" s="41" t="s">
         <v>35</v>
@@ -11101,27 +10957,27 @@
         <v>21</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>31</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="V4" s="42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="15">
       <c r="B5" s="26" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -11135,28 +10991,28 @@
       <c r="K5" s="26"/>
       <c r="L5" s="27"/>
       <c r="N5" s="26" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="O5" s="37" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="P5" s="37">
         <v>3</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="T5" s="26" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="U5" s="37">
         <v>2</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="15">
@@ -11166,7 +11022,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H6" s="37"/>
       <c r="I6" s="27"/>
@@ -11188,17 +11044,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H7" s="37"/>
       <c r="I7" s="27"/>
       <c r="K7" s="26"/>
       <c r="L7" s="27"/>
       <c r="N7" s="26" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="O7" s="37" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="P7" s="37">
         <v>5</v>
@@ -11301,348 +11157,348 @@
     <row r="4" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="5" spans="3:9" ht="16.5" thickBot="1">
       <c r="C5" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="3:9" ht="14.25" thickBot="1"/>
     <row r="7" spans="3:9" ht="18" thickBot="1">
       <c r="C7" s="19" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="3:9" ht="18" thickBot="1">
       <c r="C8" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="3:9" ht="18" thickBot="1">
       <c r="C9" s="14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="18" thickBot="1">
       <c r="C10" s="14" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="3:9" ht="18" thickBot="1">
       <c r="C11" s="14" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="3:9" ht="18" thickBot="1">
       <c r="C12" s="14" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="3:9" ht="18" thickBot="1">
       <c r="C13" s="17" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="3:9" ht="17.25">
       <c r="C14" s="17" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="3:9" ht="18" thickBot="1">
       <c r="C15" s="17" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="3:9" ht="18" thickBot="1">
       <c r="C16" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="3:9" ht="18" thickBot="1">
       <c r="C17" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="3:9" ht="18" thickBot="1">
       <c r="C18" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="3:9" ht="18" thickBot="1">
       <c r="C19" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="18" thickBot="1">
       <c r="C20" s="8" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="3:9" ht="18" thickBot="1">
       <c r="C21" s="8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="3:9" ht="18" thickBot="1">
       <c r="C22" s="8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="3:9" ht="18" thickBot="1">
       <c r="C23" s="8" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="3:9" ht="18" thickBot="1">
       <c r="C24" s="8" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="3:9" ht="18" thickBot="1">
       <c r="C25" s="8" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="3:9" ht="18" thickBot="1">
       <c r="C26" s="8" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -11678,7 +11534,7 @@
   <sheetData>
     <row r="2" spans="2:22" ht="13.5" customHeight="1">
       <c r="B2" s="125" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
@@ -11718,46 +11574,46 @@
     </row>
     <row r="4" spans="2:22" ht="13.5" customHeight="1">
       <c r="B4" s="33" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E4" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="I4" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="N4" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="O4" s="174" t="s">
         <v>241</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="O4" s="174" t="s">
-        <v>248</v>
       </c>
       <c r="P4" s="175"/>
       <c r="Q4" s="175"/>
@@ -11765,28 +11621,28 @@
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="25" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -11800,7 +11656,7 @@
     </row>
     <row r="6" spans="2:22" ht="15">
       <c r="B6" s="25" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -11813,10 +11669,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M6" s="31">
         <v>1</v>
@@ -11831,7 +11687,7 @@
     </row>
     <row r="7" spans="2:22" ht="15">
       <c r="B7" s="25" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -11844,10 +11700,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M7" s="31">
         <v>1</v>
@@ -11862,7 +11718,7 @@
     </row>
     <row r="8" spans="2:22" ht="15">
       <c r="B8" s="25" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -11875,10 +11731,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M8" s="31">
         <v>1</v>
@@ -11893,28 +11749,28 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="25" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -11928,7 +11784,7 @@
     </row>
     <row r="10" spans="2:22" ht="15">
       <c r="B10" s="25" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -11941,10 +11797,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M10" s="31">
         <v>1</v>
@@ -11959,7 +11815,7 @@
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -11980,7 +11836,7 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -12001,7 +11857,7 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -12022,7 +11878,7 @@
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -12041,13 +11897,13 @@
       <c r="Q14" s="178"/>
       <c r="R14" s="179"/>
       <c r="U14" s="192" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="V14" s="192"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -12070,7 +11926,7 @@
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -12089,15 +11945,15 @@
       <c r="Q16" s="178"/>
       <c r="R16" s="179"/>
       <c r="U16" s="192" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="V16" s="193" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -12120,7 +11976,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -12140,12 +11996,12 @@
       <c r="R18" s="179"/>
       <c r="U18" s="192"/>
       <c r="V18" s="193" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -12168,7 +12024,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -12188,12 +12044,12 @@
       <c r="R20" s="179"/>
       <c r="U20" s="192"/>
       <c r="V20" s="193" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -12216,7 +12072,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -12236,12 +12092,12 @@
       <c r="R22" s="179"/>
       <c r="U22" s="192"/>
       <c r="V22" s="193" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -12264,7 +12120,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -12284,12 +12140,12 @@
       <c r="R24" s="179"/>
       <c r="U24" s="192"/>
       <c r="V24" s="193" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -12312,7 +12168,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -12332,12 +12188,12 @@
       <c r="R26" s="179"/>
       <c r="U26" s="192"/>
       <c r="V26" s="193" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="32" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -12360,7 +12216,7 @@
     </row>
     <row r="30" spans="2:25" ht="13.5" customHeight="1">
       <c r="B30" s="125" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C30" s="126"/>
       <c r="D30" s="126"/>
@@ -12398,46 +12254,46 @@
       <c r="Q31" s="172"/>
       <c r="R31" s="173"/>
       <c r="U31" s="6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="V31" s="6"/>
       <c r="X31" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="15">
       <c r="B32" s="38" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D32" s="34" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="J32" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="K32" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="L32" s="183" t="s">
         <v>241</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="G32" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="J32" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="K32" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="L32" s="183" t="s">
-        <v>248</v>
       </c>
       <c r="M32" s="184"/>
       <c r="N32" s="184"/>
@@ -12450,36 +12306,36 @@
       </c>
       <c r="V32" s="5"/>
       <c r="X32" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Y32" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="2:29" ht="15">
       <c r="B33" s="26" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G33" s="37">
         <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J33" s="31">
         <v>1</v>
@@ -12495,7 +12351,7 @@
       <c r="Q33" s="187"/>
       <c r="R33" s="188"/>
       <c r="U33" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="V33" s="6"/>
     </row>
@@ -12518,17 +12374,17 @@
       <c r="Q34" s="187"/>
       <c r="R34" s="188"/>
       <c r="U34" s="5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="V34" s="5"/>
       <c r="X34" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Y34" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="Z34" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="2:29" ht="15">
@@ -12551,14 +12407,14 @@
       <c r="R35" s="188"/>
       <c r="S35" s="7"/>
       <c r="U35" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="V35" s="5"/>
       <c r="X35" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y35" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="2:29" ht="15">
@@ -12602,11 +12458,11 @@
       <c r="Q37" s="187"/>
       <c r="R37" s="188"/>
       <c r="U37" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="V37" s="6"/>
       <c r="X37" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="2:29" ht="15">
@@ -12628,11 +12484,11 @@
       <c r="Q38" s="187"/>
       <c r="R38" s="188"/>
       <c r="U38" s="6" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="V38" s="6"/>
       <c r="X38" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="2:29" ht="15">
@@ -12654,26 +12510,26 @@
       <c r="Q39" s="187"/>
       <c r="R39" s="188"/>
       <c r="U39" s="5" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="V39" s="5"/>
       <c r="X39" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Y39" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="Z39" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AA39" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AB39" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AC39" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="2:29">
@@ -12884,7 +12740,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="150" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B1" s="151"/>
       <c r="C1" s="151"/>
@@ -12899,7 +12755,7 @@
       <c r="L1" s="151"/>
       <c r="M1" s="152"/>
       <c r="O1" s="150" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="P1" s="151"/>
       <c r="Q1" s="151"/>
@@ -12911,7 +12767,7 @@
       <c r="W1" s="151"/>
       <c r="X1" s="152"/>
       <c r="Z1" s="200" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA1" s="201"/>
       <c r="AB1" s="201"/>
@@ -12958,7 +12814,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="206" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B3" s="207"/>
       <c r="C3" s="207"/>
@@ -12967,7 +12823,7 @@
       <c r="F3" s="207"/>
       <c r="G3" s="207"/>
       <c r="H3" s="206" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="I3" s="207"/>
       <c r="J3" s="207"/>
@@ -12985,14 +12841,14 @@
       <c r="W3" s="198"/>
       <c r="X3" s="199"/>
       <c r="Z3" s="209" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA3" s="210"/>
       <c r="AB3" s="210"/>
       <c r="AC3" s="210"/>
       <c r="AD3" s="211"/>
       <c r="AE3" s="209" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AF3" s="212"/>
       <c r="AG3" s="212"/>
@@ -13000,131 +12856,131 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="S4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="W4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="AG4" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="AF4" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>287</v>
-      </c>
       <c r="AH4" s="51" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="27"/>
@@ -13139,54 +12995,54 @@
       <c r="W5" s="31"/>
       <c r="X5" s="39"/>
       <c r="Z5" s="43" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AA5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AB5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AC5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AF5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AG5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H6" s="26"/>
       <c r="I6" s="1"/>
@@ -13205,39 +13061,39 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AE6" s="43" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AF6" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AG6" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H7" s="26"/>
       <c r="I7" s="1"/>
@@ -13256,36 +13112,36 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AE7" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="AF7" t="s">
         <v>291</v>
       </c>
-      <c r="AF7" t="s">
-        <v>298</v>
-      </c>
       <c r="AH7" s="44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="1"/>
@@ -13670,7 +13526,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -13685,7 +13541,7 @@
       <c r="L1" s="126"/>
       <c r="M1" s="127"/>
       <c r="O1" s="125" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="P1" s="126"/>
       <c r="Q1" s="126"/>
@@ -13697,7 +13553,7 @@
       <c r="W1" s="126"/>
       <c r="X1" s="127"/>
       <c r="Z1" s="215" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA1" s="216"/>
       <c r="AB1" s="216"/>
@@ -13744,7 +13600,7 @@
     </row>
     <row r="3" spans="1:34" ht="19.5" customHeight="1">
       <c r="A3" s="122" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
@@ -13753,7 +13609,7 @@
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
       <c r="H3" s="122" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="I3" s="123"/>
       <c r="J3" s="123"/>
@@ -13771,14 +13627,14 @@
       <c r="W3" s="224"/>
       <c r="X3" s="225"/>
       <c r="Z3" s="214" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA3" s="210"/>
       <c r="AB3" s="210"/>
       <c r="AC3" s="210"/>
       <c r="AD3" s="211"/>
       <c r="AE3" s="214" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AF3" s="221"/>
       <c r="AG3" s="221"/>
@@ -13786,161 +13642,161 @@
     </row>
     <row r="4" spans="1:34" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="S4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="V4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="W4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="Z4" s="41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="AC4" s="49" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AD4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AE4" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="AF4" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="AG4" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="AF4" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="AG4" s="23" t="s">
-        <v>287</v>
-      </c>
       <c r="AH4" s="51" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L5" s="31">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
       <c r="O5" s="26" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="T5" s="37">
         <v>3</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="W5" s="31">
         <v>1</v>
@@ -13949,66 +13805,66 @@
         <v>4</v>
       </c>
       <c r="Z5" s="43" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="AA5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AB5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AC5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AE5" s="43" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="AF5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AG5" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I6" s="37">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L6" s="31">
         <v>1</v>
@@ -14027,13 +13883,13 @@
       <c r="W6" s="1"/>
       <c r="X6" s="27"/>
       <c r="AF6" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AG6" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1">
@@ -14045,16 +13901,16 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I7" s="37">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L7" s="31">
         <v>1</v>
@@ -14073,7 +13929,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="27"/>
       <c r="AF7" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1">
@@ -14085,16 +13941,16 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I8" s="37">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L8" s="31">
         <v>1</v>
@@ -14234,7 +14090,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="13.5" customHeight="1">
       <c r="A1" s="125" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -14246,7 +14102,7 @@
       <c r="I1" s="126"/>
       <c r="J1" s="127"/>
       <c r="L1" s="125" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="M1" s="126"/>
       <c r="N1" s="126"/>
@@ -14258,7 +14114,7 @@
       <c r="T1" s="126"/>
       <c r="U1" s="127"/>
       <c r="W1" s="215" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="X1" s="216"/>
       <c r="Y1" s="216"/>
@@ -14302,13 +14158,13 @@
     </row>
     <row r="3" spans="1:31" ht="19.5" customHeight="1" thickBot="1">
       <c r="A3" s="122" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
       <c r="E3" s="122" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
@@ -14326,14 +14182,14 @@
       <c r="T3" s="224"/>
       <c r="U3" s="225"/>
       <c r="W3" s="214" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="X3" s="210"/>
       <c r="Y3" s="210"/>
       <c r="Z3" s="210"/>
       <c r="AA3" s="211"/>
       <c r="AB3" s="214" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AC3" s="221"/>
       <c r="AD3" s="221"/>
@@ -14341,143 +14197,143 @@
     </row>
     <row r="4" spans="1:31" ht="13.5" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L4" s="41" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q4" s="40" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="R4" s="40" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="S4" s="40" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="U4" s="42" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="W4" s="41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Y4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AA4" s="50" t="s">
         <v>6</v>
       </c>
       <c r="AB4" s="41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AC4" s="23" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AE4" s="51" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="15" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I5" s="31">
         <v>1</v>
       </c>
       <c r="J5" s="27"/>
       <c r="L5" s="26" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="Q5" s="37">
         <v>3</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="S5" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="T5" s="31">
         <v>1</v>
@@ -14486,57 +14342,57 @@
         <v>4</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="X5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Y5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="Z5" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AB5" s="43" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="AC5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AD5" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F6" s="37">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I6" s="31">
         <v>1</v>
@@ -14561,16 +14417,16 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F7" s="37">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I7" s="31">
         <v>1</v>
@@ -14595,16 +14451,16 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="26" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F8" s="37">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I8" s="31">
         <v>1</v>
@@ -15526,7 +15382,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="21">
       <c r="B2" s="226" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C2" s="226"/>
       <c r="D2" s="226"/>
@@ -15538,10 +15394,10 @@
     <row r="3" spans="2:8" ht="17.25" customHeight="1">
       <c r="B3" s="46"/>
       <c r="C3" s="47" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D3" s="227" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E3" s="227"/>
       <c r="F3" s="227"/>
@@ -15552,10 +15408,10 @@
       <c r="B4" s="46"/>
       <c r="C4" s="47"/>
       <c r="D4" s="52" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E4" s="227" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F4" s="227"/>
       <c r="G4" s="47"/>
@@ -15565,10 +15421,10 @@
       <c r="B5" s="46"/>
       <c r="C5" s="47"/>
       <c r="D5" s="52" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E5" s="227" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F5" s="227"/>
       <c r="G5" s="47"/>
@@ -15630,339 +15486,339 @@
     </row>
     <row r="13" spans="2:8" ht="15">
       <c r="B13" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="2:8" ht="15">
       <c r="B14" s="4" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15">
       <c r="B16" s="24" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="23" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="23" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="23" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15">
       <c r="B26" s="24" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="23" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="23" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="23" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D35" s="1">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -18204,10 +18060,10 @@
       <c r="C6" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="229" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="230" t="s">
         <v>77</v>
       </c>
       <c r="F6" s="42" t="s">
@@ -18229,18 +18085,10 @@
       <c r="S6" s="132"/>
     </row>
     <row r="7" spans="3:19" ht="13.5" customHeight="1">
-      <c r="C7" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>83</v>
-      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
+      <c r="F7" s="27"/>
       <c r="G7"/>
       <c r="I7" s="133"/>
       <c r="J7" s="134"/>
@@ -19066,7 +18914,7 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
@@ -19074,7 +18922,7 @@
       <c r="G5" s="124"/>
       <c r="H5"/>
       <c r="J5" s="153" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -19092,10 +18940,10 @@
         <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="23" t="s">
         <v>76</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>77</v>
@@ -19105,7 +18953,7 @@
       </c>
       <c r="H6"/>
       <c r="J6" s="130" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -19119,21 +18967,11 @@
       <c r="T6" s="132"/>
     </row>
     <row r="7" spans="3:20" ht="13.5" customHeight="1">
-      <c r="C7" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>83</v>
-      </c>
+      <c r="C7" s="26"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="27"/>
       <c r="H7"/>
       <c r="J7" s="133"/>
       <c r="K7" s="134"/>
@@ -19962,14 +19800,14 @@
     </row>
     <row r="5" spans="3:19" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="124"/>
       <c r="G5"/>
       <c r="I5" s="153" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J5" s="154"/>
       <c r="K5" s="154"/>
@@ -19984,10 +19822,10 @@
     </row>
     <row r="6" spans="3:19" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>77</v>
@@ -19997,7 +19835,7 @@
       </c>
       <c r="G6"/>
       <c r="I6" s="131" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J6" s="131"/>
       <c r="K6" s="131"/>
@@ -21091,14 +20929,14 @@
     </row>
     <row r="5" spans="3:19" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="124"/>
       <c r="G5"/>
       <c r="I5" s="153" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J5" s="154"/>
       <c r="K5" s="154"/>
@@ -21113,10 +20951,10 @@
     </row>
     <row r="6" spans="3:19" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>77</v>
@@ -21126,7 +20964,7 @@
       </c>
       <c r="G6"/>
       <c r="I6" s="130" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J6" s="131"/>
       <c r="K6" s="131"/>
@@ -22221,14 +22059,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -22243,13 +22081,13 @@
     </row>
     <row r="6" spans="3:20" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>77</v>
@@ -22258,7 +22096,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>
@@ -23435,14 +23273,14 @@
     </row>
     <row r="5" spans="3:20" ht="19.5" customHeight="1">
       <c r="C5" s="122" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D5" s="123"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="124"/>
       <c r="J5" s="153" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K5" s="154"/>
       <c r="L5" s="154"/>
@@ -23457,13 +23295,13 @@
     </row>
     <row r="6" spans="3:20" ht="13.5" customHeight="1">
       <c r="C6" s="41" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>77</v>
@@ -23472,7 +23310,7 @@
         <v>78</v>
       </c>
       <c r="J6" s="130" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K6" s="131"/>
       <c r="L6" s="131"/>

--- a/Data/Assertion_TF.xlsx
+++ b/Data/Assertion_TF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oneharman-my.sharepoint.com/personal/sophia_kim_harman_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8448669B-7E55-44BF-B15D-E1103A3CE73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93A27A4F-2CEE-4BFF-BFF9-C6B40FF5B325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="3" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="7" activeTab="4" xr2:uid="{A0D018F4-3A48-4DCB-A1A2-EA6BF4E4311F}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="9" r:id="rId1"/>
@@ -34,6 +34,9 @@
     <sheet name="Basic Assertion_개선안" sheetId="5" r:id="rId19"/>
     <sheet name="aw_builder" sheetId="2" r:id="rId20"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId21"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1881,10 +1884,10 @@
 // 윗부분까지가 생성되는 assertion_gen.sv 입니다. 아래부터는 assertion_gen_inst.sv 입니다.
 assertion_intf
 u_assertion_intf();
-assign u_assertion_hpulse.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
-assign u_assertion_hpulse.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
-assign u_assertion_hpulse.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
-assign u_assertion_hpulse.&lt;Data Enable Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;</t>
+assign u_assertion.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
+assign u_assertion.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
+assign u_assertion.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
+assign u_assertion.&lt;Data Enable Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;</t>
   </si>
   <si>
     <t>HBP</t>
@@ -1896,166 +1899,33 @@
     <t>Vsync Signal</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">`include "uvm_marcros.svh"
+    <t>`include "uvm_marcros.svh"
 import uvm_pkg::*;
 interface assertion_intf()
 (
     input &lt;Base Clock&gt;,
     input &lt;Base Reset&gt;,
-    input &lt;Target_pulse&gt;,
-    input &lt;DE&gt;
+    input &lt;Hsync Signal&gt;,
+    input &lt;Vsync Signal&gt;,
+    input &lt;Data Enable Signal&gt;
 )
 property p_hbp;
     int value_count;
-    @(posedge </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Base Clock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) disable iff(!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Base Reset</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)
-    $fell(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>target_pulse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) |-&gt; (1, value_count  = 0)
-    ##1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF215C98"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>de</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, value_count = value_count + 1)[*0:$]
-    ##1 (!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>de</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, value_count = value_count + 1)
-    ##0 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>expected_min_value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;= value_count &amp;&amp; value_count &lt;= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF156082"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>expected_max_value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);
+    @(posedge Base Clock) disable iff(!Base Reset)
+    $fell(&lt;Hsync Signal&gt;) |-&gt; (1, value_count  = 0)
+    ##1 (&lt;Data Enable Signal&gt;, value_count = value_count + 1)[*0:$]
+    ##1 (!&lt;Data Enable Signal&gt;, value_count = value_count + 1)
+    ##0 (expected_min_value &lt;= value_count &amp;&amp; value_count &lt;= expected_max_value);
 endproperty
 assert property (p_hbp)  else $error("failed at %t", $time");
 endinterface
 // 윗부분까지가 생성되는 assertion_gen.sv 입니다. 아래부터는 assertion_gen_inst.sv 입니다.
 assertion_intf
 u_assertion_intf();
-assign u_assertion_hpulse.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
-assign u_assertion_hpulse.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
-assign u_assertion_hpulse.&lt;Target_Pulse&gt; = top.dut.&lt;Target_Pulse&gt;;
-assign u_assertion_hpulse.&lt;de&gt; = top.dut.&lt;de&gt;;</t>
-    </r>
+assign u_assertion_intf.&lt;Base_Clock&gt; = top.dut.&lt;Base_Clock&gt;;
+assign u_assertion_intf.&lt;Base_Reset&gt; = top.dut.&lt;Base_Reset&gt;;
+assign u_assertion_intf.&lt;Hsync Signal&gt; = top.dut.&lt;Hsync Signal&gt;;
+assign u_assertion_intf.&lt;Data Enable Signal&gt; = top.dut.&lt;Data Enable Signal&gt;;</t>
   </si>
   <si>
     <t>HACT</t>
@@ -4238,7 +4108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4438,19 +4308,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF215C98"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3C7D22"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF156082"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -5930,6 +5788,19 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="fine"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Kim, Sophia" id="{78EA4F94-E7F0-4B09-B230-69C75990A971}" userId="S::sophia.kim@harman.com::fcd4db4f-17b4-4ad3-ac6d-2bf3489f74ea" providerId="AD"/>
